--- a/skipperplan.xlsx
+++ b/skipperplan.xlsx
@@ -26069,7 +26069,7 @@
         <v>7</v>
       </c>
       <c r="J212" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K212" s="3" t="s">
         <v>34</v>
@@ -54525,7 +54525,7 @@
         <v>8</v>
       </c>
       <c r="J575" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K575" s="5" t="s">
         <v>34</v>

--- a/skipperplan.xlsx
+++ b/skipperplan.xlsx
@@ -24233,82 +24233,82 @@
       </c>
     </row>
     <row r="189" spans="1:26">
-      <c r="A189" s="6" t="s">
+      <c r="A189" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="B189" s="6" t="s">
+      <c r="B189" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="C189" s="6" t="s">
+      <c r="C189" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="D189" s="6" t="s">
+      <c r="D189" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E189" s="6" t="s">
+      <c r="E189" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F189" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G189" s="6" t="s">
+      <c r="F189" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G189" s="7" t="s">
         <v>776</v>
       </c>
-      <c r="H189" s="6" t="s">
+      <c r="H189" s="7" t="s">
         <v>777</v>
       </c>
-      <c r="I189" s="6">
+      <c r="I189" s="7">
         <v>9</v>
       </c>
-      <c r="J189" s="6">
-        <v>0</v>
-      </c>
-      <c r="K189" s="6" t="s">
+      <c r="J189" s="7">
+        <v>2</v>
+      </c>
+      <c r="K189" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L189" s="6" t="s">
+      <c r="L189" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="M189" s="6" t="s">
+      <c r="M189" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="N189" s="6" t="s">
+      <c r="N189" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="O189" s="6" t="s">
+      <c r="O189" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P189" s="6" t="s">
+      <c r="P189" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="Q189" s="6" t="s">
+      <c r="Q189" s="7" t="s">
         <v>773</v>
       </c>
-      <c r="R189" s="6" t="s">
+      <c r="R189" s="7" t="s">
         <v>778</v>
       </c>
-      <c r="S189" s="6" t="s">
+      <c r="S189" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="T189" s="6" t="s">
+      <c r="T189" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="U189" s="6" t="s">
+      <c r="U189" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V189" s="6">
+      <c r="V189" s="7">
         <v>2018</v>
       </c>
-      <c r="W189" s="6" t="s">
-        <v>439</v>
-      </c>
-      <c r="X189" s="6" t="s">
+      <c r="W189" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X189" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="Y189" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z189" s="6"/>
+      <c r="Y189" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z189" s="7"/>
     </row>
     <row r="190" spans="1:26">
       <c r="A190" s="6" t="s">
@@ -25125,7 +25125,7 @@
         <v>9</v>
       </c>
       <c r="J200" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K200" s="3" t="s">
         <v>34</v>
@@ -28189,7 +28189,7 @@
         <v>8</v>
       </c>
       <c r="J239" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K239" s="4" t="s">
         <v>34</v>
@@ -41841,7 +41841,7 @@
         <v>8</v>
       </c>
       <c r="J413" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K413" s="5" t="s">
         <v>34</v>

--- a/skipperplan.xlsx
+++ b/skipperplan.xlsx
@@ -8556,9 +8556,114 @@
     <t>02.05.2026</t>
   </si>
   <si>
+    <t>Teneriffa → Azoren</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>8352</t>
+  </si>
+  <si>
+    <t>16608</t>
+  </si>
+  <si>
     <t>09.05.2026</t>
   </si>
   <si>
+    <t>8153</t>
+  </si>
+  <si>
+    <t>16145</t>
+  </si>
+  <si>
+    <t>16146</t>
+  </si>
+  <si>
+    <t>TOKAJ</t>
+  </si>
+  <si>
+    <t>8140</t>
+  </si>
+  <si>
+    <t>16123</t>
+  </si>
+  <si>
+    <t>16654</t>
+  </si>
+  <si>
+    <t>MALBEC Skipper Office inv</t>
+  </si>
+  <si>
+    <t>7675</t>
+  </si>
+  <si>
+    <t>15198</t>
+  </si>
+  <si>
+    <t>Kevin R, Beat A</t>
+  </si>
+  <si>
+    <t>7808</t>
+  </si>
+  <si>
+    <t>15420</t>
+  </si>
+  <si>
+    <t>Tina S, Ferdinand G</t>
+  </si>
+  <si>
+    <t>7999</t>
+  </si>
+  <si>
+    <t>15790</t>
+  </si>
+  <si>
+    <t>Benjamin C, Egemen Can G</t>
+  </si>
+  <si>
+    <t>7958</t>
+  </si>
+  <si>
+    <t>15686</t>
+  </si>
+  <si>
+    <t>Mirco K, Fabian B, Friederike W</t>
+  </si>
+  <si>
+    <t>16451</t>
+  </si>
+  <si>
+    <t>Serendipity</t>
+  </si>
+  <si>
+    <t>16690</t>
+  </si>
+  <si>
+    <t>Unicorn</t>
+  </si>
+  <si>
+    <t>7945</t>
+  </si>
+  <si>
+    <t>15661</t>
+  </si>
+  <si>
+    <t>15662</t>
+  </si>
+  <si>
+    <t>8042</t>
+  </si>
+  <si>
+    <t>15874</t>
+  </si>
+  <si>
+    <t>Maik L, Nico B, Maximilian W, Erkut C</t>
+  </si>
+  <si>
+    <t>15875</t>
+  </si>
+  <si>
     <t>8152</t>
   </si>
   <si>
@@ -8629,111 +8734,6 @@
   </si>
   <si>
     <t>15873</t>
-  </si>
-  <si>
-    <t>Teneriffa → Azoren</t>
-  </si>
-  <si>
-    <t>337</t>
-  </si>
-  <si>
-    <t>8352</t>
-  </si>
-  <si>
-    <t>16608</t>
-  </si>
-  <si>
-    <t>8153</t>
-  </si>
-  <si>
-    <t>16145</t>
-  </si>
-  <si>
-    <t>16146</t>
-  </si>
-  <si>
-    <t>TOKAJ</t>
-  </si>
-  <si>
-    <t>8140</t>
-  </si>
-  <si>
-    <t>16123</t>
-  </si>
-  <si>
-    <t>16654</t>
-  </si>
-  <si>
-    <t>MALBEC Skipper Office inv</t>
-  </si>
-  <si>
-    <t>7675</t>
-  </si>
-  <si>
-    <t>15198</t>
-  </si>
-  <si>
-    <t>Kevin R, Beat A</t>
-  </si>
-  <si>
-    <t>7808</t>
-  </si>
-  <si>
-    <t>15420</t>
-  </si>
-  <si>
-    <t>Tina S, Ferdinand G</t>
-  </si>
-  <si>
-    <t>7999</t>
-  </si>
-  <si>
-    <t>15790</t>
-  </si>
-  <si>
-    <t>Benjamin C, Egemen Can G</t>
-  </si>
-  <si>
-    <t>7958</t>
-  </si>
-  <si>
-    <t>15686</t>
-  </si>
-  <si>
-    <t>Mirco K, Fabian B, Friederike W</t>
-  </si>
-  <si>
-    <t>16451</t>
-  </si>
-  <si>
-    <t>Serendipity</t>
-  </si>
-  <si>
-    <t>16690</t>
-  </si>
-  <si>
-    <t>Unicorn</t>
-  </si>
-  <si>
-    <t>7945</t>
-  </si>
-  <si>
-    <t>15661</t>
-  </si>
-  <si>
-    <t>15662</t>
-  </si>
-  <si>
-    <t>8042</t>
-  </si>
-  <si>
-    <t>15874</t>
-  </si>
-  <si>
-    <t>Maik L, Nico B, Maximilian W, Erkut C</t>
-  </si>
-  <si>
-    <t>15875</t>
   </si>
   <si>
     <t>18.04.2026</t>
@@ -14731,7 +14731,7 @@
         <v>8</v>
       </c>
       <c r="J68" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K68" s="3" t="s">
         <v>34</v>
@@ -24955,7 +24955,7 @@
         <v>51</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>126</v>
@@ -25035,7 +25035,7 @@
         <v>51</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>108</v>
@@ -36817,7 +36817,7 @@
         <v>51</v>
       </c>
       <c r="F349" s="5" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G349" s="5" t="s">
         <v>929</v>
@@ -36897,7 +36897,7 @@
         <v>51</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G350" s="3" t="s">
         <v>1219</v>
@@ -36975,7 +36975,7 @@
         <v>51</v>
       </c>
       <c r="F351" s="6" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G351" s="6" t="s">
         <v>1072</v>
@@ -37053,7 +37053,7 @@
         <v>51</v>
       </c>
       <c r="F352" s="6" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G352" s="6" t="s">
         <v>866</v>
@@ -37131,7 +37131,7 @@
         <v>51</v>
       </c>
       <c r="F353" s="6" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G353" s="6" t="s">
         <v>1225</v>
@@ -37209,7 +37209,7 @@
         <v>51</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G354" s="3" t="s">
         <v>682</v>
@@ -39165,7 +39165,7 @@
         <v>51</v>
       </c>
       <c r="F379" s="5" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G379" s="5" t="s">
         <v>1143</v>
@@ -39245,7 +39245,7 @@
         <v>51</v>
       </c>
       <c r="F380" s="6" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G380" s="6" t="s">
         <v>1275</v>
@@ -39323,7 +39323,7 @@
         <v>51</v>
       </c>
       <c r="F381" s="6" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G381" s="6" t="s">
         <v>1184</v>
@@ -39401,7 +39401,7 @@
         <v>51</v>
       </c>
       <c r="F382" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G382" s="4" t="s">
         <v>287</v>
@@ -44575,7 +44575,7 @@
         <v>51</v>
       </c>
       <c r="F448" s="3" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G448" s="3" t="s">
         <v>108</v>
@@ -44655,7 +44655,7 @@
         <v>51</v>
       </c>
       <c r="F449" s="6" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G449" s="6" t="s">
         <v>1427</v>
@@ -44733,7 +44733,7 @@
         <v>51</v>
       </c>
       <c r="F450" s="6" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G450" s="6" t="s">
         <v>1307</v>
@@ -45179,7 +45179,7 @@
         <v>45</v>
       </c>
       <c r="X455" s="5" t="s">
-        <v>149</v>
+        <v>45</v>
       </c>
       <c r="Y455" s="5" t="s">
         <v>46</v>
@@ -46917,7 +46917,7 @@
         <v>51</v>
       </c>
       <c r="F478" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G478" s="7" t="s">
         <v>220</v>
@@ -46997,7 +46997,7 @@
         <v>51</v>
       </c>
       <c r="F479" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G479" s="7" t="s">
         <v>929</v>
@@ -65385,7 +65385,7 @@
         <v>51</v>
       </c>
       <c r="F714" s="3" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G714" s="3" t="s">
         <v>1129</v>
@@ -65465,7 +65465,7 @@
         <v>51</v>
       </c>
       <c r="F715" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G715" s="7" t="s">
         <v>560</v>
@@ -65543,7 +65543,7 @@
         <v>51</v>
       </c>
       <c r="F716" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G716" s="7" t="s">
         <v>1858</v>
@@ -65621,7 +65621,7 @@
         <v>51</v>
       </c>
       <c r="F717" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G717" s="7" t="s">
         <v>854</v>
@@ -65699,7 +65699,7 @@
         <v>51</v>
       </c>
       <c r="F718" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G718" s="7" t="s">
         <v>1979</v>
@@ -65777,7 +65777,7 @@
         <v>51</v>
       </c>
       <c r="F719" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G719" s="4" t="s">
         <v>287</v>
@@ -65853,7 +65853,7 @@
         <v>51</v>
       </c>
       <c r="F720" s="3" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G720" s="3" t="s">
         <v>61</v>
@@ -65931,7 +65931,7 @@
         <v>51</v>
       </c>
       <c r="F721" s="5" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G721" s="5" t="s">
         <v>906</v>
@@ -66009,7 +66009,7 @@
         <v>51</v>
       </c>
       <c r="F722" s="3" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G722" s="3" t="s">
         <v>369</v>
@@ -68831,7 +68831,7 @@
         <v>51</v>
       </c>
       <c r="F758" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G758" s="7" t="s">
         <v>126</v>
@@ -68911,7 +68911,7 @@
         <v>51</v>
       </c>
       <c r="F759" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G759" s="7" t="s">
         <v>776</v>
@@ -68989,7 +68989,7 @@
         <v>51</v>
       </c>
       <c r="F760" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G760" s="7" t="s">
         <v>482</v>
@@ -69067,7 +69067,7 @@
         <v>51</v>
       </c>
       <c r="F761" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G761" s="7" t="s">
         <v>2061</v>
@@ -69145,7 +69145,7 @@
         <v>51</v>
       </c>
       <c r="F762" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G762" s="7" t="s">
         <v>352</v>
@@ -69223,7 +69223,7 @@
         <v>51</v>
       </c>
       <c r="F763" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G763" s="7" t="s">
         <v>996</v>
@@ -75255,7 +75255,7 @@
         <v>51</v>
       </c>
       <c r="F840" s="3" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G840" s="3" t="s">
         <v>1385</v>
@@ -75335,7 +75335,7 @@
         <v>51</v>
       </c>
       <c r="F841" s="5" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G841" s="5" t="s">
         <v>941</v>
@@ -75413,7 +75413,7 @@
         <v>51</v>
       </c>
       <c r="F842" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G842" s="7" t="s">
         <v>1858</v>
@@ -75491,7 +75491,7 @@
         <v>51</v>
       </c>
       <c r="F843" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G843" s="4" t="s">
         <v>287</v>
@@ -80353,7 +80353,7 @@
         <v>51</v>
       </c>
       <c r="F905" s="5" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G905" s="5" t="s">
         <v>256</v>
@@ -80433,7 +80433,7 @@
         <v>51</v>
       </c>
       <c r="F906" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G906" s="7" t="s">
         <v>219</v>
@@ -80511,7 +80511,7 @@
         <v>51</v>
       </c>
       <c r="F907" s="7" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G907" s="7" t="s">
         <v>2352</v>
@@ -80589,7 +80589,7 @@
         <v>51</v>
       </c>
       <c r="F908" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G908" s="4" t="s">
         <v>287</v>
@@ -86561,7 +86561,7 @@
         <v>30</v>
       </c>
       <c r="F985" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G985" s="4" t="s">
         <v>287</v>
@@ -86639,7 +86639,7 @@
         <v>30</v>
       </c>
       <c r="F986" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G986" s="4" t="s">
         <v>287</v>
@@ -86715,7 +86715,7 @@
         <v>30</v>
       </c>
       <c r="F987" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G987" s="4" t="s">
         <v>287</v>
@@ -86791,7 +86791,7 @@
         <v>30</v>
       </c>
       <c r="F988" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G988" s="4" t="s">
         <v>287</v>
@@ -86867,7 +86867,7 @@
         <v>30</v>
       </c>
       <c r="F989" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G989" s="4" t="s">
         <v>287</v>
@@ -91253,7 +91253,7 @@
         <v>1882</v>
       </c>
       <c r="F1046" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G1046" s="4" t="s">
         <v>287</v>
@@ -91331,7 +91331,7 @@
         <v>1882</v>
       </c>
       <c r="F1047" s="4" t="s">
-        <v>31</v>
+        <v>805</v>
       </c>
       <c r="G1047" s="4" t="s">
         <v>287</v>
@@ -94938,7 +94938,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z26"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -95052,40 +95052,40 @@
         <v>2842</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>2843</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="D2" s="3" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>126</v>
+        <v>1734</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>127</v>
+        <v>1735</v>
       </c>
       <c r="I2" s="3">
+        <v>8</v>
+      </c>
+      <c r="J2" s="3">
         <v>6</v>
-      </c>
-      <c r="J2" s="3">
-        <v>5</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>54</v>
+        <v>118</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N2" s="3" t="s">
         <v>37</v>
@@ -95094,19 +95094,19 @@
         <v>38</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>56</v>
+        <v>2844</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>2844</v>
+        <v>2845</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>148</v>
+        <v>43</v>
       </c>
       <c r="U2" s="3" t="s">
         <v>44</v>
@@ -95123,16 +95123,14 @@
       <c r="Y2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="3" t="s">
-        <v>418</v>
-      </c>
+      <c r="Z2" s="3"/>
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2843</v>
+        <v>26</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>49</v>
@@ -95147,10 +95145,10 @@
         <v>31</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="I3" s="5">
         <v>6</v>
@@ -95174,25 +95172,25 @@
         <v>38</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>2846</v>
+        <v>2848</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>2847</v>
+        <v>2849</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>147</v>
+        <v>59</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>154</v>
+        <v>60</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V3" s="5">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="W3" s="5" t="s">
         <v>45</v>
@@ -95207,10 +95205,10 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2843</v>
+        <v>26</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>49</v>
@@ -95225,10 +95223,10 @@
         <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1747</v>
+        <v>126</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1748</v>
+        <v>127</v>
       </c>
       <c r="I4" s="3">
         <v>6</v>
@@ -95252,25 +95250,25 @@
         <v>38</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>2846</v>
+        <v>2848</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>2848</v>
+        <v>2850</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>2849</v>
+        <v>2851</v>
       </c>
       <c r="U4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V4" s="3">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="W4" s="3" t="s">
         <v>45</v>
@@ -95285,16 +95283,16 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>2843</v>
+        <v>26</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>237</v>
+        <v>50</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>51</v>
@@ -95303,16 +95301,16 @@
         <v>31</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>441</v>
+        <v>419</v>
       </c>
       <c r="I5" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J5" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>34</v>
@@ -95321,34 +95319,34 @@
         <v>54</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>37</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>168</v>
+        <v>38</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>238</v>
+        <v>63</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>2850</v>
+        <v>2852</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>2851</v>
+        <v>2853</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>113</v>
+        <v>59</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>255</v>
+        <v>66</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V5" s="5">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="W5" s="5" t="s">
         <v>45</v>
@@ -95360,21 +95358,21 @@
         <v>46</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>2852</v>
+        <v>418</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2843</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>51</v>
@@ -95383,16 +95381,16 @@
         <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="I6" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J6" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>34</v>
@@ -95401,7 +95399,7 @@
         <v>54</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>37</v>
@@ -95410,25 +95408,25 @@
         <v>38</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>2853</v>
+        <v>2852</v>
       </c>
       <c r="R6" s="3" t="s">
         <v>2854</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>338</v>
+        <v>123</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>1439</v>
+        <v>2855</v>
       </c>
       <c r="U6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V6" s="3">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="W6" s="3" t="s">
         <v>45</v>
@@ -95440,18 +95438,18 @@
         <v>46</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>2855</v>
+        <v>418</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2843</v>
+        <v>26</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>29</v>
@@ -95463,16 +95461,16 @@
         <v>31</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>941</v>
+        <v>1078</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>1204</v>
+        <v>1079</v>
       </c>
       <c r="I7" s="5">
         <v>9</v>
       </c>
       <c r="J7" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>34</v>
@@ -95481,7 +95479,7 @@
         <v>54</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>37</v>
@@ -95490,25 +95488,25 @@
         <v>38</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>2853</v>
+        <v>2856</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>2856</v>
+        <v>2857</v>
       </c>
       <c r="S7" s="5" t="s">
         <v>79</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V7" s="5">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="W7" s="5" t="s">
         <v>45</v>
@@ -95520,18 +95518,18 @@
         <v>46</v>
       </c>
       <c r="Z7" s="5" t="s">
-        <v>2855</v>
+        <v>2858</v>
       </c>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2843</v>
+        <v>26</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>29</v>
@@ -95543,16 +95541,16 @@
         <v>31</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>2857</v>
+        <v>82</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>2858</v>
+        <v>83</v>
       </c>
       <c r="I8" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J8" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>34</v>
@@ -95561,7 +95559,7 @@
         <v>54</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>37</v>
@@ -95570,25 +95568,25 @@
         <v>38</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>2853</v>
+        <v>2859</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>2859</v>
+        <v>2860</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>2860</v>
+        <v>59</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>2861</v>
+        <v>88</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V8" s="3">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>45</v>
@@ -95600,21 +95598,21 @@
         <v>46</v>
       </c>
       <c r="Z8" s="3" t="s">
-        <v>2855</v>
+        <v>2861</v>
       </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>2843</v>
+        <v>26</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>89</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>50</v>
+        <v>237</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>51</v>
@@ -95623,16 +95621,16 @@
         <v>31</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>108</v>
+        <v>440</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>109</v>
+        <v>441</v>
       </c>
       <c r="I9" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J9" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>34</v>
@@ -95647,10 +95645,10 @@
         <v>37</v>
       </c>
       <c r="O9" s="5" t="s">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>110</v>
+        <v>238</v>
       </c>
       <c r="Q9" s="5" t="s">
         <v>2862</v>
@@ -95659,10 +95657,10 @@
         <v>2863</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>113</v>
+        <v>338</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>114</v>
+        <v>339</v>
       </c>
       <c r="U9" s="5" t="s">
         <v>44</v>
@@ -95679,17 +95677,19 @@
       <c r="Y9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z9" s="5"/>
+      <c r="Z9" s="5" t="s">
+        <v>2864</v>
+      </c>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2843</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>29</v>
@@ -95701,16 +95701,16 @@
         <v>31</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>213</v>
+        <v>941</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>214</v>
+        <v>1204</v>
       </c>
       <c r="I10" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J10" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>34</v>
@@ -95719,7 +95719,7 @@
         <v>54</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>37</v>
@@ -95728,25 +95728,25 @@
         <v>38</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>2865</v>
+        <v>2866</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>136</v>
+        <v>338</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>137</v>
+        <v>1439</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V10" s="3">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>45</v>
@@ -95755,21 +95755,21 @@
         <v>45</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="Z10" s="3" t="s">
-        <v>2866</v>
+        <v>2867</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>2843</v>
+        <v>26</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>29</v>
@@ -95781,13 +95781,13 @@
         <v>31</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>1903</v>
+        <v>103</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>1904</v>
+        <v>104</v>
       </c>
       <c r="I11" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J11" s="5">
         <v>7</v>
@@ -95799,7 +95799,7 @@
         <v>54</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>37</v>
@@ -95808,78 +95808,78 @@
         <v>38</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>133</v>
+        <v>93</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="R11" s="5" t="s">
+        <v>2868</v>
+      </c>
+      <c r="S11" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="T11" s="5" t="s">
+        <v>2869</v>
+      </c>
+      <c r="U11" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="V11" s="5">
+        <v>2018</v>
+      </c>
+      <c r="W11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y11" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="Z11" s="5" t="s">
         <v>2867</v>
-      </c>
-      <c r="S11" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="U11" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="V11" s="5">
-        <v>2019</v>
-      </c>
-      <c r="W11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X11" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y11" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z11" s="5" t="s">
-        <v>2866</v>
       </c>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>2868</v>
+        <v>89</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>1734</v>
+        <v>1417</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>1735</v>
+        <v>1560</v>
       </c>
       <c r="I12" s="3">
         <v>8</v>
       </c>
       <c r="J12" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>34</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>118</v>
+        <v>54</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="N12" s="3" t="s">
         <v>37</v>
@@ -95888,19 +95888,19 @@
         <v>38</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>2869</v>
+        <v>93</v>
       </c>
       <c r="Q12" s="3" t="s">
+        <v>2865</v>
+      </c>
+      <c r="R12" s="3" t="s">
         <v>2870</v>
       </c>
-      <c r="R12" s="3" t="s">
+      <c r="S12" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="T12" s="3" t="s">
         <v>2871</v>
-      </c>
-      <c r="S12" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="T12" s="3" t="s">
-        <v>43</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>44</v>
@@ -95917,17 +95917,19 @@
       <c r="Y12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z12" s="3"/>
+      <c r="Z12" s="3" t="s">
+        <v>2867</v>
+      </c>
     </row>
     <row r="13" spans="1:26">
       <c r="A13" s="5" t="s">
-        <v>2843</v>
+        <v>2847</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>50</v>
@@ -95939,10 +95941,10 @@
         <v>31</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>61</v>
+        <v>108</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>62</v>
+        <v>109</v>
       </c>
       <c r="I13" s="5">
         <v>6</v>
@@ -95957,7 +95959,7 @@
         <v>54</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="N13" s="5" t="s">
         <v>37</v>
@@ -95966,7 +95968,7 @@
         <v>38</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="Q13" s="5" t="s">
         <v>2872</v>
@@ -95975,16 +95977,16 @@
         <v>2873</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>60</v>
+        <v>114</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V13" s="5">
-        <v>2019</v>
+        <v>2018</v>
       </c>
       <c r="W13" s="5" t="s">
         <v>45</v>
@@ -95995,17 +95997,19 @@
       <c r="Y13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z13" s="5"/>
+      <c r="Z13" s="5" t="s">
+        <v>968</v>
+      </c>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="3" t="s">
-        <v>2843</v>
+        <v>2847</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>50</v>
@@ -96017,16 +96021,16 @@
         <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>126</v>
+        <v>968</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>127</v>
+        <v>969</v>
       </c>
       <c r="I14" s="3">
         <v>6</v>
       </c>
       <c r="J14" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>34</v>
@@ -96035,7 +96039,7 @@
         <v>54</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>37</v>
@@ -96044,7 +96048,7 @@
         <v>38</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>56</v>
+        <v>110</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>2872</v>
@@ -96053,16 +96057,16 @@
         <v>2874</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>2875</v>
+        <v>255</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V14" s="3">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>45</v>
@@ -96073,20 +96077,22 @@
       <c r="Y14" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z14" s="3"/>
+      <c r="Z14" s="3" t="s">
+        <v>968</v>
+      </c>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="5" t="s">
-        <v>2843</v>
+        <v>2847</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>26</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>51</v>
@@ -96095,16 +96101,16 @@
         <v>31</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>418</v>
+        <v>436</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="I15" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J15" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>34</v>
@@ -96113,7 +96119,7 @@
         <v>54</v>
       </c>
       <c r="M15" s="5" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="N15" s="5" t="s">
         <v>37</v>
@@ -96122,19 +96128,19 @@
         <v>38</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="Q15" s="5" t="s">
+        <v>2875</v>
+      </c>
+      <c r="R15" s="5" t="s">
         <v>2876</v>
       </c>
-      <c r="R15" s="5" t="s">
-        <v>2877</v>
-      </c>
       <c r="S15" s="5" t="s">
-        <v>59</v>
+        <v>136</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>44</v>
@@ -96152,21 +96158,21 @@
         <v>46</v>
       </c>
       <c r="Z15" s="5" t="s">
-        <v>418</v>
+        <v>2877</v>
       </c>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="3" t="s">
-        <v>2843</v>
+        <v>2847</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>26</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>49</v>
+        <v>130</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>51</v>
@@ -96175,16 +96181,16 @@
         <v>31</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>67</v>
+        <v>213</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>68</v>
+        <v>214</v>
       </c>
       <c r="I16" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J16" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>34</v>
@@ -96193,7 +96199,7 @@
         <v>54</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>37</v>
@@ -96202,25 +96208,25 @@
         <v>38</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>63</v>
+        <v>133</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>2876</v>
+        <v>2875</v>
       </c>
       <c r="R16" s="3" t="s">
         <v>2878</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>2879</v>
+        <v>142</v>
       </c>
       <c r="U16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V16" s="3">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="W16" s="3" t="s">
         <v>45</v>
@@ -96232,807 +96238,7 @@
         <v>46</v>
       </c>
       <c r="Z16" s="3" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="17" spans="1:26">
-      <c r="A17" s="5" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>1078</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>1079</v>
-      </c>
-      <c r="I17" s="5">
-        <v>9</v>
-      </c>
-      <c r="J17" s="5">
-        <v>9</v>
-      </c>
-      <c r="K17" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L17" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M17" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N17" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O17" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P17" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q17" s="5" t="s">
-        <v>2880</v>
-      </c>
-      <c r="R17" s="5" t="s">
-        <v>2881</v>
-      </c>
-      <c r="S17" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="T17" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="U17" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="V17" s="5">
-        <v>2021</v>
-      </c>
-      <c r="W17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X17" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z17" s="5" t="s">
-        <v>2882</v>
-      </c>
-    </row>
-    <row r="18" spans="1:26">
-      <c r="A18" s="3" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="I18" s="3">
-        <v>8</v>
-      </c>
-      <c r="J18" s="3">
-        <v>8</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="N18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O18" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q18" s="3" t="s">
-        <v>2883</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>2884</v>
-      </c>
-      <c r="S18" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="T18" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="U18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V18" s="3">
-        <v>2023</v>
-      </c>
-      <c r="W18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y18" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z18" s="3" t="s">
-        <v>2885</v>
-      </c>
-    </row>
-    <row r="19" spans="1:26">
-      <c r="A19" s="5" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>440</v>
-      </c>
-      <c r="H19" s="5" t="s">
-        <v>441</v>
-      </c>
-      <c r="I19" s="5">
-        <v>8</v>
-      </c>
-      <c r="J19" s="5">
-        <v>8</v>
-      </c>
-      <c r="K19" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L19" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M19" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="N19" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O19" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="P19" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q19" s="5" t="s">
-        <v>2886</v>
-      </c>
-      <c r="R19" s="5" t="s">
-        <v>2887</v>
-      </c>
-      <c r="S19" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="T19" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="U19" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="V19" s="5">
-        <v>2018</v>
-      </c>
-      <c r="W19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X19" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y19" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z19" s="5" t="s">
-        <v>2888</v>
-      </c>
-    </row>
-    <row r="20" spans="1:26">
-      <c r="A20" s="3" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>941</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>1204</v>
-      </c>
-      <c r="I20" s="3">
-        <v>8</v>
-      </c>
-      <c r="J20" s="3">
-        <v>8</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O20" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q20" s="3" t="s">
-        <v>2889</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>2890</v>
-      </c>
-      <c r="S20" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="T20" s="3" t="s">
-        <v>1439</v>
-      </c>
-      <c r="U20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V20" s="3">
-        <v>2018</v>
-      </c>
-      <c r="W20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z20" s="3" t="s">
-        <v>2891</v>
-      </c>
-    </row>
-    <row r="21" spans="1:26">
-      <c r="A21" s="5" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="I21" s="5">
-        <v>8</v>
-      </c>
-      <c r="J21" s="5">
-        <v>7</v>
-      </c>
-      <c r="K21" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L21" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M21" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="N21" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O21" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P21" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q21" s="5" t="s">
-        <v>2889</v>
-      </c>
-      <c r="R21" s="5" t="s">
-        <v>2892</v>
-      </c>
-      <c r="S21" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="T21" s="5" t="s">
-        <v>2893</v>
-      </c>
-      <c r="U21" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="V21" s="5">
-        <v>2018</v>
-      </c>
-      <c r="W21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y21" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z21" s="5" t="s">
-        <v>2891</v>
-      </c>
-    </row>
-    <row r="22" spans="1:26">
-      <c r="A22" s="3" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>1417</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>1560</v>
-      </c>
-      <c r="I22" s="3">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3">
-        <v>7</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>2889</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>2894</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>2895</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V22" s="3">
-        <v>2023</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y22" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>2891</v>
-      </c>
-    </row>
-    <row r="23" spans="1:26">
-      <c r="A23" s="5" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="I23" s="5">
-        <v>6</v>
-      </c>
-      <c r="J23" s="5">
-        <v>6</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L23" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M23" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="N23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P23" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q23" s="5" t="s">
-        <v>2896</v>
-      </c>
-      <c r="R23" s="5" t="s">
-        <v>2897</v>
-      </c>
-      <c r="S23" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="T23" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="U23" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="V23" s="5">
-        <v>2018</v>
-      </c>
-      <c r="W23" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X23" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z23" s="5" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="24" spans="1:26">
-      <c r="A24" s="3" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>968</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>969</v>
-      </c>
-      <c r="I24" s="3">
-        <v>6</v>
-      </c>
-      <c r="J24" s="3">
-        <v>3</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="N24" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O24" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q24" s="3" t="s">
-        <v>2896</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>2898</v>
-      </c>
-      <c r="S24" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="T24" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="U24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V24" s="3">
-        <v>2017</v>
-      </c>
-      <c r="W24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X24" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y24" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z24" s="3" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="25" spans="1:26">
-      <c r="A25" s="5" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="H25" s="5" t="s">
-        <v>437</v>
-      </c>
-      <c r="I25" s="5">
-        <v>9</v>
-      </c>
-      <c r="J25" s="5">
-        <v>8</v>
-      </c>
-      <c r="K25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="L25" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M25" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="N25" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="O25" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="P25" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q25" s="5" t="s">
-        <v>2899</v>
-      </c>
-      <c r="R25" s="5" t="s">
-        <v>2900</v>
-      </c>
-      <c r="S25" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="T25" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="U25" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="V25" s="5">
-        <v>2019</v>
-      </c>
-      <c r="W25" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X25" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y25" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z25" s="5" t="s">
-        <v>2901</v>
-      </c>
-    </row>
-    <row r="26" spans="1:26">
-      <c r="A26" s="3" t="s">
-        <v>2843</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="I26" s="3">
-        <v>9</v>
-      </c>
-      <c r="J26" s="3">
-        <v>9</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="O26" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q26" s="3" t="s">
-        <v>2899</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>2902</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="V26" s="3">
-        <v>2019</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z26" s="3" t="s">
-        <v>2901</v>
+        <v>2877</v>
       </c>
     </row>
   </sheetData>
@@ -97043,7 +96249,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z21"/>
+  <dimension ref="A1:Z31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.7109375" customWidth="1"/>
@@ -97154,31 +96360,31 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="3" t="s">
-        <v>2903</v>
+        <v>2842</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>2904</v>
+        <v>49</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>1734</v>
+        <v>126</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>1735</v>
+        <v>127</v>
       </c>
       <c r="I2" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J2" s="3">
         <v>5</v>
@@ -97187,31 +96393,31 @@
         <v>34</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>2460</v>
+        <v>55</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>2461</v>
+        <v>37</v>
       </c>
       <c r="O2" s="3" t="s">
         <v>38</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>2905</v>
+        <v>56</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>2906</v>
+        <v>2879</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>2907</v>
+        <v>2880</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>42</v>
+        <v>147</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>43</v>
+        <v>148</v>
       </c>
       <c r="U2" s="3" t="s">
         <v>44</v>
@@ -97228,20 +96434,22 @@
       <c r="Y2" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z2" s="3"/>
+      <c r="Z2" s="3" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="3" spans="1:26">
       <c r="A3" s="5" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>49</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>51</v>
@@ -97250,22 +96458,22 @@
         <v>31</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>322</v>
+        <v>67</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>323</v>
+        <v>68</v>
       </c>
       <c r="I3" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J3" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>34</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>55</v>
@@ -97277,25 +96485,25 @@
         <v>38</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>215</v>
+        <v>63</v>
       </c>
       <c r="Q3" s="5" t="s">
-        <v>2909</v>
+        <v>2881</v>
       </c>
       <c r="R3" s="5" t="s">
-        <v>2910</v>
+        <v>2882</v>
       </c>
       <c r="S3" s="5" t="s">
-        <v>79</v>
+        <v>147</v>
       </c>
       <c r="T3" s="5" t="s">
-        <v>2911</v>
+        <v>154</v>
       </c>
       <c r="U3" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V3" s="5">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="W3" s="5" t="s">
         <v>45</v>
@@ -97306,16 +96514,14 @@
       <c r="Y3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z3" s="5" t="s">
-        <v>2912</v>
-      </c>
+      <c r="Z3" s="5"/>
     </row>
     <row r="4" spans="1:26">
       <c r="A4" s="3" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>49</v>
@@ -97330,10 +96536,10 @@
         <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>332</v>
+        <v>1747</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>333</v>
+        <v>1748</v>
       </c>
       <c r="I4" s="3">
         <v>6</v>
@@ -97357,25 +96563,25 @@
         <v>38</v>
       </c>
       <c r="P4" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>2913</v>
+        <v>2881</v>
       </c>
       <c r="R4" s="3" t="s">
-        <v>2914</v>
+        <v>2883</v>
       </c>
       <c r="S4" s="3" t="s">
-        <v>147</v>
+        <v>101</v>
       </c>
       <c r="T4" s="3" t="s">
-        <v>148</v>
+        <v>2884</v>
       </c>
       <c r="U4" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V4" s="3">
-        <v>2023</v>
+        <v>2017</v>
       </c>
       <c r="W4" s="3" t="s">
         <v>45</v>
@@ -97386,22 +96592,20 @@
       <c r="Y4" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z4" s="3" t="s">
-        <v>1747</v>
-      </c>
+      <c r="Z4" s="3"/>
     </row>
     <row r="5" spans="1:26">
       <c r="A5" s="5" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>50</v>
+        <v>237</v>
       </c>
       <c r="E5" s="5" t="s">
         <v>51</v>
@@ -97410,16 +96614,16 @@
         <v>31</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>83</v>
+        <v>441</v>
       </c>
       <c r="I5" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J5" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>34</v>
@@ -97428,34 +96632,34 @@
         <v>54</v>
       </c>
       <c r="M5" s="5" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>37</v>
       </c>
       <c r="O5" s="5" t="s">
-        <v>38</v>
+        <v>168</v>
       </c>
       <c r="P5" s="5" t="s">
-        <v>56</v>
+        <v>238</v>
       </c>
       <c r="Q5" s="5" t="s">
-        <v>2913</v>
+        <v>2885</v>
       </c>
       <c r="R5" s="5" t="s">
-        <v>2915</v>
+        <v>2886</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="T5" s="5" t="s">
-        <v>2916</v>
+        <v>255</v>
       </c>
       <c r="U5" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V5" s="5">
-        <v>2018</v>
+        <v>2017</v>
       </c>
       <c r="W5" s="5" t="s">
         <v>45</v>
@@ -97467,21 +96671,21 @@
         <v>46</v>
       </c>
       <c r="Z5" s="5" t="s">
-        <v>1747</v>
+        <v>2887</v>
       </c>
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="3" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>51</v>
@@ -97490,16 +96694,16 @@
         <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="I6" s="3">
         <v>8</v>
       </c>
       <c r="J6" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K6" s="3" t="s">
         <v>34</v>
@@ -97508,7 +96712,7 @@
         <v>54</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="N6" s="3" t="s">
         <v>37</v>
@@ -97517,25 +96721,25 @@
         <v>38</v>
       </c>
       <c r="P6" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>2913</v>
+        <v>2888</v>
       </c>
       <c r="R6" s="3" t="s">
-        <v>2917</v>
+        <v>2889</v>
       </c>
       <c r="S6" s="3" t="s">
-        <v>59</v>
+        <v>338</v>
       </c>
       <c r="T6" s="3" t="s">
-        <v>2918</v>
+        <v>1439</v>
       </c>
       <c r="U6" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V6" s="3">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="W6" s="3" t="s">
         <v>45</v>
@@ -97547,21 +96751,21 @@
         <v>46</v>
       </c>
       <c r="Z6" s="3" t="s">
-        <v>1747</v>
+        <v>2890</v>
       </c>
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="5" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>51</v>
@@ -97570,16 +96774,16 @@
         <v>31</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>67</v>
+        <v>941</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>68</v>
+        <v>1204</v>
       </c>
       <c r="I7" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J7" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>34</v>
@@ -97588,7 +96792,7 @@
         <v>54</v>
       </c>
       <c r="M7" s="5" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="N7" s="5" t="s">
         <v>37</v>
@@ -97597,19 +96801,19 @@
         <v>38</v>
       </c>
       <c r="P7" s="5" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="Q7" s="5" t="s">
-        <v>2919</v>
+        <v>2888</v>
       </c>
       <c r="R7" s="5" t="s">
-        <v>2920</v>
+        <v>2891</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>147</v>
+        <v>79</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>44</v>
@@ -97626,20 +96830,22 @@
       <c r="Y7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z7" s="5"/>
+      <c r="Z7" s="5" t="s">
+        <v>2890</v>
+      </c>
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="3" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>51</v>
@@ -97648,16 +96854,16 @@
         <v>31</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>1747</v>
+        <v>2892</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>1748</v>
+        <v>2893</v>
       </c>
       <c r="I8" s="3">
         <v>6</v>
       </c>
       <c r="J8" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K8" s="3" t="s">
         <v>34</v>
@@ -97666,7 +96872,7 @@
         <v>54</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>55</v>
+        <v>92</v>
       </c>
       <c r="N8" s="3" t="s">
         <v>37</v>
@@ -97675,25 +96881,25 @@
         <v>38</v>
       </c>
       <c r="P8" s="3" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>2919</v>
+        <v>2888</v>
       </c>
       <c r="R8" s="3" t="s">
-        <v>2921</v>
+        <v>2894</v>
       </c>
       <c r="S8" s="3" t="s">
-        <v>309</v>
+        <v>2895</v>
       </c>
       <c r="T8" s="3" t="s">
-        <v>2922</v>
+        <v>2896</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V8" s="3">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>45</v>
@@ -97704,20 +96910,22 @@
       <c r="Y8" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z8" s="3"/>
+      <c r="Z8" s="3" t="s">
+        <v>2890</v>
+      </c>
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="5" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E9" s="5" t="s">
         <v>51</v>
@@ -97726,25 +96934,25 @@
         <v>31</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>155</v>
+        <v>108</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>156</v>
+        <v>109</v>
       </c>
       <c r="I9" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J9" s="5">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>34</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>167</v>
+        <v>54</v>
       </c>
       <c r="M9" s="5" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="N9" s="5" t="s">
         <v>37</v>
@@ -97753,25 +96961,25 @@
         <v>38</v>
       </c>
       <c r="P9" s="5" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="Q9" s="5" t="s">
-        <v>2923</v>
+        <v>2897</v>
       </c>
       <c r="R9" s="5" t="s">
-        <v>2924</v>
+        <v>2898</v>
       </c>
       <c r="S9" s="5" t="s">
-        <v>884</v>
+        <v>113</v>
       </c>
       <c r="T9" s="5" t="s">
-        <v>1271</v>
+        <v>114</v>
       </c>
       <c r="U9" s="5" t="s">
-        <v>174</v>
+        <v>44</v>
       </c>
       <c r="V9" s="5">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="W9" s="5" t="s">
         <v>45</v>
@@ -97782,19 +96990,17 @@
       <c r="Y9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z9" s="5" t="s">
-        <v>2925</v>
-      </c>
+      <c r="Z9" s="5"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10" s="3" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>29</v>
@@ -97806,16 +97012,16 @@
         <v>31</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>941</v>
+        <v>213</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>1204</v>
+        <v>214</v>
       </c>
       <c r="I10" s="3">
         <v>9</v>
       </c>
       <c r="J10" s="3">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>34</v>
@@ -97824,7 +97030,7 @@
         <v>54</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="N10" s="3" t="s">
         <v>37</v>
@@ -97833,25 +97039,25 @@
         <v>38</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>2926</v>
+        <v>2899</v>
       </c>
       <c r="R10" s="3" t="s">
-        <v>2927</v>
+        <v>2900</v>
       </c>
       <c r="S10" s="3" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="T10" s="3" t="s">
-        <v>184</v>
+        <v>137</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V10" s="3">
-        <v>2023</v>
+        <v>2019</v>
       </c>
       <c r="W10" s="3" t="s">
         <v>45</v>
@@ -97860,21 +97066,21 @@
         <v>45</v>
       </c>
       <c r="Y10" s="3" t="s">
-        <v>46</v>
+        <v>107</v>
       </c>
       <c r="Z10" s="3" t="s">
-        <v>2928</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="5" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>2842</v>
+        <v>2847</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>89</v>
+        <v>130</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>29</v>
@@ -97886,16 +97092,16 @@
         <v>31</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>2929</v>
+        <v>1903</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>2930</v>
+        <v>1904</v>
       </c>
       <c r="I11" s="5">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J11" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>34</v>
@@ -97904,7 +97110,7 @@
         <v>54</v>
       </c>
       <c r="M11" s="5" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="N11" s="5" t="s">
         <v>37</v>
@@ -97913,25 +97119,25 @@
         <v>38</v>
       </c>
       <c r="P11" s="5" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="Q11" s="5" t="s">
-        <v>2926</v>
+        <v>2899</v>
       </c>
       <c r="R11" s="5" t="s">
-        <v>2931</v>
+        <v>2902</v>
       </c>
       <c r="S11" s="5" t="s">
-        <v>289</v>
+        <v>136</v>
       </c>
       <c r="T11" s="5" t="s">
-        <v>2932</v>
+        <v>142</v>
       </c>
       <c r="U11" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V11" s="5">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="W11" s="5" t="s">
         <v>45</v>
@@ -97943,75 +97149,75 @@
         <v>46</v>
       </c>
       <c r="Z11" s="5" t="s">
-        <v>2928</v>
+        <v>2901</v>
       </c>
     </row>
     <row r="12" spans="1:26">
       <c r="A12" s="3" t="s">
-        <v>2908</v>
+        <v>2903</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>2842</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>89</v>
+        <v>2904</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>31</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>32</v>
+        <v>1734</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>33</v>
+        <v>1735</v>
       </c>
       <c r="I12" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J12" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>34</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>92</v>
+        <v>2460</v>
       </c>
       <c r="N12" s="3" t="s">
-        <v>37</v>
+        <v>2461</v>
       </c>
       <c r="O12" s="3" t="s">
         <v>38</v>
       </c>
       <c r="P12" s="3" t="s">
-        <v>110</v>
+        <v>2905</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>2933</v>
+        <v>2906</v>
       </c>
       <c r="R12" s="3" t="s">
-        <v>2934</v>
+        <v>2907</v>
       </c>
       <c r="S12" s="3" t="s">
-        <v>113</v>
+        <v>42</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>114</v>
+        <v>43</v>
       </c>
       <c r="U12" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V12" s="3">
-        <v>2018</v>
+        <v>2023</v>
       </c>
       <c r="W12" s="3" t="s">
         <v>45</v>
@@ -98032,7 +97238,7 @@
         <v>2842</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>130</v>
+        <v>49</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>29</v>
@@ -98044,25 +97250,25 @@
         <v>31</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>213</v>
+        <v>322</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>214</v>
+        <v>323</v>
       </c>
       <c r="I13" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J13" s="5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>34</v>
       </c>
       <c r="L13" s="5" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="M13" s="5" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="N13" s="5" t="s">
         <v>37</v>
@@ -98071,25 +97277,25 @@
         <v>38</v>
       </c>
       <c r="P13" s="5" t="s">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="Q13" s="5" t="s">
-        <v>2935</v>
+        <v>2909</v>
       </c>
       <c r="R13" s="5" t="s">
-        <v>2936</v>
+        <v>2910</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="T13" s="5" t="s">
-        <v>137</v>
+        <v>2911</v>
       </c>
       <c r="U13" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V13" s="5">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="W13" s="5" t="s">
         <v>45</v>
@@ -98101,15 +97307,15 @@
         <v>46</v>
       </c>
       <c r="Z13" s="5" t="s">
-        <v>2937</v>
+        <v>2912</v>
       </c>
     </row>
     <row r="14" spans="1:26">
       <c r="A14" s="3" t="s">
-        <v>2903</v>
+        <v>2908</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>49</v>
@@ -98124,10 +97330,10 @@
         <v>31</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>2938</v>
+        <v>332</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>2939</v>
+        <v>333</v>
       </c>
       <c r="I14" s="3">
         <v>6</v>
@@ -98151,25 +97357,25 @@
         <v>38</v>
       </c>
       <c r="P14" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="Q14" s="3" t="s">
-        <v>2940</v>
+        <v>2913</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>2941</v>
+        <v>2914</v>
       </c>
       <c r="S14" s="3" t="s">
-        <v>285</v>
+        <v>147</v>
       </c>
       <c r="T14" s="3" t="s">
-        <v>286</v>
+        <v>148</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V14" s="3">
-        <v>2015</v>
+        <v>2023</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>45</v>
@@ -98181,15 +97387,15 @@
         <v>46</v>
       </c>
       <c r="Z14" s="3" t="s">
-        <v>2942</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="15" spans="1:26">
       <c r="A15" s="5" t="s">
-        <v>2903</v>
+        <v>2908</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>49</v>
@@ -98204,16 +97410,16 @@
         <v>31</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="I15" s="5">
         <v>6</v>
       </c>
       <c r="J15" s="5">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>34</v>
@@ -98231,25 +97437,25 @@
         <v>38</v>
       </c>
       <c r="P15" s="5" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="Q15" s="5" t="s">
-        <v>2940</v>
+        <v>2913</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>2943</v>
+        <v>2915</v>
       </c>
       <c r="S15" s="5" t="s">
-        <v>285</v>
+        <v>59</v>
       </c>
       <c r="T15" s="5" t="s">
-        <v>386</v>
+        <v>2916</v>
       </c>
       <c r="U15" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V15" s="5">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="W15" s="5" t="s">
         <v>45</v>
@@ -98260,20 +97466,22 @@
       <c r="Y15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z15" s="5"/>
+      <c r="Z15" s="5" t="s">
+        <v>1747</v>
+      </c>
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="3" t="s">
-        <v>2903</v>
+        <v>2908</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>51</v>
@@ -98282,16 +97490,16 @@
         <v>31</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>540</v>
+        <v>116</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>541</v>
+        <v>117</v>
       </c>
       <c r="I16" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J16" s="3">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>34</v>
@@ -98300,7 +97508,7 @@
         <v>54</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="N16" s="3" t="s">
         <v>37</v>
@@ -98309,25 +97517,25 @@
         <v>38</v>
       </c>
       <c r="P16" s="3" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="Q16" s="3" t="s">
-        <v>2944</v>
+        <v>2913</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>2945</v>
+        <v>2917</v>
       </c>
       <c r="S16" s="3" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="T16" s="3" t="s">
-        <v>184</v>
+        <v>2918</v>
       </c>
       <c r="U16" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V16" s="3">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="W16" s="3" t="s">
         <v>45</v>
@@ -98339,18 +97547,18 @@
         <v>46</v>
       </c>
       <c r="Z16" s="3" t="s">
-        <v>2946</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="17" spans="1:26">
       <c r="A17" s="5" t="s">
-        <v>2903</v>
+        <v>2908</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>2908</v>
+        <v>2842</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>50</v>
@@ -98362,16 +97570,16 @@
         <v>31</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I17" s="5">
         <v>6</v>
       </c>
       <c r="J17" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>34</v>
@@ -98380,7 +97588,7 @@
         <v>54</v>
       </c>
       <c r="M17" s="5" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="N17" s="5" t="s">
         <v>37</v>
@@ -98389,19 +97597,19 @@
         <v>38</v>
       </c>
       <c r="P17" s="5" t="s">
-        <v>110</v>
+        <v>63</v>
       </c>
       <c r="Q17" s="5" t="s">
-        <v>2947</v>
+        <v>2919</v>
       </c>
       <c r="R17" s="5" t="s">
-        <v>2948</v>
+        <v>2920</v>
       </c>
       <c r="S17" s="5" t="s">
         <v>147</v>
       </c>
       <c r="T17" s="5" t="s">
-        <v>2949</v>
+        <v>154</v>
       </c>
       <c r="U17" s="5" t="s">
         <v>44</v>
@@ -98418,16 +97626,14 @@
       <c r="Y17" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z17" s="5" t="s">
-        <v>2729</v>
-      </c>
+      <c r="Z17" s="5"/>
     </row>
     <row r="18" spans="1:26">
       <c r="A18" s="3" t="s">
-        <v>2950</v>
+        <v>2908</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>2903</v>
+        <v>2842</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>49</v>
@@ -98442,16 +97648,16 @@
         <v>31</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>941</v>
+        <v>1747</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1204</v>
+        <v>1748</v>
       </c>
       <c r="I18" s="3">
         <v>6</v>
       </c>
       <c r="J18" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>34</v>
@@ -98469,25 +97675,25 @@
         <v>38</v>
       </c>
       <c r="P18" s="3" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>2951</v>
+        <v>2919</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>2952</v>
+        <v>2921</v>
       </c>
       <c r="S18" s="3" t="s">
-        <v>285</v>
+        <v>309</v>
       </c>
       <c r="T18" s="3" t="s">
-        <v>386</v>
+        <v>2922</v>
       </c>
       <c r="U18" s="3" t="s">
         <v>44</v>
       </c>
       <c r="V18" s="3">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="W18" s="3" t="s">
         <v>45</v>
@@ -98498,22 +97704,20 @@
       <c r="Y18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z18" s="3" t="s">
-        <v>2942</v>
-      </c>
+      <c r="Z18" s="3"/>
     </row>
     <row r="19" spans="1:26">
       <c r="A19" s="5" t="s">
-        <v>2950</v>
+        <v>2908</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>2903</v>
+        <v>2842</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>51</v>
@@ -98522,25 +97726,25 @@
         <v>31</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>2938</v>
+        <v>155</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>2939</v>
+        <v>156</v>
       </c>
       <c r="I19" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J19" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>34</v>
       </c>
       <c r="L19" s="5" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="M19" s="5" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="N19" s="5" t="s">
         <v>37</v>
@@ -98549,25 +97753,25 @@
         <v>38</v>
       </c>
       <c r="P19" s="5" t="s">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="Q19" s="5" t="s">
-        <v>2953</v>
+        <v>2923</v>
       </c>
       <c r="R19" s="5" t="s">
-        <v>2954</v>
+        <v>2924</v>
       </c>
       <c r="S19" s="5" t="s">
-        <v>285</v>
+        <v>884</v>
       </c>
       <c r="T19" s="5" t="s">
-        <v>286</v>
+        <v>1271</v>
       </c>
       <c r="U19" s="5" t="s">
-        <v>44</v>
+        <v>174</v>
       </c>
       <c r="V19" s="5">
-        <v>2015</v>
+        <v>2020</v>
       </c>
       <c r="W19" s="5" t="s">
         <v>45</v>
@@ -98579,15 +97783,15 @@
         <v>46</v>
       </c>
       <c r="Z19" s="5" t="s">
-        <v>2942</v>
+        <v>2925</v>
       </c>
     </row>
     <row r="20" spans="1:26">
       <c r="A20" s="3" t="s">
-        <v>2950</v>
+        <v>2908</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>2903</v>
+        <v>2842</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>89</v>
@@ -98602,16 +97806,16 @@
         <v>31</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>540</v>
+        <v>941</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>541</v>
+        <v>1204</v>
       </c>
       <c r="I20" s="3">
         <v>9</v>
       </c>
       <c r="J20" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K20" s="3" t="s">
         <v>34</v>
@@ -98632,10 +97836,10 @@
         <v>93</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>2955</v>
+        <v>2926</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>2956</v>
+        <v>2927</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>79</v>
@@ -98659,21 +97863,21 @@
         <v>46</v>
       </c>
       <c r="Z20" s="3" t="s">
-        <v>2957</v>
+        <v>2928</v>
       </c>
     </row>
     <row r="21" spans="1:26">
       <c r="A21" s="5" t="s">
-        <v>2950</v>
+        <v>2908</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>2903</v>
+        <v>2842</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>89</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="E21" s="5" t="s">
         <v>51</v>
@@ -98682,10 +97886,10 @@
         <v>31</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>61</v>
+        <v>2929</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>62</v>
+        <v>2930</v>
       </c>
       <c r="I21" s="5">
         <v>6</v>
@@ -98709,36 +97913,832 @@
         <v>38</v>
       </c>
       <c r="P21" s="5" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="Q21" s="5" t="s">
-        <v>2958</v>
+        <v>2926</v>
       </c>
       <c r="R21" s="5" t="s">
-        <v>2959</v>
+        <v>2931</v>
       </c>
       <c r="S21" s="5" t="s">
-        <v>113</v>
+        <v>289</v>
       </c>
       <c r="T21" s="5" t="s">
-        <v>114</v>
+        <v>2932</v>
       </c>
       <c r="U21" s="5" t="s">
         <v>44</v>
       </c>
       <c r="V21" s="5">
+        <v>2022</v>
+      </c>
+      <c r="W21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X21" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z21" s="5" t="s">
+        <v>2928</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26">
+      <c r="A22" s="3" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="3">
+        <v>6</v>
+      </c>
+      <c r="J22" s="3">
+        <v>4</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>2933</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>2934</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="T22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="U22" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V22" s="3">
         <v>2018</v>
       </c>
-      <c r="W21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="X21" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z21" s="5" t="s">
+      <c r="W22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X22" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y22" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z22" s="3"/>
+    </row>
+    <row r="23" spans="1:26">
+      <c r="A23" s="5" t="s">
+        <v>2908</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>2842</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I23" s="5">
+        <v>9</v>
+      </c>
+      <c r="J23" s="5">
+        <v>9</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P23" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q23" s="5" t="s">
+        <v>2935</v>
+      </c>
+      <c r="R23" s="5" t="s">
+        <v>2936</v>
+      </c>
+      <c r="S23" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="T23" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="U23" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V23" s="5">
+        <v>2019</v>
+      </c>
+      <c r="W23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X23" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z23" s="5" t="s">
+        <v>2937</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26">
+      <c r="A24" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>2908</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>2938</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>2939</v>
+      </c>
+      <c r="I24" s="3">
+        <v>6</v>
+      </c>
+      <c r="J24" s="3">
+        <v>6</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>2940</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>2941</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="U24" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V24" s="3">
+        <v>2015</v>
+      </c>
+      <c r="W24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X24" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y24" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z24" s="3" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26">
+      <c r="A25" s="5" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>2908</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="5">
+        <v>6</v>
+      </c>
+      <c r="J25" s="5">
+        <v>1</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N25" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P25" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>2940</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>2943</v>
+      </c>
+      <c r="S25" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="T25" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="U25" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V25" s="5">
+        <v>2017</v>
+      </c>
+      <c r="W25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X25" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z25" s="5"/>
+    </row>
+    <row r="26" spans="1:26">
+      <c r="A26" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>2908</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="I26" s="3">
+        <v>9</v>
+      </c>
+      <c r="J26" s="3">
+        <v>9</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>2944</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>2945</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="U26" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V26" s="3">
+        <v>2023</v>
+      </c>
+      <c r="W26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z26" s="3" t="s">
+        <v>2946</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26">
+      <c r="A27" s="5" t="s">
+        <v>2903</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>2908</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H27" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I27" s="5">
+        <v>6</v>
+      </c>
+      <c r="J27" s="5">
+        <v>5</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L27" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="N27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P27" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q27" s="5" t="s">
+        <v>2947</v>
+      </c>
+      <c r="R27" s="5" t="s">
+        <v>2948</v>
+      </c>
+      <c r="S27" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="T27" s="5" t="s">
+        <v>2949</v>
+      </c>
+      <c r="U27" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V27" s="5">
+        <v>2023</v>
+      </c>
+      <c r="W27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X27" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y27" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z27" s="5" t="s">
+        <v>2729</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26">
+      <c r="A28" s="3" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>941</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>1204</v>
+      </c>
+      <c r="I28" s="3">
+        <v>6</v>
+      </c>
+      <c r="J28" s="3">
+        <v>4</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>2951</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>2952</v>
+      </c>
+      <c r="S28" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="T28" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="U28" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V28" s="3">
+        <v>2017</v>
+      </c>
+      <c r="W28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X28" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y28" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z28" s="3" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26">
+      <c r="A29" s="5" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G29" s="5" t="s">
+        <v>2938</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>2939</v>
+      </c>
+      <c r="I29" s="5">
+        <v>6</v>
+      </c>
+      <c r="J29" s="5">
+        <v>6</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L29" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="N29" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P29" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q29" s="5" t="s">
+        <v>2953</v>
+      </c>
+      <c r="R29" s="5" t="s">
+        <v>2954</v>
+      </c>
+      <c r="S29" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="T29" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="U29" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V29" s="5">
+        <v>2015</v>
+      </c>
+      <c r="W29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X29" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z29" s="5" t="s">
+        <v>2942</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26">
+      <c r="A30" s="3" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="I30" s="3">
+        <v>9</v>
+      </c>
+      <c r="J30" s="3">
+        <v>9</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>2955</v>
+      </c>
+      <c r="R30" s="3" t="s">
+        <v>2956</v>
+      </c>
+      <c r="S30" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="T30" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="U30" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="V30" s="3">
+        <v>2023</v>
+      </c>
+      <c r="W30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X30" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y30" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z30" s="3" t="s">
+        <v>2957</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26">
+      <c r="A31" s="5" t="s">
+        <v>2950</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>2903</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G31" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I31" s="5">
+        <v>6</v>
+      </c>
+      <c r="J31" s="5">
+        <v>6</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L31" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="P31" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q31" s="5" t="s">
+        <v>2958</v>
+      </c>
+      <c r="R31" s="5" t="s">
+        <v>2959</v>
+      </c>
+      <c r="S31" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="T31" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="U31" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="V31" s="5">
+        <v>2018</v>
+      </c>
+      <c r="W31" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X31" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y31" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z31" s="5" t="s">
         <v>941</v>
       </c>
     </row>

--- a/skipperplan.xlsx
+++ b/skipperplan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25743" uniqueCount="2970">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25770" uniqueCount="2972">
   <si>
     <t>Startdatum</t>
   </si>
@@ -3429,7 +3429,7 @@
     <t>15220</t>
   </si>
   <si>
-    <t>Jonas B</t>
+    <t>Jonas B, Lukas H</t>
   </si>
   <si>
     <t>Fabian F</t>
@@ -3624,7 +3624,7 @@
     <t>15726</t>
   </si>
   <si>
-    <t>Philipp K, Christian K, Florian B, Korbinian R, Sebastian W, Martin W, Marlon S, Lukas H</t>
+    <t>Philipp K, Christian K, Florian B, Korbinian R, Sebastian W, Martin W, Marlon S</t>
   </si>
   <si>
     <t>15727</t>
@@ -3849,7 +3849,7 @@
     <t>15528</t>
   </si>
   <si>
-    <t>Simon B, Lukas F, Sven H</t>
+    <t>Simon B, Lukas F, Sven H, Lukas H</t>
   </si>
   <si>
     <t>Lennart M</t>
@@ -5109,7 +5109,7 @@
     <t>15741</t>
   </si>
   <si>
-    <t>Nils K, Martin W, Marc D, Hendrik B, David S, Jaqueline N</t>
+    <t>Nils K, Martin W, Marc D, Hendrik B, Jaqueline N</t>
   </si>
   <si>
     <t>15743</t>
@@ -6039,7 +6039,7 @@
     <t>16245</t>
   </si>
   <si>
-    <t>Andreas N, David Ben T, Martin W, Matthias S, Christina T, Benjamin W, Jasper P</t>
+    <t>Andreas N, David Ben T, Martin W, Matthias S, Christina T, Benjamin W, Jasper P, Miro W</t>
   </si>
   <si>
     <t>16246</t>
@@ -8067,7 +8067,7 @@
     <t>16819</t>
   </si>
   <si>
-    <t>Nicole M, Johanna S, Miriam M, Marlon S, Leon H, Constantin R</t>
+    <t>Nicole M, Johanna S, Miriam M, Marlon S, Leon H, Constantin R, Miro W</t>
   </si>
   <si>
     <t>17159</t>
@@ -8914,6 +8914,12 @@
   </si>
   <si>
     <t>Neue Bewerbungen</t>
+  </si>
+  <si>
+    <t>Neue Bewerbung(en)</t>
+  </si>
+  <si>
+    <t>Miro W</t>
   </si>
   <si>
     <t>ID</t>
@@ -11505,7 +11511,7 @@
         <v>9</v>
       </c>
       <c r="J27" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>34</v>
@@ -11661,7 +11667,7 @@
         <v>8</v>
       </c>
       <c r="J29" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>34</v>
@@ -12767,7 +12773,7 @@
         <v>8</v>
       </c>
       <c r="J43" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K43" s="7" t="s">
         <v>34</v>
@@ -13553,7 +13559,7 @@
         <v>10</v>
       </c>
       <c r="J53" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K53" s="5" t="s">
         <v>34</v>
@@ -13945,7 +13951,7 @@
         <v>8</v>
       </c>
       <c r="J58" s="3">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>34</v>
@@ -17969,7 +17975,7 @@
         <v>9</v>
       </c>
       <c r="J109" s="5">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K109" s="5" t="s">
         <v>34</v>
@@ -18283,7 +18289,7 @@
         <v>9</v>
       </c>
       <c r="J113" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K113" s="5" t="s">
         <v>34</v>
@@ -19149,7 +19155,7 @@
         <v>9</v>
       </c>
       <c r="J124" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K124" s="3" t="s">
         <v>34</v>
@@ -22535,7 +22541,7 @@
         <v>10</v>
       </c>
       <c r="J167" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K167" s="5" t="s">
         <v>34</v>
@@ -22929,7 +22935,7 @@
         <v>8</v>
       </c>
       <c r="J172" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K172" s="3" t="s">
         <v>34</v>
@@ -23323,7 +23329,7 @@
         <v>9</v>
       </c>
       <c r="J177" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K177" s="6" t="s">
         <v>34</v>
@@ -24955,7 +24961,7 @@
         <v>51</v>
       </c>
       <c r="F198" s="3" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G198" s="3" t="s">
         <v>126</v>
@@ -25035,7 +25041,7 @@
         <v>51</v>
       </c>
       <c r="F199" s="5" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G199" s="5" t="s">
         <v>108</v>
@@ -27955,7 +27961,7 @@
         <v>8</v>
       </c>
       <c r="J236" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K236" s="3" t="s">
         <v>34</v>
@@ -28503,7 +28509,7 @@
         <v>8</v>
       </c>
       <c r="J243" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K243" s="5" t="s">
         <v>34</v>
@@ -36203,7 +36209,7 @@
         <v>8</v>
       </c>
       <c r="J341" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K341" s="5" t="s">
         <v>34</v>
@@ -36515,7 +36521,7 @@
         <v>9</v>
       </c>
       <c r="J345" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K345" s="5" t="s">
         <v>34</v>
@@ -36671,7 +36677,7 @@
         <v>8</v>
       </c>
       <c r="J347" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K347" s="5" t="s">
         <v>34</v>
@@ -36817,7 +36823,7 @@
         <v>51</v>
       </c>
       <c r="F349" s="5" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G349" s="5" t="s">
         <v>929</v>
@@ -36897,7 +36903,7 @@
         <v>51</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G350" s="3" t="s">
         <v>1219</v>
@@ -36975,7 +36981,7 @@
         <v>51</v>
       </c>
       <c r="F351" s="6" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G351" s="6" t="s">
         <v>1072</v>
@@ -37053,7 +37059,7 @@
         <v>51</v>
       </c>
       <c r="F352" s="6" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G352" s="6" t="s">
         <v>866</v>
@@ -37131,7 +37137,7 @@
         <v>51</v>
       </c>
       <c r="F353" s="6" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G353" s="6" t="s">
         <v>1225</v>
@@ -37209,7 +37215,7 @@
         <v>51</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G354" s="3" t="s">
         <v>682</v>
@@ -39165,7 +39171,7 @@
         <v>51</v>
       </c>
       <c r="F379" s="5" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G379" s="5" t="s">
         <v>1143</v>
@@ -39245,7 +39251,7 @@
         <v>51</v>
       </c>
       <c r="F380" s="6" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G380" s="6" t="s">
         <v>1275</v>
@@ -39323,7 +39329,7 @@
         <v>51</v>
       </c>
       <c r="F381" s="6" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G381" s="6" t="s">
         <v>1184</v>
@@ -39401,7 +39407,7 @@
         <v>51</v>
       </c>
       <c r="F382" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G382" s="4" t="s">
         <v>287</v>
@@ -42073,7 +42079,7 @@
         <v>9</v>
       </c>
       <c r="J416" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K416" s="3" t="s">
         <v>34</v>
@@ -44575,7 +44581,7 @@
         <v>51</v>
       </c>
       <c r="F448" s="3" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G448" s="3" t="s">
         <v>108</v>
@@ -44655,7 +44661,7 @@
         <v>51</v>
       </c>
       <c r="F449" s="6" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G449" s="6" t="s">
         <v>1427</v>
@@ -44733,7 +44739,7 @@
         <v>51</v>
       </c>
       <c r="F450" s="6" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G450" s="6" t="s">
         <v>1307</v>
@@ -46541,7 +46547,7 @@
         <v>7</v>
       </c>
       <c r="J473" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K473" s="5" t="s">
         <v>34</v>
@@ -46917,7 +46923,7 @@
         <v>51</v>
       </c>
       <c r="F478" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G478" s="7" t="s">
         <v>220</v>
@@ -46997,7 +47003,7 @@
         <v>51</v>
       </c>
       <c r="F479" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G479" s="7" t="s">
         <v>929</v>
@@ -50531,7 +50537,7 @@
         <v>8</v>
       </c>
       <c r="J524" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K524" s="4" t="s">
         <v>34</v>
@@ -52877,7 +52883,7 @@
         <v>9</v>
       </c>
       <c r="J554" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K554" s="3" t="s">
         <v>34</v>
@@ -54525,7 +54531,7 @@
         <v>8</v>
       </c>
       <c r="J575" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K575" s="5" t="s">
         <v>34</v>
@@ -54759,7 +54765,7 @@
         <v>9</v>
       </c>
       <c r="J578" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K578" s="3" t="s">
         <v>34</v>
@@ -55931,7 +55937,7 @@
         <v>10</v>
       </c>
       <c r="J593" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K593" s="7" t="s">
         <v>34</v>
@@ -56241,7 +56247,7 @@
         <v>7</v>
       </c>
       <c r="J597" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K597" s="5" t="s">
         <v>34</v>
@@ -60775,7 +60781,7 @@
         <v>9</v>
       </c>
       <c r="J655" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K655" s="5" t="s">
         <v>34</v>
@@ -61399,7 +61405,7 @@
         <v>7</v>
       </c>
       <c r="J663" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K663" s="5" t="s">
         <v>34</v>
@@ -65085,7 +65091,7 @@
         <v>8</v>
       </c>
       <c r="J710" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K710" s="3" t="s">
         <v>34</v>
@@ -65385,7 +65391,7 @@
         <v>51</v>
       </c>
       <c r="F714" s="3" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G714" s="3" t="s">
         <v>1129</v>
@@ -65397,7 +65403,7 @@
         <v>9</v>
       </c>
       <c r="J714" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K714" s="3" t="s">
         <v>34</v>
@@ -65465,7 +65471,7 @@
         <v>51</v>
       </c>
       <c r="F715" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G715" s="7" t="s">
         <v>560</v>
@@ -65543,7 +65549,7 @@
         <v>51</v>
       </c>
       <c r="F716" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G716" s="7" t="s">
         <v>1858</v>
@@ -65621,7 +65627,7 @@
         <v>51</v>
       </c>
       <c r="F717" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G717" s="7" t="s">
         <v>854</v>
@@ -65699,7 +65705,7 @@
         <v>51</v>
       </c>
       <c r="F718" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G718" s="7" t="s">
         <v>1979</v>
@@ -65777,7 +65783,7 @@
         <v>51</v>
       </c>
       <c r="F719" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G719" s="4" t="s">
         <v>287</v>
@@ -65853,7 +65859,7 @@
         <v>51</v>
       </c>
       <c r="F720" s="3" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G720" s="3" t="s">
         <v>61</v>
@@ -65931,7 +65937,7 @@
         <v>51</v>
       </c>
       <c r="F721" s="5" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G721" s="5" t="s">
         <v>906</v>
@@ -66009,7 +66015,7 @@
         <v>51</v>
       </c>
       <c r="F722" s="3" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G722" s="3" t="s">
         <v>369</v>
@@ -68831,7 +68837,7 @@
         <v>51</v>
       </c>
       <c r="F758" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G758" s="7" t="s">
         <v>126</v>
@@ -68911,7 +68917,7 @@
         <v>51</v>
       </c>
       <c r="F759" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G759" s="7" t="s">
         <v>776</v>
@@ -68989,7 +68995,7 @@
         <v>51</v>
       </c>
       <c r="F760" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G760" s="7" t="s">
         <v>482</v>
@@ -69067,7 +69073,7 @@
         <v>51</v>
       </c>
       <c r="F761" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G761" s="7" t="s">
         <v>2061</v>
@@ -69145,7 +69151,7 @@
         <v>51</v>
       </c>
       <c r="F762" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G762" s="7" t="s">
         <v>352</v>
@@ -69223,7 +69229,7 @@
         <v>51</v>
       </c>
       <c r="F763" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G763" s="7" t="s">
         <v>996</v>
@@ -69313,7 +69319,7 @@
         <v>8</v>
       </c>
       <c r="J764" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K764" s="7" t="s">
         <v>34</v>
@@ -75255,7 +75261,7 @@
         <v>51</v>
       </c>
       <c r="F840" s="3" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G840" s="3" t="s">
         <v>1385</v>
@@ -75335,7 +75341,7 @@
         <v>51</v>
       </c>
       <c r="F841" s="5" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G841" s="5" t="s">
         <v>941</v>
@@ -75413,7 +75419,7 @@
         <v>51</v>
       </c>
       <c r="F842" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G842" s="7" t="s">
         <v>1858</v>
@@ -75491,7 +75497,7 @@
         <v>51</v>
       </c>
       <c r="F843" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G843" s="4" t="s">
         <v>287</v>
@@ -80353,7 +80359,7 @@
         <v>51</v>
       </c>
       <c r="F905" s="5" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G905" s="5" t="s">
         <v>256</v>
@@ -80433,7 +80439,7 @@
         <v>51</v>
       </c>
       <c r="F906" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G906" s="7" t="s">
         <v>219</v>
@@ -80511,7 +80517,7 @@
         <v>51</v>
       </c>
       <c r="F907" s="7" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G907" s="7" t="s">
         <v>2352</v>
@@ -80589,7 +80595,7 @@
         <v>51</v>
       </c>
       <c r="F908" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G908" s="4" t="s">
         <v>287</v>
@@ -80677,7 +80683,7 @@
         <v>6</v>
       </c>
       <c r="J909" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K909" s="7" t="s">
         <v>34</v>
@@ -84253,7 +84259,7 @@
         <v>1882</v>
       </c>
       <c r="F955" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G955" s="4" t="s">
         <v>287</v>
@@ -84331,7 +84337,7 @@
         <v>1882</v>
       </c>
       <c r="F956" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G956" s="4" t="s">
         <v>287</v>
@@ -86341,7 +86347,7 @@
         <v>8</v>
       </c>
       <c r="J982" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K982" s="4" t="s">
         <v>34</v>
@@ -86561,7 +86567,7 @@
         <v>30</v>
       </c>
       <c r="F985" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G985" s="4" t="s">
         <v>287</v>
@@ -86639,7 +86645,7 @@
         <v>30</v>
       </c>
       <c r="F986" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G986" s="4" t="s">
         <v>287</v>
@@ -86715,7 +86721,7 @@
         <v>30</v>
       </c>
       <c r="F987" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G987" s="4" t="s">
         <v>287</v>
@@ -86791,7 +86797,7 @@
         <v>30</v>
       </c>
       <c r="F988" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G988" s="4" t="s">
         <v>287</v>
@@ -86867,7 +86873,7 @@
         <v>30</v>
       </c>
       <c r="F989" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G989" s="4" t="s">
         <v>287</v>
@@ -91253,7 +91259,7 @@
         <v>1882</v>
       </c>
       <c r="F1046" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G1046" s="4" t="s">
         <v>287</v>
@@ -91331,7 +91337,7 @@
         <v>1882</v>
       </c>
       <c r="F1047" s="4" t="s">
-        <v>805</v>
+        <v>31</v>
       </c>
       <c r="G1047" s="4" t="s">
         <v>287</v>
@@ -98750,7 +98756,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -98789,6 +98795,104 @@
       </c>
       <c r="I1" s="1" t="s">
         <v>2962</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="3" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="3" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1102</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="3" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1871</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1887</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>2964</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="3" t="s">
+        <v>2963</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>2428</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>2649</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2677</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3" t="s">
+        <v>2434</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
+        <v>2964</v>
       </c>
     </row>
   </sheetData>
@@ -98814,16 +98918,16 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2963</v>
+        <v>2965</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2964</v>
+        <v>2966</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2965</v>
+        <v>2967</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2966</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -98840,7 +98944,7 @@
         <v>19</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -98857,7 +98961,7 @@
         <v>16</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -98874,7 +98978,7 @@
         <v>15</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -98891,7 +98995,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -98908,7 +99012,7 @@
         <v>16</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -98925,7 +99029,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -98942,7 +99046,7 @@
         <v>14</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -98959,7 +99063,7 @@
         <v>13</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -98976,7 +99080,7 @@
         <v>14</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -98993,7 +99097,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -99010,7 +99114,7 @@
         <v>14</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -99027,7 +99131,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -99044,7 +99148,7 @@
         <v>12</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -99061,7 +99165,7 @@
         <v>11</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -99078,7 +99182,7 @@
         <v>12</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -99095,7 +99199,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -99112,7 +99216,7 @@
         <v>8</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -99129,7 +99233,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -99146,7 +99250,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -99163,7 +99267,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -99180,7 +99284,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -99197,7 +99301,7 @@
         <v>7</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -99214,7 +99318,7 @@
         <v>7</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -99231,7 +99335,7 @@
         <v>7</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -99248,7 +99352,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -99265,7 +99369,7 @@
         <v>7</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -99282,7 +99386,7 @@
         <v>7</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -99299,7 +99403,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -99316,7 +99420,7 @@
         <v>7</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -99333,7 +99437,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -99350,7 +99454,7 @@
         <v>6</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -99367,7 +99471,7 @@
         <v>6</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -99384,7 +99488,7 @@
         <v>6</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -99401,7 +99505,7 @@
         <v>6</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -99418,7 +99522,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -99435,7 +99539,7 @@
         <v>6</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -99452,7 +99556,7 @@
         <v>6</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>2968</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -99469,7 +99573,7 @@
         <v>5</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -99486,7 +99590,7 @@
         <v>5</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -99503,7 +99607,7 @@
         <v>5</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -99520,7 +99624,7 @@
         <v>5</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -99537,7 +99641,7 @@
         <v>5</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -99554,7 +99658,7 @@
         <v>5</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -99571,7 +99675,7 @@
         <v>5</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -99588,7 +99692,7 @@
         <v>5</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -99605,7 +99709,7 @@
         <v>5</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -99622,7 +99726,7 @@
         <v>5</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -99639,7 +99743,7 @@
         <v>7</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -99656,7 +99760,7 @@
         <v>5</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -99673,7 +99777,7 @@
         <v>5</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -99690,7 +99794,7 @@
         <v>5</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -99707,7 +99811,7 @@
         <v>5</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -99724,7 +99828,7 @@
         <v>5</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -99741,7 +99845,7 @@
         <v>5</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -99758,7 +99862,7 @@
         <v>5</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -99775,7 +99879,7 @@
         <v>5</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -99792,7 +99896,7 @@
         <v>4</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -99809,7 +99913,7 @@
         <v>4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -99826,7 +99930,7 @@
         <v>4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -99843,7 +99947,7 @@
         <v>4</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -99860,7 +99964,7 @@
         <v>4</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -99877,7 +99981,7 @@
         <v>4</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -99894,7 +99998,7 @@
         <v>4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -99911,7 +100015,7 @@
         <v>4</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -99928,7 +100032,7 @@
         <v>4</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -99945,7 +100049,7 @@
         <v>4</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -99962,7 +100066,7 @@
         <v>4</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -99979,7 +100083,7 @@
         <v>4</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -99996,7 +100100,7 @@
         <v>4</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -100013,7 +100117,7 @@
         <v>4</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -100030,7 +100134,7 @@
         <v>4</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -100047,7 +100151,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -100064,7 +100168,7 @@
         <v>4</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -100081,7 +100185,7 @@
         <v>5</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -100098,7 +100202,7 @@
         <v>4</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -100115,7 +100219,7 @@
         <v>4</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="78" spans="1:5">
@@ -100132,7 +100236,7 @@
         <v>4</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -100149,7 +100253,7 @@
         <v>4</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -100166,7 +100270,7 @@
         <v>4</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -100183,7 +100287,7 @@
         <v>4</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -100200,7 +100304,7 @@
         <v>4</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -100217,7 +100321,7 @@
         <v>4</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -100234,7 +100338,7 @@
         <v>4</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -100251,7 +100355,7 @@
         <v>6</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -100268,7 +100372,7 @@
         <v>4</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -100285,7 +100389,7 @@
         <v>3</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -100302,7 +100406,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -100319,7 +100423,7 @@
         <v>3</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -100336,7 +100440,7 @@
         <v>3</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -100353,7 +100457,7 @@
         <v>3</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -100370,7 +100474,7 @@
         <v>3</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -100387,7 +100491,7 @@
         <v>3</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -100404,7 +100508,7 @@
         <v>3</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -100421,7 +100525,7 @@
         <v>3</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -100438,7 +100542,7 @@
         <v>3</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -100455,7 +100559,7 @@
         <v>3</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -100472,7 +100576,7 @@
         <v>3</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -100489,7 +100593,7 @@
         <v>3</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -100506,7 +100610,7 @@
         <v>3</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -100523,7 +100627,7 @@
         <v>3</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -100540,7 +100644,7 @@
         <v>3</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -100557,7 +100661,7 @@
         <v>3</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -100574,7 +100678,7 @@
         <v>3</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -100591,7 +100695,7 @@
         <v>3</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -100608,7 +100712,7 @@
         <v>3</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -100625,7 +100729,7 @@
         <v>3</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="108" spans="1:5">
@@ -100642,7 +100746,7 @@
         <v>3</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -100659,7 +100763,7 @@
         <v>3</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -100676,7 +100780,7 @@
         <v>3</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -100693,7 +100797,7 @@
         <v>3</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -100710,7 +100814,7 @@
         <v>3</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -100727,7 +100831,7 @@
         <v>3</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -100744,7 +100848,7 @@
         <v>3</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -100761,7 +100865,7 @@
         <v>3</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -100778,7 +100882,7 @@
         <v>3</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -100795,7 +100899,7 @@
         <v>4</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -100812,7 +100916,7 @@
         <v>3</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -100829,7 +100933,7 @@
         <v>3</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -100846,7 +100950,7 @@
         <v>3</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -100863,7 +100967,7 @@
         <v>3</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -100880,7 +100984,7 @@
         <v>3</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -100897,7 +101001,7 @@
         <v>3</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -100914,7 +101018,7 @@
         <v>3</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -100931,7 +101035,7 @@
         <v>3</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -100948,7 +101052,7 @@
         <v>2</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -100965,7 +101069,7 @@
         <v>2</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -100982,7 +101086,7 @@
         <v>3</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -100999,7 +101103,7 @@
         <v>2</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -101016,7 +101120,7 @@
         <v>2</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -101033,7 +101137,7 @@
         <v>2</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -101050,7 +101154,7 @@
         <v>2</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -101067,7 +101171,7 @@
         <v>2</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -101084,7 +101188,7 @@
         <v>2</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -101101,7 +101205,7 @@
         <v>2</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -101118,7 +101222,7 @@
         <v>2</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -101135,7 +101239,7 @@
         <v>2</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -101152,7 +101256,7 @@
         <v>2</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -101169,7 +101273,7 @@
         <v>2</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -101186,7 +101290,7 @@
         <v>2</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -101203,7 +101307,7 @@
         <v>2</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -101220,7 +101324,7 @@
         <v>2</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -101237,7 +101341,7 @@
         <v>2</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -101254,7 +101358,7 @@
         <v>2</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -101271,7 +101375,7 @@
         <v>2</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -101288,7 +101392,7 @@
         <v>2</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -101305,7 +101409,7 @@
         <v>2</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>2967</v>
+        <v>2969</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -101322,7 +101426,7 @@
         <v>2</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -101339,7 +101443,7 @@
         <v>2</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -101356,7 +101460,7 @@
         <v>2</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -101373,7 +101477,7 @@
         <v>2</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -101390,7 +101494,7 @@
         <v>2</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -101407,7 +101511,7 @@
         <v>2</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -101424,7 +101528,7 @@
         <v>2</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="155" spans="1:5">
@@ -101441,7 +101545,7 @@
         <v>2</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -101458,7 +101562,7 @@
         <v>2</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -101475,7 +101579,7 @@
         <v>2</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -101492,7 +101596,7 @@
         <v>2</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -101509,7 +101613,7 @@
         <v>2</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -101526,7 +101630,7 @@
         <v>2</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -101543,7 +101647,7 @@
         <v>2</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -101560,7 +101664,7 @@
         <v>2</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -101577,7 +101681,7 @@
         <v>2</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -101594,7 +101698,7 @@
         <v>2</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -101611,7 +101715,7 @@
         <v>2</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -101628,7 +101732,7 @@
         <v>2</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -101645,7 +101749,7 @@
         <v>2</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -101662,7 +101766,7 @@
         <v>2</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -101679,7 +101783,7 @@
         <v>2</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -101696,7 +101800,7 @@
         <v>2</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -101713,7 +101817,7 @@
         <v>2</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -101730,7 +101834,7 @@
         <v>2</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -101747,7 +101851,7 @@
         <v>2</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -101764,7 +101868,7 @@
         <v>2</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -101781,7 +101885,7 @@
         <v>2</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -101798,7 +101902,7 @@
         <v>2</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -101815,7 +101919,7 @@
         <v>2</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -101832,7 +101936,7 @@
         <v>1</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -101849,7 +101953,7 @@
         <v>1</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -101866,7 +101970,7 @@
         <v>1</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -101883,7 +101987,7 @@
         <v>1</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -101900,7 +102004,7 @@
         <v>1</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -101917,7 +102021,7 @@
         <v>1</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -101934,7 +102038,7 @@
         <v>1</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -101951,7 +102055,7 @@
         <v>1</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -101968,7 +102072,7 @@
         <v>1</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -101985,7 +102089,7 @@
         <v>1</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -102002,7 +102106,7 @@
         <v>1</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -102019,7 +102123,7 @@
         <v>1</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -102036,7 +102140,7 @@
         <v>1</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -102053,7 +102157,7 @@
         <v>1</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -102070,7 +102174,7 @@
         <v>1</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -102087,7 +102191,7 @@
         <v>1</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -102104,7 +102208,7 @@
         <v>1</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -102121,7 +102225,7 @@
         <v>1</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -102138,7 +102242,7 @@
         <v>1</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -102155,7 +102259,7 @@
         <v>1</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -102172,7 +102276,7 @@
         <v>1</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -102189,7 +102293,7 @@
         <v>1</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -102206,7 +102310,7 @@
         <v>1</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -102223,7 +102327,7 @@
         <v>1</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -102240,7 +102344,7 @@
         <v>1</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -102257,7 +102361,7 @@
         <v>1</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -102274,7 +102378,7 @@
         <v>1</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -102291,7 +102395,7 @@
         <v>1</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -102308,7 +102412,7 @@
         <v>1</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -102325,7 +102429,7 @@
         <v>1</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="208" spans="1:5">
@@ -102342,7 +102446,7 @@
         <v>1</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="209" spans="1:5">
@@ -102359,7 +102463,7 @@
         <v>1</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="210" spans="1:5">
@@ -102376,7 +102480,7 @@
         <v>1</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="211" spans="1:5">
@@ -102393,7 +102497,7 @@
         <v>1</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -102410,7 +102514,7 @@
         <v>1</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -102427,7 +102531,7 @@
         <v>1</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -102444,7 +102548,7 @@
         <v>1</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -102461,7 +102565,7 @@
         <v>1</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -102478,7 +102582,7 @@
         <v>1</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -102495,7 +102599,7 @@
         <v>1</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -102512,7 +102616,7 @@
         <v>1</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -102529,7 +102633,7 @@
         <v>1</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -102546,7 +102650,7 @@
         <v>1</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -102563,7 +102667,7 @@
         <v>1</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -102580,7 +102684,7 @@
         <v>1</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -102597,7 +102701,7 @@
         <v>1</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -102614,7 +102718,7 @@
         <v>1</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -102631,7 +102735,7 @@
         <v>2</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -102648,7 +102752,7 @@
         <v>1</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -102665,7 +102769,7 @@
         <v>1</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -102682,7 +102786,7 @@
         <v>1</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="229" spans="1:5">
@@ -102699,7 +102803,7 @@
         <v>1</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -102716,7 +102820,7 @@
         <v>1</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -102733,7 +102837,7 @@
         <v>1</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -102750,7 +102854,7 @@
         <v>1</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -102767,7 +102871,7 @@
         <v>1</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -102784,7 +102888,7 @@
         <v>1</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -102801,7 +102905,7 @@
         <v>1</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -102818,7 +102922,7 @@
         <v>1</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -102835,7 +102939,7 @@
         <v>1</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -102852,7 +102956,7 @@
         <v>1</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>2969</v>
+        <v>2971</v>
       </c>
     </row>
   </sheetData>

--- a/skipperplan.xlsx
+++ b/skipperplan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25575" uniqueCount="2994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25484" uniqueCount="2992">
   <si>
     <t>Startdatum</t>
   </si>
@@ -3594,6 +3594,9 @@
     <t>15583</t>
   </si>
   <si>
+    <t>confirmed_by_admin_overdue</t>
+  </si>
+  <si>
     <t>16677</t>
   </si>
   <si>
@@ -3897,9 +3900,6 @@
     <t>15329</t>
   </si>
   <si>
-    <t>confirmed_by_admin_overdue</t>
-  </si>
-  <si>
     <t>Peter G, Ilga P, Laura L</t>
   </si>
   <si>
@@ -4206,7 +4206,7 @@
     <t>15291</t>
   </si>
   <si>
-    <t>Tom Ole O, Paul M, Moritz M, Marlon S, Nicole M</t>
+    <t>Tom Ole O, Paul M, Moritz M, Marlon S</t>
   </si>
   <si>
     <t>Paul M</t>
@@ -5205,7 +5205,7 @@
     <t>15182</t>
   </si>
   <si>
-    <t>Nils K, Sharleen S, Dina T, Luca B, Martin W</t>
+    <t>Nils K, Dina T, Luca B, Martin W</t>
   </si>
   <si>
     <t>15183</t>
@@ -7128,7 +7128,7 @@
     <t>SOUTHERN CROSS</t>
   </si>
   <si>
-    <t>Sharleen S, Nicole M, Philippe Z, Marlon S, Johan M, Marlena G, Lena P</t>
+    <t>Sharleen S, Philippe Z, Marlon S, Johan M, Marlena G, Lena P</t>
   </si>
   <si>
     <t>17158</t>
@@ -7737,7 +7737,7 @@
     <t>16769</t>
   </si>
   <si>
-    <t>Marlon S, Lukas F, Johanna S, Constantin R, Florian B, Gregor K, Maurice K</t>
+    <t>Marlon S, Lukas F, Johanna S, Constantin R, Florian B, Gregor K, Maurice K, Nicole M</t>
   </si>
   <si>
     <t>16770</t>
@@ -8976,13 +8976,7 @@
     <t>Neue Bewerbung(en)</t>
   </si>
   <si>
-    <t>Daniel S</t>
-  </si>
-  <si>
     <t>Skipper geändert</t>
-  </si>
-  <si>
-    <t>Bianca G</t>
   </si>
   <si>
     <t>(Kein Skipper)</t>
@@ -11586,7 +11580,7 @@
         <v>10</v>
       </c>
       <c r="J27" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>34</v>
@@ -16230,7 +16224,7 @@
         <v>8</v>
       </c>
       <c r="J86" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K86" s="3" t="s">
         <v>34</v>
@@ -17732,7 +17726,7 @@
         <v>10</v>
       </c>
       <c r="J105" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K105" s="5" t="s">
         <v>34</v>
@@ -21512,7 +21506,7 @@
         <v>9</v>
       </c>
       <c r="J153" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K153" s="7" t="s">
         <v>34</v>
@@ -22926,7 +22920,7 @@
         <v>7</v>
       </c>
       <c r="J171" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K171" s="5" t="s">
         <v>34</v>
@@ -23162,7 +23156,7 @@
         <v>8</v>
       </c>
       <c r="J174" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K174" s="3" t="s">
         <v>34</v>
@@ -23480,7 +23474,7 @@
         <v>9</v>
       </c>
       <c r="J178" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K178" s="3" t="s">
         <v>34</v>
@@ -26388,7 +26382,7 @@
         <v>8</v>
       </c>
       <c r="J215" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K215" s="5" t="s">
         <v>34</v>
@@ -27568,7 +27562,7 @@
         <v>8</v>
       </c>
       <c r="J230" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K230" s="7" t="s">
         <v>34</v>
@@ -27646,7 +27640,7 @@
         <v>8</v>
       </c>
       <c r="J231" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K231" s="5" t="s">
         <v>34</v>
@@ -29538,7 +29532,7 @@
         <v>8</v>
       </c>
       <c r="J255" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K255" s="7" t="s">
         <v>34</v>
@@ -36330,7 +36324,7 @@
         <v>45</v>
       </c>
       <c r="X341" s="5" t="s">
-        <v>158</v>
+        <v>1189</v>
       </c>
       <c r="Y341" s="5" t="s">
         <v>143</v>
@@ -36388,13 +36382,13 @@
         <v>1187</v>
       </c>
       <c r="R342" s="4" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="S342" s="4" t="s">
         <v>790</v>
       </c>
       <c r="T342" s="4" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="U342" s="4" t="s">
         <v>44</v>
@@ -36463,10 +36457,10 @@
         <v>187</v>
       </c>
       <c r="Q343" s="5" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="R343" s="5" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="S343" s="5" t="s">
         <v>401</v>
@@ -36490,7 +36484,7 @@
         <v>46</v>
       </c>
       <c r="Z343" s="5" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="344" spans="1:26">
@@ -36513,10 +36507,10 @@
         <v>31</v>
       </c>
       <c r="G344" s="6" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H344" s="6" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="I344" s="6">
         <v>10</v>
@@ -36543,16 +36537,16 @@
         <v>187</v>
       </c>
       <c r="Q344" s="6" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="R344" s="6" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="S344" s="6" t="s">
         <v>401</v>
       </c>
       <c r="T344" s="6" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="U344" s="6" t="s">
         <v>61</v>
@@ -36621,10 +36615,10 @@
         <v>187</v>
       </c>
       <c r="Q345" s="7" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="R345" s="7" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S345" s="7" t="s">
         <v>116</v>
@@ -36669,10 +36663,10 @@
         <v>31</v>
       </c>
       <c r="G346" s="7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H346" s="7" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="I346" s="7">
         <v>6</v>
@@ -36699,16 +36693,16 @@
         <v>187</v>
       </c>
       <c r="Q346" s="7" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="R346" s="7" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="S346" s="7" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="T346" s="7" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="U346" s="7" t="s">
         <v>61</v>
@@ -36747,10 +36741,10 @@
         <v>31</v>
       </c>
       <c r="G347" s="5" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="H347" s="5" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="I347" s="5">
         <v>9</v>
@@ -36777,10 +36771,10 @@
         <v>322</v>
       </c>
       <c r="Q347" s="5" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="R347" s="5" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="S347" s="5" t="s">
         <v>59</v>
@@ -36827,10 +36821,10 @@
         <v>31</v>
       </c>
       <c r="G348" s="6" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H348" s="6" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="I348" s="6">
         <v>9</v>
@@ -36857,10 +36851,10 @@
         <v>322</v>
       </c>
       <c r="Q348" s="6" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="R348" s="6" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="S348" s="6" t="s">
         <v>59</v>
@@ -36914,7 +36908,7 @@
         <v>9</v>
       </c>
       <c r="J349" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K349" s="5" t="s">
         <v>34</v>
@@ -36935,10 +36929,10 @@
         <v>510</v>
       </c>
       <c r="Q349" s="5" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="R349" s="5" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="S349" s="5" t="s">
         <v>200</v>
@@ -36962,7 +36956,7 @@
         <v>46</v>
       </c>
       <c r="Z349" s="5" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="350" spans="1:26">
@@ -37015,10 +37009,10 @@
         <v>510</v>
       </c>
       <c r="Q350" s="6" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="R350" s="6" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="S350" s="6" t="s">
         <v>200</v>
@@ -37093,10 +37087,10 @@
         <v>793</v>
       </c>
       <c r="Q351" s="7" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="R351" s="7" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="S351" s="7" t="s">
         <v>116</v>
@@ -37120,7 +37114,7 @@
         <v>46</v>
       </c>
       <c r="Z351" s="7" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="352" spans="1:26">
@@ -37173,10 +37167,10 @@
         <v>793</v>
       </c>
       <c r="Q352" s="6" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="R352" s="6" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="S352" s="6" t="s">
         <v>210</v>
@@ -37251,10 +37245,10 @@
         <v>405</v>
       </c>
       <c r="Q353" s="6" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="R353" s="6" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="S353" s="6" t="s">
         <v>200</v>
@@ -37278,7 +37272,7 @@
         <v>46</v>
       </c>
       <c r="Z353" s="6" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="354" spans="1:26">
@@ -37304,7 +37298,7 @@
         <v>771</v>
       </c>
       <c r="H354" s="3" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="I354" s="3">
         <v>9</v>
@@ -37331,10 +37325,10 @@
         <v>197</v>
       </c>
       <c r="Q354" s="3" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="R354" s="3" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="S354" s="3" t="s">
         <v>200</v>
@@ -37358,7 +37352,7 @@
         <v>46</v>
       </c>
       <c r="Z354" s="3" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="355" spans="1:26">
@@ -37381,10 +37375,10 @@
         <v>31</v>
       </c>
       <c r="G355" s="6" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="H355" s="6" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="I355" s="6">
         <v>10</v>
@@ -37411,10 +37405,10 @@
         <v>197</v>
       </c>
       <c r="Q355" s="6" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="R355" s="6" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="S355" s="6" t="s">
         <v>624</v>
@@ -37459,10 +37453,10 @@
         <v>31</v>
       </c>
       <c r="G356" s="6" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H356" s="6" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="I356" s="6">
         <v>9</v>
@@ -37489,10 +37483,10 @@
         <v>197</v>
       </c>
       <c r="Q356" s="6" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="R356" s="6" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="S356" s="6" t="s">
         <v>210</v>
@@ -37565,16 +37559,16 @@
         <v>197</v>
       </c>
       <c r="Q357" s="4" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="R357" s="4" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="S357" s="4" t="s">
         <v>177</v>
       </c>
       <c r="T357" s="4" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="U357" s="4" t="s">
         <v>61</v>
@@ -37613,10 +37607,10 @@
         <v>31</v>
       </c>
       <c r="G358" s="3" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H358" s="3" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="I358" s="3">
         <v>8</v>
@@ -37643,10 +37637,10 @@
         <v>94</v>
       </c>
       <c r="Q358" s="3" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="R358" s="3" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="S358" s="3" t="s">
         <v>97</v>
@@ -37670,7 +37664,7 @@
         <v>46</v>
       </c>
       <c r="Z358" s="3" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="359" spans="1:26">
@@ -37723,10 +37717,10 @@
         <v>94</v>
       </c>
       <c r="Q359" s="5" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="R359" s="5" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="S359" s="5" t="s">
         <v>97</v>
@@ -37771,10 +37765,10 @@
         <v>31</v>
       </c>
       <c r="G360" s="3" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="H360" s="3" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="I360" s="3">
         <v>9</v>
@@ -37801,10 +37795,10 @@
         <v>106</v>
       </c>
       <c r="Q360" s="3" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="R360" s="3" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="S360" s="3" t="s">
         <v>59</v>
@@ -37879,10 +37873,10 @@
         <v>113</v>
       </c>
       <c r="Q361" s="5" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="R361" s="5" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="S361" s="5" t="s">
         <v>116</v>
@@ -37906,7 +37900,7 @@
         <v>46</v>
       </c>
       <c r="Z361" s="5" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="362" spans="1:26">
@@ -37959,10 +37953,10 @@
         <v>113</v>
       </c>
       <c r="Q362" s="3" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="R362" s="3" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="S362" s="3" t="s">
         <v>233</v>
@@ -38010,7 +38004,7 @@
         <v>470</v>
       </c>
       <c r="H363" s="6" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="I363" s="6">
         <v>8</v>
@@ -38037,10 +38031,10 @@
         <v>113</v>
       </c>
       <c r="Q363" s="6" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="R363" s="6" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="S363" s="6" t="s">
         <v>233</v>
@@ -38085,10 +38079,10 @@
         <v>31</v>
       </c>
       <c r="G364" s="6" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="H364" s="6" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="I364" s="6">
         <v>8</v>
@@ -38115,10 +38109,10 @@
         <v>113</v>
       </c>
       <c r="Q364" s="6" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="R364" s="6" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="S364" s="6" t="s">
         <v>233</v>
@@ -38193,10 +38187,10 @@
         <v>113</v>
       </c>
       <c r="Q365" s="5" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="R365" s="5" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="S365" s="5" t="s">
         <v>248</v>
@@ -38271,10 +38265,10 @@
         <v>113</v>
       </c>
       <c r="Q366" s="7" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="R366" s="7" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="S366" s="7" t="s">
         <v>116</v>
@@ -38349,10 +38343,10 @@
         <v>346</v>
       </c>
       <c r="Q367" s="5" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="R367" s="5" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="S367" s="5" t="s">
         <v>152</v>
@@ -38429,16 +38423,16 @@
         <v>346</v>
       </c>
       <c r="Q368" s="6" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="R368" s="6" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="S368" s="6" t="s">
         <v>152</v>
       </c>
       <c r="T368" s="6" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="U368" s="6" t="s">
         <v>61</v>
@@ -38507,10 +38501,10 @@
         <v>138</v>
       </c>
       <c r="Q369" s="5" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="R369" s="5" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="S369" s="5" t="s">
         <v>141</v>
@@ -38534,7 +38528,7 @@
         <v>46</v>
       </c>
       <c r="Z369" s="5" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="370" spans="1:26">
@@ -38557,10 +38551,10 @@
         <v>31</v>
       </c>
       <c r="G370" s="6" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H370" s="6" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="I370" s="6">
         <v>9</v>
@@ -38587,10 +38581,10 @@
         <v>138</v>
       </c>
       <c r="Q370" s="6" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="R370" s="6" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="S370" s="6" t="s">
         <v>141</v>
@@ -38665,10 +38659,10 @@
         <v>138</v>
       </c>
       <c r="Q371" s="6" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="R371" s="6" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="S371" s="6" t="s">
         <v>152</v>
@@ -38743,10 +38737,10 @@
         <v>138</v>
       </c>
       <c r="Q372" s="6" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="R372" s="6" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="S372" s="6" t="s">
         <v>152</v>
@@ -38821,10 +38815,10 @@
         <v>138</v>
       </c>
       <c r="Q373" s="5" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="R373" s="5" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="S373" s="5" t="s">
         <v>50</v>
@@ -38899,10 +38893,10 @@
         <v>578</v>
       </c>
       <c r="Q374" s="3" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="R374" s="3" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="S374" s="3" t="s">
         <v>152</v>
@@ -38924,7 +38918,7 @@
         <v>46</v>
       </c>
       <c r="Z374" s="3" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="375" spans="1:26">
@@ -38977,10 +38971,10 @@
         <v>578</v>
       </c>
       <c r="Q375" s="5" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="R375" s="5" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="S375" s="5" t="s">
         <v>152</v>
@@ -39008,7 +39002,7 @@
         <v>1152</v>
       </c>
       <c r="B376" s="3" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C376" s="3" t="s">
         <v>443</v>
@@ -39026,7 +39020,7 @@
         <v>261</v>
       </c>
       <c r="H376" s="3" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="I376" s="3">
         <v>9</v>
@@ -39053,10 +39047,10 @@
         <v>446</v>
       </c>
       <c r="Q376" s="3" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="R376" s="3" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="S376" s="3" t="s">
         <v>215</v>
@@ -39080,7 +39074,7 @@
         <v>46</v>
       </c>
       <c r="Z376" s="3" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="377" spans="1:26">
@@ -39088,7 +39082,7 @@
         <v>1152</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C377" s="5" t="s">
         <v>443</v>
@@ -39133,10 +39127,10 @@
         <v>446</v>
       </c>
       <c r="Q377" s="5" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="R377" s="5" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="S377" s="5" t="s">
         <v>603</v>
@@ -39166,7 +39160,7 @@
         <v>1152</v>
       </c>
       <c r="B378" s="3" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C378" s="3" t="s">
         <v>443</v>
@@ -39181,10 +39175,10 @@
         <v>31</v>
       </c>
       <c r="G378" s="3" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H378" s="3" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I378" s="3">
         <v>7</v>
@@ -39211,10 +39205,10 @@
         <v>446</v>
       </c>
       <c r="Q378" s="3" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="R378" s="3" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="S378" s="3" t="s">
         <v>603</v>
@@ -39244,7 +39238,7 @@
         <v>1020</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C379" s="5" t="s">
         <v>452</v>
@@ -39289,10 +39283,10 @@
         <v>454</v>
       </c>
       <c r="Q379" s="5" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="R379" s="5" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="S379" s="5" t="s">
         <v>200</v>
@@ -39322,7 +39316,7 @@
         <v>1020</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C380" s="3" t="s">
         <v>280</v>
@@ -39367,10 +39361,10 @@
         <v>285</v>
       </c>
       <c r="Q380" s="3" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="R380" s="3" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="S380" s="3" t="s">
         <v>116</v>
@@ -39394,7 +39388,7 @@
         <v>46</v>
       </c>
       <c r="Z380" s="3" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="381" spans="1:26">
@@ -39402,7 +39396,7 @@
         <v>1020</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C381" s="5" t="s">
         <v>618</v>
@@ -39447,10 +39441,10 @@
         <v>621</v>
       </c>
       <c r="Q381" s="5" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="R381" s="5" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="S381" s="5" t="s">
         <v>624</v>
@@ -39468,7 +39462,7 @@
         <v>45</v>
       </c>
       <c r="X381" s="5" t="s">
-        <v>1290</v>
+        <v>1189</v>
       </c>
       <c r="Y381" s="5" t="s">
         <v>46</v>
@@ -39482,7 +39476,7 @@
         <v>1020</v>
       </c>
       <c r="B382" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C382" s="6" t="s">
         <v>618</v>
@@ -39527,7 +39521,7 @@
         <v>621</v>
       </c>
       <c r="Q382" s="6" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="R382" s="6" t="s">
         <v>1292</v>
@@ -39560,7 +39554,7 @@
         <v>1020</v>
       </c>
       <c r="B383" s="7" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C383" s="7" t="s">
         <v>52</v>
@@ -39638,7 +39632,7 @@
         <v>1020</v>
       </c>
       <c r="B384" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C384" s="6" t="s">
         <v>52</v>
@@ -39716,7 +39710,7 @@
         <v>1020</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C385" s="5" t="s">
         <v>52</v>
@@ -39796,7 +39790,7 @@
         <v>1020</v>
       </c>
       <c r="B386" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C386" s="6" t="s">
         <v>52</v>
@@ -39874,7 +39868,7 @@
         <v>1020</v>
       </c>
       <c r="B387" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C387" s="6" t="s">
         <v>52</v>
@@ -39952,7 +39946,7 @@
         <v>1020</v>
       </c>
       <c r="B388" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C388" s="6" t="s">
         <v>52</v>
@@ -40030,7 +40024,7 @@
         <v>1020</v>
       </c>
       <c r="B389" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C389" s="6" t="s">
         <v>52</v>
@@ -40108,7 +40102,7 @@
         <v>1020</v>
       </c>
       <c r="B390" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C390" s="3" t="s">
         <v>300</v>
@@ -40188,7 +40182,7 @@
         <v>1020</v>
       </c>
       <c r="B391" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C391" s="6" t="s">
         <v>300</v>
@@ -40266,7 +40260,7 @@
         <v>1020</v>
       </c>
       <c r="B392" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C392" s="3" t="s">
         <v>184</v>
@@ -40344,7 +40338,7 @@
         <v>1020</v>
       </c>
       <c r="B393" s="7" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C393" s="7" t="s">
         <v>184</v>
@@ -40424,7 +40418,7 @@
         <v>1020</v>
       </c>
       <c r="B394" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C394" s="6" t="s">
         <v>184</v>
@@ -40439,10 +40433,10 @@
         <v>31</v>
       </c>
       <c r="G394" s="6" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H394" s="6" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="I394" s="6">
         <v>10</v>
@@ -40478,7 +40472,7 @@
         <v>401</v>
       </c>
       <c r="T394" s="6" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="U394" s="6" t="s">
         <v>61</v>
@@ -40502,7 +40496,7 @@
         <v>1020</v>
       </c>
       <c r="B395" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C395" s="6" t="s">
         <v>184</v>
@@ -40517,10 +40511,10 @@
         <v>31</v>
       </c>
       <c r="G395" s="6" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H395" s="6" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="I395" s="6">
         <v>10</v>
@@ -40580,7 +40574,7 @@
         <v>1020</v>
       </c>
       <c r="B396" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C396" s="3" t="s">
         <v>184</v>
@@ -40658,7 +40652,7 @@
         <v>1020</v>
       </c>
       <c r="B397" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C397" s="6" t="s">
         <v>319</v>
@@ -40738,7 +40732,7 @@
         <v>1020</v>
       </c>
       <c r="B398" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C398" s="6" t="s">
         <v>319</v>
@@ -40816,7 +40810,7 @@
         <v>1020</v>
       </c>
       <c r="B399" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C399" s="5" t="s">
         <v>507</v>
@@ -40896,7 +40890,7 @@
         <v>1020</v>
       </c>
       <c r="B400" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C400" s="6" t="s">
         <v>507</v>
@@ -40974,7 +40968,7 @@
         <v>1020</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C401" s="5" t="s">
         <v>792</v>
@@ -41046,7 +41040,7 @@
         <v>46</v>
       </c>
       <c r="Z401" s="5" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="402" spans="1:26">
@@ -41054,7 +41048,7 @@
         <v>1020</v>
       </c>
       <c r="B402" s="7" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C402" s="7" t="s">
         <v>792</v>
@@ -41132,7 +41126,7 @@
         <v>1020</v>
       </c>
       <c r="B403" s="7" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C403" s="7" t="s">
         <v>194</v>
@@ -41150,7 +41144,7 @@
         <v>771</v>
       </c>
       <c r="H403" s="7" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="I403" s="7">
         <v>9</v>
@@ -41212,7 +41206,7 @@
         <v>1020</v>
       </c>
       <c r="B404" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C404" s="3" t="s">
         <v>194</v>
@@ -41292,7 +41286,7 @@
         <v>1020</v>
       </c>
       <c r="B405" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C405" s="6" t="s">
         <v>194</v>
@@ -41370,7 +41364,7 @@
         <v>1020</v>
       </c>
       <c r="B406" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C406" s="3" t="s">
         <v>194</v>
@@ -41450,7 +41444,7 @@
         <v>1020</v>
       </c>
       <c r="B407" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C407" s="6" t="s">
         <v>194</v>
@@ -41528,7 +41522,7 @@
         <v>1020</v>
       </c>
       <c r="B408" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C408" s="6" t="s">
         <v>194</v>
@@ -41543,10 +41537,10 @@
         <v>31</v>
       </c>
       <c r="G408" s="6" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H408" s="6" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="I408" s="6">
         <v>9</v>
@@ -41606,7 +41600,7 @@
         <v>1020</v>
       </c>
       <c r="B409" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C409" s="6" t="s">
         <v>90</v>
@@ -41621,10 +41615,10 @@
         <v>31</v>
       </c>
       <c r="G409" s="6" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H409" s="6" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="I409" s="6">
         <v>8</v>
@@ -41686,7 +41680,7 @@
         <v>1020</v>
       </c>
       <c r="B410" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C410" s="6" t="s">
         <v>90</v>
@@ -41764,7 +41758,7 @@
         <v>1020</v>
       </c>
       <c r="B411" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C411" s="6" t="s">
         <v>90</v>
@@ -41842,7 +41836,7 @@
         <v>1020</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C412" s="3" t="s">
         <v>100</v>
@@ -41920,7 +41914,7 @@
         <v>1020</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C413" s="5" t="s">
         <v>100</v>
@@ -41938,7 +41932,7 @@
         <v>470</v>
       </c>
       <c r="H413" s="5" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="I413" s="5">
         <v>8</v>
@@ -41998,7 +41992,7 @@
         <v>1020</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>100</v>
@@ -42022,7 +42016,7 @@
         <v>10</v>
       </c>
       <c r="J414" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K414" s="3" t="s">
         <v>34</v>
@@ -42078,7 +42072,7 @@
         <v>1020</v>
       </c>
       <c r="B415" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C415" s="6" t="s">
         <v>100</v>
@@ -42156,7 +42150,7 @@
         <v>1020</v>
       </c>
       <c r="B416" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C416" s="6" t="s">
         <v>100</v>
@@ -42234,7 +42228,7 @@
         <v>1020</v>
       </c>
       <c r="B417" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C417" s="6" t="s">
         <v>100</v>
@@ -42312,7 +42306,7 @@
         <v>1020</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>100</v>
@@ -42390,7 +42384,7 @@
         <v>1020</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C419" s="5" t="s">
         <v>135</v>
@@ -42414,7 +42408,7 @@
         <v>8</v>
       </c>
       <c r="J419" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K419" s="5" t="s">
         <v>34</v>
@@ -42470,7 +42464,7 @@
         <v>1020</v>
       </c>
       <c r="B420" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C420" s="6" t="s">
         <v>135</v>
@@ -42524,7 +42518,7 @@
         <v>152</v>
       </c>
       <c r="T420" s="6" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="U420" s="6" t="s">
         <v>61</v>
@@ -42548,7 +42542,7 @@
         <v>1020</v>
       </c>
       <c r="B421" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C421" s="6" t="s">
         <v>135</v>
@@ -42624,7 +42618,7 @@
         <v>1020</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>135</v>
@@ -42704,7 +42698,7 @@
         <v>1020</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C423" s="5" t="s">
         <v>135</v>
@@ -42782,7 +42776,7 @@
         <v>1020</v>
       </c>
       <c r="B424" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C424" s="6" t="s">
         <v>135</v>
@@ -42860,7 +42854,7 @@
         <v>1020</v>
       </c>
       <c r="B425" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C425" s="6" t="s">
         <v>135</v>
@@ -42938,7 +42932,7 @@
         <v>1020</v>
       </c>
       <c r="B426" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C426" s="6" t="s">
         <v>135</v>
@@ -42953,10 +42947,10 @@
         <v>31</v>
       </c>
       <c r="G426" s="6" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H426" s="6" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="I426" s="6">
         <v>8</v>
@@ -43016,7 +43010,7 @@
         <v>1020</v>
       </c>
       <c r="B427" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C427" s="6" t="s">
         <v>135</v>
@@ -43094,7 +43088,7 @@
         <v>1020</v>
       </c>
       <c r="B428" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C428" s="6" t="s">
         <v>135</v>
@@ -43170,7 +43164,7 @@
         <v>1020</v>
       </c>
       <c r="B429" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C429" s="5" t="s">
         <v>135</v>
@@ -43248,7 +43242,7 @@
         <v>1020</v>
       </c>
       <c r="B430" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C430" s="3" t="s">
         <v>574</v>
@@ -43326,7 +43320,7 @@
         <v>1020</v>
       </c>
       <c r="B431" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C431" s="5" t="s">
         <v>574</v>
@@ -43399,10 +43393,10 @@
     </row>
     <row r="432" spans="1:26">
       <c r="A432" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B432" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C432" s="3" t="s">
         <v>452</v>
@@ -43479,10 +43473,10 @@
     </row>
     <row r="433" spans="1:26">
       <c r="A433" s="4" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C433" s="4" t="s">
         <v>452</v>
@@ -43555,10 +43549,10 @@
     </row>
     <row r="434" spans="1:26">
       <c r="A434" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B434" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C434" s="3" t="s">
         <v>28</v>
@@ -43635,10 +43629,10 @@
     </row>
     <row r="435" spans="1:26">
       <c r="A435" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C435" s="5" t="s">
         <v>28</v>
@@ -43715,10 +43709,10 @@
     </row>
     <row r="436" spans="1:26">
       <c r="A436" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B436" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C436" s="6" t="s">
         <v>28</v>
@@ -43793,10 +43787,10 @@
     </row>
     <row r="437" spans="1:26">
       <c r="A437" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C437" s="5" t="s">
         <v>618</v>
@@ -43873,10 +43867,10 @@
     </row>
     <row r="438" spans="1:26">
       <c r="A438" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B438" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C438" s="6" t="s">
         <v>618</v>
@@ -43951,10 +43945,10 @@
     </row>
     <row r="439" spans="1:26">
       <c r="A439" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C439" s="5" t="s">
         <v>52</v>
@@ -44031,10 +44025,10 @@
     </row>
     <row r="440" spans="1:26">
       <c r="A440" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B440" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C440" s="6" t="s">
         <v>52</v>
@@ -44109,10 +44103,10 @@
     </row>
     <row r="441" spans="1:26">
       <c r="A441" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C441" s="5" t="s">
         <v>52</v>
@@ -44189,10 +44183,10 @@
     </row>
     <row r="442" spans="1:26">
       <c r="A442" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B442" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C442" s="6" t="s">
         <v>52</v>
@@ -44267,10 +44261,10 @@
     </row>
     <row r="443" spans="1:26">
       <c r="A443" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B443" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C443" s="6" t="s">
         <v>52</v>
@@ -44345,10 +44339,10 @@
     </row>
     <row r="444" spans="1:26">
       <c r="A444" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B444" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C444" s="6" t="s">
         <v>52</v>
@@ -44423,10 +44417,10 @@
     </row>
     <row r="445" spans="1:26">
       <c r="A445" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C445" s="5" t="s">
         <v>52</v>
@@ -44501,10 +44495,10 @@
     </row>
     <row r="446" spans="1:26">
       <c r="A446" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B446" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C446" s="3" t="s">
         <v>300</v>
@@ -44581,10 +44575,10 @@
     </row>
     <row r="447" spans="1:26">
       <c r="A447" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B447" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C447" s="6" t="s">
         <v>300</v>
@@ -44659,10 +44653,10 @@
     </row>
     <row r="448" spans="1:26">
       <c r="A448" s="7" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B448" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C448" s="7" t="s">
         <v>184</v>
@@ -44739,10 +44733,10 @@
     </row>
     <row r="449" spans="1:26">
       <c r="A449" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B449" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C449" s="6" t="s">
         <v>184</v>
@@ -44817,10 +44811,10 @@
     </row>
     <row r="450" spans="1:26">
       <c r="A450" s="7" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B450" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C450" s="7" t="s">
         <v>184</v>
@@ -44895,10 +44889,10 @@
     </row>
     <row r="451" spans="1:26">
       <c r="A451" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C451" s="5" t="s">
         <v>184</v>
@@ -44975,10 +44969,10 @@
     </row>
     <row r="452" spans="1:26">
       <c r="A452" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B452" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C452" s="6" t="s">
         <v>184</v>
@@ -45032,7 +45026,7 @@
         <v>401</v>
       </c>
       <c r="T452" s="6" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="U452" s="6" t="s">
         <v>61</v>
@@ -45053,10 +45047,10 @@
     </row>
     <row r="453" spans="1:26">
       <c r="A453" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B453" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C453" s="5" t="s">
         <v>184</v>
@@ -45131,10 +45125,10 @@
     </row>
     <row r="454" spans="1:26">
       <c r="A454" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B454" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C454" s="6" t="s">
         <v>184</v>
@@ -45209,10 +45203,10 @@
     </row>
     <row r="455" spans="1:26">
       <c r="A455" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B455" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C455" s="5" t="s">
         <v>319</v>
@@ -45289,10 +45283,10 @@
     </row>
     <row r="456" spans="1:26">
       <c r="A456" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B456" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C456" s="6" t="s">
         <v>319</v>
@@ -45367,10 +45361,10 @@
     </row>
     <row r="457" spans="1:26">
       <c r="A457" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C457" s="5" t="s">
         <v>507</v>
@@ -45447,10 +45441,10 @@
     </row>
     <row r="458" spans="1:26">
       <c r="A458" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B458" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C458" s="6" t="s">
         <v>507</v>
@@ -45525,10 +45519,10 @@
     </row>
     <row r="459" spans="1:26">
       <c r="A459" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B459" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C459" s="5" t="s">
         <v>507</v>
@@ -45603,10 +45597,10 @@
     </row>
     <row r="460" spans="1:26">
       <c r="A460" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B460" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C460" s="3" t="s">
         <v>792</v>
@@ -45683,10 +45677,10 @@
     </row>
     <row r="461" spans="1:26">
       <c r="A461" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B461" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C461" s="6" t="s">
         <v>792</v>
@@ -45761,10 +45755,10 @@
     </row>
     <row r="462" spans="1:26">
       <c r="A462" s="7" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B462" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C462" s="7" t="s">
         <v>194</v>
@@ -45841,10 +45835,10 @@
     </row>
     <row r="463" spans="1:26">
       <c r="A463" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B463" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C463" s="6" t="s">
         <v>194</v>
@@ -45919,10 +45913,10 @@
     </row>
     <row r="464" spans="1:26">
       <c r="A464" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B464" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C464" s="3" t="s">
         <v>194</v>
@@ -45999,10 +45993,10 @@
     </row>
     <row r="465" spans="1:26">
       <c r="A465" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B465" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C465" s="6" t="s">
         <v>194</v>
@@ -46077,10 +46071,10 @@
     </row>
     <row r="466" spans="1:26">
       <c r="A466" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B466" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C466" s="6" t="s">
         <v>194</v>
@@ -46095,10 +46089,10 @@
         <v>31</v>
       </c>
       <c r="G466" s="6" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H466" s="6" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="I466" s="6">
         <v>8</v>
@@ -46155,10 +46149,10 @@
     </row>
     <row r="467" spans="1:26">
       <c r="A467" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C467" s="5" t="s">
         <v>90</v>
@@ -46233,10 +46227,10 @@
     </row>
     <row r="468" spans="1:26">
       <c r="A468" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B468" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C468" s="6" t="s">
         <v>90</v>
@@ -46311,10 +46305,10 @@
     </row>
     <row r="469" spans="1:26">
       <c r="A469" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B469" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C469" s="6" t="s">
         <v>90</v>
@@ -46389,10 +46383,10 @@
     </row>
     <row r="470" spans="1:26">
       <c r="A470" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B470" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C470" s="3" t="s">
         <v>100</v>
@@ -46467,10 +46461,10 @@
     </row>
     <row r="471" spans="1:26">
       <c r="A471" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B471" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C471" s="6" t="s">
         <v>100</v>
@@ -46485,10 +46479,10 @@
         <v>31</v>
       </c>
       <c r="G471" s="6" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H471" s="6" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I471" s="6">
         <v>8</v>
@@ -46545,10 +46539,10 @@
     </row>
     <row r="472" spans="1:26">
       <c r="A472" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B472" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C472" s="3" t="s">
         <v>100</v>
@@ -46625,10 +46619,10 @@
     </row>
     <row r="473" spans="1:26">
       <c r="A473" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B473" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C473" s="5" t="s">
         <v>100</v>
@@ -46703,10 +46697,10 @@
     </row>
     <row r="474" spans="1:26">
       <c r="A474" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B474" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C474" s="6" t="s">
         <v>100</v>
@@ -46781,10 +46775,10 @@
     </row>
     <row r="475" spans="1:26">
       <c r="A475" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B475" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C475" s="6" t="s">
         <v>100</v>
@@ -46859,10 +46853,10 @@
     </row>
     <row r="476" spans="1:26">
       <c r="A476" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B476" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C476" s="3" t="s">
         <v>100</v>
@@ -46937,10 +46931,10 @@
     </row>
     <row r="477" spans="1:26">
       <c r="A477" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C477" s="5" t="s">
         <v>100</v>
@@ -47015,10 +47009,10 @@
     </row>
     <row r="478" spans="1:26">
       <c r="A478" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B478" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C478" s="3" t="s">
         <v>135</v>
@@ -47093,10 +47087,10 @@
     </row>
     <row r="479" spans="1:26">
       <c r="A479" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B479" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C479" s="5" t="s">
         <v>135</v>
@@ -47150,7 +47144,7 @@
         <v>152</v>
       </c>
       <c r="T479" s="5" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="U479" s="5" t="s">
         <v>61</v>
@@ -47171,10 +47165,10 @@
     </row>
     <row r="480" spans="1:26">
       <c r="A480" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B480" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C480" s="3" t="s">
         <v>135</v>
@@ -47249,10 +47243,10 @@
     </row>
     <row r="481" spans="1:26">
       <c r="A481" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C481" s="5" t="s">
         <v>135</v>
@@ -47329,10 +47323,10 @@
     </row>
     <row r="482" spans="1:26">
       <c r="A482" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B482" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C482" s="3" t="s">
         <v>135</v>
@@ -47407,10 +47401,10 @@
     </row>
     <row r="483" spans="1:26">
       <c r="A483" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B483" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C483" s="5" t="s">
         <v>135</v>
@@ -47485,10 +47479,10 @@
     </row>
     <row r="484" spans="1:26">
       <c r="A484" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B484" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C484" s="6" t="s">
         <v>135</v>
@@ -47563,10 +47557,10 @@
     </row>
     <row r="485" spans="1:26">
       <c r="A485" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B485" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C485" s="6" t="s">
         <v>135</v>
@@ -47641,10 +47635,10 @@
     </row>
     <row r="486" spans="1:26">
       <c r="A486" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B486" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C486" s="6" t="s">
         <v>135</v>
@@ -47719,10 +47713,10 @@
     </row>
     <row r="487" spans="1:26">
       <c r="A487" s="5" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B487" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C487" s="5" t="s">
         <v>135</v>
@@ -47797,10 +47791,10 @@
     </row>
     <row r="488" spans="1:26">
       <c r="A488" s="3" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B488" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C488" s="3" t="s">
         <v>574</v>
@@ -47875,10 +47869,10 @@
     </row>
     <row r="489" spans="1:26">
       <c r="A489" s="6" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="B489" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C489" s="6" t="s">
         <v>574</v>
@@ -47951,7 +47945,7 @@
     </row>
     <row r="490" spans="1:26">
       <c r="A490" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>1512</v>
@@ -48031,7 +48025,7 @@
     </row>
     <row r="491" spans="1:26">
       <c r="A491" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B491" s="6" t="s">
         <v>1512</v>
@@ -48111,7 +48105,7 @@
     </row>
     <row r="492" spans="1:26">
       <c r="A492" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>1512</v>
@@ -48191,7 +48185,7 @@
     </row>
     <row r="493" spans="1:26">
       <c r="A493" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B493" s="6" t="s">
         <v>1512</v>
@@ -48209,10 +48203,10 @@
         <v>31</v>
       </c>
       <c r="G493" s="6" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H493" s="6" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="I493" s="6">
         <v>8</v>
@@ -48269,7 +48263,7 @@
     </row>
     <row r="494" spans="1:26">
       <c r="A494" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>1523</v>
@@ -48347,7 +48341,7 @@
     </row>
     <row r="495" spans="1:26">
       <c r="A495" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B495" s="7" t="s">
         <v>1512</v>
@@ -48368,13 +48362,13 @@
         <v>470</v>
       </c>
       <c r="H495" s="7" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="I495" s="7">
         <v>10</v>
       </c>
       <c r="J495" s="7">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K495" s="7" t="s">
         <v>34</v>
@@ -48427,7 +48421,7 @@
     </row>
     <row r="496" spans="1:26">
       <c r="A496" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B496" s="6" t="s">
         <v>1512</v>
@@ -48505,7 +48499,7 @@
     </row>
     <row r="497" spans="1:26">
       <c r="A497" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B497" s="5" t="s">
         <v>1512</v>
@@ -48583,7 +48577,7 @@
     </row>
     <row r="498" spans="1:26">
       <c r="A498" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>1512</v>
@@ -48661,7 +48655,7 @@
     </row>
     <row r="499" spans="1:26">
       <c r="A499" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B499" s="6" t="s">
         <v>1512</v>
@@ -48739,7 +48733,7 @@
     </row>
     <row r="500" spans="1:26">
       <c r="A500" s="4" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B500" s="4" t="s">
         <v>1512</v>
@@ -48815,7 +48809,7 @@
     </row>
     <row r="501" spans="1:26">
       <c r="A501" s="4" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B501" s="4" t="s">
         <v>1512</v>
@@ -48891,7 +48885,7 @@
     </row>
     <row r="502" spans="1:26">
       <c r="A502" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B502" s="7" t="s">
         <v>1512</v>
@@ -48971,7 +48965,7 @@
     </row>
     <row r="503" spans="1:26">
       <c r="A503" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B503" s="6" t="s">
         <v>1512</v>
@@ -49049,7 +49043,7 @@
     </row>
     <row r="504" spans="1:26">
       <c r="A504" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B504" s="6" t="s">
         <v>1512</v>
@@ -49127,7 +49121,7 @@
     </row>
     <row r="505" spans="1:26">
       <c r="A505" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B505" s="6" t="s">
         <v>1512</v>
@@ -49205,7 +49199,7 @@
     </row>
     <row r="506" spans="1:26">
       <c r="A506" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B506" s="6" t="s">
         <v>1512</v>
@@ -49283,7 +49277,7 @@
     </row>
     <row r="507" spans="1:26">
       <c r="A507" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B507" s="5" t="s">
         <v>1512</v>
@@ -49361,7 +49355,7 @@
     </row>
     <row r="508" spans="1:26">
       <c r="A508" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B508" s="3" t="s">
         <v>1512</v>
@@ -49441,7 +49435,7 @@
     </row>
     <row r="509" spans="1:26">
       <c r="A509" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B509" s="5" t="s">
         <v>1512</v>
@@ -49516,12 +49510,12 @@
         <v>46</v>
       </c>
       <c r="Z509" s="5" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="510" spans="1:26">
       <c r="A510" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B510" s="6" t="s">
         <v>1512</v>
@@ -49599,7 +49593,7 @@
     </row>
     <row r="511" spans="1:26">
       <c r="A511" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B511" s="7" t="s">
         <v>1512</v>
@@ -49677,7 +49671,7 @@
     </row>
     <row r="512" spans="1:26">
       <c r="A512" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B512" s="6" t="s">
         <v>1512</v>
@@ -49755,7 +49749,7 @@
     </row>
     <row r="513" spans="1:26">
       <c r="A513" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B513" s="5" t="s">
         <v>1512</v>
@@ -49833,7 +49827,7 @@
     </row>
     <row r="514" spans="1:26">
       <c r="A514" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B514" s="6" t="s">
         <v>1512</v>
@@ -49911,7 +49905,7 @@
     </row>
     <row r="515" spans="1:26">
       <c r="A515" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B515" s="5" t="s">
         <v>1512</v>
@@ -49989,7 +49983,7 @@
     </row>
     <row r="516" spans="1:26">
       <c r="A516" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B516" s="3" t="s">
         <v>1512</v>
@@ -50069,7 +50063,7 @@
     </row>
     <row r="517" spans="1:26">
       <c r="A517" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B517" s="6" t="s">
         <v>1512</v>
@@ -50147,7 +50141,7 @@
     </row>
     <row r="518" spans="1:26">
       <c r="A518" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B518" s="3" t="s">
         <v>1512</v>
@@ -50227,7 +50221,7 @@
     </row>
     <row r="519" spans="1:26">
       <c r="A519" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B519" s="6" t="s">
         <v>1512</v>
@@ -50305,7 +50299,7 @@
     </row>
     <row r="520" spans="1:26">
       <c r="A520" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B520" s="3" t="s">
         <v>1512</v>
@@ -50383,7 +50377,7 @@
     </row>
     <row r="521" spans="1:26">
       <c r="A521" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B521" s="5" t="s">
         <v>1512</v>
@@ -50463,7 +50457,7 @@
     </row>
     <row r="522" spans="1:26">
       <c r="A522" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B522" s="6" t="s">
         <v>1512</v>
@@ -50541,7 +50535,7 @@
     </row>
     <row r="523" spans="1:26">
       <c r="A523" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B523" s="5" t="s">
         <v>1512</v>
@@ -50621,7 +50615,7 @@
     </row>
     <row r="524" spans="1:26">
       <c r="A524" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B524" s="6" t="s">
         <v>1512</v>
@@ -50697,7 +50691,7 @@
     </row>
     <row r="525" spans="1:26">
       <c r="A525" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B525" s="5" t="s">
         <v>1512</v>
@@ -50715,10 +50709,10 @@
         <v>31</v>
       </c>
       <c r="G525" s="5" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H525" s="5" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="I525" s="5">
         <v>9</v>
@@ -50777,7 +50771,7 @@
     </row>
     <row r="526" spans="1:26">
       <c r="A526" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B526" s="7" t="s">
         <v>1512</v>
@@ -50855,7 +50849,7 @@
     </row>
     <row r="527" spans="1:26">
       <c r="A527" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B527" s="6" t="s">
         <v>1512</v>
@@ -50933,7 +50927,7 @@
     </row>
     <row r="528" spans="1:26">
       <c r="A528" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B528" s="6" t="s">
         <v>1512</v>
@@ -51011,7 +51005,7 @@
     </row>
     <row r="529" spans="1:26">
       <c r="A529" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B529" s="5" t="s">
         <v>1512</v>
@@ -51089,7 +51083,7 @@
     </row>
     <row r="530" spans="1:26">
       <c r="A530" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B530" s="3" t="s">
         <v>1512</v>
@@ -51167,7 +51161,7 @@
     </row>
     <row r="531" spans="1:26">
       <c r="A531" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B531" s="5" t="s">
         <v>1512</v>
@@ -51245,7 +51239,7 @@
     </row>
     <row r="532" spans="1:26">
       <c r="A532" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B532" s="7" t="s">
         <v>1512</v>
@@ -51323,7 +51317,7 @@
     </row>
     <row r="533" spans="1:26">
       <c r="A533" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B533" s="5" t="s">
         <v>1512</v>
@@ -51341,10 +51335,10 @@
         <v>31</v>
       </c>
       <c r="G533" s="5" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H533" s="5" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I533" s="5">
         <v>9</v>
@@ -51403,7 +51397,7 @@
     </row>
     <row r="534" spans="1:26">
       <c r="A534" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B534" s="6" t="s">
         <v>1512</v>
@@ -51481,7 +51475,7 @@
     </row>
     <row r="535" spans="1:26">
       <c r="A535" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B535" s="5" t="s">
         <v>1512</v>
@@ -51561,7 +51555,7 @@
     </row>
     <row r="536" spans="1:26">
       <c r="A536" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B536" s="6" t="s">
         <v>1512</v>
@@ -51579,10 +51573,10 @@
         <v>31</v>
       </c>
       <c r="G536" s="6" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H536" s="6" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="I536" s="6">
         <v>8</v>
@@ -51639,7 +51633,7 @@
     </row>
     <row r="537" spans="1:26">
       <c r="A537" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B537" s="6" t="s">
         <v>1512</v>
@@ -51717,7 +51711,7 @@
     </row>
     <row r="538" spans="1:26">
       <c r="A538" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B538" s="6" t="s">
         <v>1512</v>
@@ -51795,7 +51789,7 @@
     </row>
     <row r="539" spans="1:26">
       <c r="A539" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B539" s="5" t="s">
         <v>1512</v>
@@ -51873,7 +51867,7 @@
     </row>
     <row r="540" spans="1:26">
       <c r="A540" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B540" s="3" t="s">
         <v>1512</v>
@@ -51951,7 +51945,7 @@
     </row>
     <row r="541" spans="1:26">
       <c r="A541" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B541" s="5" t="s">
         <v>1512</v>
@@ -52029,7 +52023,7 @@
     </row>
     <row r="542" spans="1:26">
       <c r="A542" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B542" s="3" t="s">
         <v>1512</v>
@@ -52107,7 +52101,7 @@
     </row>
     <row r="543" spans="1:26">
       <c r="A543" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B543" s="5" t="s">
         <v>1512</v>
@@ -52185,7 +52179,7 @@
     </row>
     <row r="544" spans="1:26">
       <c r="A544" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B544" s="3" t="s">
         <v>1512</v>
@@ -52265,7 +52259,7 @@
     </row>
     <row r="545" spans="1:26">
       <c r="A545" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B545" s="5" t="s">
         <v>1512</v>
@@ -52343,7 +52337,7 @@
     </row>
     <row r="546" spans="1:26">
       <c r="A546" s="7" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B546" s="7" t="s">
         <v>1512</v>
@@ -52421,7 +52415,7 @@
     </row>
     <row r="547" spans="1:26">
       <c r="A547" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B547" s="5" t="s">
         <v>1512</v>
@@ -52499,7 +52493,7 @@
     </row>
     <row r="548" spans="1:26">
       <c r="A548" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B548" s="3" t="s">
         <v>1512</v>
@@ -52577,7 +52571,7 @@
     </row>
     <row r="549" spans="1:26">
       <c r="A549" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B549" s="6" t="s">
         <v>1512</v>
@@ -52655,7 +52649,7 @@
     </row>
     <row r="550" spans="1:26">
       <c r="A550" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B550" s="3" t="s">
         <v>1512</v>
@@ -52733,7 +52727,7 @@
     </row>
     <row r="551" spans="1:26">
       <c r="A551" s="5" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B551" s="5" t="s">
         <v>1512</v>
@@ -52811,7 +52805,7 @@
     </row>
     <row r="552" spans="1:26">
       <c r="A552" s="3" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B552" s="3" t="s">
         <v>1512</v>
@@ -52889,7 +52883,7 @@
     </row>
     <row r="553" spans="1:26">
       <c r="A553" s="6" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="B553" s="6" t="s">
         <v>1512</v>
@@ -53074,7 +53068,7 @@
         <v>8</v>
       </c>
       <c r="J555" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K555" s="5" t="s">
         <v>34</v>
@@ -53232,7 +53226,7 @@
         <v>8</v>
       </c>
       <c r="J557" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K557" s="7" t="s">
         <v>34</v>
@@ -53301,10 +53295,10 @@
         <v>31</v>
       </c>
       <c r="G558" s="7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H558" s="7" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="I558" s="7">
         <v>8</v>
@@ -53925,7 +53919,7 @@
         <v>31</v>
       </c>
       <c r="G566" s="7" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H566" s="7" t="s">
         <v>1686</v>
@@ -54446,7 +54440,7 @@
         <v>143</v>
       </c>
       <c r="Z572" s="3" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="573" spans="1:26">
@@ -55095,10 +55089,10 @@
         <v>31</v>
       </c>
       <c r="G581" s="7" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H581" s="7" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="I581" s="7">
         <v>9</v>
@@ -55173,10 +55167,10 @@
         <v>31</v>
       </c>
       <c r="G582" s="3" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="H582" s="3" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="I582" s="3">
         <v>9</v>
@@ -56347,10 +56341,10 @@
         <v>31</v>
       </c>
       <c r="G597" s="5" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H597" s="5" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I597" s="5">
         <v>9</v>
@@ -56427,10 +56421,10 @@
         <v>31</v>
       </c>
       <c r="G598" s="6" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="H598" s="6" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="I598" s="6">
         <v>8</v>
@@ -56505,10 +56499,10 @@
         <v>31</v>
       </c>
       <c r="G599" s="5" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H599" s="5" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="I599" s="5">
         <v>10</v>
@@ -56663,10 +56657,10 @@
         <v>31</v>
       </c>
       <c r="G601" s="6" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H601" s="6" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="I601" s="6">
         <v>8</v>
@@ -57218,7 +57212,7 @@
         <v>8</v>
       </c>
       <c r="J608" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K608" s="3" t="s">
         <v>34</v>
@@ -57326,7 +57320,7 @@
         <v>152</v>
       </c>
       <c r="T609" s="6" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="U609" s="6" t="s">
         <v>61</v>
@@ -58278,82 +58272,82 @@
       <c r="Z621" s="7"/>
     </row>
     <row r="622" spans="1:26">
-      <c r="A622" s="7" t="s">
+      <c r="A622" s="3" t="s">
         <v>1523</v>
       </c>
-      <c r="B622" s="7" t="s">
+      <c r="B622" s="3" t="s">
         <v>1793</v>
       </c>
-      <c r="C622" s="7" t="s">
+      <c r="C622" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D622" s="7" t="s">
+      <c r="D622" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="E622" s="7" t="s">
+      <c r="E622" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F622" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G622" s="7" t="s">
+      <c r="F622" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G622" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="H622" s="7" t="s">
+      <c r="H622" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="I622" s="7">
+      <c r="I622" s="3">
         <v>8</v>
       </c>
-      <c r="J622" s="7">
-        <v>2</v>
-      </c>
-      <c r="K622" s="7" t="s">
+      <c r="J622" s="3">
+        <v>1</v>
+      </c>
+      <c r="K622" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L622" s="7" t="s">
+      <c r="L622" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="M622" s="7" t="s">
+      <c r="M622" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="N622" s="7" t="s">
+      <c r="N622" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O622" s="7" t="s">
+      <c r="O622" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="P622" s="7" t="s">
+      <c r="P622" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="Q622" s="7" t="s">
+      <c r="Q622" s="3" t="s">
         <v>1794</v>
       </c>
-      <c r="R622" s="7" t="s">
+      <c r="R622" s="3" t="s">
         <v>1795</v>
       </c>
-      <c r="S622" s="7" t="s">
+      <c r="S622" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="T622" s="7" t="s">
+      <c r="T622" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="U622" s="7" t="s">
+      <c r="U622" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V622" s="7">
+      <c r="V622" s="3">
         <v>2018</v>
       </c>
-      <c r="W622" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X622" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="Y622" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z622" s="7" t="s">
+      <c r="W622" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X622" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y622" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z622" s="3" t="s">
         <v>1666</v>
       </c>
     </row>
@@ -61281,10 +61275,10 @@
         <v>31</v>
       </c>
       <c r="G660" s="6" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H660" s="6" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I660" s="6">
         <v>8</v>
@@ -61517,10 +61511,10 @@
         <v>31</v>
       </c>
       <c r="G663" s="6" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H663" s="6" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="I663" s="6">
         <v>8</v>
@@ -61968,160 +61962,160 @@
       </c>
     </row>
     <row r="669" spans="1:26">
-      <c r="A669" s="7" t="s">
+      <c r="A669" s="6" t="s">
         <v>1523</v>
       </c>
-      <c r="B669" s="7" t="s">
+      <c r="B669" s="6" t="s">
         <v>1793</v>
       </c>
-      <c r="C669" s="7" t="s">
+      <c r="C669" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D669" s="7" t="s">
+      <c r="D669" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E669" s="7" t="s">
+      <c r="E669" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F669" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G669" s="7" t="s">
+      <c r="F669" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G669" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="H669" s="7" t="s">
+      <c r="H669" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="I669" s="7">
+      <c r="I669" s="6">
         <v>8</v>
       </c>
-      <c r="J669" s="7">
+      <c r="J669" s="6">
         <v>0</v>
       </c>
-      <c r="K669" s="7" t="s">
+      <c r="K669" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L669" s="7" t="s">
+      <c r="L669" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M669" s="7" t="s">
+      <c r="M669" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N669" s="7" t="s">
+      <c r="N669" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O669" s="7" t="s">
+      <c r="O669" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="P669" s="7" t="s">
+      <c r="P669" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="Q669" s="7" t="s">
+      <c r="Q669" s="6" t="s">
         <v>1890</v>
       </c>
-      <c r="R669" s="7" t="s">
+      <c r="R669" s="6" t="s">
         <v>1893</v>
       </c>
-      <c r="S669" s="7" t="s">
+      <c r="S669" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="T669" s="7" t="s">
+      <c r="T669" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="U669" s="7" t="s">
+      <c r="U669" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V669" s="7">
+      <c r="V669" s="6">
         <v>2015</v>
       </c>
-      <c r="W669" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X669" s="7" t="s">
+      <c r="W669" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="X669" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="Y669" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z669" s="7"/>
+      <c r="Y669" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z669" s="6"/>
     </row>
     <row r="670" spans="1:26">
-      <c r="A670" s="7" t="s">
+      <c r="A670" s="6" t="s">
         <v>1523</v>
       </c>
-      <c r="B670" s="7" t="s">
+      <c r="B670" s="6" t="s">
         <v>1793</v>
       </c>
-      <c r="C670" s="7" t="s">
+      <c r="C670" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D670" s="7" t="s">
+      <c r="D670" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E670" s="7" t="s">
+      <c r="E670" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F670" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G670" s="7" t="s">
+      <c r="F670" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G670" s="6" t="s">
         <v>1894</v>
       </c>
-      <c r="H670" s="7" t="s">
+      <c r="H670" s="6" t="s">
         <v>1895</v>
       </c>
-      <c r="I670" s="7">
+      <c r="I670" s="6">
         <v>8</v>
       </c>
-      <c r="J670" s="7">
+      <c r="J670" s="6">
         <v>0</v>
       </c>
-      <c r="K670" s="7" t="s">
+      <c r="K670" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L670" s="7" t="s">
+      <c r="L670" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M670" s="7" t="s">
+      <c r="M670" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N670" s="7" t="s">
+      <c r="N670" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O670" s="7" t="s">
+      <c r="O670" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="P670" s="7" t="s">
+      <c r="P670" s="6" t="s">
         <v>346</v>
       </c>
-      <c r="Q670" s="7" t="s">
+      <c r="Q670" s="6" t="s">
         <v>1890</v>
       </c>
-      <c r="R670" s="7" t="s">
+      <c r="R670" s="6" t="s">
         <v>1896</v>
       </c>
-      <c r="S670" s="7" t="s">
+      <c r="S670" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="T670" s="7" t="s">
+      <c r="T670" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="U670" s="7" t="s">
+      <c r="U670" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V670" s="7">
+      <c r="V670" s="6">
         <v>2016</v>
       </c>
-      <c r="W670" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X670" s="7" t="s">
+      <c r="W670" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="X670" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="Y670" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z670" s="7"/>
+      <c r="Y670" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z670" s="6"/>
     </row>
     <row r="671" spans="1:26">
       <c r="A671" s="5" t="s">
@@ -62282,314 +62276,314 @@
       <c r="Z672" s="7"/>
     </row>
     <row r="673" spans="1:26">
-      <c r="A673" s="7" t="s">
+      <c r="A673" s="6" t="s">
         <v>1523</v>
       </c>
-      <c r="B673" s="7" t="s">
+      <c r="B673" s="6" t="s">
         <v>1793</v>
       </c>
-      <c r="C673" s="7" t="s">
+      <c r="C673" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D673" s="7" t="s">
+      <c r="D673" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E673" s="7" t="s">
+      <c r="E673" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F673" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G673" s="7" t="s">
+      <c r="F673" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G673" s="6" t="s">
         <v>1775</v>
       </c>
-      <c r="H673" s="7" t="s">
+      <c r="H673" s="6" t="s">
         <v>1776</v>
       </c>
-      <c r="I673" s="7">
+      <c r="I673" s="6">
         <v>8</v>
       </c>
-      <c r="J673" s="7">
+      <c r="J673" s="6">
         <v>0</v>
       </c>
-      <c r="K673" s="7" t="s">
+      <c r="K673" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L673" s="7" t="s">
+      <c r="L673" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M673" s="7" t="s">
+      <c r="M673" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N673" s="7" t="s">
+      <c r="N673" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O673" s="7" t="s">
+      <c r="O673" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P673" s="7" t="s">
+      <c r="P673" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="Q673" s="7" t="s">
+      <c r="Q673" s="6" t="s">
         <v>1897</v>
       </c>
-      <c r="R673" s="7" t="s">
+      <c r="R673" s="6" t="s">
         <v>1901</v>
       </c>
-      <c r="S673" s="7" t="s">
+      <c r="S673" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="T673" s="7" t="s">
+      <c r="T673" s="6" t="s">
         <v>555</v>
       </c>
-      <c r="U673" s="7" t="s">
+      <c r="U673" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V673" s="7">
+      <c r="V673" s="6">
         <v>2017</v>
       </c>
-      <c r="W673" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X673" s="7" t="s">
+      <c r="W673" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="X673" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="Y673" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z673" s="7"/>
+      <c r="Y673" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z673" s="6"/>
     </row>
     <row r="674" spans="1:26">
-      <c r="A674" s="7" t="s">
+      <c r="A674" s="6" t="s">
         <v>1523</v>
       </c>
-      <c r="B674" s="7" t="s">
+      <c r="B674" s="6" t="s">
         <v>1793</v>
       </c>
-      <c r="C674" s="7" t="s">
+      <c r="C674" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D674" s="7" t="s">
+      <c r="D674" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E674" s="7" t="s">
+      <c r="E674" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F674" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G674" s="7" t="s">
+      <c r="F674" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G674" s="6" t="s">
         <v>760</v>
       </c>
-      <c r="H674" s="7" t="s">
+      <c r="H674" s="6" t="s">
         <v>761</v>
       </c>
-      <c r="I674" s="7">
+      <c r="I674" s="6">
         <v>10</v>
       </c>
-      <c r="J674" s="7">
+      <c r="J674" s="6">
         <v>0</v>
       </c>
-      <c r="K674" s="7" t="s">
+      <c r="K674" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L674" s="7" t="s">
+      <c r="L674" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M674" s="7" t="s">
+      <c r="M674" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N674" s="7" t="s">
+      <c r="N674" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O674" s="7" t="s">
+      <c r="O674" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P674" s="7" t="s">
+      <c r="P674" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="Q674" s="7" t="s">
+      <c r="Q674" s="6" t="s">
         <v>1897</v>
       </c>
-      <c r="R674" s="7" t="s">
+      <c r="R674" s="6" t="s">
         <v>1902</v>
       </c>
-      <c r="S674" s="7" t="s">
+      <c r="S674" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="T674" s="7" t="s">
+      <c r="T674" s="6" t="s">
         <v>851</v>
       </c>
-      <c r="U674" s="7" t="s">
+      <c r="U674" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V674" s="7">
+      <c r="V674" s="6">
         <v>2017</v>
       </c>
-      <c r="W674" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X674" s="7" t="s">
+      <c r="W674" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="X674" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="Y674" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z674" s="7"/>
+      <c r="Y674" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z674" s="6"/>
     </row>
     <row r="675" spans="1:26">
-      <c r="A675" s="7" t="s">
+      <c r="A675" s="6" t="s">
         <v>1523</v>
       </c>
-      <c r="B675" s="7" t="s">
+      <c r="B675" s="6" t="s">
         <v>1793</v>
       </c>
-      <c r="C675" s="7" t="s">
+      <c r="C675" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D675" s="7" t="s">
+      <c r="D675" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E675" s="7" t="s">
+      <c r="E675" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F675" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G675" s="7" t="s">
+      <c r="F675" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G675" s="6" t="s">
         <v>1903</v>
       </c>
-      <c r="H675" s="7" t="s">
+      <c r="H675" s="6" t="s">
         <v>1904</v>
       </c>
-      <c r="I675" s="7">
+      <c r="I675" s="6">
         <v>8</v>
       </c>
-      <c r="J675" s="7">
+      <c r="J675" s="6">
         <v>0</v>
       </c>
-      <c r="K675" s="7" t="s">
+      <c r="K675" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L675" s="7" t="s">
+      <c r="L675" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M675" s="7" t="s">
+      <c r="M675" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N675" s="7" t="s">
+      <c r="N675" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O675" s="7" t="s">
+      <c r="O675" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P675" s="7" t="s">
+      <c r="P675" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="Q675" s="7" t="s">
+      <c r="Q675" s="6" t="s">
         <v>1897</v>
       </c>
-      <c r="R675" s="7" t="s">
+      <c r="R675" s="6" t="s">
         <v>1905</v>
       </c>
-      <c r="S675" s="7" t="s">
+      <c r="S675" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="T675" s="7" t="s">
+      <c r="T675" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="U675" s="7" t="s">
+      <c r="U675" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V675" s="7">
+      <c r="V675" s="6">
         <v>2015</v>
       </c>
-      <c r="W675" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X675" s="7" t="s">
+      <c r="W675" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="X675" s="6" t="s">
         <v>489</v>
       </c>
-      <c r="Y675" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z675" s="7"/>
+      <c r="Y675" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z675" s="6"/>
     </row>
     <row r="676" spans="1:26">
-      <c r="A676" s="4" t="s">
+      <c r="A676" s="6" t="s">
         <v>1523</v>
       </c>
-      <c r="B676" s="4" t="s">
+      <c r="B676" s="6" t="s">
         <v>1793</v>
       </c>
-      <c r="C676" s="4" t="s">
+      <c r="C676" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D676" s="4" t="s">
+      <c r="D676" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E676" s="4" t="s">
+      <c r="E676" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F676" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G676" s="4" t="s">
+      <c r="F676" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="G676" s="6" t="s">
         <v>326</v>
       </c>
-      <c r="H676" s="4"/>
-      <c r="I676" s="4">
+      <c r="H676" s="6"/>
+      <c r="I676" s="6">
         <v>8</v>
       </c>
-      <c r="J676" s="4">
+      <c r="J676" s="6">
         <v>0</v>
       </c>
-      <c r="K676" s="4" t="s">
+      <c r="K676" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="L676" s="4" t="s">
+      <c r="L676" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="M676" s="4" t="s">
+      <c r="M676" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="N676" s="4" t="s">
+      <c r="N676" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="O676" s="4" t="s">
+      <c r="O676" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="P676" s="4" t="s">
+      <c r="P676" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="Q676" s="4" t="s">
+      <c r="Q676" s="6" t="s">
         <v>1897</v>
       </c>
-      <c r="R676" s="4" t="s">
+      <c r="R676" s="6" t="s">
         <v>1906</v>
       </c>
-      <c r="S676" s="4" t="s">
+      <c r="S676" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="T676" s="4" t="s">
+      <c r="T676" s="6" t="s">
         <v>931</v>
       </c>
-      <c r="U676" s="4" t="s">
+      <c r="U676" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="V676" s="4">
+      <c r="V676" s="6">
         <v>2016</v>
       </c>
-      <c r="W676" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X676" s="4" t="s">
+      <c r="W676" s="6" t="s">
+        <v>488</v>
+      </c>
+      <c r="X676" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="Y676" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z676" s="4"/>
+      <c r="Y676" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z676" s="6"/>
     </row>
     <row r="677" spans="1:26">
       <c r="A677" s="5" t="s">
@@ -63060,82 +63054,82 @@
       <c r="Z682" s="7"/>
     </row>
     <row r="683" spans="1:26">
-      <c r="A683" s="7" t="s">
+      <c r="A683" s="5" t="s">
         <v>1793</v>
       </c>
-      <c r="B683" s="7" t="s">
+      <c r="B683" s="5" t="s">
         <v>1916</v>
       </c>
-      <c r="C683" s="7" t="s">
+      <c r="C683" s="5" t="s">
         <v>1803</v>
       </c>
-      <c r="D683" s="7" t="s">
+      <c r="D683" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E683" s="7" t="s">
+      <c r="E683" s="5" t="s">
         <v>1804</v>
       </c>
-      <c r="F683" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G683" s="7" t="s">
+      <c r="F683" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G683" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="H683" s="7" t="s">
+      <c r="H683" s="5" t="s">
         <v>806</v>
       </c>
-      <c r="I683" s="7">
+      <c r="I683" s="5">
         <v>9</v>
       </c>
-      <c r="J683" s="7">
+      <c r="J683" s="5">
         <v>4</v>
       </c>
-      <c r="K683" s="7" t="s">
+      <c r="K683" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L683" s="7" t="s">
+      <c r="L683" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="M683" s="7" t="s">
+      <c r="M683" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="N683" s="7" t="s">
+      <c r="N683" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O683" s="7" t="s">
+      <c r="O683" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P683" s="7" t="s">
+      <c r="P683" s="5" t="s">
         <v>1805</v>
       </c>
-      <c r="Q683" s="7" t="s">
+      <c r="Q683" s="5" t="s">
         <v>1917</v>
       </c>
-      <c r="R683" s="7" t="s">
+      <c r="R683" s="5" t="s">
         <v>1918</v>
       </c>
-      <c r="S683" s="7" t="s">
+      <c r="S683" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="T683" s="7" t="s">
+      <c r="T683" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="U683" s="7" t="s">
+      <c r="U683" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="V683" s="7">
+      <c r="V683" s="5">
         <v>2018</v>
       </c>
-      <c r="W683" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X683" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="Y683" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z683" s="7" t="s">
+      <c r="W683" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X683" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y683" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z683" s="5" t="s">
         <v>1919</v>
       </c>
     </row>
@@ -64883,10 +64877,10 @@
         <v>31</v>
       </c>
       <c r="G706" s="3" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H706" s="3" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I706" s="3">
         <v>9</v>
@@ -66104,7 +66098,7 @@
         <v>152</v>
       </c>
       <c r="T721" s="7" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="U721" s="7" t="s">
         <v>61</v>
@@ -67998,7 +67992,7 @@
         <v>45</v>
       </c>
       <c r="X745" s="5" t="s">
-        <v>158</v>
+        <v>45</v>
       </c>
       <c r="Y745" s="5" t="s">
         <v>46</v>
@@ -68105,10 +68099,10 @@
         <v>31</v>
       </c>
       <c r="G747" s="7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="H747" s="7" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="I747" s="7">
         <v>8</v>
@@ -68731,10 +68725,10 @@
         <v>31</v>
       </c>
       <c r="G755" s="5" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H755" s="5" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I755" s="5">
         <v>9</v>
@@ -68782,7 +68776,7 @@
         <v>45</v>
       </c>
       <c r="X755" s="5" t="s">
-        <v>1290</v>
+        <v>1189</v>
       </c>
       <c r="Y755" s="5" t="s">
         <v>46</v>
@@ -71166,7 +71160,7 @@
         <v>6</v>
       </c>
       <c r="J786" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K786" s="7" t="s">
         <v>34</v>
@@ -71324,7 +71318,7 @@
         <v>6</v>
       </c>
       <c r="J788" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K788" s="3" t="s">
         <v>34</v>
@@ -71366,7 +71360,7 @@
         <v>45</v>
       </c>
       <c r="X788" s="3" t="s">
-        <v>372</v>
+        <v>45</v>
       </c>
       <c r="Y788" s="3" t="s">
         <v>46</v>
@@ -71396,7 +71390,7 @@
         <v>261</v>
       </c>
       <c r="H789" s="6" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="I789" s="6">
         <v>6</v>
@@ -72727,10 +72721,10 @@
         <v>31</v>
       </c>
       <c r="G806" s="6" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="H806" s="6" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="I806" s="6">
         <v>8</v>
@@ -74514,82 +74508,82 @@
       </c>
     </row>
     <row r="829" spans="1:26">
-      <c r="A829" s="7" t="s">
+      <c r="A829" s="5" t="s">
         <v>2113</v>
       </c>
-      <c r="B829" s="7" t="s">
+      <c r="B829" s="5" t="s">
         <v>2178</v>
       </c>
-      <c r="C829" s="7" t="s">
+      <c r="C829" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D829" s="7" t="s">
+      <c r="D829" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E829" s="7" t="s">
+      <c r="E829" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F829" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G829" s="7" t="s">
+      <c r="F829" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G829" s="5" t="s">
         <v>261</v>
       </c>
-      <c r="H829" s="7" t="s">
-        <v>1273</v>
-      </c>
-      <c r="I829" s="7">
+      <c r="H829" s="5" t="s">
+        <v>1274</v>
+      </c>
+      <c r="I829" s="5">
         <v>6</v>
       </c>
-      <c r="J829" s="7">
+      <c r="J829" s="5">
         <v>2</v>
       </c>
-      <c r="K829" s="7" t="s">
+      <c r="K829" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L829" s="7" t="s">
+      <c r="L829" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M829" s="7" t="s">
+      <c r="M829" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="N829" s="7" t="s">
+      <c r="N829" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O829" s="7" t="s">
+      <c r="O829" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P829" s="7" t="s">
+      <c r="P829" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="Q829" s="7" t="s">
+      <c r="Q829" s="5" t="s">
         <v>2216</v>
       </c>
-      <c r="R829" s="7" t="s">
+      <c r="R829" s="5" t="s">
         <v>2218</v>
       </c>
-      <c r="S829" s="7" t="s">
+      <c r="S829" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="T829" s="7" t="s">
+      <c r="T829" s="5" t="s">
         <v>2047</v>
       </c>
-      <c r="U829" s="7" t="s">
+      <c r="U829" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="V829" s="7">
+      <c r="V829" s="5">
         <v>2017</v>
       </c>
-      <c r="W829" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X829" s="7" t="s">
-        <v>489</v>
-      </c>
-      <c r="Y829" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z829" s="7"/>
+      <c r="W829" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X829" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y829" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z829" s="5"/>
     </row>
     <row r="830" spans="1:26">
       <c r="A830" s="7" t="s">
@@ -76474,7 +76468,7 @@
         <v>46</v>
       </c>
       <c r="Z853" s="7" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="854" spans="1:26">
@@ -77998,7 +77992,7 @@
         <v>6</v>
       </c>
       <c r="J873" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K873" s="7" t="s">
         <v>34</v>
@@ -81112,7 +81106,7 @@
         <v>12</v>
       </c>
       <c r="J913" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K913" s="4" t="s">
         <v>2180</v>
@@ -85886,7 +85880,7 @@
         <v>8</v>
       </c>
       <c r="J975" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K975" s="4" t="s">
         <v>2180</v>
@@ -86610,7 +86604,7 @@
         <v>401</v>
       </c>
       <c r="T984" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="U984" s="4" t="s">
         <v>61</v>
@@ -87608,7 +87602,7 @@
         <v>401</v>
       </c>
       <c r="T997" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="U997" s="4" t="s">
         <v>61</v>
@@ -87762,7 +87756,7 @@
         <v>401</v>
       </c>
       <c r="T999" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="U999" s="4" t="s">
         <v>61</v>
@@ -88580,7 +88574,7 @@
         <v>8</v>
       </c>
       <c r="J1010" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K1010" s="4" t="s">
         <v>2180</v>
@@ -88762,7 +88756,7 @@
         <v>401</v>
       </c>
       <c r="T1012" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="U1012" s="4" t="s">
         <v>61</v>
@@ -89454,7 +89448,7 @@
         <v>401</v>
       </c>
       <c r="T1021" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="U1021" s="4" t="s">
         <v>61</v>
@@ -90532,7 +90526,7 @@
         <v>401</v>
       </c>
       <c r="T1035" s="4" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="U1035" s="4" t="s">
         <v>61</v>
@@ -91476,80 +91470,82 @@
       <c r="Z1047" s="4"/>
     </row>
     <row r="1048" spans="1:26">
-      <c r="A1048" s="4" t="s">
+      <c r="A1048" s="7" t="s">
         <v>2723</v>
       </c>
-      <c r="B1048" s="4" t="s">
+      <c r="B1048" s="7" t="s">
         <v>2769</v>
       </c>
-      <c r="C1048" s="4" t="s">
+      <c r="C1048" s="7" t="s">
         <v>2380</v>
       </c>
-      <c r="D1048" s="4" t="s">
+      <c r="D1048" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E1048" s="4" t="s">
+      <c r="E1048" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="F1048" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G1048" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="H1048" s="4"/>
-      <c r="I1048" s="4">
+      <c r="F1048" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1048" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1048" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1048" s="7">
         <v>12</v>
       </c>
-      <c r="J1048" s="4">
+      <c r="J1048" s="7">
         <v>3</v>
       </c>
-      <c r="K1048" s="4" t="s">
+      <c r="K1048" s="7" t="s">
         <v>2180</v>
       </c>
-      <c r="L1048" s="4" t="s">
+      <c r="L1048" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="M1048" s="4" t="s">
+      <c r="M1048" s="7" t="s">
         <v>2381</v>
       </c>
-      <c r="N1048" s="4" t="s">
+      <c r="N1048" s="7" t="s">
         <v>2011</v>
       </c>
-      <c r="O1048" s="4" t="s">
+      <c r="O1048" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P1048" s="4" t="s">
+      <c r="P1048" s="7" t="s">
         <v>2382</v>
       </c>
-      <c r="Q1048" s="4" t="s">
+      <c r="Q1048" s="7" t="s">
         <v>2777</v>
       </c>
-      <c r="R1048" s="4" t="s">
+      <c r="R1048" s="7" t="s">
         <v>2778</v>
       </c>
-      <c r="S1048" s="4" t="s">
+      <c r="S1048" s="7" t="s">
         <v>2779</v>
       </c>
-      <c r="T1048" s="4" t="s">
+      <c r="T1048" s="7" t="s">
         <v>2780</v>
       </c>
-      <c r="U1048" s="4" t="s">
+      <c r="U1048" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V1048" s="4">
+      <c r="V1048" s="7">
         <v>2020</v>
       </c>
-      <c r="W1048" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="X1048" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="Y1048" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="Z1048" s="4"/>
+      <c r="W1048" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X1048" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="Y1048" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="Z1048" s="7"/>
     </row>
     <row r="1049" spans="1:26">
       <c r="A1049" s="4" t="s">
@@ -93026,10 +93022,10 @@
         <v>31</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="I15" s="5">
         <v>9</v>
@@ -94019,10 +94015,10 @@
         <v>31</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="I11" s="5">
         <v>9</v>
@@ -96760,7 +96756,7 @@
         <v>790</v>
       </c>
       <c r="T45" s="5" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="U45" s="5" t="s">
         <v>44</v>
@@ -97277,10 +97273,10 @@
         <v>31</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I52" s="3">
         <v>9</v>
@@ -97597,10 +97593,10 @@
         <v>31</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="I56" s="3">
         <v>9</v>
@@ -97745,7 +97741,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -97791,366 +97787,50 @@
         <v>2982</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>443</v>
+        <v>2380</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>442</v>
+        <v>2566</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>589</v>
+        <v>2567</v>
       </c>
       <c r="E2" s="3"/>
       <c r="F2" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>444</v>
-      </c>
+        <v>2428</v>
+      </c>
+      <c r="G2" s="3"/>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>2983</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="8" t="s">
+        <v>2983</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>2380</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>2723</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>2769</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>2779</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>2780</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>2984</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>743</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>899</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>896</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>544</v>
-      </c>
       <c r="I3" s="8"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="3" t="s">
-        <v>2982</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>574</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>743</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3" t="s">
-        <v>1143</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3" t="s">
-        <v>2983</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="3" t="s">
-        <v>2982</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>940</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>1020</v>
-      </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>575</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>1281</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>779</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>689</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>2985</v>
-      </c>
-      <c r="I6" s="8"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>1020</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>1281</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>1322</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>689</v>
-      </c>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>1281</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>1284</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>297</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>1098</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>2986</v>
-      </c>
-      <c r="I8" s="8"/>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>1523</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>1523</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>976</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>1735</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>420</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>2986</v>
-      </c>
-      <c r="I10" s="8"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>1523</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>210</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>211</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>1740</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>2986</v>
-      </c>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>1523</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8" t="s">
-        <v>814</v>
-      </c>
-      <c r="I12" s="8"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>1512</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>1523</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>1786</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>814</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>2986</v>
-      </c>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>1803</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>1793</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>1916</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>805</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>2986</v>
-      </c>
-      <c r="I14" s="8"/>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="8" t="s">
-        <v>2984</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>2018</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>2113</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>2986</v>
-      </c>
-      <c r="I15" s="8"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I1"/>
@@ -98175,16 +97855,16 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2985</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2986</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2987</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2988</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2989</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2990</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -98201,7 +97881,7 @@
         <v>16</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -98218,7 +97898,7 @@
         <v>15</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -98235,75 +97915,75 @@
         <v>17</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B5" s="11">
-        <v>15339</v>
+        <v>26767</v>
       </c>
       <c r="C5" s="11">
         <v>14</v>
       </c>
       <c r="D5" s="11">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B6" s="9">
-        <v>27191</v>
+        <v>15339</v>
       </c>
       <c r="C6" s="9">
         <v>14</v>
       </c>
       <c r="D6" s="9">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
-        <v>344</v>
+        <v>64</v>
       </c>
       <c r="B7" s="11">
-        <v>38249</v>
+        <v>27191</v>
       </c>
       <c r="C7" s="11">
         <v>14</v>
       </c>
       <c r="D7" s="11">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>344</v>
       </c>
       <c r="B8" s="9">
-        <v>26767</v>
+        <v>38249</v>
       </c>
       <c r="C8" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D8" s="9">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -98320,7 +98000,7 @@
         <v>12</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -98337,7 +98017,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -98354,7 +98034,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -98371,7 +98051,7 @@
         <v>12</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -98388,7 +98068,7 @@
         <v>11</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -98405,7 +98085,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -98422,7 +98102,7 @@
         <v>12</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -98439,7 +98119,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -98456,7 +98136,7 @@
         <v>11</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -98473,7 +98153,7 @@
         <v>12</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -98490,7 +98170,7 @@
         <v>8</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -98507,7 +98187,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -98524,7 +98204,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -98541,7 +98221,7 @@
         <v>7</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -98558,7 +98238,7 @@
         <v>7</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -98575,7 +98255,7 @@
         <v>7</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -98592,7 +98272,7 @@
         <v>7</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -98609,7 +98289,7 @@
         <v>7</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -98626,7 +98306,7 @@
         <v>7</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -98643,12 +98323,12 @@
         <v>7</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B29" s="11">
         <v>38991</v>
@@ -98660,12 +98340,12 @@
         <v>7</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="B30" s="9">
         <v>9849</v>
@@ -98677,7 +98357,7 @@
         <v>7</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -98694,7 +98374,7 @@
         <v>6</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -98711,7 +98391,7 @@
         <v>6</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -98728,7 +98408,7 @@
         <v>6</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -98745,7 +98425,7 @@
         <v>6</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -98762,7 +98442,7 @@
         <v>6</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -98779,7 +98459,7 @@
         <v>6</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -98796,7 +98476,7 @@
         <v>6</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>2991</v>
+        <v>2989</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -98813,7 +98493,7 @@
         <v>5</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -98830,7 +98510,7 @@
         <v>5</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -98847,7 +98527,7 @@
         <v>5</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -98864,7 +98544,7 @@
         <v>5</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -98881,7 +98561,7 @@
         <v>5</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -98898,7 +98578,7 @@
         <v>5</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -98915,7 +98595,7 @@
         <v>5</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -98932,7 +98612,7 @@
         <v>5</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -98949,7 +98629,7 @@
         <v>5</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -98966,7 +98646,7 @@
         <v>5</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -98983,7 +98663,7 @@
         <v>7</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -99000,7 +98680,7 @@
         <v>5</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -99017,7 +98697,7 @@
         <v>5</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -99034,7 +98714,7 @@
         <v>5</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="52" spans="1:5">
@@ -99051,12 +98731,12 @@
         <v>5</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B53" s="11">
         <v>20953</v>
@@ -99068,7 +98748,7 @@
         <v>5</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -99085,7 +98765,7 @@
         <v>5</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="55" spans="1:5">
@@ -99102,7 +98782,7 @@
         <v>5</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -99119,7 +98799,7 @@
         <v>4</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -99136,7 +98816,7 @@
         <v>4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="58" spans="1:5">
@@ -99153,7 +98833,7 @@
         <v>4</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="59" spans="1:5">
@@ -99170,7 +98850,7 @@
         <v>4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -99187,7 +98867,7 @@
         <v>4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -99204,7 +98884,7 @@
         <v>4</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="62" spans="1:5">
@@ -99221,7 +98901,7 @@
         <v>4</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -99238,7 +98918,7 @@
         <v>4</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -99255,7 +98935,7 @@
         <v>4</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -99272,7 +98952,7 @@
         <v>4</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -99289,7 +98969,7 @@
         <v>4</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -99306,7 +98986,7 @@
         <v>4</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -99323,7 +99003,7 @@
         <v>4</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -99340,7 +99020,7 @@
         <v>4</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -99357,7 +99037,7 @@
         <v>5</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -99374,7 +99054,7 @@
         <v>4</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="72" spans="1:5">
@@ -99391,7 +99071,7 @@
         <v>4</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -99408,7 +99088,7 @@
         <v>4</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -99425,7 +99105,7 @@
         <v>4</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -99442,7 +99122,7 @@
         <v>4</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -99459,7 +99139,7 @@
         <v>4</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -99476,12 +99156,12 @@
         <v>4</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B78" s="9">
         <v>31118</v>
@@ -99493,7 +99173,7 @@
         <v>4</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -99510,7 +99190,7 @@
         <v>6</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -99527,7 +99207,7 @@
         <v>4</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -99544,7 +99224,7 @@
         <v>4</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -99561,7 +99241,7 @@
         <v>3</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -99578,7 +99258,7 @@
         <v>3</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -99595,7 +99275,7 @@
         <v>3</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -99612,7 +99292,7 @@
         <v>3</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -99629,7 +99309,7 @@
         <v>3</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -99646,7 +99326,7 @@
         <v>3</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="88" spans="1:5">
@@ -99663,7 +99343,7 @@
         <v>3</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="89" spans="1:5">
@@ -99680,7 +99360,7 @@
         <v>3</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -99697,7 +99377,7 @@
         <v>3</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -99714,7 +99394,7 @@
         <v>4</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="92" spans="1:5">
@@ -99731,7 +99411,7 @@
         <v>3</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="93" spans="1:5">
@@ -99748,7 +99428,7 @@
         <v>3</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -99765,7 +99445,7 @@
         <v>3</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="95" spans="1:5">
@@ -99782,7 +99462,7 @@
         <v>3</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="96" spans="1:5">
@@ -99799,7 +99479,7 @@
         <v>4</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -99816,7 +99496,7 @@
         <v>3</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="98" spans="1:5">
@@ -99833,7 +99513,7 @@
         <v>3</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="99" spans="1:5">
@@ -99850,7 +99530,7 @@
         <v>3</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="100" spans="1:5">
@@ -99867,7 +99547,7 @@
         <v>3</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="101" spans="1:5">
@@ -99884,7 +99564,7 @@
         <v>3</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="102" spans="1:5">
@@ -99901,7 +99581,7 @@
         <v>3</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="103" spans="1:5">
@@ -99918,7 +99598,7 @@
         <v>3</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="104" spans="1:5">
@@ -99935,7 +99615,7 @@
         <v>3</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="105" spans="1:5">
@@ -99952,7 +99632,7 @@
         <v>3</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -99969,7 +99649,7 @@
         <v>3</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="107" spans="1:5">
@@ -99986,12 +99666,12 @@
         <v>3</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="3" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B108" s="9">
         <v>9740</v>
@@ -100003,7 +99683,7 @@
         <v>3</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="109" spans="1:5">
@@ -100020,12 +99700,12 @@
         <v>3</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="3" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B110" s="9">
         <v>41770</v>
@@ -100037,7 +99717,7 @@
         <v>3</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -100054,7 +99734,7 @@
         <v>3</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="112" spans="1:5">
@@ -100071,7 +99751,7 @@
         <v>3</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="113" spans="1:5">
@@ -100088,7 +99768,7 @@
         <v>3</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -100105,7 +99785,7 @@
         <v>3</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="115" spans="1:5">
@@ -100122,7 +99802,7 @@
         <v>4</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="116" spans="1:5">
@@ -100139,7 +99819,7 @@
         <v>3</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -100156,7 +99836,7 @@
         <v>3</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="118" spans="1:5">
@@ -100173,7 +99853,7 @@
         <v>3</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="119" spans="1:5">
@@ -100190,7 +99870,7 @@
         <v>3</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="120" spans="1:5">
@@ -100207,7 +99887,7 @@
         <v>3</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="121" spans="1:5">
@@ -100224,7 +99904,7 @@
         <v>3</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="122" spans="1:5">
@@ -100241,7 +99921,7 @@
         <v>3</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="123" spans="1:5">
@@ -100258,7 +99938,7 @@
         <v>3</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="124" spans="1:5">
@@ -100275,7 +99955,7 @@
         <v>2</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="125" spans="1:5">
@@ -100292,7 +99972,7 @@
         <v>2</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -100309,7 +99989,7 @@
         <v>2</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="127" spans="1:5">
@@ -100326,7 +100006,7 @@
         <v>3</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="128" spans="1:5">
@@ -100343,7 +100023,7 @@
         <v>2</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="129" spans="1:5">
@@ -100360,7 +100040,7 @@
         <v>2</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="130" spans="1:5">
@@ -100377,7 +100057,7 @@
         <v>2</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="131" spans="1:5">
@@ -100394,7 +100074,7 @@
         <v>2</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="132" spans="1:5">
@@ -100411,7 +100091,7 @@
         <v>2</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="133" spans="1:5">
@@ -100428,7 +100108,7 @@
         <v>2</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="134" spans="1:5">
@@ -100445,7 +100125,7 @@
         <v>2</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="135" spans="1:5">
@@ -100462,7 +100142,7 @@
         <v>2</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -100479,7 +100159,7 @@
         <v>2</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -100496,7 +100176,7 @@
         <v>2</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -100513,7 +100193,7 @@
         <v>2</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="139" spans="1:5">
@@ -100530,7 +100210,7 @@
         <v>2</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="140" spans="1:5">
@@ -100547,7 +100227,7 @@
         <v>2</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="141" spans="1:5">
@@ -100564,7 +100244,7 @@
         <v>2</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="142" spans="1:5">
@@ -100581,7 +100261,7 @@
         <v>2</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="143" spans="1:5">
@@ -100598,7 +100278,7 @@
         <v>2</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="144" spans="1:5">
@@ -100615,7 +100295,7 @@
         <v>2</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -100632,7 +100312,7 @@
         <v>2</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="146" spans="1:5">
@@ -100649,7 +100329,7 @@
         <v>2</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>2992</v>
+        <v>2990</v>
       </c>
     </row>
     <row r="147" spans="1:5">
@@ -100666,7 +100346,7 @@
         <v>2</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="148" spans="1:5">
@@ -100683,7 +100363,7 @@
         <v>2</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="149" spans="1:5">
@@ -100700,7 +100380,7 @@
         <v>2</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -100717,7 +100397,7 @@
         <v>2</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="151" spans="1:5">
@@ -100734,7 +100414,7 @@
         <v>2</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -100751,7 +100431,7 @@
         <v>2</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="153" spans="1:5">
@@ -100768,7 +100448,7 @@
         <v>2</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="154" spans="1:5">
@@ -100785,12 +100465,12 @@
         <v>2</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B155" s="11">
         <v>8329</v>
@@ -100802,7 +100482,7 @@
         <v>2</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="156" spans="1:5">
@@ -100819,7 +100499,7 @@
         <v>2</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="157" spans="1:5">
@@ -100836,7 +100516,7 @@
         <v>2</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="158" spans="1:5">
@@ -100853,7 +100533,7 @@
         <v>2</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="159" spans="1:5">
@@ -100870,7 +100550,7 @@
         <v>2</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="160" spans="1:5">
@@ -100887,7 +100567,7 @@
         <v>2</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="161" spans="1:5">
@@ -100904,7 +100584,7 @@
         <v>3</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="162" spans="1:5">
@@ -100921,7 +100601,7 @@
         <v>2</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="163" spans="1:5">
@@ -100938,7 +100618,7 @@
         <v>2</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="164" spans="1:5">
@@ -100955,7 +100635,7 @@
         <v>2</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="165" spans="1:5">
@@ -100972,7 +100652,7 @@
         <v>2</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="166" spans="1:5">
@@ -100989,7 +100669,7 @@
         <v>2</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="167" spans="1:5">
@@ -101006,7 +100686,7 @@
         <v>2</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="168" spans="1:5">
@@ -101023,7 +100703,7 @@
         <v>2</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="169" spans="1:5">
@@ -101040,7 +100720,7 @@
         <v>2</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="170" spans="1:5">
@@ -101057,7 +100737,7 @@
         <v>2</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="171" spans="1:5">
@@ -101074,7 +100754,7 @@
         <v>2</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="172" spans="1:5">
@@ -101091,7 +100771,7 @@
         <v>2</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="173" spans="1:5">
@@ -101108,7 +100788,7 @@
         <v>2</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="174" spans="1:5">
@@ -101125,7 +100805,7 @@
         <v>2</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="175" spans="1:5">
@@ -101142,7 +100822,7 @@
         <v>2</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="176" spans="1:5">
@@ -101159,7 +100839,7 @@
         <v>2</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="177" spans="1:5">
@@ -101176,7 +100856,7 @@
         <v>2</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="178" spans="1:5">
@@ -101193,7 +100873,7 @@
         <v>2</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="179" spans="1:5">
@@ -101210,7 +100890,7 @@
         <v>2</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="180" spans="1:5">
@@ -101227,7 +100907,7 @@
         <v>1</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="181" spans="1:5">
@@ -101244,7 +100924,7 @@
         <v>1</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="182" spans="1:5">
@@ -101261,7 +100941,7 @@
         <v>1</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="183" spans="1:5">
@@ -101278,7 +100958,7 @@
         <v>1</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="184" spans="1:5">
@@ -101295,7 +100975,7 @@
         <v>1</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="185" spans="1:5">
@@ -101312,7 +100992,7 @@
         <v>1</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="186" spans="1:5">
@@ -101329,7 +101009,7 @@
         <v>1</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="187" spans="1:5">
@@ -101346,7 +101026,7 @@
         <v>1</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="188" spans="1:5">
@@ -101363,7 +101043,7 @@
         <v>1</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="189" spans="1:5">
@@ -101380,7 +101060,7 @@
         <v>1</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="190" spans="1:5">
@@ -101397,7 +101077,7 @@
         <v>1</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="191" spans="1:5">
@@ -101414,7 +101094,7 @@
         <v>1</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="192" spans="1:5">
@@ -101431,7 +101111,7 @@
         <v>1</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="193" spans="1:5">
@@ -101448,7 +101128,7 @@
         <v>1</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="194" spans="1:5">
@@ -101465,7 +101145,7 @@
         <v>1</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="195" spans="1:5">
@@ -101482,7 +101162,7 @@
         <v>1</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="196" spans="1:5">
@@ -101499,7 +101179,7 @@
         <v>1</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="197" spans="1:5">
@@ -101516,7 +101196,7 @@
         <v>1</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="198" spans="1:5">
@@ -101533,7 +101213,7 @@
         <v>1</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="199" spans="1:5">
@@ -101550,7 +101230,7 @@
         <v>1</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="200" spans="1:5">
@@ -101567,7 +101247,7 @@
         <v>1</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="201" spans="1:5">
@@ -101584,7 +101264,7 @@
         <v>1</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="202" spans="1:5">
@@ -101601,7 +101281,7 @@
         <v>1</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="203" spans="1:5">
@@ -101618,7 +101298,7 @@
         <v>1</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="204" spans="1:5">
@@ -101635,7 +101315,7 @@
         <v>1</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="205" spans="1:5">
@@ -101652,7 +101332,7 @@
         <v>1</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="206" spans="1:5">
@@ -101669,7 +101349,7 @@
         <v>1</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="207" spans="1:5">
@@ -101686,12 +101366,12 @@
         <v>1</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="3" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B208" s="9">
         <v>18424</v>
@@ -101703,12 +101383,12 @@
         <v>1</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="5" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B209" s="11">
         <v>331</v>
@@ -101720,12 +101400,12 @@
         <v>1</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="3" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B210" s="9">
         <v>11802</v>
@@ -101737,12 +101417,12 @@
         <v>1</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="5" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B211" s="11">
         <v>18862</v>
@@ -101754,7 +101434,7 @@
         <v>1</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="212" spans="1:5">
@@ -101771,7 +101451,7 @@
         <v>1</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="213" spans="1:5">
@@ -101788,7 +101468,7 @@
         <v>1</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="214" spans="1:5">
@@ -101805,7 +101485,7 @@
         <v>1</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="215" spans="1:5">
@@ -101822,7 +101502,7 @@
         <v>1</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="216" spans="1:5">
@@ -101839,7 +101519,7 @@
         <v>1</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="217" spans="1:5">
@@ -101856,7 +101536,7 @@
         <v>1</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="218" spans="1:5">
@@ -101873,7 +101553,7 @@
         <v>1</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="219" spans="1:5">
@@ -101890,7 +101570,7 @@
         <v>1</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="220" spans="1:5">
@@ -101907,7 +101587,7 @@
         <v>1</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="221" spans="1:5">
@@ -101924,7 +101604,7 @@
         <v>1</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="222" spans="1:5">
@@ -101941,7 +101621,7 @@
         <v>1</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="223" spans="1:5">
@@ -101958,7 +101638,7 @@
         <v>1</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="224" spans="1:5">
@@ -101975,7 +101655,7 @@
         <v>1</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="225" spans="1:5">
@@ -101992,7 +101672,7 @@
         <v>1</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="226" spans="1:5">
@@ -102009,7 +101689,7 @@
         <v>1</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="227" spans="1:5">
@@ -102026,7 +101706,7 @@
         <v>1</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="228" spans="1:5">
@@ -102043,12 +101723,12 @@
         <v>1</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="5" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B229" s="11">
         <v>23068</v>
@@ -102060,7 +101740,7 @@
         <v>1</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="230" spans="1:5">
@@ -102077,7 +101757,7 @@
         <v>1</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="231" spans="1:5">
@@ -102094,7 +101774,7 @@
         <v>2</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="232" spans="1:5">
@@ -102111,7 +101791,7 @@
         <v>1</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="233" spans="1:5">
@@ -102128,7 +101808,7 @@
         <v>1</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="234" spans="1:5">
@@ -102145,7 +101825,7 @@
         <v>1</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="235" spans="1:5">
@@ -102162,7 +101842,7 @@
         <v>1</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="236" spans="1:5">
@@ -102179,7 +101859,7 @@
         <v>1</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="237" spans="1:5">
@@ -102196,7 +101876,7 @@
         <v>1</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="238" spans="1:5">
@@ -102213,7 +101893,7 @@
         <v>1</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="239" spans="1:5">
@@ -102230,7 +101910,7 @@
         <v>1</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="240" spans="1:5">
@@ -102247,7 +101927,7 @@
         <v>1</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="241" spans="1:5">
@@ -102264,7 +101944,7 @@
         <v>1</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="242" spans="1:5">
@@ -102281,7 +101961,7 @@
         <v>1</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="243" spans="1:5">
@@ -102298,7 +101978,7 @@
         <v>1</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="244" spans="1:5">
@@ -102315,7 +101995,7 @@
         <v>1</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
     <row r="245" spans="1:5">
@@ -102332,7 +102012,7 @@
         <v>1</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>2993</v>
+        <v>2991</v>
       </c>
     </row>
   </sheetData>

--- a/skipperplan.xlsx
+++ b/skipperplan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25062" uniqueCount="2975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25072" uniqueCount="2973">
   <si>
     <t>Startdatum</t>
   </si>
@@ -2079,7 +2079,7 @@
     <t>15249</t>
   </si>
   <si>
-    <t>Stefan W, Jens B, Michele A, Daniel P</t>
+    <t>Stefan W, Jens B, Daniel P</t>
   </si>
   <si>
     <t>15250</t>
@@ -2856,7 +2856,7 @@
     <t>15285</t>
   </si>
   <si>
-    <t>Dina T, Marlon S, Stefan D, Max S</t>
+    <t>Dina T, Marlon S, Stefan D, Max S, Cüneyt G</t>
   </si>
   <si>
     <t>15286</t>
@@ -3636,7 +3636,7 @@
     <t>15942</t>
   </si>
   <si>
-    <t>Philipp K, Timo B, Nico B, Martin W, Philipp S</t>
+    <t>Timo B, Nico B, Martin W, Philipp S</t>
   </si>
   <si>
     <t>41770</t>
@@ -3879,7 +3879,7 @@
     <t>15459</t>
   </si>
   <si>
-    <t>Stefan H, Fabio M</t>
+    <t>Stefan H, Fabio M, Philipp K</t>
   </si>
   <si>
     <t>15460</t>
@@ -5277,7 +5277,7 @@
     <t>16240</t>
   </si>
   <si>
-    <t>Martin W, Benjamin W, Timon S, Jasper P, Jonas S, Michael H</t>
+    <t>Martin W, Benjamin W, Timon S, Jasper P, Jonas S, Michael H, Wilhelm W</t>
   </si>
   <si>
     <t>16241</t>
@@ -7407,7 +7407,7 @@
     <t>FARALLO</t>
   </si>
   <si>
-    <t>Ralf B, Bettina R, Lennart M, Marlon S, Laila-Inga M, Philipp K, Florian B, Jasper P, Jonas H, Giovanna S</t>
+    <t>Ralf B, Bettina R, Lennart M, Marlon S, Laila-Inga M, Philipp K, Florian B, Jasper P, Jonas H, Giovanna S, Cüneyt G</t>
   </si>
   <si>
     <t>16830</t>
@@ -7443,7 +7443,7 @@
     <t>16804</t>
   </si>
   <si>
-    <t>Ralf B, Marlon S, Jaqueline N, Laila-Inga M</t>
+    <t>Ralf B, Marlon S, Jaqueline N, Laila-Inga M, Cüneyt G</t>
   </si>
   <si>
     <t>16805</t>
@@ -7536,7 +7536,7 @@
     <t>16767</t>
   </si>
   <si>
-    <t>Ralf B, Sebastian S, Marlon S, Lukas F, Lukas B, Sebastian W, Marlena G, Maurice K, Giovanna S</t>
+    <t>Ralf B, Sebastian S, Marlon S, Lukas F, Lukas B, Sebastian W, Marlena G, Maurice K, Giovanna S, Cüneyt G</t>
   </si>
   <si>
     <t>16789</t>
@@ -7710,7 +7710,7 @@
     <t>16819</t>
   </si>
   <si>
-    <t>Nicole M, Johanna S, Miriam M, Marlon S, Leon H, Constantin R, Miro W, Jaqueline N, Lukas B</t>
+    <t>Nicole M, Johanna S, Miriam M, Marlon S, Leon H, Constantin R, Miro W, Jaqueline N, Lukas B, Cüneyt G</t>
   </si>
   <si>
     <t>17159</t>
@@ -7833,7 +7833,7 @@
     <t>16735</t>
   </si>
   <si>
-    <t>Sebastian S, Viktoria B, Florian B</t>
+    <t>Sebastian S, Viktoria B, Florian B, Jan J</t>
   </si>
   <si>
     <t>16736</t>
@@ -7911,7 +7911,7 @@
     <t>DIOGENES</t>
   </si>
   <si>
-    <t>Marlon S, Constantin R, Lena E, Jaqueline N, Mareike W</t>
+    <t>Marlon S, Constantin R, Lena E, Jaqueline N, Mareike W, Cüneyt G</t>
   </si>
   <si>
     <t>16795</t>
@@ -8922,13 +8922,7 @@
     <t>Neue Bewerbung(en)</t>
   </si>
   <si>
-    <t>Skipper geändert</t>
-  </si>
-  <si>
-    <t>(Kein Skipper)</t>
-  </si>
-  <si>
-    <t>Roman B</t>
+    <t>Wilhelm W</t>
   </si>
   <si>
     <t>ID</t>
@@ -8985,7 +8979,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9030,12 +9024,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -9074,7 +9062,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9097,19 +9085,16 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -10897,7 +10882,7 @@
         <v>8</v>
       </c>
       <c r="J19" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>34</v>
@@ -11523,7 +11508,7 @@
         <v>8</v>
       </c>
       <c r="J27" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K27" s="5" t="s">
         <v>34</v>
@@ -13809,7 +13794,7 @@
         <v>9</v>
       </c>
       <c r="J56" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>34</v>
@@ -17521,7 +17506,7 @@
         <v>9</v>
       </c>
       <c r="J103" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K103" s="5" t="s">
         <v>34</v>
@@ -21979,82 +21964,82 @@
       </c>
     </row>
     <row r="160" spans="1:26">
-      <c r="A160" s="7" t="s">
+      <c r="A160" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="B160" s="7" t="s">
+      <c r="B160" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="C160" s="7" t="s">
+      <c r="C160" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="D160" s="7" t="s">
+      <c r="D160" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E160" s="7" t="s">
+      <c r="E160" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F160" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G160" s="7" t="s">
+      <c r="F160" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G160" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="H160" s="7" t="s">
+      <c r="H160" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="I160" s="7">
+      <c r="I160" s="3">
         <v>10</v>
       </c>
-      <c r="J160" s="7">
+      <c r="J160" s="3">
         <v>2</v>
       </c>
-      <c r="K160" s="7" t="s">
+      <c r="K160" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L160" s="7" t="s">
+      <c r="L160" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="M160" s="7" t="s">
+      <c r="M160" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="N160" s="7" t="s">
+      <c r="N160" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O160" s="7" t="s">
+      <c r="O160" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="P160" s="7" t="s">
+      <c r="P160" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="Q160" s="7" t="s">
+      <c r="Q160" s="3" t="s">
         <v>692</v>
       </c>
-      <c r="R160" s="7" t="s">
+      <c r="R160" s="3" t="s">
         <v>693</v>
       </c>
-      <c r="S160" s="7" t="s">
+      <c r="S160" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="T160" s="7" t="s">
+      <c r="T160" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="U160" s="7" t="s">
+      <c r="U160" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="V160" s="7">
+      <c r="V160" s="3">
         <v>2020</v>
       </c>
-      <c r="W160" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X160" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="Y160" s="7" t="s">
+      <c r="W160" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X160" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y160" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z160" s="7" t="s">
+      <c r="Z160" s="3" t="s">
         <v>568</v>
       </c>
     </row>
@@ -23318,9 +23303,7 @@
       <c r="Y176" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z176" s="3" t="s">
-        <v>699</v>
-      </c>
+      <c r="Z176" s="3"/>
     </row>
     <row r="177" spans="1:26">
       <c r="A177" s="5" t="s">
@@ -24525,7 +24508,7 @@
         <v>8</v>
       </c>
       <c r="J192" s="4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K192" s="4" t="s">
         <v>34</v>
@@ -25071,7 +25054,7 @@
         <v>6</v>
       </c>
       <c r="J199" s="6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K199" s="6" t="s">
         <v>34</v>
@@ -26723,7 +26706,7 @@
         <v>10</v>
       </c>
       <c r="J220" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K220" s="3" t="s">
         <v>34</v>
@@ -26803,7 +26786,7 @@
         <v>10</v>
       </c>
       <c r="J221" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K221" s="5" t="s">
         <v>34</v>
@@ -26961,7 +26944,7 @@
         <v>9</v>
       </c>
       <c r="J223" s="5">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K223" s="5" t="s">
         <v>34</v>
@@ -27041,7 +27024,7 @@
         <v>9</v>
       </c>
       <c r="J224" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K224" s="3" t="s">
         <v>34</v>
@@ -27517,7 +27500,7 @@
         <v>10</v>
       </c>
       <c r="J230" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K230" s="3" t="s">
         <v>34</v>
@@ -28065,7 +28048,7 @@
         <v>8</v>
       </c>
       <c r="J237" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K237" s="5" t="s">
         <v>34</v>
@@ -28459,7 +28442,7 @@
         <v>9</v>
       </c>
       <c r="J242" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K242" s="3" t="s">
         <v>34</v>
@@ -29287,82 +29270,82 @@
       </c>
     </row>
     <row r="253" spans="1:26">
-      <c r="A253" s="7" t="s">
+      <c r="A253" s="5" t="s">
         <v>688</v>
       </c>
-      <c r="B253" s="7" t="s">
+      <c r="B253" s="5" t="s">
         <v>888</v>
       </c>
-      <c r="C253" s="7" t="s">
+      <c r="C253" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D253" s="7" t="s">
+      <c r="D253" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E253" s="7" t="s">
+      <c r="E253" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F253" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G253" s="7" t="s">
+      <c r="F253" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G253" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="H253" s="7" t="s">
+      <c r="H253" s="5" t="s">
         <v>448</v>
       </c>
-      <c r="I253" s="7">
+      <c r="I253" s="5">
         <v>8</v>
       </c>
-      <c r="J253" s="7">
-        <v>5</v>
-      </c>
-      <c r="K253" s="7" t="s">
+      <c r="J253" s="5">
+        <v>7</v>
+      </c>
+      <c r="K253" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L253" s="7" t="s">
+      <c r="L253" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="M253" s="7" t="s">
+      <c r="M253" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="N253" s="7" t="s">
+      <c r="N253" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O253" s="7" t="s">
+      <c r="O253" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P253" s="7" t="s">
+      <c r="P253" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="Q253" s="7" t="s">
+      <c r="Q253" s="5" t="s">
         <v>959</v>
       </c>
-      <c r="R253" s="7" t="s">
+      <c r="R253" s="5" t="s">
         <v>962</v>
       </c>
-      <c r="S253" s="7" t="s">
+      <c r="S253" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="T253" s="7" t="s">
+      <c r="T253" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="U253" s="7" t="s">
+      <c r="U253" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="V253" s="7">
+      <c r="V253" s="5">
         <v>2022</v>
       </c>
-      <c r="W253" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X253" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="Y253" s="7" t="s">
+      <c r="W253" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X253" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y253" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z253" s="7"/>
+      <c r="Z253" s="5"/>
     </row>
     <row r="254" spans="1:26">
       <c r="A254" s="3" t="s">
@@ -30973,7 +30956,7 @@
         <v>10</v>
       </c>
       <c r="J274" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K274" s="3" t="s">
         <v>34</v>
@@ -32543,7 +32526,7 @@
         <v>10</v>
       </c>
       <c r="J294" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K294" s="3" t="s">
         <v>34</v>
@@ -33323,7 +33306,7 @@
         <v>7</v>
       </c>
       <c r="J304" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K304" s="3" t="s">
         <v>34</v>
@@ -36545,7 +36528,7 @@
         <v>9</v>
       </c>
       <c r="J345" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K345" s="5" t="s">
         <v>34</v>
@@ -37015,7 +36998,7 @@
         <v>7</v>
       </c>
       <c r="J351" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K351" s="5" t="s">
         <v>34</v>
@@ -37485,7 +37468,7 @@
         <v>10</v>
       </c>
       <c r="J357" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K357" s="5" t="s">
         <v>34</v>
@@ -41099,7 +41082,7 @@
         <v>8</v>
       </c>
       <c r="J403" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K403" s="5" t="s">
         <v>34</v>
@@ -42047,7 +42030,7 @@
         <v>10</v>
       </c>
       <c r="J415" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K415" s="7" t="s">
         <v>34</v>
@@ -42441,7 +42424,7 @@
         <v>10</v>
       </c>
       <c r="J420" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K420" s="3" t="s">
         <v>34</v>
@@ -44445,7 +44428,7 @@
         <v>45</v>
       </c>
       <c r="X445" s="5" t="s">
-        <v>309</v>
+        <v>45</v>
       </c>
       <c r="Y445" s="5" t="s">
         <v>46</v>
@@ -44479,7 +44462,7 @@
         <v>9</v>
       </c>
       <c r="J446" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K446" s="4" t="s">
         <v>34</v>
@@ -44793,7 +44776,7 @@
         <v>10</v>
       </c>
       <c r="J450" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K450" s="7" t="s">
         <v>34</v>
@@ -45311,82 +45294,82 @@
       </c>
     </row>
     <row r="457" spans="1:26">
-      <c r="A457" s="6" t="s">
+      <c r="A457" s="7" t="s">
         <v>1225</v>
       </c>
-      <c r="B457" s="6" t="s">
+      <c r="B457" s="7" t="s">
         <v>1442</v>
       </c>
-      <c r="C457" s="6" t="s">
+      <c r="C457" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D457" s="6" t="s">
+      <c r="D457" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="E457" s="6" t="s">
+      <c r="E457" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F457" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G457" s="6" t="s">
+      <c r="F457" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G457" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="H457" s="6" t="s">
+      <c r="H457" s="7" t="s">
         <v>282</v>
       </c>
-      <c r="I457" s="6">
+      <c r="I457" s="7">
         <v>8</v>
       </c>
-      <c r="J457" s="6">
-        <v>0</v>
-      </c>
-      <c r="K457" s="6" t="s">
+      <c r="J457" s="7">
+        <v>2</v>
+      </c>
+      <c r="K457" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L457" s="6" t="s">
+      <c r="L457" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="M457" s="6" t="s">
+      <c r="M457" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="N457" s="6" t="s">
+      <c r="N457" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="O457" s="6" t="s">
+      <c r="O457" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="P457" s="6" t="s">
+      <c r="P457" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="Q457" s="6" t="s">
+      <c r="Q457" s="7" t="s">
         <v>1446</v>
       </c>
-      <c r="R457" s="6" t="s">
+      <c r="R457" s="7" t="s">
         <v>1447</v>
       </c>
-      <c r="S457" s="6" t="s">
+      <c r="S457" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="T457" s="6" t="s">
+      <c r="T457" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="U457" s="6" t="s">
+      <c r="U457" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V457" s="6">
+      <c r="V457" s="7">
         <v>2018</v>
       </c>
-      <c r="W457" s="6" t="s">
-        <v>489</v>
-      </c>
-      <c r="X457" s="6" t="s">
+      <c r="W457" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X457" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="Y457" s="6" t="s">
+      <c r="Y457" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="Z457" s="6" t="s">
+      <c r="Z457" s="7" t="s">
         <v>1448</v>
       </c>
     </row>
@@ -47141,7 +47124,7 @@
         <v>10</v>
       </c>
       <c r="J480" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K480" s="3" t="s">
         <v>34</v>
@@ -50901,7 +50884,7 @@
         <v>8</v>
       </c>
       <c r="J528" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K528" s="7" t="s">
         <v>34</v>
@@ -54499,7 +54482,7 @@
         <v>9</v>
       </c>
       <c r="J574" s="7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K574" s="7" t="s">
         <v>34</v>
@@ -55317,7 +55300,7 @@
         <v>45</v>
       </c>
       <c r="X584" s="3" t="s">
-        <v>349</v>
+        <v>45</v>
       </c>
       <c r="Y584" s="3" t="s">
         <v>46</v>
@@ -55827,7 +55810,7 @@
         <v>10</v>
       </c>
       <c r="J591" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K591" s="5" t="s">
         <v>34</v>
@@ -56925,7 +56908,7 @@
         <v>9</v>
       </c>
       <c r="J605" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K605" s="5" t="s">
         <v>34</v>
@@ -59015,82 +58998,82 @@
       </c>
     </row>
     <row r="632" spans="1:26">
-      <c r="A632" s="7" t="s">
+      <c r="A632" s="3" t="s">
         <v>1453</v>
       </c>
-      <c r="B632" s="7" t="s">
+      <c r="B632" s="3" t="s">
         <v>1721</v>
       </c>
-      <c r="C632" s="7" t="s">
+      <c r="C632" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D632" s="7" t="s">
+      <c r="D632" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E632" s="7" t="s">
+      <c r="E632" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F632" s="7" t="s">
+      <c r="F632" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="G632" s="7" t="s">
+      <c r="G632" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="H632" s="7" t="s">
+      <c r="H632" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="I632" s="7">
+      <c r="I632" s="3">
         <v>9</v>
       </c>
-      <c r="J632" s="7">
+      <c r="J632" s="3">
         <v>7</v>
       </c>
-      <c r="K632" s="7" t="s">
+      <c r="K632" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L632" s="7" t="s">
+      <c r="L632" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="M632" s="7" t="s">
+      <c r="M632" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="N632" s="7" t="s">
+      <c r="N632" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O632" s="7" t="s">
+      <c r="O632" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="P632" s="7" t="s">
+      <c r="P632" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="Q632" s="7" t="s">
+      <c r="Q632" s="3" t="s">
         <v>1821</v>
       </c>
-      <c r="R632" s="7" t="s">
+      <c r="R632" s="3" t="s">
         <v>1824</v>
       </c>
-      <c r="S632" s="7" t="s">
+      <c r="S632" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="T632" s="7" t="s">
+      <c r="T632" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="U632" s="7" t="s">
+      <c r="U632" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="V632" s="7">
+      <c r="V632" s="3">
         <v>2018</v>
       </c>
-      <c r="W632" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X632" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="Y632" s="7" t="s">
+      <c r="W632" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X632" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="Y632" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="Z632" s="7"/>
+      <c r="Z632" s="3"/>
     </row>
     <row r="633" spans="1:26">
       <c r="A633" s="6" t="s">
@@ -59899,7 +59882,7 @@
         <v>9</v>
       </c>
       <c r="J643" s="5">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K643" s="5" t="s">
         <v>34</v>
@@ -59941,7 +59924,7 @@
         <v>45</v>
       </c>
       <c r="X643" s="5" t="s">
-        <v>349</v>
+        <v>45</v>
       </c>
       <c r="Y643" s="5" t="s">
         <v>46</v>
@@ -60217,7 +60200,7 @@
         <v>8</v>
       </c>
       <c r="J647" s="5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K647" s="5" t="s">
         <v>34</v>
@@ -63041,7 +63024,7 @@
         <v>9</v>
       </c>
       <c r="J683" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K683" s="5" t="s">
         <v>34</v>
@@ -63121,7 +63104,7 @@
         <v>9</v>
       </c>
       <c r="J684" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K684" s="7" t="s">
         <v>34</v>
@@ -67353,7 +67336,7 @@
         <v>9</v>
       </c>
       <c r="J738" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K738" s="4" t="s">
         <v>34</v>
@@ -69703,7 +69686,7 @@
         <v>8</v>
       </c>
       <c r="J768" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K768" s="3" t="s">
         <v>34</v>
@@ -71395,7 +71378,7 @@
         <v>45</v>
       </c>
       <c r="X789" s="5" t="s">
-        <v>349</v>
+        <v>746</v>
       </c>
       <c r="Y789" s="5" t="s">
         <v>46</v>
@@ -77605,7 +77588,7 @@
         <v>8</v>
       </c>
       <c r="J869" s="4">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K869" s="4" t="s">
         <v>2118</v>
@@ -83231,7 +83214,7 @@
         <v>8</v>
       </c>
       <c r="J942" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K942" s="4" t="s">
         <v>2118</v>
@@ -96062,7 +96045,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -96108,74 +96091,72 @@
         <v>2964</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>391</v>
+        <v>515</v>
       </c>
       <c r="C2" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>888</v>
-      </c>
       <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
-        <v>549</v>
-      </c>
-      <c r="G2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>939</v>
+      </c>
       <c r="H2" s="3"/>
       <c r="I2" s="3" t="s">
-        <v>955</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="8" t="s">
-        <v>2965</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>1225</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>1442</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>976</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>2966</v>
-      </c>
-      <c r="I3" s="8"/>
+      <c r="A3" s="3" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>963</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
+        <v>1137</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="3" t="s">
         <v>2964</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>1737</v>
+        <v>1453</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>1944</v>
+        <v>1721</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3" t="s">
-        <v>110</v>
+        <v>846</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1219</v>
+        <v>265</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>2967</v>
+        <v>2965</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -96183,22 +96164,22 @@
         <v>2964</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>2305</v>
+        <v>2315</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>2303</v>
+        <v>2432</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>2304</v>
+        <v>2447</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="3" t="s">
-        <v>2311</v>
+        <v>2459</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="s">
-        <v>568</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -96206,22 +96187,22 @@
         <v>2964</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>2305</v>
+        <v>2349</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>2304</v>
+        <v>2432</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>2378</v>
+        <v>2447</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>2382</v>
+        <v>2353</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="s">
-        <v>568</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -96229,22 +96210,22 @@
         <v>2964</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>2654</v>
+        <v>2325</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>2636</v>
+        <v>2494</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>2615</v>
+        <v>2495</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3" t="s">
-        <v>2402</v>
+        <v>2376</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>568</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -96252,22 +96233,68 @@
         <v>2964</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>2654</v>
+        <v>2305</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>2615</v>
+        <v>2528</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>2666</v>
+        <v>2558</v>
       </c>
       <c r="E8" s="3"/>
       <c r="F8" s="3" t="s">
-        <v>2402</v>
+        <v>2311</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>568</v>
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="3" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>2403</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>2558</v>
+      </c>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3" t="s">
+        <v>1135</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="3" t="s">
+        <v>2964</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>2623</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>2615</v>
+      </c>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3" t="s">
+        <v>2627</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>1174</v>
       </c>
     </row>
   </sheetData>
@@ -96293,4198 +96320,4198 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2966</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2967</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2968</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2969</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2970</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2971</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>13707</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>15</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>17</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>2972</v>
+      <c r="E2" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>31914</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>15</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>15</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>2973</v>
+      <c r="E3" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>951</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>14</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>14</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>2972</v>
+      <c r="E4" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
         <v>281</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>38249</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>14</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>14</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>2973</v>
+      <c r="E5" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>15339</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>13</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>13</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>2973</v>
+      <c r="E6" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>26767</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>13</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>14</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>2973</v>
+      <c r="E7" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>27191</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>13</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>15</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>2973</v>
+      <c r="E8" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>27366</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>12</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>12</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>2973</v>
+      <c r="E9" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>28325</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>12</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>12</v>
       </c>
-      <c r="E10" s="10" t="s">
-        <v>2972</v>
+      <c r="E10" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
         <v>383</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <v>2430</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>12</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>12</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>2972</v>
+      <c r="E11" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
         <v>655</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>26133</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>12</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>12</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>2973</v>
+      <c r="E12" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>13035</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>10</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>10</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>2972</v>
+      <c r="E13" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>17277</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>10</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>12</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>2972</v>
+      <c r="E14" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <v>25583</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>10</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <v>10</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>2973</v>
+      <c r="E15" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <v>20147</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>9</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>11</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>2972</v>
+      <c r="E16" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
         <v>416</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <v>17056</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>9</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <v>12</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>2973</v>
+      <c r="E17" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="8">
         <v>38409</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="8">
         <v>8</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>8</v>
       </c>
-      <c r="E18" s="12" t="s">
-        <v>2973</v>
+      <c r="E18" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
         <v>463</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>10468</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>8</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <v>8</v>
       </c>
-      <c r="E19" s="12" t="s">
-        <v>2973</v>
+      <c r="E19" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="8">
         <v>6429</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>8</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>8</v>
       </c>
-      <c r="E20" s="10" t="s">
-        <v>2972</v>
+      <c r="E20" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <v>7022</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>7</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <v>7</v>
       </c>
-      <c r="E21" s="10" t="s">
-        <v>2972</v>
+      <c r="E21" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="8">
         <v>15492</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <v>7</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>7</v>
       </c>
-      <c r="E22" s="12" t="s">
-        <v>2973</v>
+      <c r="E22" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
         <v>331</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>27428</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>7</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <v>7</v>
       </c>
-      <c r="E23" s="12" t="s">
-        <v>2973</v>
+      <c r="E23" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="8">
         <v>9630</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="8">
         <v>7</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>7</v>
       </c>
-      <c r="E24" s="12" t="s">
-        <v>2973</v>
+      <c r="E24" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
         <v>804</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>13045</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>7</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <v>7</v>
       </c>
-      <c r="E25" s="12" t="s">
-        <v>2973</v>
+      <c r="E25" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
         <v>1169</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="8">
         <v>38991</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="8">
         <v>7</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <v>7</v>
       </c>
-      <c r="E26" s="12" t="s">
-        <v>2973</v>
+      <c r="E26" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
         <v>1219</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>9849</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <v>7</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <v>7</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>2973</v>
+      <c r="E27" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="8">
         <v>14767</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="8">
         <v>6</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>6</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>2973</v>
+      <c r="E28" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="10">
         <v>12024</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <v>6</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <v>6</v>
       </c>
-      <c r="E29" s="12" t="s">
-        <v>2973</v>
+      <c r="E29" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="8">
         <v>17321</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="8">
         <v>6</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="8">
         <v>6</v>
       </c>
-      <c r="E30" s="12" t="s">
-        <v>2973</v>
+      <c r="E30" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
         <v>641</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="10">
         <v>19891</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="10">
         <v>6</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <v>6</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>2973</v>
+      <c r="E31" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="8">
         <v>20741</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <v>6</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>6</v>
       </c>
-      <c r="E32" s="12" t="s">
-        <v>2973</v>
+      <c r="E32" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
         <v>852</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="10">
         <v>27342</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>6</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <v>6</v>
       </c>
-      <c r="E33" s="12" t="s">
-        <v>2973</v>
+      <c r="E33" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
         <v>889</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="8">
         <v>28683</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="8">
         <v>6</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="8">
         <v>7</v>
       </c>
-      <c r="E34" s="12" t="s">
-        <v>2973</v>
+      <c r="E34" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
         <v>1596</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="10">
         <v>25998</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>6</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <v>6</v>
       </c>
-      <c r="E35" s="12" t="s">
-        <v>2973</v>
+      <c r="E35" s="11" t="s">
+        <v>2971</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="8">
         <v>27871</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="8">
         <v>5</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>5</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
         <v>193</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="10">
         <v>10463</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>5</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <v>5</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="8">
         <v>3853</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="8">
         <v>5</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>5</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
         <v>300</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="10">
         <v>347</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <v>5</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <v>5</v>
       </c>
-      <c r="E39" s="10" t="s">
-        <v>2972</v>
+      <c r="E39" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="8">
         <v>31002</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="8">
         <v>5</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <v>5</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
         <v>369</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="10">
         <v>21510</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="10">
         <v>5</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="10">
         <v>5</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="8">
         <v>5688</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="8">
         <v>5</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <v>5</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <v>9724</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <v>5</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <v>7</v>
       </c>
-      <c r="E43" s="10" t="s">
-        <v>2972</v>
+      <c r="E43" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="8">
         <v>14023</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="8">
         <v>5</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="8">
         <v>5</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
         <v>999</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="10">
         <v>21701</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <v>5</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <v>5</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
         <v>1033</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="8">
         <v>37857</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="8">
         <v>5</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="8">
         <v>5</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
         <v>1590</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <v>13834</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <v>5</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <v>5</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="8">
         <v>39495</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="8">
         <v>4</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="8">
         <v>4</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <v>9736</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="10">
         <v>4</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="10">
         <v>4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="8">
         <v>25322</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="8">
         <v>4</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="8">
         <v>4</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="10">
         <v>19229</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="10">
         <v>4</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="10">
         <v>4</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="8">
         <v>33177</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="8">
         <v>4</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <v>4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
         <v>360</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="10">
         <v>27408</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="10">
         <v>4</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <v>4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="8">
         <v>20508</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="8">
         <v>4</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="8">
         <v>4</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
         <v>432</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="10">
         <v>34963</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="10">
         <v>4</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="10">
         <v>4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="8">
         <v>12507</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="8">
         <v>4</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="8">
         <v>4</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B57" s="11">
+      <c r="B57" s="10">
         <v>27838</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="10">
         <v>4</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="10">
         <v>4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
         <v>628</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="8">
         <v>14252</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="8">
         <v>4</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="8">
         <v>4</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
         <v>667</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="10">
         <v>27634</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="10">
         <v>4</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="10">
         <v>4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="8">
         <v>16471</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="8">
         <v>4</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="8">
         <v>4</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
         <v>742</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="10">
         <v>30709</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="10">
         <v>4</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="10">
         <v>4</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
         <v>760</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="8">
         <v>9676</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="8">
         <v>4</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="8">
         <v>4</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
         <v>789</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="10">
         <v>27030</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="10">
         <v>4</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="10">
         <v>4</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
         <v>830</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="8">
         <v>22942</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64" s="8">
         <v>4</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="8">
         <v>5</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="10">
         <v>16563</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <v>4</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="10">
         <v>4</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="8">
         <v>33600</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="8">
         <v>4</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="8">
         <v>4</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
         <v>908</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="10">
         <v>7436</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="10">
         <v>4</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="10">
         <v>4</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
         <v>932</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="8">
         <v>38535</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="8">
         <v>4</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="8">
         <v>4</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
         <v>935</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="10">
         <v>21133</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="10">
         <v>4</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="10">
         <v>4</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
         <v>976</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="8">
         <v>26745</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70" s="8">
         <v>4</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="8">
         <v>4</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
         <v>1100</v>
       </c>
-      <c r="B71" s="11">
+      <c r="B71" s="10">
         <v>3641</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="10">
         <v>4</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="10">
         <v>4</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
         <v>1132</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="8">
         <v>31118</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C72" s="8">
         <v>4</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="8">
         <v>4</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
         <v>1137</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="10">
         <v>20953</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="10">
         <v>4</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="10">
         <v>4</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
         <v>1347</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="8">
         <v>16666</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="8">
         <v>4</v>
       </c>
-      <c r="D74" s="9">
+      <c r="D74" s="8">
         <v>4</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
         <v>1367</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="10">
         <v>6758</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="10">
         <v>4</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="10">
         <v>6</v>
       </c>
-      <c r="E75" s="10" t="s">
-        <v>2972</v>
+      <c r="E75" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
         <v>1703</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="8">
         <v>23628</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="8">
         <v>4</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="8">
         <v>4</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B77" s="11">
+      <c r="B77" s="10">
         <v>14111</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="10">
         <v>4</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="10">
         <v>4</v>
       </c>
-      <c r="E77" s="10" t="s">
-        <v>2972</v>
+      <c r="E77" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="B78" s="9">
+      <c r="B78" s="8">
         <v>22825</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="8">
         <v>3</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="8">
         <v>3</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="10">
         <v>19655</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="10">
         <v>3</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="10">
         <v>3</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="8">
         <v>19184</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="8">
         <v>3</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="8">
         <v>3</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
         <v>293</v>
       </c>
-      <c r="B81" s="11">
+      <c r="B81" s="10">
         <v>23898</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="10">
         <v>3</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="10">
         <v>3</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="8">
         <v>44643</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="8">
         <v>3</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="8">
         <v>3</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
         <v>425</v>
       </c>
-      <c r="B83" s="11">
+      <c r="B83" s="10">
         <v>13755</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <v>3</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="10">
         <v>3</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="8">
         <v>17475</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="8">
         <v>3</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="8">
         <v>3</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
         <v>437</v>
       </c>
-      <c r="B85" s="11">
+      <c r="B85" s="10">
         <v>9283</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="10">
         <v>3</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="10">
         <v>3</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="8">
         <v>22247</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="8">
         <v>3</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="8">
         <v>3</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="B87" s="11">
+      <c r="B87" s="10">
         <v>5081</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="10">
         <v>3</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="10">
         <v>3</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="8">
         <v>9265</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="8">
         <v>3</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="8">
         <v>4</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="B89" s="11">
+      <c r="B89" s="10">
         <v>20450</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="10">
         <v>3</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="10">
         <v>3</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="8">
         <v>7418</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="8">
         <v>3</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="8">
         <v>3</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="B91" s="11">
+      <c r="B91" s="10">
         <v>53539</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <v>3</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="10">
         <v>3</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="8">
         <v>11162</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="8">
         <v>3</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="8">
         <v>4</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="B93" s="11">
+      <c r="B93" s="10">
         <v>29369</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="10">
         <v>3</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="10">
         <v>3</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
         <v>814</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="8">
         <v>11105</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="8">
         <v>3</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="8">
         <v>3</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="10">
         <v>5443</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="10">
         <v>3</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="10">
         <v>3</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="3" t="s">
         <v>856</v>
       </c>
-      <c r="B96" s="9">
+      <c r="B96" s="8">
         <v>12209</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="8">
         <v>3</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="8">
         <v>3</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
         <v>866</v>
       </c>
-      <c r="B97" s="11">
+      <c r="B97" s="10">
         <v>38191</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="10">
         <v>3</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="10">
         <v>3</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="8">
         <v>23061</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="8">
         <v>3</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="8">
         <v>3</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="10">
         <v>31391</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="10">
         <v>3</v>
       </c>
-      <c r="D99" s="11">
+      <c r="D99" s="10">
         <v>3</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="3" t="s">
         <v>1043</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="8">
         <v>26443</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="8">
         <v>3</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="8">
         <v>3</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
         <v>1174</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="10">
         <v>9740</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <v>3</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="10">
         <v>3</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="B102" s="9">
+      <c r="B102" s="8">
         <v>5331</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="8">
         <v>3</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="8">
         <v>3</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
         <v>983</v>
       </c>
-      <c r="B103" s="11">
+      <c r="B103" s="10">
         <v>41770</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="10">
         <v>3</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="10">
         <v>3</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="B104" s="9">
+      <c r="B104" s="8">
         <v>5432</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="8">
         <v>3</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="8">
         <v>3</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="10">
         <v>6773</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <v>3</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="10">
         <v>3</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="3" t="s">
         <v>1323</v>
       </c>
-      <c r="B106" s="9">
+      <c r="B106" s="8">
         <v>3163</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="8">
         <v>3</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="8">
         <v>3</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
         <v>1385</v>
       </c>
-      <c r="B107" s="11">
+      <c r="B107" s="10">
         <v>6935</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <v>3</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="10">
         <v>4</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="3" t="s">
         <v>1419</v>
       </c>
-      <c r="B108" s="9">
+      <c r="B108" s="8">
         <v>51060</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C108" s="8">
         <v>3</v>
       </c>
-      <c r="D108" s="9">
+      <c r="D108" s="8">
         <v>3</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
         <v>1434</v>
       </c>
-      <c r="B109" s="11">
+      <c r="B109" s="10">
         <v>7841</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="10">
         <v>3</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="10">
         <v>3</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="3" t="s">
         <v>1482</v>
       </c>
-      <c r="B110" s="9">
+      <c r="B110" s="8">
         <v>18695</v>
       </c>
-      <c r="C110" s="9">
+      <c r="C110" s="8">
         <v>3</v>
       </c>
-      <c r="D110" s="9">
+      <c r="D110" s="8">
         <v>3</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
         <v>1531</v>
       </c>
-      <c r="B111" s="11">
+      <c r="B111" s="10">
         <v>17859</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <v>3</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="10">
         <v>3</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="3" t="s">
         <v>1534</v>
       </c>
-      <c r="B112" s="9">
+      <c r="B112" s="8">
         <v>26972</v>
       </c>
-      <c r="C112" s="9">
+      <c r="C112" s="8">
         <v>3</v>
       </c>
-      <c r="D112" s="9">
+      <c r="D112" s="8">
         <v>3</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
         <v>1625</v>
       </c>
-      <c r="B113" s="11">
+      <c r="B113" s="10">
         <v>25974</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="10">
         <v>3</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="10">
         <v>3</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="3" t="s">
         <v>1904</v>
       </c>
-      <c r="B114" s="9">
+      <c r="B114" s="8">
         <v>39389</v>
       </c>
-      <c r="C114" s="9">
+      <c r="C114" s="8">
         <v>3</v>
       </c>
-      <c r="D114" s="9">
+      <c r="D114" s="8">
         <v>3</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B115" s="11">
+      <c r="B115" s="10">
         <v>7063</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="10">
         <v>2</v>
       </c>
-      <c r="D115" s="11">
+      <c r="D115" s="10">
         <v>2</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B116" s="9">
+      <c r="B116" s="8">
         <v>7668</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C116" s="8">
         <v>2</v>
       </c>
-      <c r="D116" s="9">
+      <c r="D116" s="8">
         <v>2</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
         <v>214</v>
       </c>
-      <c r="B117" s="11">
+      <c r="B117" s="10">
         <v>26167</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="10">
         <v>2</v>
       </c>
-      <c r="D117" s="11">
+      <c r="D117" s="10">
         <v>3</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B118" s="9">
+      <c r="B118" s="8">
         <v>22102</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C118" s="8">
         <v>2</v>
       </c>
-      <c r="D118" s="9">
+      <c r="D118" s="8">
         <v>2</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B119" s="11">
+      <c r="B119" s="10">
         <v>10551</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>2</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D119" s="10">
         <v>2</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B120" s="9">
+      <c r="B120" s="8">
         <v>5079</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C120" s="8">
         <v>2</v>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="8">
         <v>2</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="B121" s="11">
+      <c r="B121" s="10">
         <v>14288</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121" s="10">
         <v>2</v>
       </c>
-      <c r="D121" s="11">
+      <c r="D121" s="10">
         <v>2</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B122" s="9">
+      <c r="B122" s="8">
         <v>1463</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C122" s="8">
         <v>2</v>
       </c>
-      <c r="D122" s="9">
+      <c r="D122" s="8">
         <v>2</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B123" s="11">
+      <c r="B123" s="10">
         <v>9320</v>
       </c>
-      <c r="C123" s="11">
+      <c r="C123" s="10">
         <v>2</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="10">
         <v>2</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="B124" s="9">
+      <c r="B124" s="8">
         <v>24573</v>
       </c>
-      <c r="C124" s="9">
+      <c r="C124" s="8">
         <v>2</v>
       </c>
-      <c r="D124" s="9">
+      <c r="D124" s="8">
         <v>2</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="B125" s="11">
+      <c r="B125" s="10">
         <v>19975</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="10">
         <v>2</v>
       </c>
-      <c r="D125" s="11">
+      <c r="D125" s="10">
         <v>2</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="B126" s="9">
+      <c r="B126" s="8">
         <v>5335</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C126" s="8">
         <v>2</v>
       </c>
-      <c r="D126" s="9">
+      <c r="D126" s="8">
         <v>3</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="B127" s="11">
+      <c r="B127" s="10">
         <v>35532</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="10">
         <v>2</v>
       </c>
-      <c r="D127" s="11">
+      <c r="D127" s="10">
         <v>2</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="B128" s="9">
+      <c r="B128" s="8">
         <v>8818</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C128" s="8">
         <v>2</v>
       </c>
-      <c r="D128" s="9">
+      <c r="D128" s="8">
         <v>2</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="B129" s="11">
+      <c r="B129" s="10">
         <v>38787</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <v>2</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D129" s="10">
         <v>2</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="B130" s="9">
+      <c r="B130" s="8">
         <v>37876</v>
       </c>
-      <c r="C130" s="9">
+      <c r="C130" s="8">
         <v>2</v>
       </c>
-      <c r="D130" s="9">
+      <c r="D130" s="8">
         <v>2</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
         <v>634</v>
       </c>
-      <c r="B131" s="11">
+      <c r="B131" s="10">
         <v>13451</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="10">
         <v>2</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D131" s="10">
         <v>2</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="B132" s="9">
+      <c r="B132" s="8">
         <v>19061</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C132" s="8">
         <v>2</v>
       </c>
-      <c r="D132" s="9">
+      <c r="D132" s="8">
         <v>2</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="B133" s="11">
+      <c r="B133" s="10">
         <v>14804</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="10">
         <v>2</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="10">
         <v>2</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="3" t="s">
         <v>680</v>
       </c>
-      <c r="B134" s="9">
+      <c r="B134" s="8">
         <v>17123</v>
       </c>
-      <c r="C134" s="9">
+      <c r="C134" s="8">
         <v>2</v>
       </c>
-      <c r="D134" s="9">
+      <c r="D134" s="8">
         <v>2</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
         <v>720</v>
       </c>
-      <c r="B135" s="11">
+      <c r="B135" s="10">
         <v>20038</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="10">
         <v>2</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D135" s="10">
         <v>2</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="3" t="s">
         <v>756</v>
       </c>
-      <c r="B136" s="9">
+      <c r="B136" s="8">
         <v>3351</v>
       </c>
-      <c r="C136" s="9">
+      <c r="C136" s="8">
         <v>2</v>
       </c>
-      <c r="D136" s="9">
+      <c r="D136" s="8">
         <v>2</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="B137" s="11">
+      <c r="B137" s="10">
         <v>40808</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="10">
         <v>2</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="10">
         <v>2</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="3" t="s">
         <v>794</v>
       </c>
-      <c r="B138" s="9">
+      <c r="B138" s="8">
         <v>22163</v>
       </c>
-      <c r="C138" s="9">
+      <c r="C138" s="8">
         <v>2</v>
       </c>
-      <c r="D138" s="9">
+      <c r="D138" s="8">
         <v>2</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
         <v>827</v>
       </c>
-      <c r="B139" s="11">
+      <c r="B139" s="10">
         <v>4842</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="10">
         <v>2</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="10">
         <v>2</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="3" t="s">
         <v>847</v>
       </c>
-      <c r="B140" s="9">
+      <c r="B140" s="8">
         <v>3826</v>
       </c>
-      <c r="C140" s="9">
+      <c r="C140" s="8">
         <v>2</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="8">
         <v>2</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
         <v>862</v>
       </c>
-      <c r="B141" s="11">
+      <c r="B141" s="10">
         <v>9375</v>
       </c>
-      <c r="C141" s="11">
+      <c r="C141" s="10">
         <v>2</v>
       </c>
-      <c r="D141" s="11">
+      <c r="D141" s="10">
         <v>2</v>
       </c>
-      <c r="E141" s="10" t="s">
-        <v>2972</v>
+      <c r="E141" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="3" t="s">
         <v>884</v>
       </c>
-      <c r="B142" s="9">
+      <c r="B142" s="8">
         <v>9490</v>
       </c>
-      <c r="C142" s="9">
+      <c r="C142" s="8">
         <v>2</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="8">
         <v>2</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
         <v>917</v>
       </c>
-      <c r="B143" s="11">
+      <c r="B143" s="10">
         <v>23794</v>
       </c>
-      <c r="C143" s="11">
+      <c r="C143" s="10">
         <v>2</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="10">
         <v>2</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="3" t="s">
         <v>926</v>
       </c>
-      <c r="B144" s="9">
+      <c r="B144" s="8">
         <v>20625</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C144" s="8">
         <v>2</v>
       </c>
-      <c r="D144" s="9">
+      <c r="D144" s="8">
         <v>2</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
         <v>950</v>
       </c>
-      <c r="B145" s="11">
+      <c r="B145" s="10">
         <v>13592</v>
       </c>
-      <c r="C145" s="11">
+      <c r="C145" s="10">
         <v>2</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="10">
         <v>2</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="B146" s="9">
+      <c r="B146" s="8">
         <v>21130</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C146" s="8">
         <v>2</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D146" s="8">
         <v>2</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
         <v>1011</v>
       </c>
-      <c r="B147" s="11">
+      <c r="B147" s="10">
         <v>23188</v>
       </c>
-      <c r="C147" s="11">
+      <c r="C147" s="10">
         <v>2</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="10">
         <v>2</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="3" t="s">
         <v>1016</v>
       </c>
-      <c r="B148" s="9">
+      <c r="B148" s="8">
         <v>21381</v>
       </c>
-      <c r="C148" s="9">
+      <c r="C148" s="8">
         <v>2</v>
       </c>
-      <c r="D148" s="9">
+      <c r="D148" s="8">
         <v>2</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
         <v>1084</v>
       </c>
-      <c r="B149" s="11">
+      <c r="B149" s="10">
         <v>24619</v>
       </c>
-      <c r="C149" s="11">
+      <c r="C149" s="10">
         <v>2</v>
       </c>
-      <c r="D149" s="11">
+      <c r="D149" s="10">
         <v>2</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="3" t="s">
         <v>1146</v>
       </c>
-      <c r="B150" s="9">
+      <c r="B150" s="8">
         <v>8329</v>
       </c>
-      <c r="C150" s="9">
+      <c r="C150" s="8">
         <v>2</v>
       </c>
-      <c r="D150" s="9">
+      <c r="D150" s="8">
         <v>2</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="B151" s="11">
+      <c r="B151" s="10">
         <v>33770</v>
       </c>
-      <c r="C151" s="11">
+      <c r="C151" s="10">
         <v>2</v>
       </c>
-      <c r="D151" s="11">
+      <c r="D151" s="10">
         <v>2</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="B152" s="9">
+      <c r="B152" s="8">
         <v>8650</v>
       </c>
-      <c r="C152" s="9">
+      <c r="C152" s="8">
         <v>2</v>
       </c>
-      <c r="D152" s="9">
+      <c r="D152" s="8">
         <v>2</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
         <v>1293</v>
       </c>
-      <c r="B153" s="11">
+      <c r="B153" s="10">
         <v>20707</v>
       </c>
-      <c r="C153" s="11">
+      <c r="C153" s="10">
         <v>2</v>
       </c>
-      <c r="D153" s="11">
+      <c r="D153" s="10">
         <v>2</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="3" t="s">
         <v>1297</v>
       </c>
-      <c r="B154" s="9">
+      <c r="B154" s="8">
         <v>10711</v>
       </c>
-      <c r="C154" s="9">
+      <c r="C154" s="8">
         <v>2</v>
       </c>
-      <c r="D154" s="9">
+      <c r="D154" s="8">
         <v>2</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
         <v>1303</v>
       </c>
-      <c r="B155" s="11">
+      <c r="B155" s="10">
         <v>6896</v>
       </c>
-      <c r="C155" s="11">
+      <c r="C155" s="10">
         <v>2</v>
       </c>
-      <c r="D155" s="11">
+      <c r="D155" s="10">
         <v>2</v>
       </c>
-      <c r="E155" s="10" t="s">
-        <v>2972</v>
+      <c r="E155" s="9" t="s">
+        <v>2970</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
         <v>1364</v>
       </c>
-      <c r="B156" s="9">
+      <c r="B156" s="8">
         <v>14118</v>
       </c>
-      <c r="C156" s="9">
+      <c r="C156" s="8">
         <v>2</v>
       </c>
-      <c r="D156" s="9">
+      <c r="D156" s="8">
         <v>2</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
         <v>1373</v>
       </c>
-      <c r="B157" s="11">
+      <c r="B157" s="10">
         <v>22489</v>
       </c>
-      <c r="C157" s="11">
+      <c r="C157" s="10">
         <v>2</v>
       </c>
-      <c r="D157" s="11">
+      <c r="D157" s="10">
         <v>2</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B158" s="9">
+      <c r="B158" s="8">
         <v>27417</v>
       </c>
-      <c r="C158" s="9">
+      <c r="C158" s="8">
         <v>2</v>
       </c>
-      <c r="D158" s="9">
+      <c r="D158" s="8">
         <v>2</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
         <v>1459</v>
       </c>
-      <c r="B159" s="11">
+      <c r="B159" s="10">
         <v>50516</v>
       </c>
-      <c r="C159" s="11">
+      <c r="C159" s="10">
         <v>2</v>
       </c>
-      <c r="D159" s="11">
+      <c r="D159" s="10">
         <v>2</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="3" t="s">
         <v>1491</v>
       </c>
-      <c r="B160" s="9">
+      <c r="B160" s="8">
         <v>3612</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C160" s="8">
         <v>2</v>
       </c>
-      <c r="D160" s="9">
+      <c r="D160" s="8">
         <v>2</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
         <v>1508</v>
       </c>
-      <c r="B161" s="11">
+      <c r="B161" s="10">
         <v>19127</v>
       </c>
-      <c r="C161" s="11">
+      <c r="C161" s="10">
         <v>2</v>
       </c>
-      <c r="D161" s="11">
+      <c r="D161" s="10">
         <v>2</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
         <v>1545</v>
       </c>
-      <c r="B162" s="9">
+      <c r="B162" s="8">
         <v>20050</v>
       </c>
-      <c r="C162" s="9">
+      <c r="C162" s="8">
         <v>2</v>
       </c>
-      <c r="D162" s="9">
+      <c r="D162" s="8">
         <v>2</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
         <v>1556</v>
       </c>
-      <c r="B163" s="11">
+      <c r="B163" s="10">
         <v>17023</v>
       </c>
-      <c r="C163" s="11">
+      <c r="C163" s="10">
         <v>2</v>
       </c>
-      <c r="D163" s="11">
+      <c r="D163" s="10">
         <v>2</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
         <v>1583</v>
       </c>
-      <c r="B164" s="9">
+      <c r="B164" s="8">
         <v>2257</v>
       </c>
-      <c r="C164" s="9">
+      <c r="C164" s="8">
         <v>2</v>
       </c>
-      <c r="D164" s="9">
+      <c r="D164" s="8">
         <v>2</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
         <v>1612</v>
       </c>
-      <c r="B165" s="11">
+      <c r="B165" s="10">
         <v>23592</v>
       </c>
-      <c r="C165" s="11">
+      <c r="C165" s="10">
         <v>2</v>
       </c>
-      <c r="D165" s="11">
+      <c r="D165" s="10">
         <v>2</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="3" t="s">
         <v>1621</v>
       </c>
-      <c r="B166" s="9">
+      <c r="B166" s="8">
         <v>26938</v>
       </c>
-      <c r="C166" s="9">
+      <c r="C166" s="8">
         <v>2</v>
       </c>
-      <c r="D166" s="9">
+      <c r="D166" s="8">
         <v>2</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="B167" s="11">
+      <c r="B167" s="10">
         <v>4719</v>
       </c>
-      <c r="C167" s="11">
+      <c r="C167" s="10">
         <v>2</v>
       </c>
-      <c r="D167" s="11">
+      <c r="D167" s="10">
         <v>2</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="3" t="s">
         <v>1641</v>
       </c>
-      <c r="B168" s="9">
+      <c r="B168" s="8">
         <v>40896</v>
       </c>
-      <c r="C168" s="9">
+      <c r="C168" s="8">
         <v>2</v>
       </c>
-      <c r="D168" s="9">
+      <c r="D168" s="8">
         <v>2</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
         <v>955</v>
       </c>
-      <c r="B169" s="11">
+      <c r="B169" s="10">
         <v>24701</v>
       </c>
-      <c r="C169" s="11">
+      <c r="C169" s="10">
         <v>2</v>
       </c>
-      <c r="D169" s="11">
+      <c r="D169" s="10">
         <v>2</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="3" t="s">
         <v>1718</v>
       </c>
-      <c r="B170" s="9">
+      <c r="B170" s="8">
         <v>7191</v>
       </c>
-      <c r="C170" s="9">
+      <c r="C170" s="8">
         <v>2</v>
       </c>
-      <c r="D170" s="9">
+      <c r="D170" s="8">
         <v>2</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
         <v>1752</v>
       </c>
-      <c r="B171" s="11">
+      <c r="B171" s="10">
         <v>20228</v>
       </c>
-      <c r="C171" s="11">
+      <c r="C171" s="10">
         <v>2</v>
       </c>
-      <c r="D171" s="11">
+      <c r="D171" s="10">
         <v>2</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="3" t="s">
         <v>1818</v>
       </c>
-      <c r="B172" s="9">
+      <c r="B172" s="8">
         <v>20516</v>
       </c>
-      <c r="C172" s="9">
+      <c r="C172" s="8">
         <v>2</v>
       </c>
-      <c r="D172" s="9">
+      <c r="D172" s="8">
         <v>2</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="5" t="s">
         <v>1827</v>
       </c>
-      <c r="B173" s="11">
+      <c r="B173" s="10">
         <v>25299</v>
       </c>
-      <c r="C173" s="11">
+      <c r="C173" s="10">
         <v>2</v>
       </c>
-      <c r="D173" s="11">
+      <c r="D173" s="10">
         <v>2</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="B174" s="9">
+      <c r="B174" s="8">
         <v>36958</v>
       </c>
-      <c r="C174" s="9">
+      <c r="C174" s="8">
         <v>2</v>
       </c>
-      <c r="D174" s="9">
+      <c r="D174" s="8">
         <v>2</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="5" t="s">
         <v>1971</v>
       </c>
-      <c r="B175" s="11">
+      <c r="B175" s="10">
         <v>26955</v>
       </c>
-      <c r="C175" s="11">
+      <c r="C175" s="10">
         <v>2</v>
       </c>
-      <c r="D175" s="11">
+      <c r="D175" s="10">
         <v>2</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="3" t="s">
         <v>2139</v>
       </c>
-      <c r="B176" s="9">
+      <c r="B176" s="8">
         <v>27712</v>
       </c>
-      <c r="C176" s="9">
+      <c r="C176" s="8">
         <v>2</v>
       </c>
-      <c r="D176" s="9">
+      <c r="D176" s="8">
         <v>2</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="5" t="s">
         <v>2171</v>
       </c>
-      <c r="B177" s="11">
+      <c r="B177" s="10">
         <v>3223</v>
       </c>
-      <c r="C177" s="11">
+      <c r="C177" s="10">
         <v>2</v>
       </c>
-      <c r="D177" s="11">
+      <c r="D177" s="10">
         <v>2</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="B178" s="9">
+      <c r="B178" s="8">
         <v>26600</v>
       </c>
-      <c r="C178" s="9">
+      <c r="C178" s="8">
         <v>1</v>
       </c>
-      <c r="D178" s="9">
+      <c r="D178" s="8">
         <v>1</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="5" t="s">
         <v>201</v>
       </c>
-      <c r="B179" s="11">
+      <c r="B179" s="10">
         <v>26549</v>
       </c>
-      <c r="C179" s="11">
+      <c r="C179" s="10">
         <v>1</v>
       </c>
-      <c r="D179" s="11">
+      <c r="D179" s="10">
         <v>1</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B180" s="9">
+      <c r="B180" s="8">
         <v>14299</v>
       </c>
-      <c r="C180" s="9">
+      <c r="C180" s="8">
         <v>1</v>
       </c>
-      <c r="D180" s="9">
+      <c r="D180" s="8">
         <v>1</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="5" t="s">
         <v>320</v>
       </c>
-      <c r="B181" s="11">
+      <c r="B181" s="10">
         <v>10596</v>
       </c>
-      <c r="C181" s="11">
+      <c r="C181" s="10">
         <v>1</v>
       </c>
-      <c r="D181" s="11">
+      <c r="D181" s="10">
         <v>1</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="B182" s="9">
+      <c r="B182" s="8">
         <v>24580</v>
       </c>
-      <c r="C182" s="9">
+      <c r="C182" s="8">
         <v>1</v>
       </c>
-      <c r="D182" s="9">
+      <c r="D182" s="8">
         <v>1</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="5" t="s">
         <v>486</v>
       </c>
-      <c r="B183" s="11">
+      <c r="B183" s="10">
         <v>8885</v>
       </c>
-      <c r="C183" s="11">
+      <c r="C183" s="10">
         <v>1</v>
       </c>
-      <c r="D183" s="11">
+      <c r="D183" s="10">
         <v>1</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="B184" s="9">
+      <c r="B184" s="8">
         <v>15449</v>
       </c>
-      <c r="C184" s="9">
+      <c r="C184" s="8">
         <v>1</v>
       </c>
-      <c r="D184" s="9">
+      <c r="D184" s="8">
         <v>1</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="5" t="s">
         <v>503</v>
       </c>
-      <c r="B185" s="11">
+      <c r="B185" s="10">
         <v>39723</v>
       </c>
-      <c r="C185" s="11">
+      <c r="C185" s="10">
         <v>1</v>
       </c>
-      <c r="D185" s="11">
+      <c r="D185" s="10">
         <v>1</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B186" s="9">
+      <c r="B186" s="8">
         <v>34668</v>
       </c>
-      <c r="C186" s="9">
+      <c r="C186" s="8">
         <v>1</v>
       </c>
-      <c r="D186" s="9">
+      <c r="D186" s="8">
         <v>1</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="B187" s="11">
+      <c r="B187" s="10">
         <v>3310</v>
       </c>
-      <c r="C187" s="11">
+      <c r="C187" s="10">
         <v>1</v>
       </c>
-      <c r="D187" s="11">
+      <c r="D187" s="10">
         <v>1</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="B188" s="9">
+      <c r="B188" s="8">
         <v>44116</v>
       </c>
-      <c r="C188" s="9">
+      <c r="C188" s="8">
         <v>1</v>
       </c>
-      <c r="D188" s="9">
+      <c r="D188" s="8">
         <v>1</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="5" t="s">
         <v>436</v>
       </c>
-      <c r="B189" s="11">
+      <c r="B189" s="10">
         <v>15416</v>
       </c>
-      <c r="C189" s="11">
+      <c r="C189" s="10">
         <v>1</v>
       </c>
-      <c r="D189" s="11">
+      <c r="D189" s="10">
         <v>1</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="3" t="s">
         <v>699</v>
       </c>
-      <c r="B190" s="9">
+      <c r="B190" s="8">
         <v>4059</v>
       </c>
-      <c r="C190" s="9">
+      <c r="C190" s="8">
         <v>1</v>
       </c>
-      <c r="D190" s="9">
+      <c r="D190" s="8">
         <v>1</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="B191" s="11">
+      <c r="B191" s="10">
         <v>5948</v>
       </c>
-      <c r="C191" s="11">
+      <c r="C191" s="10">
         <v>1</v>
       </c>
-      <c r="D191" s="11">
+      <c r="D191" s="10">
         <v>1</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="3" t="s">
         <v>840</v>
       </c>
-      <c r="B192" s="9">
+      <c r="B192" s="8">
         <v>40633</v>
       </c>
-      <c r="C192" s="9">
+      <c r="C192" s="8">
         <v>1</v>
       </c>
-      <c r="D192" s="9">
+      <c r="D192" s="8">
         <v>1</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="B193" s="11">
+      <c r="B193" s="10">
         <v>10651</v>
       </c>
-      <c r="C193" s="11">
+      <c r="C193" s="10">
         <v>1</v>
       </c>
-      <c r="D193" s="11">
+      <c r="D193" s="10">
         <v>1</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="3" t="s">
         <v>957</v>
       </c>
-      <c r="B194" s="9">
+      <c r="B194" s="8">
         <v>27677</v>
       </c>
-      <c r="C194" s="9">
+      <c r="C194" s="8">
         <v>1</v>
       </c>
-      <c r="D194" s="9">
+      <c r="D194" s="8">
         <v>1</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="5" t="s">
         <v>989</v>
       </c>
-      <c r="B195" s="11">
+      <c r="B195" s="10">
         <v>41171</v>
       </c>
-      <c r="C195" s="11">
+      <c r="C195" s="10">
         <v>1</v>
       </c>
-      <c r="D195" s="11">
+      <c r="D195" s="10">
         <v>1</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="B196" s="9">
+      <c r="B196" s="8">
         <v>11679</v>
       </c>
-      <c r="C196" s="9">
+      <c r="C196" s="8">
         <v>1</v>
       </c>
-      <c r="D196" s="9">
+      <c r="D196" s="8">
         <v>1</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="5" t="s">
         <v>1036</v>
       </c>
-      <c r="B197" s="11">
+      <c r="B197" s="10">
         <v>8458</v>
       </c>
-      <c r="C197" s="11">
+      <c r="C197" s="10">
         <v>1</v>
       </c>
-      <c r="D197" s="11">
+      <c r="D197" s="10">
         <v>1</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="3" t="s">
         <v>1046</v>
       </c>
-      <c r="B198" s="9">
+      <c r="B198" s="8">
         <v>29484</v>
       </c>
-      <c r="C198" s="9">
+      <c r="C198" s="8">
         <v>1</v>
       </c>
-      <c r="D198" s="9">
+      <c r="D198" s="8">
         <v>1</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="5" t="s">
         <v>1063</v>
       </c>
-      <c r="B199" s="11">
+      <c r="B199" s="10">
         <v>26815</v>
       </c>
-      <c r="C199" s="11">
+      <c r="C199" s="10">
         <v>1</v>
       </c>
-      <c r="D199" s="11">
+      <c r="D199" s="10">
         <v>1</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="3" t="s">
         <v>1072</v>
       </c>
-      <c r="B200" s="9">
+      <c r="B200" s="8">
         <v>8006</v>
       </c>
-      <c r="C200" s="9">
+      <c r="C200" s="8">
         <v>1</v>
       </c>
-      <c r="D200" s="9">
+      <c r="D200" s="8">
         <v>1</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="5" t="s">
         <v>716</v>
       </c>
-      <c r="B201" s="11">
+      <c r="B201" s="10">
         <v>15132</v>
       </c>
-      <c r="C201" s="11">
+      <c r="C201" s="10">
         <v>1</v>
       </c>
-      <c r="D201" s="11">
+      <c r="D201" s="10">
         <v>1</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="3" t="s">
         <v>1079</v>
       </c>
-      <c r="B202" s="9">
+      <c r="B202" s="8">
         <v>41518</v>
       </c>
-      <c r="C202" s="9">
+      <c r="C202" s="8">
         <v>1</v>
       </c>
-      <c r="D202" s="9">
+      <c r="D202" s="8">
         <v>1</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="B203" s="11">
+      <c r="B203" s="10">
         <v>6974</v>
       </c>
-      <c r="C203" s="11">
+      <c r="C203" s="10">
         <v>1</v>
       </c>
-      <c r="D203" s="11">
+      <c r="D203" s="10">
         <v>1</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="3" t="s">
         <v>1091</v>
       </c>
-      <c r="B204" s="9">
+      <c r="B204" s="8">
         <v>703</v>
       </c>
-      <c r="C204" s="9">
+      <c r="C204" s="8">
         <v>1</v>
       </c>
-      <c r="D204" s="9">
+      <c r="D204" s="8">
         <v>1</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="5" t="s">
         <v>1142</v>
       </c>
-      <c r="B205" s="11">
+      <c r="B205" s="10">
         <v>18424</v>
       </c>
-      <c r="C205" s="11">
+      <c r="C205" s="10">
         <v>1</v>
       </c>
-      <c r="D205" s="11">
+      <c r="D205" s="10">
         <v>1</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="3" t="s">
         <v>1166</v>
       </c>
-      <c r="B206" s="9">
+      <c r="B206" s="8">
         <v>331</v>
       </c>
-      <c r="C206" s="9">
+      <c r="C206" s="8">
         <v>1</v>
       </c>
-      <c r="D206" s="9">
+      <c r="D206" s="8">
         <v>1</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="5" t="s">
         <v>1180</v>
       </c>
-      <c r="B207" s="11">
+      <c r="B207" s="10">
         <v>11802</v>
       </c>
-      <c r="C207" s="11">
+      <c r="C207" s="10">
         <v>1</v>
       </c>
-      <c r="D207" s="11">
+      <c r="D207" s="10">
         <v>1</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="3" t="s">
         <v>1190</v>
       </c>
-      <c r="B208" s="9">
+      <c r="B208" s="8">
         <v>18862</v>
       </c>
-      <c r="C208" s="9">
+      <c r="C208" s="8">
         <v>1</v>
       </c>
-      <c r="D208" s="9">
+      <c r="D208" s="8">
         <v>1</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="5" t="s">
         <v>1197</v>
       </c>
-      <c r="B209" s="11">
+      <c r="B209" s="10">
         <v>19890</v>
       </c>
-      <c r="C209" s="11">
+      <c r="C209" s="10">
         <v>1</v>
       </c>
-      <c r="D209" s="11">
+      <c r="D209" s="10">
         <v>1</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="3" t="s">
         <v>1251</v>
       </c>
-      <c r="B210" s="9">
+      <c r="B210" s="8">
         <v>23531</v>
       </c>
-      <c r="C210" s="9">
+      <c r="C210" s="8">
         <v>1</v>
       </c>
-      <c r="D210" s="9">
+      <c r="D210" s="8">
         <v>1</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="5" t="s">
         <v>872</v>
       </c>
-      <c r="B211" s="11">
+      <c r="B211" s="10">
         <v>20052</v>
       </c>
-      <c r="C211" s="11">
+      <c r="C211" s="10">
         <v>1</v>
       </c>
-      <c r="D211" s="11">
+      <c r="D211" s="10">
         <v>1</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="3" t="s">
         <v>1278</v>
       </c>
-      <c r="B212" s="9">
+      <c r="B212" s="8">
         <v>8556</v>
       </c>
-      <c r="C212" s="9">
+      <c r="C212" s="8">
         <v>1</v>
       </c>
-      <c r="D212" s="9">
+      <c r="D212" s="8">
         <v>1</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="5" t="s">
         <v>1300</v>
       </c>
-      <c r="B213" s="11">
+      <c r="B213" s="10">
         <v>27112</v>
       </c>
-      <c r="C213" s="11">
+      <c r="C213" s="10">
         <v>1</v>
       </c>
-      <c r="D213" s="11">
+      <c r="D213" s="10">
         <v>1</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="3" t="s">
         <v>1309</v>
       </c>
-      <c r="B214" s="9">
+      <c r="B214" s="8">
         <v>51089</v>
       </c>
-      <c r="C214" s="9">
+      <c r="C214" s="8">
         <v>1</v>
       </c>
-      <c r="D214" s="9">
+      <c r="D214" s="8">
         <v>1</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="5" t="s">
         <v>856</v>
       </c>
-      <c r="B215" s="11">
+      <c r="B215" s="10">
         <v>10666</v>
       </c>
-      <c r="C215" s="11">
+      <c r="C215" s="10">
         <v>1</v>
       </c>
-      <c r="D215" s="11">
+      <c r="D215" s="10">
         <v>1</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="3" t="s">
         <v>1358</v>
       </c>
-      <c r="B216" s="9">
+      <c r="B216" s="8">
         <v>40001</v>
       </c>
-      <c r="C216" s="9">
+      <c r="C216" s="8">
         <v>1</v>
       </c>
-      <c r="D216" s="9">
+      <c r="D216" s="8">
         <v>1</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="5" t="s">
         <v>1397</v>
       </c>
-      <c r="B217" s="11">
+      <c r="B217" s="10">
         <v>17561</v>
       </c>
-      <c r="C217" s="11">
+      <c r="C217" s="10">
         <v>1</v>
       </c>
-      <c r="D217" s="11">
+      <c r="D217" s="10">
         <v>1</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="3" t="s">
         <v>1268</v>
       </c>
-      <c r="B218" s="9">
+      <c r="B218" s="8">
         <v>6044</v>
       </c>
-      <c r="C218" s="9">
+      <c r="C218" s="8">
         <v>1</v>
       </c>
-      <c r="D218" s="9">
+      <c r="D218" s="8">
         <v>1</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="5" t="s">
         <v>1415</v>
       </c>
-      <c r="B219" s="11">
+      <c r="B219" s="10">
         <v>27276</v>
       </c>
-      <c r="C219" s="11">
+      <c r="C219" s="10">
         <v>1</v>
       </c>
-      <c r="D219" s="11">
+      <c r="D219" s="10">
         <v>1</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="3" t="s">
         <v>1425</v>
       </c>
-      <c r="B220" s="9">
+      <c r="B220" s="8">
         <v>26124</v>
       </c>
-      <c r="C220" s="9">
+      <c r="C220" s="8">
         <v>1</v>
       </c>
-      <c r="D220" s="9">
+      <c r="D220" s="8">
         <v>1</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="5" t="s">
         <v>1487</v>
       </c>
-      <c r="B221" s="11">
+      <c r="B221" s="10">
         <v>7195</v>
       </c>
-      <c r="C221" s="11">
+      <c r="C221" s="10">
         <v>1</v>
       </c>
-      <c r="D221" s="11">
+      <c r="D221" s="10">
         <v>1</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="3" t="s">
         <v>1525</v>
       </c>
-      <c r="B222" s="9">
+      <c r="B222" s="8">
         <v>32458</v>
       </c>
-      <c r="C222" s="9">
+      <c r="C222" s="8">
         <v>1</v>
       </c>
-      <c r="D222" s="9">
+      <c r="D222" s="8">
         <v>1</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="5" t="s">
         <v>1550</v>
       </c>
-      <c r="B223" s="11">
+      <c r="B223" s="10">
         <v>3156</v>
       </c>
-      <c r="C223" s="11">
+      <c r="C223" s="10">
         <v>1</v>
       </c>
-      <c r="D223" s="11">
+      <c r="D223" s="10">
         <v>1</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="3" t="s">
         <v>1570</v>
       </c>
-      <c r="B224" s="9">
+      <c r="B224" s="8">
         <v>17172</v>
       </c>
-      <c r="C224" s="9">
+      <c r="C224" s="8">
         <v>1</v>
       </c>
-      <c r="D224" s="9">
+      <c r="D224" s="8">
         <v>1</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="5" t="s">
         <v>1574</v>
       </c>
-      <c r="B225" s="11">
+      <c r="B225" s="10">
         <v>21321</v>
       </c>
-      <c r="C225" s="11">
+      <c r="C225" s="10">
         <v>1</v>
       </c>
-      <c r="D225" s="11">
+      <c r="D225" s="10">
         <v>1</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B226" s="9">
+      <c r="B226" s="8">
         <v>27456</v>
       </c>
-      <c r="C226" s="9">
+      <c r="C226" s="8">
         <v>1</v>
       </c>
-      <c r="D226" s="9">
+      <c r="D226" s="8">
         <v>1</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="5" t="s">
         <v>983</v>
       </c>
-      <c r="B227" s="11">
+      <c r="B227" s="10">
         <v>23068</v>
       </c>
-      <c r="C227" s="11">
+      <c r="C227" s="10">
         <v>1</v>
       </c>
-      <c r="D227" s="11">
+      <c r="D227" s="10">
         <v>1</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="3" t="s">
         <v>1668</v>
       </c>
-      <c r="B228" s="9">
+      <c r="B228" s="8">
         <v>6565</v>
       </c>
-      <c r="C228" s="9">
+      <c r="C228" s="8">
         <v>1</v>
       </c>
-      <c r="D228" s="9">
+      <c r="D228" s="8">
         <v>1</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="5" t="s">
         <v>1738</v>
       </c>
-      <c r="B229" s="11">
+      <c r="B229" s="10">
         <v>6971</v>
       </c>
-      <c r="C229" s="11">
+      <c r="C229" s="10">
         <v>1</v>
       </c>
-      <c r="D229" s="11">
+      <c r="D229" s="10">
         <v>2</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="230" spans="1:5">
       <c r="A230" s="3" t="s">
         <v>1771</v>
       </c>
-      <c r="B230" s="9">
+      <c r="B230" s="8">
         <v>5865</v>
       </c>
-      <c r="C230" s="9">
+      <c r="C230" s="8">
         <v>1</v>
       </c>
-      <c r="D230" s="9">
+      <c r="D230" s="8">
         <v>1</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="231" spans="1:5">
       <c r="A231" s="5" t="s">
         <v>1785</v>
       </c>
-      <c r="B231" s="11">
+      <c r="B231" s="10">
         <v>6292</v>
       </c>
-      <c r="C231" s="11">
+      <c r="C231" s="10">
         <v>1</v>
       </c>
-      <c r="D231" s="11">
+      <c r="D231" s="10">
         <v>1</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="232" spans="1:5">
       <c r="A232" s="3" t="s">
         <v>1793</v>
       </c>
-      <c r="B232" s="9">
+      <c r="B232" s="8">
         <v>18863</v>
       </c>
-      <c r="C232" s="9">
+      <c r="C232" s="8">
         <v>1</v>
       </c>
-      <c r="D232" s="9">
+      <c r="D232" s="8">
         <v>1</v>
       </c>
       <c r="E232" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="233" spans="1:5">
       <c r="A233" s="5" t="s">
         <v>1800</v>
       </c>
-      <c r="B233" s="11">
+      <c r="B233" s="10">
         <v>5205</v>
       </c>
-      <c r="C233" s="11">
+      <c r="C233" s="10">
         <v>1</v>
       </c>
-      <c r="D233" s="11">
+      <c r="D233" s="10">
         <v>1</v>
       </c>
       <c r="E233" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="234" spans="1:5">
       <c r="A234" s="3" t="s">
         <v>1808</v>
       </c>
-      <c r="B234" s="9">
+      <c r="B234" s="8">
         <v>15788</v>
       </c>
-      <c r="C234" s="9">
+      <c r="C234" s="8">
         <v>1</v>
       </c>
-      <c r="D234" s="9">
+      <c r="D234" s="8">
         <v>1</v>
       </c>
       <c r="E234" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="235" spans="1:5">
       <c r="A235" s="5" t="s">
         <v>1866</v>
       </c>
-      <c r="B235" s="11">
+      <c r="B235" s="10">
         <v>20520</v>
       </c>
-      <c r="C235" s="11">
+      <c r="C235" s="10">
         <v>1</v>
       </c>
-      <c r="D235" s="11">
+      <c r="D235" s="10">
         <v>1</v>
       </c>
       <c r="E235" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="236" spans="1:5">
       <c r="A236" s="3" t="s">
         <v>1845</v>
       </c>
-      <c r="B236" s="9">
+      <c r="B236" s="8">
         <v>8231</v>
       </c>
-      <c r="C236" s="9">
+      <c r="C236" s="8">
         <v>1</v>
       </c>
-      <c r="D236" s="9">
+      <c r="D236" s="8">
         <v>1</v>
       </c>
       <c r="E236" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="237" spans="1:5">
       <c r="A237" s="5" t="s">
         <v>1935</v>
       </c>
-      <c r="B237" s="11">
+      <c r="B237" s="10">
         <v>18875</v>
       </c>
-      <c r="C237" s="11">
+      <c r="C237" s="10">
         <v>1</v>
       </c>
-      <c r="D237" s="11">
+      <c r="D237" s="10">
         <v>1</v>
       </c>
       <c r="E237" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="238" spans="1:5">
       <c r="A238" s="3" t="s">
         <v>1951</v>
       </c>
-      <c r="B238" s="9">
+      <c r="B238" s="8">
         <v>3762</v>
       </c>
-      <c r="C238" s="9">
+      <c r="C238" s="8">
         <v>1</v>
       </c>
-      <c r="D238" s="9">
+      <c r="D238" s="8">
         <v>1</v>
       </c>
       <c r="E238" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="239" spans="1:5">
       <c r="A239" s="5" t="s">
         <v>2003</v>
       </c>
-      <c r="B239" s="11">
+      <c r="B239" s="10">
         <v>19484</v>
       </c>
-      <c r="C239" s="11">
+      <c r="C239" s="10">
         <v>1</v>
       </c>
-      <c r="D239" s="11">
+      <c r="D239" s="10">
         <v>1</v>
       </c>
       <c r="E239" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="240" spans="1:5">
       <c r="A240" s="3" t="s">
         <v>2007</v>
       </c>
-      <c r="B240" s="9">
+      <c r="B240" s="8">
         <v>26653</v>
       </c>
-      <c r="C240" s="9">
+      <c r="C240" s="8">
         <v>1</v>
       </c>
-      <c r="D240" s="9">
+      <c r="D240" s="8">
         <v>1</v>
       </c>
       <c r="E240" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="241" spans="1:5">
       <c r="A241" s="5" t="s">
         <v>2024</v>
       </c>
-      <c r="B241" s="11">
+      <c r="B241" s="10">
         <v>1194</v>
       </c>
-      <c r="C241" s="11">
+      <c r="C241" s="10">
         <v>1</v>
       </c>
-      <c r="D241" s="11">
+      <c r="D241" s="10">
         <v>1</v>
       </c>
       <c r="E241" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="242" spans="1:5">
       <c r="A242" s="3" t="s">
         <v>2072</v>
       </c>
-      <c r="B242" s="9">
+      <c r="B242" s="8">
         <v>31457</v>
       </c>
-      <c r="C242" s="9">
+      <c r="C242" s="8">
         <v>1</v>
       </c>
-      <c r="D242" s="9">
+      <c r="D242" s="8">
         <v>1</v>
       </c>
       <c r="E242" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="243" spans="1:5">
       <c r="A243" s="5" t="s">
         <v>2084</v>
       </c>
-      <c r="B243" s="11">
+      <c r="B243" s="10">
         <v>6756</v>
       </c>
-      <c r="C243" s="11">
+      <c r="C243" s="10">
         <v>1</v>
       </c>
-      <c r="D243" s="11">
+      <c r="D243" s="10">
         <v>1</v>
       </c>
       <c r="E243" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="244" spans="1:5">
       <c r="A244" s="3" t="s">
         <v>2091</v>
       </c>
-      <c r="B244" s="9">
+      <c r="B244" s="8">
         <v>18683</v>
       </c>
-      <c r="C244" s="9">
+      <c r="C244" s="8">
         <v>1</v>
       </c>
-      <c r="D244" s="9">
+      <c r="D244" s="8">
         <v>1</v>
       </c>
       <c r="E244" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="245" spans="1:5">
       <c r="A245" s="5" t="s">
         <v>2223</v>
       </c>
-      <c r="B245" s="11">
+      <c r="B245" s="10">
         <v>4911</v>
       </c>
-      <c r="C245" s="11">
+      <c r="C245" s="10">
         <v>1</v>
       </c>
-      <c r="D245" s="11">
+      <c r="D245" s="10">
         <v>1</v>
       </c>
       <c r="E245" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="246" spans="1:5">
       <c r="A246" s="3" t="s">
         <v>2264</v>
       </c>
-      <c r="B246" s="9">
+      <c r="B246" s="8">
         <v>14124</v>
       </c>
-      <c r="C246" s="9">
+      <c r="C246" s="8">
         <v>1</v>
       </c>
-      <c r="D246" s="9">
+      <c r="D246" s="8">
         <v>1</v>
       </c>
       <c r="E246" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
     <row r="247" spans="1:5">
       <c r="A247" s="5" t="s">
         <v>2367</v>
       </c>
-      <c r="B247" s="11">
+      <c r="B247" s="10">
         <v>9985</v>
       </c>
-      <c r="C247" s="11">
+      <c r="C247" s="10">
         <v>1</v>
       </c>
-      <c r="D247" s="11">
+      <c r="D247" s="10">
         <v>2</v>
       </c>
       <c r="E247" s="5" t="s">
-        <v>2974</v>
+        <v>2972</v>
       </c>
     </row>
   </sheetData>

--- a/skipperplan.xlsx
+++ b/skipperplan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23819" uniqueCount="2952">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23814" uniqueCount="2951">
   <si>
     <t>Startdatum</t>
   </si>
@@ -2148,7 +2148,7 @@
     <t>15158</t>
   </si>
   <si>
-    <t>Tom O, Jan H, Max S, Korbinian R, Sven-Bjarne S, Mareike W</t>
+    <t>Tom O, Jan H, Korbinian R, Sven-Bjarne S, Mareike W</t>
   </si>
   <si>
     <t>15159</t>
@@ -2757,7 +2757,7 @@
     <t>15733</t>
   </si>
   <si>
-    <t>Malte K, Lerina O, Martin W, Volker N, Miriam M, Philipp K</t>
+    <t>Malte K, Lerina O, Martin W, Volker N, Miriam M</t>
   </si>
   <si>
     <t>Maximilian P</t>
@@ -4299,7 +4299,7 @@
     <t>15751</t>
   </si>
   <si>
-    <t>Nils K, Lukas F, Martin W, Matthias S, Ruwen Q, Andre E, Malte K</t>
+    <t>Nils K, Lukas F, Martin W, Matthias S, Ruwen Q, Andre E, Malte K, Christoph C</t>
   </si>
   <si>
     <t>15752</t>
@@ -8854,9 +8854,6 @@
   </si>
   <si>
     <t>Neue Bewerbungen</t>
-  </si>
-  <si>
-    <t>Neues Boot</t>
   </si>
   <si>
     <t>Neue Bewerbung(en)</t>
@@ -8916,7 +8913,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8961,12 +8958,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2EFDA"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -9005,7 +8996,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -9028,19 +9019,16 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9712,7 +9700,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G5" s="5" t="s">
         <v>72</v>
@@ -9792,7 +9780,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G6" s="3" t="s">
         <v>79</v>
@@ -10754,7 +10742,7 @@
         <v>9</v>
       </c>
       <c r="J18" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K18" s="3" t="s">
         <v>34</v>
@@ -10992,7 +10980,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K21" s="5" t="s">
         <v>34</v>
@@ -12406,7 +12394,7 @@
         <v>8</v>
       </c>
       <c r="J39" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K39" s="5" t="s">
         <v>34</v>
@@ -13578,7 +13566,7 @@
         <v>7</v>
       </c>
       <c r="J54" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" s="3" t="s">
         <v>34</v>
@@ -14050,7 +14038,7 @@
         <v>8</v>
       </c>
       <c r="J60" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K60" s="3" t="s">
         <v>34</v>
@@ -14366,7 +14354,7 @@
         <v>9</v>
       </c>
       <c r="J64" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>34</v>
@@ -14602,7 +14590,7 @@
         <v>8</v>
       </c>
       <c r="J67" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K67" s="7" t="s">
         <v>34</v>
@@ -14758,7 +14746,7 @@
         <v>8</v>
       </c>
       <c r="J69" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K69" s="5" t="s">
         <v>34</v>
@@ -14836,7 +14824,7 @@
         <v>7</v>
       </c>
       <c r="J70" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K70" s="3" t="s">
         <v>34</v>
@@ -16182,7 +16170,7 @@
         <v>9</v>
       </c>
       <c r="J87" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K87" s="5" t="s">
         <v>34</v>
@@ -16734,7 +16722,7 @@
         <v>8</v>
       </c>
       <c r="J94" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>34</v>
@@ -18152,7 +18140,7 @@
         <v>8</v>
       </c>
       <c r="J112" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>34</v>
@@ -18308,7 +18296,7 @@
         <v>7</v>
       </c>
       <c r="J114" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K114" s="3" t="s">
         <v>34</v>
@@ -19256,7 +19244,7 @@
         <v>10</v>
       </c>
       <c r="J126" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K126" s="3" t="s">
         <v>34</v>
@@ -19968,7 +19956,7 @@
         <v>8</v>
       </c>
       <c r="J135" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K135" s="5" t="s">
         <v>34</v>
@@ -20348,7 +20336,7 @@
         <v>30</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G140" s="3" t="s">
         <v>350</v>
@@ -20428,7 +20416,7 @@
         <v>30</v>
       </c>
       <c r="F141" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G141" s="5" t="s">
         <v>682</v>
@@ -20506,7 +20494,7 @@
         <v>30</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G142" s="3" t="s">
         <v>685</v>
@@ -20584,7 +20572,7 @@
         <v>30</v>
       </c>
       <c r="F143" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G143" s="5" t="s">
         <v>533</v>
@@ -20662,7 +20650,7 @@
         <v>30</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G144" s="3" t="s">
         <v>529</v>
@@ -20740,7 +20728,7 @@
         <v>30</v>
       </c>
       <c r="F145" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G145" s="5" t="s">
         <v>140</v>
@@ -22308,7 +22296,7 @@
         <v>30</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G165" s="5" t="s">
         <v>614</v>
@@ -22388,7 +22376,7 @@
         <v>30</v>
       </c>
       <c r="F166" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G166" s="6" t="s">
         <v>745</v>
@@ -22466,7 +22454,7 @@
         <v>30</v>
       </c>
       <c r="F167" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G167" s="5" t="s">
         <v>748</v>
@@ -23426,7 +23414,7 @@
         <v>10</v>
       </c>
       <c r="J179" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K179" s="5" t="s">
         <v>34</v>
@@ -23782,7 +23770,7 @@
         <v>45</v>
       </c>
       <c r="X183" s="5" t="s">
-        <v>690</v>
+        <v>45</v>
       </c>
       <c r="Y183" s="5" t="s">
         <v>47</v>
@@ -24026,82 +24014,82 @@
       </c>
     </row>
     <row r="187" spans="1:26">
-      <c r="A187" s="6" t="s">
+      <c r="A187" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B187" s="6" t="s">
+      <c r="B187" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="C187" s="6" t="s">
+      <c r="C187" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D187" s="6" t="s">
+      <c r="D187" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E187" s="6" t="s">
+      <c r="E187" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F187" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G187" s="6" t="s">
+      <c r="F187" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G187" s="7" t="s">
         <v>809</v>
       </c>
-      <c r="H187" s="6" t="s">
+      <c r="H187" s="7" t="s">
         <v>810</v>
       </c>
-      <c r="I187" s="6">
+      <c r="I187" s="7">
         <v>8</v>
       </c>
-      <c r="J187" s="6">
-        <v>0</v>
-      </c>
-      <c r="K187" s="6" t="s">
+      <c r="J187" s="7">
+        <v>1</v>
+      </c>
+      <c r="K187" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L187" s="6" t="s">
+      <c r="L187" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="M187" s="6" t="s">
+      <c r="M187" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="N187" s="6" t="s">
+      <c r="N187" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="O187" s="6" t="s">
+      <c r="O187" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="P187" s="6" t="s">
+      <c r="P187" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="Q187" s="6" t="s">
+      <c r="Q187" s="7" t="s">
         <v>807</v>
       </c>
-      <c r="R187" s="6" t="s">
+      <c r="R187" s="7" t="s">
         <v>811</v>
       </c>
-      <c r="S187" s="6" t="s">
+      <c r="S187" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="T187" s="6" t="s">
+      <c r="T187" s="7" t="s">
         <v>812</v>
       </c>
-      <c r="U187" s="6" t="s">
+      <c r="U187" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V187" s="6">
+      <c r="V187" s="7">
         <v>2018</v>
       </c>
-      <c r="W187" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="X187" s="6" t="s">
+      <c r="W187" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X187" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="Y187" s="6" t="s">
+      <c r="Y187" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="Z187" s="6"/>
+      <c r="Z187" s="7"/>
     </row>
     <row r="188" spans="1:26">
       <c r="A188" s="3" t="s">
@@ -24262,82 +24250,82 @@
       <c r="Z189" s="5"/>
     </row>
     <row r="190" spans="1:26">
-      <c r="A190" s="6" t="s">
+      <c r="A190" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="B190" s="6" t="s">
+      <c r="B190" s="7" t="s">
         <v>577</v>
       </c>
-      <c r="C190" s="6" t="s">
+      <c r="C190" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D190" s="6" t="s">
+      <c r="D190" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E190" s="6" t="s">
+      <c r="E190" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F190" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G190" s="6" t="s">
+      <c r="F190" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G190" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="H190" s="6" t="s">
+      <c r="H190" s="7" t="s">
         <v>413</v>
       </c>
-      <c r="I190" s="6">
+      <c r="I190" s="7">
         <v>8</v>
       </c>
-      <c r="J190" s="6">
-        <v>0</v>
-      </c>
-      <c r="K190" s="6" t="s">
+      <c r="J190" s="7">
+        <v>1</v>
+      </c>
+      <c r="K190" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L190" s="6" t="s">
+      <c r="L190" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="M190" s="6" t="s">
+      <c r="M190" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="N190" s="6" t="s">
+      <c r="N190" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="O190" s="6" t="s">
+      <c r="O190" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P190" s="6" t="s">
+      <c r="P190" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="Q190" s="6" t="s">
+      <c r="Q190" s="7" t="s">
         <v>813</v>
       </c>
-      <c r="R190" s="6" t="s">
+      <c r="R190" s="7" t="s">
         <v>817</v>
       </c>
-      <c r="S190" s="6" t="s">
+      <c r="S190" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="T190" s="6" t="s">
+      <c r="T190" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="U190" s="6" t="s">
+      <c r="U190" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V190" s="6">
+      <c r="V190" s="7">
         <v>2015</v>
       </c>
-      <c r="W190" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="X190" s="6" t="s">
+      <c r="W190" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X190" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="Y190" s="6" t="s">
+      <c r="Y190" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="Z190" s="6"/>
+      <c r="Z190" s="7"/>
     </row>
     <row r="191" spans="1:26">
       <c r="A191" s="6" t="s">
@@ -25152,7 +25140,7 @@
         <v>9</v>
       </c>
       <c r="J201" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K201" s="5" t="s">
         <v>34</v>
@@ -26562,7 +26550,7 @@
         <v>30</v>
       </c>
       <c r="F219" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G219" s="5" t="s">
         <v>79</v>
@@ -26642,7 +26630,7 @@
         <v>30</v>
       </c>
       <c r="F220" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G220" s="6" t="s">
         <v>897</v>
@@ -27718,7 +27706,7 @@
         <v>45</v>
       </c>
       <c r="X233" s="5" t="s">
-        <v>690</v>
+        <v>45</v>
       </c>
       <c r="Y233" s="5" t="s">
         <v>47</v>
@@ -28212,7 +28200,7 @@
         <v>30</v>
       </c>
       <c r="F240" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G240" s="3" t="s">
         <v>150</v>
@@ -28292,7 +28280,7 @@
         <v>30</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G241" s="4" t="s">
         <v>954</v>
@@ -32228,7 +32216,7 @@
         <v>9</v>
       </c>
       <c r="J291" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K291" s="5" t="s">
         <v>34</v>
@@ -32386,7 +32374,7 @@
         <v>8</v>
       </c>
       <c r="J293" s="5">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K293" s="5" t="s">
         <v>34</v>
@@ -34882,7 +34870,7 @@
         <v>30</v>
       </c>
       <c r="F325" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G325" s="5" t="s">
         <v>590</v>
@@ -34962,7 +34950,7 @@
         <v>30</v>
       </c>
       <c r="F326" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G326" s="3" t="s">
         <v>745</v>
@@ -35040,7 +35028,7 @@
         <v>30</v>
       </c>
       <c r="F327" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G327" s="6" t="s">
         <v>239</v>
@@ -35118,7 +35106,7 @@
         <v>30</v>
       </c>
       <c r="F328" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G328" s="6" t="s">
         <v>1168</v>
@@ -35196,7 +35184,7 @@
         <v>30</v>
       </c>
       <c r="F329" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G329" s="5" t="s">
         <v>140</v>
@@ -35274,7 +35262,7 @@
         <v>30</v>
       </c>
       <c r="F330" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G330" s="3" t="s">
         <v>1173</v>
@@ -35352,7 +35340,7 @@
         <v>30</v>
       </c>
       <c r="F331" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G331" s="5" t="s">
         <v>757</v>
@@ -37240,7 +37228,7 @@
         <v>8</v>
       </c>
       <c r="J355" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K355" s="5" t="s">
         <v>34</v>
@@ -38896,7 +38884,7 @@
         <v>8</v>
       </c>
       <c r="J376" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K376" s="3" t="s">
         <v>34</v>
@@ -40774,7 +40762,7 @@
         <v>8</v>
       </c>
       <c r="J400" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K400" s="3" t="s">
         <v>34</v>
@@ -41012,7 +41000,7 @@
         <v>8</v>
       </c>
       <c r="J403" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K403" s="5" t="s">
         <v>34</v>
@@ -42356,7 +42344,7 @@
         <v>9</v>
       </c>
       <c r="J420" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K420" s="3" t="s">
         <v>34</v>
@@ -44068,7 +44056,7 @@
         <v>30</v>
       </c>
       <c r="F442" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>564</v>
@@ -44148,7 +44136,7 @@
         <v>30</v>
       </c>
       <c r="F443" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G443" s="5" t="s">
         <v>1197</v>
@@ -44226,7 +44214,7 @@
         <v>30</v>
       </c>
       <c r="F444" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G444" s="3" t="s">
         <v>1329</v>
@@ -44304,7 +44292,7 @@
         <v>30</v>
       </c>
       <c r="F445" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G445" s="6" t="s">
         <v>1454</v>
@@ -44382,7 +44370,7 @@
         <v>30</v>
       </c>
       <c r="F446" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G446" s="3" t="s">
         <v>1307</v>
@@ -44460,7 +44448,7 @@
         <v>30</v>
       </c>
       <c r="F447" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G447" s="5" t="s">
         <v>1336</v>
@@ -44538,7 +44526,7 @@
         <v>30</v>
       </c>
       <c r="F448" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G448" s="3" t="s">
         <v>296</v>
@@ -46044,7 +46032,7 @@
         <v>10</v>
       </c>
       <c r="J467" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K467" s="5" t="s">
         <v>34</v>
@@ -46752,7 +46740,7 @@
         <v>8</v>
       </c>
       <c r="J476" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K476" s="3" t="s">
         <v>34</v>
@@ -46976,7 +46964,7 @@
         <v>30</v>
       </c>
       <c r="F479" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G479" s="5" t="s">
         <v>72</v>
@@ -47056,7 +47044,7 @@
         <v>30</v>
       </c>
       <c r="F480" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G480" s="6" t="s">
         <v>1538</v>
@@ -47134,7 +47122,7 @@
         <v>30</v>
       </c>
       <c r="F481" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G481" s="6" t="s">
         <v>1541</v>
@@ -47212,7 +47200,7 @@
         <v>30</v>
       </c>
       <c r="F482" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G482" s="6" t="s">
         <v>954</v>
@@ -47288,7 +47276,7 @@
         <v>30</v>
       </c>
       <c r="F483" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G483" s="5" t="s">
         <v>451</v>
@@ -47366,7 +47354,7 @@
         <v>30</v>
       </c>
       <c r="F484" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G484" s="3" t="s">
         <v>366</v>
@@ -48478,7 +48466,7 @@
         <v>8</v>
       </c>
       <c r="J498" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K498" s="3" t="s">
         <v>34</v>
@@ -50444,7 +50432,7 @@
         <v>10</v>
       </c>
       <c r="J523" s="5">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K523" s="5" t="s">
         <v>34</v>
@@ -51122,82 +51110,82 @@
       <c r="Z531" s="5"/>
     </row>
     <row r="532" spans="1:26">
-      <c r="A532" s="6" t="s">
+      <c r="A532" s="7" t="s">
         <v>1363</v>
       </c>
-      <c r="B532" s="6" t="s">
+      <c r="B532" s="7" t="s">
         <v>1580</v>
       </c>
-      <c r="C532" s="6" t="s">
+      <c r="C532" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="D532" s="6" t="s">
+      <c r="D532" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E532" s="6" t="s">
+      <c r="E532" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F532" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G532" s="6" t="s">
+      <c r="F532" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G532" s="7" t="s">
         <v>1559</v>
       </c>
-      <c r="H532" s="6" t="s">
+      <c r="H532" s="7" t="s">
         <v>1560</v>
       </c>
-      <c r="I532" s="6">
+      <c r="I532" s="7">
         <v>10</v>
       </c>
-      <c r="J532" s="6">
-        <v>0</v>
-      </c>
-      <c r="K532" s="6" t="s">
+      <c r="J532" s="7">
+        <v>2</v>
+      </c>
+      <c r="K532" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L532" s="6" t="s">
+      <c r="L532" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="M532" s="6" t="s">
+      <c r="M532" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="N532" s="6" t="s">
+      <c r="N532" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="O532" s="6" t="s">
+      <c r="O532" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P532" s="6" t="s">
+      <c r="P532" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="Q532" s="6" t="s">
+      <c r="Q532" s="7" t="s">
         <v>1665</v>
       </c>
-      <c r="R532" s="6" t="s">
+      <c r="R532" s="7" t="s">
         <v>1669</v>
       </c>
-      <c r="S532" s="6" t="s">
+      <c r="S532" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="T532" s="6" t="s">
+      <c r="T532" s="7" t="s">
         <v>1440</v>
       </c>
-      <c r="U532" s="6" t="s">
+      <c r="U532" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V532" s="6">
+      <c r="V532" s="7">
         <v>2013</v>
       </c>
-      <c r="W532" s="6" t="s">
-        <v>594</v>
-      </c>
-      <c r="X532" s="6" t="s">
+      <c r="W532" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X532" s="7" t="s">
         <v>433</v>
       </c>
-      <c r="Y532" s="6" t="s">
+      <c r="Y532" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="Z532" s="6"/>
+      <c r="Z532" s="7"/>
     </row>
     <row r="533" spans="1:26">
       <c r="A533" s="6" t="s">
@@ -51856,7 +51844,7 @@
         <v>9</v>
       </c>
       <c r="J541" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K541" s="7" t="s">
         <v>34</v>
@@ -52326,7 +52314,7 @@
         <v>6</v>
       </c>
       <c r="J547" s="4">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K547" s="4" t="s">
         <v>34</v>
@@ -52536,82 +52524,82 @@
       </c>
     </row>
     <row r="550" spans="1:26">
-      <c r="A550" s="7" t="s">
+      <c r="A550" s="3" t="s">
         <v>1580</v>
       </c>
-      <c r="B550" s="7" t="s">
+      <c r="B550" s="3" t="s">
         <v>1677</v>
       </c>
-      <c r="C550" s="7" t="s">
+      <c r="C550" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D550" s="7" t="s">
+      <c r="D550" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E550" s="7" t="s">
+      <c r="E550" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F550" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G550" s="7" t="s">
+      <c r="F550" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G550" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="H550" s="7" t="s">
+      <c r="H550" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="I550" s="7">
+      <c r="I550" s="3">
         <v>8</v>
       </c>
-      <c r="J550" s="7">
+      <c r="J550" s="3">
         <v>6</v>
       </c>
-      <c r="K550" s="7" t="s">
+      <c r="K550" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L550" s="7" t="s">
+      <c r="L550" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="M550" s="7" t="s">
+      <c r="M550" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="N550" s="7" t="s">
+      <c r="N550" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O550" s="7" t="s">
+      <c r="O550" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="P550" s="7" t="s">
+      <c r="P550" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="Q550" s="7" t="s">
+      <c r="Q550" s="3" t="s">
         <v>1711</v>
       </c>
-      <c r="R550" s="7" t="s">
+      <c r="R550" s="3" t="s">
         <v>1714</v>
       </c>
-      <c r="S550" s="7" t="s">
+      <c r="S550" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="T550" s="7" t="s">
+      <c r="T550" s="3" t="s">
         <v>1715</v>
       </c>
-      <c r="U550" s="7" t="s">
+      <c r="U550" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V550" s="7">
+      <c r="V550" s="3">
         <v>2019</v>
       </c>
-      <c r="W550" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X550" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="Y550" s="7" t="s">
+      <c r="W550" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X550" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y550" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="Z550" s="7"/>
+      <c r="Z550" s="3"/>
     </row>
     <row r="551" spans="1:26">
       <c r="A551" s="5" t="s">
@@ -52710,7 +52698,7 @@
         <v>30</v>
       </c>
       <c r="F552" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G552" s="3" t="s">
         <v>1719</v>
@@ -52790,7 +52778,7 @@
         <v>30</v>
       </c>
       <c r="F553" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G553" s="5" t="s">
         <v>382</v>
@@ -52868,7 +52856,7 @@
         <v>30</v>
       </c>
       <c r="F554" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G554" s="6" t="s">
         <v>1329</v>
@@ -52946,7 +52934,7 @@
         <v>30</v>
       </c>
       <c r="F555" s="5" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G555" s="5" t="s">
         <v>595</v>
@@ -56488,7 +56476,7 @@
         <v>8</v>
       </c>
       <c r="J600" s="3">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K600" s="3" t="s">
         <v>34</v>
@@ -57270,7 +57258,7 @@
         <v>6</v>
       </c>
       <c r="J610" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K610" s="7" t="s">
         <v>34</v>
@@ -57888,7 +57876,7 @@
         <v>30</v>
       </c>
       <c r="F618" s="3" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G618" s="3" t="s">
         <v>635</v>
@@ -57968,7 +57956,7 @@
         <v>30</v>
       </c>
       <c r="F619" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G619" s="6" t="s">
         <v>991</v>
@@ -58046,7 +58034,7 @@
         <v>30</v>
       </c>
       <c r="F620" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G620" s="6" t="s">
         <v>1865</v>
@@ -58124,7 +58112,7 @@
         <v>30</v>
       </c>
       <c r="F621" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G621" s="6" t="s">
         <v>1197</v>
@@ -58256,7 +58244,7 @@
         <v>45</v>
       </c>
       <c r="X622" s="3" t="s">
-        <v>855</v>
+        <v>1774</v>
       </c>
       <c r="Y622" s="3" t="s">
         <v>47</v>
@@ -58606,7 +58594,7 @@
         <v>8</v>
       </c>
       <c r="J627" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K627" s="5" t="s">
         <v>1757</v>
@@ -59540,7 +59528,7 @@
         <v>30</v>
       </c>
       <c r="F639" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G639" s="6" t="s">
         <v>635</v>
@@ -59620,7 +59608,7 @@
         <v>30</v>
       </c>
       <c r="F640" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G640" s="6" t="s">
         <v>1255</v>
@@ -59698,7 +59686,7 @@
         <v>30</v>
       </c>
       <c r="F641" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G641" s="6" t="s">
         <v>204</v>
@@ -59776,7 +59764,7 @@
         <v>30</v>
       </c>
       <c r="F642" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G642" s="6" t="s">
         <v>322</v>
@@ -59854,7 +59842,7 @@
         <v>30</v>
       </c>
       <c r="F643" s="6" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G643" s="6" t="s">
         <v>954</v>
@@ -61650,7 +61638,7 @@
         <v>8</v>
       </c>
       <c r="J666" s="4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K666" s="4" t="s">
         <v>1757</v>
@@ -61872,7 +61860,7 @@
         <v>1358</v>
       </c>
       <c r="F669" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G669" s="4" t="s">
         <v>954</v>
@@ -61960,7 +61948,7 @@
         <v>12</v>
       </c>
       <c r="J670" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K670" s="4" t="s">
         <v>1757</v>
@@ -63886,7 +63874,7 @@
         <v>8</v>
       </c>
       <c r="J695" s="4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K695" s="4" t="s">
         <v>34</v>
@@ -64030,7 +64018,7 @@
         <v>121</v>
       </c>
       <c r="F697" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G697" s="4" t="s">
         <v>954</v>
@@ -64108,7 +64096,7 @@
         <v>121</v>
       </c>
       <c r="F698" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G698" s="4" t="s">
         <v>954</v>
@@ -64184,7 +64172,7 @@
         <v>121</v>
       </c>
       <c r="F699" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G699" s="4" t="s">
         <v>954</v>
@@ -65184,7 +65172,7 @@
         <v>1358</v>
       </c>
       <c r="F712" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G712" s="4" t="s">
         <v>954</v>
@@ -65194,7 +65182,7 @@
         <v>8</v>
       </c>
       <c r="J712" s="4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K712" s="4" t="s">
         <v>1757</v>
@@ -65262,7 +65250,7 @@
         <v>1358</v>
       </c>
       <c r="F713" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G713" s="4" t="s">
         <v>954</v>
@@ -65338,7 +65326,7 @@
         <v>1358</v>
       </c>
       <c r="F714" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G714" s="4" t="s">
         <v>954</v>
@@ -66804,7 +66792,7 @@
         <v>121</v>
       </c>
       <c r="F733" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G733" s="4" t="s">
         <v>954</v>
@@ -66882,7 +66870,7 @@
         <v>121</v>
       </c>
       <c r="F734" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G734" s="4" t="s">
         <v>954</v>
@@ -66958,7 +66946,7 @@
         <v>121</v>
       </c>
       <c r="F735" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G735" s="4" t="s">
         <v>954</v>
@@ -68652,7 +68640,7 @@
         <v>1358</v>
       </c>
       <c r="F757" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G757" s="4" t="s">
         <v>954</v>
@@ -68730,7 +68718,7 @@
         <v>1358</v>
       </c>
       <c r="F758" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G758" s="4" t="s">
         <v>954</v>
@@ -68806,7 +68794,7 @@
         <v>1358</v>
       </c>
       <c r="F759" s="4" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="G759" s="4" t="s">
         <v>954</v>
@@ -71822,7 +71810,7 @@
         <v>8</v>
       </c>
       <c r="J798" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K798" s="4" t="s">
         <v>1757</v>
@@ -91673,7 +91661,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -91715,49 +91703,28 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="3" t="s">
         <v>2943</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="3" t="s">
         <v>1074</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="3" t="s">
         <v>1346</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>1096</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>1437</v>
-      </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
-        <v>2944</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2047</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>2235</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>2283</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
-        <v>791</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
-        <v>758</v>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>1420</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>2576</v>
       </c>
     </row>
   </sheetData>
@@ -91783,3892 +91750,3892 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2944</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2945</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2946</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>2947</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2948</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>31914</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>11</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>11</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>2949</v>
+      <c r="E2" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>13707</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>11</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>13</v>
       </c>
-      <c r="E3" s="12" t="s">
-        <v>2950</v>
+      <c r="E3" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>26133</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>11</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>11</v>
       </c>
-      <c r="E4" s="10" t="s">
-        <v>2949</v>
+      <c r="E4" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>2430</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>10</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>10</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>2950</v>
+      <c r="E5" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>28325</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>10</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>10</v>
       </c>
-      <c r="E6" s="12" t="s">
-        <v>2950</v>
+      <c r="E6" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>27191</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>10</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>12</v>
       </c>
-      <c r="E7" s="10" t="s">
-        <v>2949</v>
+      <c r="E7" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>26767</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>10</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>11</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>2949</v>
+      <c r="E8" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>38249</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>10</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>10</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>2949</v>
+      <c r="E9" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>951</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>10</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>10</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>2950</v>
+      <c r="E10" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <v>15339</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>9</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>9</v>
       </c>
-      <c r="E11" s="10" t="s">
-        <v>2949</v>
+      <c r="E11" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>17056</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>8</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>10</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>2949</v>
+      <c r="E12" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
         <v>386</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>27366</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>8</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>8</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>2949</v>
+      <c r="E13" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>13035</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>8</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>8</v>
       </c>
-      <c r="E14" s="12" t="s">
-        <v>2950</v>
+      <c r="E14" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <v>6429</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>8</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <v>8</v>
       </c>
-      <c r="E15" s="12" t="s">
-        <v>2950</v>
+      <c r="E15" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <v>17277</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>7</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>9</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>2950</v>
+      <c r="E16" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <v>25583</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>7</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <v>7</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>2949</v>
+      <c r="E17" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="8">
         <v>13045</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="8">
         <v>7</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>7</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>2949</v>
+      <c r="E18" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>25998</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>7</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <v>7</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>2949</v>
+      <c r="E19" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
         <v>823</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="8">
         <v>7022</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>7</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>8</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>2950</v>
+      <c r="E20" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
         <v>933</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <v>20147</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>7</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <v>9</v>
       </c>
-      <c r="E21" s="12" t="s">
-        <v>2950</v>
+      <c r="E21" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="8">
         <v>10468</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <v>6</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>6</v>
       </c>
-      <c r="E22" s="10" t="s">
-        <v>2949</v>
+      <c r="E22" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
         <v>322</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>13834</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>6</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <v>6</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>2949</v>
+      <c r="E23" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="8">
         <v>38991</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="8">
         <v>6</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>6</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>2949</v>
+      <c r="E24" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
         <v>1197</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>9630</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>6</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <v>6</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>2949</v>
+      <c r="E25" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="8">
         <v>14023</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="8">
         <v>5</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <v>5</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>38409</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <v>5</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <v>5</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="8">
         <v>15492</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="8">
         <v>5</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>5</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="10">
         <v>10463</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <v>5</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <v>5</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="8">
         <v>14767</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="8">
         <v>5</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="8">
         <v>6</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
         <v>366</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="10">
         <v>19891</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="10">
         <v>5</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <v>5</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="8">
         <v>27342</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <v>5</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>5</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="10">
         <v>28683</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>5</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <v>6</v>
       </c>
-      <c r="E33" s="10" t="s">
-        <v>2949</v>
+      <c r="E33" s="9" t="s">
+        <v>2948</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="8">
         <v>17321</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="8">
         <v>5</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="8">
         <v>5</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="10">
         <v>21701</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>5</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <v>5</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="8">
         <v>12024</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="8">
         <v>5</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>5</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="10">
         <v>37857</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>5</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <v>5</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
         <v>779</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="8">
         <v>22825</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="8">
         <v>5</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>5</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="10">
         <v>9724</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <v>4</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <v>6</v>
       </c>
-      <c r="E39" s="12" t="s">
-        <v>2950</v>
+      <c r="E39" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="8">
         <v>27634</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="8">
         <v>4</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <v>4</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="10">
         <v>27871</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="10">
         <v>4</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="10">
         <v>4</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="8">
         <v>20741</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="8">
         <v>4</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <v>4</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <v>40896</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <v>4</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <v>4</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="8">
         <v>22942</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="8">
         <v>4</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="8">
         <v>5</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="10">
         <v>33600</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <v>4</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <v>4</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="8">
         <v>20625</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="8">
         <v>4</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="8">
         <v>4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <v>38535</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <v>4</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <v>4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="8">
         <v>24701</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="8">
         <v>4</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="8">
         <v>4</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <v>21510</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="10">
         <v>4</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="10">
         <v>4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
         <v>745</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="8">
         <v>31118</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="8">
         <v>4</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="8">
         <v>4</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
         <v>774</v>
       </c>
-      <c r="B51" s="11">
+      <c r="B51" s="10">
         <v>16666</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="10">
         <v>4</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="10">
         <v>4</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
         <v>832</v>
       </c>
-      <c r="B52" s="9">
+      <c r="B52" s="8">
         <v>9849</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="8">
         <v>4</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <v>4</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
         <v>903</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="10">
         <v>27428</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="10">
         <v>4</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <v>4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
         <v>985</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="8">
         <v>6758</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="8">
         <v>4</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="8">
         <v>6</v>
       </c>
-      <c r="E54" s="12" t="s">
-        <v>2950</v>
+      <c r="E54" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
         <v>1329</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="10">
         <v>23628</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="10">
         <v>4</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="10">
         <v>4</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
         <v>1307</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="8">
         <v>14111</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="8">
         <v>4</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="8">
         <v>4</v>
       </c>
-      <c r="E56" s="12" t="s">
-        <v>2950</v>
+      <c r="E56" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="B57" s="11">
+      <c r="B57" s="10">
         <v>20508</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="10">
         <v>3</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="10">
         <v>3</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="8">
         <v>3853</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="8">
         <v>3</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="8">
         <v>3</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
         <v>233</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="10">
         <v>16471</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="10">
         <v>3</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="10">
         <v>3</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="8">
         <v>30709</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="8">
         <v>3</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="8">
         <v>3</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="10">
         <v>27408</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="10">
         <v>3</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="10">
         <v>3</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="8">
         <v>27712</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="8">
         <v>3</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="8">
         <v>3</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="10">
         <v>27030</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="10">
         <v>3</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="10">
         <v>3</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="8">
         <v>34963</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64" s="8">
         <v>3</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="8">
         <v>3</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
         <v>358</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="10">
         <v>12507</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <v>3</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="10">
         <v>3</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="8">
         <v>11105</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="8">
         <v>3</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="8">
         <v>3</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
         <v>399</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="10">
         <v>5443</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="10">
         <v>3</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="10">
         <v>3</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="8">
         <v>16563</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="8">
         <v>3</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="8">
         <v>3</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="10">
         <v>38191</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="10">
         <v>3</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="10">
         <v>3</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="8">
         <v>39495</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70" s="8">
         <v>3</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="8">
         <v>3</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
         <v>502</v>
       </c>
-      <c r="B71" s="11">
+      <c r="B71" s="10">
         <v>7436</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="10">
         <v>3</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="10">
         <v>3</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="8">
         <v>27838</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C72" s="8">
         <v>3</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="8">
         <v>3</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="10">
         <v>5688</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="10">
         <v>3</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="10">
         <v>3</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="8">
         <v>23061</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="8">
         <v>3</v>
       </c>
-      <c r="D74" s="9">
+      <c r="D74" s="8">
         <v>3</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
         <v>652</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="10">
         <v>31391</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="10">
         <v>3</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="10">
         <v>3</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
         <v>673</v>
       </c>
-      <c r="B76" s="9">
+      <c r="B76" s="8">
         <v>14252</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="8">
         <v>3</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="8">
         <v>3</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
         <v>709</v>
       </c>
-      <c r="B77" s="11">
+      <c r="B77" s="10">
         <v>3641</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="10">
         <v>3</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="10">
         <v>3</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
         <v>802</v>
       </c>
-      <c r="B78" s="9">
+      <c r="B78" s="8">
         <v>5331</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="8">
         <v>3</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="8">
         <v>3</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
         <v>836</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="10">
         <v>31002</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="10">
         <v>3</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="10">
         <v>3</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="8">
         <v>6773</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="8">
         <v>3</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="8">
         <v>3</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
         <v>939</v>
       </c>
-      <c r="B81" s="11">
+      <c r="B81" s="10">
         <v>3163</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="10">
         <v>3</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="10">
         <v>3</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
         <v>1035</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="8">
         <v>51060</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="8">
         <v>3</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="8">
         <v>3</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
         <v>1108</v>
       </c>
-      <c r="B83" s="11">
+      <c r="B83" s="10">
         <v>18695</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <v>3</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="10">
         <v>3</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="3" t="s">
         <v>1153</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="8">
         <v>17859</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="8">
         <v>3</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="8">
         <v>3</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
         <v>1156</v>
       </c>
-      <c r="B85" s="11">
+      <c r="B85" s="10">
         <v>26972</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="10">
         <v>3</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="10">
         <v>3</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="3" t="s">
         <v>1235</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="8">
         <v>26443</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="8">
         <v>3</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="8">
         <v>4</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
         <v>1255</v>
       </c>
-      <c r="B87" s="11">
+      <c r="B87" s="10">
         <v>25974</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="10">
         <v>3</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="10">
         <v>3</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="3" t="s">
         <v>1454</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="8">
         <v>25299</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="8">
         <v>3</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="8">
         <v>3</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B89" s="11">
+      <c r="B89" s="10">
         <v>347</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="10">
         <v>2</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="10">
         <v>2</v>
       </c>
-      <c r="E89" s="12" t="s">
-        <v>2950</v>
+      <c r="E89" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="8">
         <v>17123</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="8">
         <v>2</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="8">
         <v>2</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B91" s="11">
+      <c r="B91" s="10">
         <v>20450</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <v>2</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="10">
         <v>2</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="8">
         <v>20038</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="8">
         <v>2</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="8">
         <v>2</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="B93" s="11">
+      <c r="B93" s="10">
         <v>19229</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="10">
         <v>2</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="10">
         <v>2</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="8">
         <v>40808</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="8">
         <v>2</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="8">
         <v>2</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="10">
         <v>29369</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="10">
         <v>2</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="10">
         <v>2</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B96" s="9">
+      <c r="B96" s="8">
         <v>19184</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="8">
         <v>2</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="8">
         <v>2</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
         <v>303</v>
       </c>
-      <c r="B97" s="11">
+      <c r="B97" s="10">
         <v>9736</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="10">
         <v>2</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="10">
         <v>2</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="8">
         <v>7195</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="8">
         <v>2</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="8">
         <v>2</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
         <v>362</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="10">
         <v>22163</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="10">
         <v>2</v>
       </c>
-      <c r="D99" s="11">
+      <c r="D99" s="10">
         <v>2</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="8">
         <v>4842</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="8">
         <v>2</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="8">
         <v>2</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
         <v>434</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="10">
         <v>3826</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <v>2</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="10">
         <v>2</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B102" s="9">
+      <c r="B102" s="8">
         <v>12209</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="8">
         <v>2</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="8">
         <v>2</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="B103" s="11">
+      <c r="B103" s="10">
         <v>9375</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="10">
         <v>2</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="10">
         <v>2</v>
       </c>
-      <c r="E103" s="12" t="s">
-        <v>2950</v>
+      <c r="E103" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B104" s="9">
+      <c r="B104" s="8">
         <v>33770</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="8">
         <v>2</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="8">
         <v>2</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="10">
         <v>23794</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <v>2</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="10">
         <v>2</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="B106" s="9">
+      <c r="B106" s="8">
         <v>7418</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="8">
         <v>2</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="8">
         <v>2</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="B107" s="11">
+      <c r="B107" s="10">
         <v>19127</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <v>2</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="10">
         <v>2</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="B108" s="9">
+      <c r="B108" s="8">
         <v>13592</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C108" s="8">
         <v>2</v>
       </c>
-      <c r="D108" s="9">
+      <c r="D108" s="8">
         <v>2</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="B109" s="11">
+      <c r="B109" s="10">
         <v>9265</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="10">
         <v>2</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="10">
         <v>3</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="B110" s="9">
+      <c r="B110" s="8">
         <v>18683</v>
       </c>
-      <c r="C110" s="9">
+      <c r="C110" s="8">
         <v>2</v>
       </c>
-      <c r="D110" s="9">
+      <c r="D110" s="8">
         <v>2</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="B111" s="11">
+      <c r="B111" s="10">
         <v>21130</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <v>2</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="10">
         <v>2</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="B112" s="9">
+      <c r="B112" s="8">
         <v>23188</v>
       </c>
-      <c r="C112" s="9">
+      <c r="C112" s="8">
         <v>2</v>
       </c>
-      <c r="D112" s="9">
+      <c r="D112" s="8">
         <v>2</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
         <v>631</v>
       </c>
-      <c r="B113" s="11">
+      <c r="B113" s="10">
         <v>21381</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="10">
         <v>2</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="10">
         <v>2</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="3" t="s">
         <v>685</v>
       </c>
-      <c r="B114" s="9">
+      <c r="B114" s="8">
         <v>21133</v>
       </c>
-      <c r="C114" s="9">
+      <c r="C114" s="8">
         <v>2</v>
       </c>
-      <c r="D114" s="9">
+      <c r="D114" s="8">
         <v>2</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="B115" s="11">
+      <c r="B115" s="10">
         <v>24619</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="10">
         <v>2</v>
       </c>
-      <c r="D115" s="11">
+      <c r="D115" s="10">
         <v>2</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="B116" s="9">
+      <c r="B116" s="8">
         <v>5081</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C116" s="8">
         <v>2</v>
       </c>
-      <c r="D116" s="9">
+      <c r="D116" s="8">
         <v>2</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="B117" s="11">
+      <c r="B117" s="10">
         <v>39389</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="10">
         <v>2</v>
       </c>
-      <c r="D117" s="11">
+      <c r="D117" s="10">
         <v>2</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="3" t="s">
         <v>748</v>
       </c>
-      <c r="B118" s="9">
+      <c r="B118" s="8">
         <v>20953</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C118" s="8">
         <v>2</v>
       </c>
-      <c r="D118" s="9">
+      <c r="D118" s="8">
         <v>2</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
         <v>758</v>
       </c>
-      <c r="B119" s="11">
+      <c r="B119" s="10">
         <v>8329</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>2</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D119" s="10">
         <v>2</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="3" t="s">
         <v>911</v>
       </c>
-      <c r="B120" s="9">
+      <c r="B120" s="8">
         <v>20707</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C120" s="8">
         <v>2</v>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="8">
         <v>2</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
         <v>915</v>
       </c>
-      <c r="B121" s="11">
+      <c r="B121" s="10">
         <v>10711</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121" s="10">
         <v>2</v>
       </c>
-      <c r="D121" s="11">
+      <c r="D121" s="10">
         <v>2</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="3" t="s">
         <v>918</v>
       </c>
-      <c r="B122" s="9">
+      <c r="B122" s="8">
         <v>6896</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C122" s="8">
         <v>2</v>
       </c>
-      <c r="D122" s="9">
+      <c r="D122" s="8">
         <v>2</v>
       </c>
-      <c r="E122" s="12" t="s">
-        <v>2950</v>
+      <c r="E122" s="11" t="s">
+        <v>2949</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
         <v>945</v>
       </c>
-      <c r="B123" s="11">
+      <c r="B123" s="10">
         <v>6935</v>
       </c>
-      <c r="C123" s="11">
+      <c r="C123" s="10">
         <v>2</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="10">
         <v>3</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="3" t="s">
         <v>1046</v>
       </c>
-      <c r="B124" s="9">
+      <c r="B124" s="8">
         <v>13755</v>
       </c>
-      <c r="C124" s="9">
+      <c r="C124" s="8">
         <v>2</v>
       </c>
-      <c r="D124" s="9">
+      <c r="D124" s="8">
         <v>2</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
         <v>1061</v>
       </c>
-      <c r="B125" s="11">
+      <c r="B125" s="10">
         <v>27417</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="10">
         <v>2</v>
       </c>
-      <c r="D125" s="11">
+      <c r="D125" s="10">
         <v>2</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="3" t="s">
         <v>1080</v>
       </c>
-      <c r="B126" s="9">
+      <c r="B126" s="8">
         <v>50516</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C126" s="8">
         <v>2</v>
       </c>
-      <c r="D126" s="9">
+      <c r="D126" s="8">
         <v>2</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
         <v>1116</v>
       </c>
-      <c r="B127" s="11">
+      <c r="B127" s="10">
         <v>3612</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="10">
         <v>2</v>
       </c>
-      <c r="D127" s="11">
+      <c r="D127" s="10">
         <v>2</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="3" t="s">
         <v>1168</v>
       </c>
-      <c r="B128" s="9">
+      <c r="B128" s="8">
         <v>20050</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C128" s="8">
         <v>2</v>
       </c>
-      <c r="D128" s="9">
+      <c r="D128" s="8">
         <v>2</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
         <v>1180</v>
       </c>
-      <c r="B129" s="11">
+      <c r="B129" s="10">
         <v>17023</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <v>2</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D129" s="10">
         <v>2</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="3" t="s">
         <v>1203</v>
       </c>
-      <c r="B130" s="9">
+      <c r="B130" s="8">
         <v>7841</v>
       </c>
-      <c r="C130" s="9">
+      <c r="C130" s="8">
         <v>2</v>
       </c>
-      <c r="D130" s="9">
+      <c r="D130" s="8">
         <v>2</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
         <v>1217</v>
       </c>
-      <c r="B131" s="11">
+      <c r="B131" s="10">
         <v>2257</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="10">
         <v>2</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D131" s="10">
         <v>2</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="3" t="s">
         <v>1243</v>
       </c>
-      <c r="B132" s="9">
+      <c r="B132" s="8">
         <v>23592</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C132" s="8">
         <v>2</v>
       </c>
-      <c r="D132" s="9">
+      <c r="D132" s="8">
         <v>2</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
         <v>1251</v>
       </c>
-      <c r="B133" s="11">
+      <c r="B133" s="10">
         <v>26938</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="10">
         <v>2</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="10">
         <v>2</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="3" t="s">
         <v>1336</v>
       </c>
-      <c r="B134" s="9">
+      <c r="B134" s="8">
         <v>9676</v>
       </c>
-      <c r="C134" s="9">
+      <c r="C134" s="8">
         <v>2</v>
       </c>
-      <c r="D134" s="9">
+      <c r="D134" s="8">
         <v>2</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
         <v>1343</v>
       </c>
-      <c r="B135" s="11">
+      <c r="B135" s="10">
         <v>7191</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="10">
         <v>2</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D135" s="10">
         <v>2</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="3" t="s">
         <v>1377</v>
       </c>
-      <c r="B136" s="9">
+      <c r="B136" s="8">
         <v>20228</v>
       </c>
-      <c r="C136" s="9">
+      <c r="C136" s="8">
         <v>2</v>
       </c>
-      <c r="D136" s="9">
+      <c r="D136" s="8">
         <v>2</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
         <v>1446</v>
       </c>
-      <c r="B137" s="11">
+      <c r="B137" s="10">
         <v>20516</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="10">
         <v>2</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="10">
         <v>2</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="3" t="s">
         <v>1541</v>
       </c>
-      <c r="B138" s="9">
+      <c r="B138" s="8">
         <v>33177</v>
       </c>
-      <c r="C138" s="9">
+      <c r="C138" s="8">
         <v>2</v>
       </c>
-      <c r="D138" s="9">
+      <c r="D138" s="8">
         <v>2</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
         <v>1559</v>
       </c>
-      <c r="B139" s="11">
+      <c r="B139" s="10">
         <v>23898</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="10">
         <v>2</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="10">
         <v>2</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="3" t="s">
         <v>1563</v>
       </c>
-      <c r="B140" s="9">
+      <c r="B140" s="8">
         <v>17475</v>
       </c>
-      <c r="C140" s="9">
+      <c r="C140" s="8">
         <v>2</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="8">
         <v>2</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
         <v>1614</v>
       </c>
-      <c r="B141" s="11">
+      <c r="B141" s="10">
         <v>26955</v>
       </c>
-      <c r="C141" s="11">
+      <c r="C141" s="10">
         <v>2</v>
       </c>
-      <c r="D141" s="11">
+      <c r="D141" s="10">
         <v>2</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="3" t="s">
         <v>1697</v>
       </c>
-      <c r="B142" s="9">
+      <c r="B142" s="8">
         <v>36958</v>
       </c>
-      <c r="C142" s="9">
+      <c r="C142" s="8">
         <v>2</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="8">
         <v>2</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
         <v>1737</v>
       </c>
-      <c r="B143" s="11">
+      <c r="B143" s="10">
         <v>44643</v>
       </c>
-      <c r="C143" s="11">
+      <c r="C143" s="10">
         <v>2</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="10">
         <v>2</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="3" t="s">
         <v>1810</v>
       </c>
-      <c r="B144" s="9">
+      <c r="B144" s="8">
         <v>3223</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C144" s="8">
         <v>2</v>
       </c>
-      <c r="D144" s="9">
+      <c r="D144" s="8">
         <v>2</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="B145" s="11">
+      <c r="B145" s="10">
         <v>35532</v>
       </c>
-      <c r="C145" s="11">
+      <c r="C145" s="10">
         <v>1</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="10">
         <v>1</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B146" s="9">
+      <c r="B146" s="8">
         <v>4059</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C146" s="8">
         <v>1</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D146" s="8">
         <v>1</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="B147" s="11">
+      <c r="B147" s="10">
         <v>5948</v>
       </c>
-      <c r="C147" s="11">
+      <c r="C147" s="10">
         <v>1</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="10">
         <v>1</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B148" s="9">
+      <c r="B148" s="8">
         <v>38787</v>
       </c>
-      <c r="C148" s="9">
+      <c r="C148" s="8">
         <v>1</v>
       </c>
-      <c r="D148" s="9">
+      <c r="D148" s="8">
         <v>1</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="B149" s="11">
+      <c r="B149" s="10">
         <v>3351</v>
       </c>
-      <c r="C149" s="11">
+      <c r="C149" s="10">
         <v>1</v>
       </c>
-      <c r="D149" s="11">
+      <c r="D149" s="10">
         <v>1</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B150" s="9">
+      <c r="B150" s="8">
         <v>26815</v>
       </c>
-      <c r="C150" s="9">
+      <c r="C150" s="8">
         <v>1</v>
       </c>
-      <c r="D150" s="9">
+      <c r="D150" s="8">
         <v>1</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="B151" s="11">
+      <c r="B151" s="10">
         <v>19061</v>
       </c>
-      <c r="C151" s="11">
+      <c r="C151" s="10">
         <v>1</v>
       </c>
-      <c r="D151" s="11">
+      <c r="D151" s="10">
         <v>1</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="B152" s="9">
+      <c r="B152" s="8">
         <v>19014</v>
       </c>
-      <c r="C152" s="9">
+      <c r="C152" s="8">
         <v>1</v>
       </c>
-      <c r="D152" s="9">
+      <c r="D152" s="8">
         <v>1</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
         <v>407</v>
       </c>
-      <c r="B153" s="11">
+      <c r="B153" s="10">
         <v>8818</v>
       </c>
-      <c r="C153" s="11">
+      <c r="C153" s="10">
         <v>1</v>
       </c>
-      <c r="D153" s="11">
+      <c r="D153" s="10">
         <v>1</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="B154" s="9">
+      <c r="B154" s="8">
         <v>40633</v>
       </c>
-      <c r="C154" s="9">
+      <c r="C154" s="8">
         <v>1</v>
       </c>
-      <c r="D154" s="9">
+      <c r="D154" s="8">
         <v>1</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
         <v>473</v>
       </c>
-      <c r="B155" s="11">
+      <c r="B155" s="10">
         <v>9490</v>
       </c>
-      <c r="C155" s="11">
+      <c r="C155" s="10">
         <v>1</v>
       </c>
-      <c r="D155" s="11">
+      <c r="D155" s="10">
         <v>1</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B156" s="9">
+      <c r="B156" s="8">
         <v>9740</v>
       </c>
-      <c r="C156" s="9">
+      <c r="C156" s="8">
         <v>1</v>
       </c>
-      <c r="D156" s="9">
+      <c r="D156" s="8">
         <v>1</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="B157" s="11">
+      <c r="B157" s="10">
         <v>10651</v>
       </c>
-      <c r="C157" s="11">
+      <c r="C157" s="10">
         <v>1</v>
       </c>
-      <c r="D157" s="11">
+      <c r="D157" s="10">
         <v>1</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="B158" s="9">
+      <c r="B158" s="8">
         <v>27677</v>
       </c>
-      <c r="C158" s="9">
+      <c r="C158" s="8">
         <v>1</v>
       </c>
-      <c r="D158" s="9">
+      <c r="D158" s="8">
         <v>1</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="B159" s="11">
+      <c r="B159" s="10">
         <v>41171</v>
       </c>
-      <c r="C159" s="11">
+      <c r="C159" s="10">
         <v>1</v>
       </c>
-      <c r="D159" s="11">
+      <c r="D159" s="10">
         <v>1</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="B160" s="9">
+      <c r="B160" s="8">
         <v>11679</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C160" s="8">
         <v>1</v>
       </c>
-      <c r="D160" s="9">
+      <c r="D160" s="8">
         <v>1</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
         <v>656</v>
       </c>
-      <c r="B161" s="11">
+      <c r="B161" s="10">
         <v>29484</v>
       </c>
-      <c r="C161" s="11">
+      <c r="C161" s="10">
         <v>1</v>
       </c>
-      <c r="D161" s="11">
+      <c r="D161" s="10">
         <v>1</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="B162" s="9">
+      <c r="B162" s="8">
         <v>8458</v>
       </c>
-      <c r="C162" s="9">
+      <c r="C162" s="8">
         <v>1</v>
       </c>
-      <c r="D162" s="9">
+      <c r="D162" s="8">
         <v>1</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
         <v>682</v>
       </c>
-      <c r="B163" s="11">
+      <c r="B163" s="10">
         <v>8006</v>
       </c>
-      <c r="C163" s="11">
+      <c r="C163" s="10">
         <v>1</v>
       </c>
-      <c r="D163" s="11">
+      <c r="D163" s="10">
         <v>1</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="B164" s="9">
+      <c r="B164" s="8">
         <v>6974</v>
       </c>
-      <c r="C164" s="9">
+      <c r="C164" s="8">
         <v>1</v>
       </c>
-      <c r="D164" s="9">
+      <c r="D164" s="8">
         <v>1</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
         <v>700</v>
       </c>
-      <c r="B165" s="11">
+      <c r="B165" s="10">
         <v>703</v>
       </c>
-      <c r="C165" s="11">
+      <c r="C165" s="10">
         <v>1</v>
       </c>
-      <c r="D165" s="11">
+      <c r="D165" s="10">
         <v>1</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="B166" s="9">
+      <c r="B166" s="8">
         <v>18424</v>
       </c>
-      <c r="C166" s="9">
+      <c r="C166" s="8">
         <v>1</v>
       </c>
-      <c r="D166" s="9">
+      <c r="D166" s="8">
         <v>1</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
         <v>461</v>
       </c>
-      <c r="B167" s="11">
+      <c r="B167" s="10">
         <v>20052</v>
       </c>
-      <c r="C167" s="11">
+      <c r="C167" s="10">
         <v>1</v>
       </c>
-      <c r="D167" s="11">
+      <c r="D167" s="10">
         <v>1</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="3" t="s">
         <v>782</v>
       </c>
-      <c r="B168" s="9">
+      <c r="B168" s="8">
         <v>44116</v>
       </c>
-      <c r="C168" s="9">
+      <c r="C168" s="8">
         <v>1</v>
       </c>
-      <c r="D168" s="9">
+      <c r="D168" s="8">
         <v>1</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
         <v>792</v>
       </c>
-      <c r="B169" s="11">
+      <c r="B169" s="10">
         <v>11802</v>
       </c>
-      <c r="C169" s="11">
+      <c r="C169" s="10">
         <v>1</v>
       </c>
-      <c r="D169" s="11">
+      <c r="D169" s="10">
         <v>1</v>
       </c>
       <c r="E169" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="3" t="s">
         <v>799</v>
       </c>
-      <c r="B170" s="9">
+      <c r="B170" s="8">
         <v>14804</v>
       </c>
-      <c r="C170" s="9">
+      <c r="C170" s="8">
         <v>1</v>
       </c>
-      <c r="D170" s="9">
+      <c r="D170" s="8">
         <v>1</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
         <v>809</v>
       </c>
-      <c r="B171" s="11">
+      <c r="B171" s="10">
         <v>19890</v>
       </c>
-      <c r="C171" s="11">
+      <c r="C171" s="10">
         <v>1</v>
       </c>
-      <c r="D171" s="11">
+      <c r="D171" s="10">
         <v>1</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="B172" s="9">
+      <c r="B172" s="8">
         <v>5432</v>
       </c>
-      <c r="C172" s="9">
+      <c r="C172" s="8">
         <v>1</v>
       </c>
-      <c r="D172" s="9">
+      <c r="D172" s="8">
         <v>1</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="B173" s="11">
+      <c r="B173" s="10">
         <v>23531</v>
       </c>
-      <c r="C173" s="11">
+      <c r="C173" s="10">
         <v>1</v>
       </c>
-      <c r="D173" s="11">
+      <c r="D173" s="10">
         <v>1</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="3" t="s">
         <v>871</v>
       </c>
-      <c r="B174" s="9">
+      <c r="B174" s="8">
         <v>13451</v>
       </c>
-      <c r="C174" s="9">
+      <c r="C174" s="8">
         <v>1</v>
       </c>
-      <c r="D174" s="9">
+      <c r="D174" s="8">
         <v>1</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B175" s="11">
+      <c r="B175" s="10">
         <v>8650</v>
       </c>
-      <c r="C175" s="11">
+      <c r="C175" s="10">
         <v>1</v>
       </c>
-      <c r="D175" s="11">
+      <c r="D175" s="10">
         <v>1</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="3" t="s">
         <v>924</v>
       </c>
-      <c r="B176" s="9">
+      <c r="B176" s="8">
         <v>51089</v>
       </c>
-      <c r="C176" s="9">
+      <c r="C176" s="8">
         <v>1</v>
       </c>
-      <c r="D176" s="9">
+      <c r="D176" s="8">
         <v>1</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="5" t="s">
         <v>443</v>
       </c>
-      <c r="B177" s="11">
+      <c r="B177" s="10">
         <v>10666</v>
       </c>
-      <c r="C177" s="11">
+      <c r="C177" s="10">
         <v>1</v>
       </c>
-      <c r="D177" s="11">
+      <c r="D177" s="10">
         <v>1</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="3" t="s">
         <v>976</v>
       </c>
-      <c r="B178" s="9">
+      <c r="B178" s="8">
         <v>40001</v>
       </c>
-      <c r="C178" s="9">
+      <c r="C178" s="8">
         <v>1</v>
       </c>
-      <c r="D178" s="9">
+      <c r="D178" s="8">
         <v>1</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="5" t="s">
         <v>982</v>
       </c>
-      <c r="B179" s="11">
+      <c r="B179" s="10">
         <v>14118</v>
       </c>
-      <c r="C179" s="11">
+      <c r="C179" s="10">
         <v>1</v>
       </c>
-      <c r="D179" s="11">
+      <c r="D179" s="10">
         <v>1</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="3" t="s">
         <v>995</v>
       </c>
-      <c r="B180" s="9">
+      <c r="B180" s="8">
         <v>37682</v>
       </c>
-      <c r="C180" s="9">
+      <c r="C180" s="8">
         <v>1</v>
       </c>
-      <c r="D180" s="9">
+      <c r="D180" s="8">
         <v>1</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="5" t="s">
         <v>1013</v>
       </c>
-      <c r="B181" s="11">
+      <c r="B181" s="10">
         <v>17561</v>
       </c>
-      <c r="C181" s="11">
+      <c r="C181" s="10">
         <v>1</v>
       </c>
-      <c r="D181" s="11">
+      <c r="D181" s="10">
         <v>1</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="3" t="s">
         <v>886</v>
       </c>
-      <c r="B182" s="9">
+      <c r="B182" s="8">
         <v>6044</v>
       </c>
-      <c r="C182" s="9">
+      <c r="C182" s="8">
         <v>1</v>
       </c>
-      <c r="D182" s="9">
+      <c r="D182" s="8">
         <v>1</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="B183" s="11">
+      <c r="B183" s="10">
         <v>27276</v>
       </c>
-      <c r="C183" s="11">
+      <c r="C183" s="10">
         <v>1</v>
       </c>
-      <c r="D183" s="11">
+      <c r="D183" s="10">
         <v>1</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="3" t="s">
         <v>1041</v>
       </c>
-      <c r="B184" s="9">
+      <c r="B184" s="8">
         <v>26124</v>
       </c>
-      <c r="C184" s="9">
+      <c r="C184" s="8">
         <v>1</v>
       </c>
-      <c r="D184" s="9">
+      <c r="D184" s="8">
         <v>1</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="5" t="s">
         <v>886</v>
       </c>
-      <c r="B185" s="11">
+      <c r="B185" s="10">
         <v>20483</v>
       </c>
-      <c r="C185" s="11">
+      <c r="C185" s="10">
         <v>1</v>
       </c>
-      <c r="D185" s="11">
+      <c r="D185" s="10">
         <v>1</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="3" t="s">
         <v>1071</v>
       </c>
-      <c r="B186" s="9">
+      <c r="B186" s="8">
         <v>18797</v>
       </c>
-      <c r="C186" s="9">
+      <c r="C186" s="8">
         <v>1</v>
       </c>
-      <c r="D186" s="9">
+      <c r="D186" s="8">
         <v>1</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="5" t="s">
         <v>1088</v>
       </c>
-      <c r="B187" s="11">
+      <c r="B187" s="10">
         <v>16503</v>
       </c>
-      <c r="C187" s="11">
+      <c r="C187" s="10">
         <v>1</v>
       </c>
-      <c r="D187" s="11">
+      <c r="D187" s="10">
         <v>1</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="3" t="s">
         <v>1093</v>
       </c>
-      <c r="B188" s="9">
+      <c r="B188" s="8">
         <v>19273</v>
       </c>
-      <c r="C188" s="9">
+      <c r="C188" s="8">
         <v>1</v>
       </c>
-      <c r="D188" s="9">
+      <c r="D188" s="8">
         <v>1</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="5" t="s">
         <v>1102</v>
       </c>
-      <c r="B189" s="11">
+      <c r="B189" s="10">
         <v>22247</v>
       </c>
-      <c r="C189" s="11">
+      <c r="C189" s="10">
         <v>1</v>
       </c>
-      <c r="D189" s="11">
+      <c r="D189" s="10">
         <v>1</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="3" t="s">
         <v>1136</v>
       </c>
-      <c r="B190" s="9">
+      <c r="B190" s="8">
         <v>9283</v>
       </c>
-      <c r="C190" s="9">
+      <c r="C190" s="8">
         <v>1</v>
       </c>
-      <c r="D190" s="9">
+      <c r="D190" s="8">
         <v>1</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="5" t="s">
         <v>1147</v>
       </c>
-      <c r="B191" s="11">
+      <c r="B191" s="10">
         <v>32458</v>
       </c>
-      <c r="C191" s="11">
+      <c r="C191" s="10">
         <v>1</v>
       </c>
-      <c r="D191" s="11">
+      <c r="D191" s="10">
         <v>1</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="3" t="s">
         <v>1173</v>
       </c>
-      <c r="B192" s="9">
+      <c r="B192" s="8">
         <v>3156</v>
       </c>
-      <c r="C192" s="9">
+      <c r="C192" s="8">
         <v>1</v>
       </c>
-      <c r="D192" s="9">
+      <c r="D192" s="8">
         <v>1</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="5" t="s">
         <v>757</v>
       </c>
-      <c r="B193" s="11">
+      <c r="B193" s="10">
         <v>26745</v>
       </c>
-      <c r="C193" s="11">
+      <c r="C193" s="10">
         <v>1</v>
       </c>
-      <c r="D193" s="11">
+      <c r="D193" s="10">
         <v>1</v>
       </c>
       <c r="E193" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="3" t="s">
         <v>1192</v>
       </c>
-      <c r="B194" s="9">
+      <c r="B194" s="8">
         <v>53539</v>
       </c>
-      <c r="C194" s="9">
+      <c r="C194" s="8">
         <v>1</v>
       </c>
-      <c r="D194" s="9">
+      <c r="D194" s="8">
         <v>1</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="5" t="s">
         <v>1200</v>
       </c>
-      <c r="B195" s="11">
+      <c r="B195" s="10">
         <v>17172</v>
       </c>
-      <c r="C195" s="11">
+      <c r="C195" s="10">
         <v>1</v>
       </c>
-      <c r="D195" s="11">
+      <c r="D195" s="10">
         <v>1</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="3" t="s">
         <v>1206</v>
       </c>
-      <c r="B196" s="9">
+      <c r="B196" s="8">
         <v>21321</v>
       </c>
-      <c r="C196" s="9">
+      <c r="C196" s="8">
         <v>1</v>
       </c>
-      <c r="D196" s="9">
+      <c r="D196" s="8">
         <v>1</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="B197" s="11">
+      <c r="B197" s="10">
         <v>27456</v>
       </c>
-      <c r="C197" s="11">
+      <c r="C197" s="10">
         <v>1</v>
       </c>
-      <c r="D197" s="11">
+      <c r="D197" s="10">
         <v>1</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B198" s="9">
+      <c r="B198" s="8">
         <v>23068</v>
       </c>
-      <c r="C198" s="9">
+      <c r="C198" s="8">
         <v>1</v>
       </c>
-      <c r="D198" s="9">
+      <c r="D198" s="8">
         <v>1</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="5" t="s">
         <v>1288</v>
       </c>
-      <c r="B199" s="11">
+      <c r="B199" s="10">
         <v>6565</v>
       </c>
-      <c r="C199" s="11">
+      <c r="C199" s="10">
         <v>1</v>
       </c>
-      <c r="D199" s="11">
+      <c r="D199" s="10">
         <v>1</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B200" s="9">
+      <c r="B200" s="8">
         <v>41770</v>
       </c>
-      <c r="C200" s="9">
+      <c r="C200" s="8">
         <v>1</v>
       </c>
-      <c r="D200" s="9">
+      <c r="D200" s="8">
         <v>1</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="201" spans="1:5">
       <c r="A201" s="5" t="s">
         <v>1307</v>
       </c>
-      <c r="B201" s="11">
+      <c r="B201" s="10">
         <v>25322</v>
       </c>
-      <c r="C201" s="11">
+      <c r="C201" s="10">
         <v>1</v>
       </c>
-      <c r="D201" s="11">
+      <c r="D201" s="10">
         <v>1</v>
       </c>
       <c r="E201" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="202" spans="1:5">
       <c r="A202" s="3" t="s">
         <v>1315</v>
       </c>
-      <c r="B202" s="9">
+      <c r="B202" s="8">
         <v>5079</v>
       </c>
-      <c r="C202" s="9">
+      <c r="C202" s="8">
         <v>1</v>
       </c>
-      <c r="D202" s="9">
+      <c r="D202" s="8">
         <v>1</v>
       </c>
       <c r="E202" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="203" spans="1:5">
       <c r="A203" s="5" t="s">
         <v>1364</v>
       </c>
-      <c r="B203" s="11">
+      <c r="B203" s="10">
         <v>6971</v>
       </c>
-      <c r="C203" s="11">
+      <c r="C203" s="10">
         <v>1</v>
       </c>
-      <c r="D203" s="11">
+      <c r="D203" s="10">
         <v>2</v>
       </c>
       <c r="E203" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="204" spans="1:5">
       <c r="A204" s="3" t="s">
         <v>1393</v>
       </c>
-      <c r="B204" s="9">
+      <c r="B204" s="8">
         <v>5865</v>
       </c>
-      <c r="C204" s="9">
+      <c r="C204" s="8">
         <v>1</v>
       </c>
-      <c r="D204" s="9">
+      <c r="D204" s="8">
         <v>1</v>
       </c>
       <c r="E204" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="205" spans="1:5">
       <c r="A205" s="5" t="s">
         <v>1407</v>
       </c>
-      <c r="B205" s="11">
+      <c r="B205" s="10">
         <v>6292</v>
       </c>
-      <c r="C205" s="11">
+      <c r="C205" s="10">
         <v>1</v>
       </c>
-      <c r="D205" s="11">
+      <c r="D205" s="10">
         <v>1</v>
       </c>
       <c r="E205" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="206" spans="1:5">
       <c r="A206" s="3" t="s">
         <v>1414</v>
       </c>
-      <c r="B206" s="9">
+      <c r="B206" s="8">
         <v>18863</v>
       </c>
-      <c r="C206" s="9">
+      <c r="C206" s="8">
         <v>1</v>
       </c>
-      <c r="D206" s="9">
+      <c r="D206" s="8">
         <v>1</v>
       </c>
       <c r="E206" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="207" spans="1:5">
       <c r="A207" s="5" t="s">
         <v>1420</v>
       </c>
-      <c r="B207" s="11">
+      <c r="B207" s="10">
         <v>5205</v>
       </c>
-      <c r="C207" s="11">
+      <c r="C207" s="10">
         <v>1</v>
       </c>
-      <c r="D207" s="11">
+      <c r="D207" s="10">
         <v>1</v>
       </c>
       <c r="E207" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="208" spans="1:5">
       <c r="A208" s="3" t="s">
         <v>1427</v>
       </c>
-      <c r="B208" s="9">
+      <c r="B208" s="8">
         <v>27112</v>
       </c>
-      <c r="C208" s="9">
+      <c r="C208" s="8">
         <v>1</v>
       </c>
-      <c r="D208" s="9">
+      <c r="D208" s="8">
         <v>1</v>
       </c>
       <c r="E208" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="209" spans="1:5">
       <c r="A209" s="5" t="s">
         <v>1430</v>
       </c>
-      <c r="B209" s="11">
+      <c r="B209" s="10">
         <v>15788</v>
       </c>
-      <c r="C209" s="11">
+      <c r="C209" s="10">
         <v>1</v>
       </c>
-      <c r="D209" s="11">
+      <c r="D209" s="10">
         <v>1</v>
       </c>
       <c r="E209" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="210" spans="1:5">
       <c r="A210" s="3" t="s">
         <v>1466</v>
       </c>
-      <c r="B210" s="9">
+      <c r="B210" s="8">
         <v>11162</v>
       </c>
-      <c r="C210" s="9">
+      <c r="C210" s="8">
         <v>1</v>
       </c>
-      <c r="D210" s="9">
+      <c r="D210" s="8">
         <v>2</v>
       </c>
       <c r="E210" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="211" spans="1:5">
       <c r="A211" s="5" t="s">
         <v>1491</v>
       </c>
-      <c r="B211" s="11">
+      <c r="B211" s="10">
         <v>20520</v>
       </c>
-      <c r="C211" s="11">
+      <c r="C211" s="10">
         <v>1</v>
       </c>
-      <c r="D211" s="11">
+      <c r="D211" s="10">
         <v>1</v>
       </c>
       <c r="E211" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="212" spans="1:5">
       <c r="A212" s="3" t="s">
         <v>1503</v>
       </c>
-      <c r="B212" s="9">
+      <c r="B212" s="8">
         <v>1463</v>
       </c>
-      <c r="C212" s="9">
+      <c r="C212" s="8">
         <v>1</v>
       </c>
-      <c r="D212" s="9">
+      <c r="D212" s="8">
         <v>1</v>
       </c>
       <c r="E212" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="213" spans="1:5">
       <c r="A213" s="5" t="s">
         <v>1506</v>
       </c>
-      <c r="B213" s="11">
+      <c r="B213" s="10">
         <v>26167</v>
       </c>
-      <c r="C213" s="11">
+      <c r="C213" s="10">
         <v>1</v>
       </c>
-      <c r="D213" s="11">
+      <c r="D213" s="10">
         <v>1</v>
       </c>
       <c r="E213" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="214" spans="1:5">
       <c r="A214" s="3" t="s">
         <v>1518</v>
       </c>
-      <c r="B214" s="9">
+      <c r="B214" s="8">
         <v>7526</v>
       </c>
-      <c r="C214" s="9">
+      <c r="C214" s="8">
         <v>1</v>
       </c>
-      <c r="D214" s="9">
+      <c r="D214" s="8">
         <v>1</v>
       </c>
       <c r="E214" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="215" spans="1:5">
       <c r="A215" s="5" t="s">
         <v>1538</v>
       </c>
-      <c r="B215" s="11">
+      <c r="B215" s="10">
         <v>3984</v>
       </c>
-      <c r="C215" s="11">
+      <c r="C215" s="10">
         <v>1</v>
       </c>
-      <c r="D215" s="11">
+      <c r="D215" s="10">
         <v>1</v>
       </c>
       <c r="E215" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="216" spans="1:5">
       <c r="A216" s="3" t="s">
         <v>1571</v>
       </c>
-      <c r="B216" s="9">
+      <c r="B216" s="8">
         <v>18875</v>
       </c>
-      <c r="C216" s="9">
+      <c r="C216" s="8">
         <v>1</v>
       </c>
-      <c r="D216" s="9">
+      <c r="D216" s="8">
         <v>1</v>
       </c>
       <c r="E216" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="217" spans="1:5">
       <c r="A217" s="5" t="s">
         <v>1587</v>
       </c>
-      <c r="B217" s="11">
+      <c r="B217" s="10">
         <v>3762</v>
       </c>
-      <c r="C217" s="11">
+      <c r="C217" s="10">
         <v>1</v>
       </c>
-      <c r="D217" s="11">
+      <c r="D217" s="10">
         <v>1</v>
       </c>
       <c r="E217" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="218" spans="1:5">
       <c r="A218" s="3" t="s">
         <v>1597</v>
       </c>
-      <c r="B218" s="9">
+      <c r="B218" s="8">
         <v>39941</v>
       </c>
-      <c r="C218" s="9">
+      <c r="C218" s="8">
         <v>1</v>
       </c>
-      <c r="D218" s="9">
+      <c r="D218" s="8">
         <v>1</v>
       </c>
       <c r="E218" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="219" spans="1:5">
       <c r="A219" s="5" t="s">
         <v>1637</v>
       </c>
-      <c r="B219" s="11">
+      <c r="B219" s="10">
         <v>19484</v>
       </c>
-      <c r="C219" s="11">
+      <c r="C219" s="10">
         <v>1</v>
       </c>
-      <c r="D219" s="11">
+      <c r="D219" s="10">
         <v>1</v>
       </c>
       <c r="E219" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="220" spans="1:5">
       <c r="A220" s="3" t="s">
         <v>1641</v>
       </c>
-      <c r="B220" s="9">
+      <c r="B220" s="8">
         <v>26653</v>
       </c>
-      <c r="C220" s="9">
+      <c r="C220" s="8">
         <v>1</v>
       </c>
-      <c r="D220" s="9">
+      <c r="D220" s="8">
         <v>1</v>
       </c>
       <c r="E220" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="221" spans="1:5">
       <c r="A221" s="5" t="s">
         <v>1656</v>
       </c>
-      <c r="B221" s="11">
+      <c r="B221" s="10">
         <v>1194</v>
       </c>
-      <c r="C221" s="11">
+      <c r="C221" s="10">
         <v>1</v>
       </c>
-      <c r="D221" s="11">
+      <c r="D221" s="10">
         <v>1</v>
       </c>
       <c r="E221" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="222" spans="1:5">
       <c r="A222" s="3" t="s">
         <v>1678</v>
       </c>
-      <c r="B222" s="9">
+      <c r="B222" s="8">
         <v>22102</v>
       </c>
-      <c r="C222" s="9">
+      <c r="C222" s="8">
         <v>1</v>
       </c>
-      <c r="D222" s="9">
+      <c r="D222" s="8">
         <v>2</v>
       </c>
       <c r="E222" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="223" spans="1:5">
       <c r="A223" s="5" t="s">
         <v>1719</v>
       </c>
-      <c r="B223" s="11">
+      <c r="B223" s="10">
         <v>6756</v>
       </c>
-      <c r="C223" s="11">
+      <c r="C223" s="10">
         <v>1</v>
       </c>
-      <c r="D223" s="11">
+      <c r="D223" s="10">
         <v>1</v>
       </c>
       <c r="E223" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="224" spans="1:5">
       <c r="A224" s="3" t="s">
         <v>1731</v>
       </c>
-      <c r="B224" s="9">
+      <c r="B224" s="8">
         <v>37876</v>
       </c>
-      <c r="C224" s="9">
+      <c r="C224" s="8">
         <v>1</v>
       </c>
-      <c r="D224" s="9">
+      <c r="D224" s="8">
         <v>1</v>
       </c>
       <c r="E224" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="225" spans="1:5">
       <c r="A225" s="5" t="s">
         <v>1752</v>
       </c>
-      <c r="B225" s="11">
+      <c r="B225" s="10">
         <v>19975</v>
       </c>
-      <c r="C225" s="11">
+      <c r="C225" s="10">
         <v>1</v>
       </c>
-      <c r="D225" s="11">
+      <c r="D225" s="10">
         <v>1</v>
       </c>
       <c r="E225" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="226" spans="1:5">
       <c r="A226" s="3" t="s">
         <v>991</v>
       </c>
-      <c r="B226" s="9">
+      <c r="B226" s="8">
         <v>22489</v>
       </c>
-      <c r="C226" s="9">
+      <c r="C226" s="8">
         <v>1</v>
       </c>
-      <c r="D226" s="9">
+      <c r="D226" s="8">
         <v>1</v>
       </c>
       <c r="E226" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="227" spans="1:5">
       <c r="A227" s="5" t="s">
         <v>1865</v>
       </c>
-      <c r="B227" s="11">
+      <c r="B227" s="10">
         <v>4911</v>
       </c>
-      <c r="C227" s="11">
+      <c r="C227" s="10">
         <v>1</v>
       </c>
-      <c r="D227" s="11">
+      <c r="D227" s="10">
         <v>1</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="228" spans="1:5">
       <c r="A228" s="3" t="s">
         <v>1906</v>
       </c>
-      <c r="B228" s="9">
+      <c r="B228" s="8">
         <v>14124</v>
       </c>
-      <c r="C228" s="9">
+      <c r="C228" s="8">
         <v>1</v>
       </c>
-      <c r="D228" s="9">
+      <c r="D228" s="8">
         <v>1</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
     <row r="229" spans="1:5">
       <c r="A229" s="5" t="s">
         <v>2346</v>
       </c>
-      <c r="B229" s="11">
+      <c r="B229" s="10">
         <v>5335</v>
       </c>
-      <c r="C229" s="11">
+      <c r="C229" s="10">
         <v>1</v>
       </c>
-      <c r="D229" s="11">
+      <c r="D229" s="10">
         <v>2</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>2951</v>
+        <v>2950</v>
       </c>
     </row>
   </sheetData>

--- a/skipperplan.xlsx
+++ b/skipperplan.xlsx
@@ -2445,6 +2445,9 @@
     <t>16277</t>
   </si>
   <si>
+    <t>confirmed_by_admin_delayed</t>
+  </si>
+  <si>
     <t>8188</t>
   </si>
   <si>
@@ -3628,9 +3631,6 @@
   </si>
   <si>
     <t>15276</t>
-  </si>
-  <si>
-    <t>confirmed_by_admin_delayed</t>
   </si>
   <si>
     <t>8191</t>
@@ -10141,7 +10141,7 @@
         <v>10</v>
       </c>
       <c r="J11" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>34</v>
@@ -10377,7 +10377,7 @@
         <v>8</v>
       </c>
       <c r="J14" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>34</v>
@@ -11953,7 +11953,7 @@
         <v>8</v>
       </c>
       <c r="J34" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K34" s="3" t="s">
         <v>34</v>
@@ -13683,7 +13683,7 @@
         <v>10</v>
       </c>
       <c r="J56" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K56" s="3" t="s">
         <v>34</v>
@@ -14317,7 +14317,7 @@
         <v>8</v>
       </c>
       <c r="J64" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K64" s="3" t="s">
         <v>34</v>
@@ -14947,7 +14947,7 @@
         <v>8</v>
       </c>
       <c r="J72" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K72" s="3" t="s">
         <v>34</v>
@@ -17543,7 +17543,7 @@
         <v>9</v>
       </c>
       <c r="J105" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K105" s="5" t="s">
         <v>34</v>
@@ -18095,7 +18095,7 @@
         <v>8</v>
       </c>
       <c r="J112" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K112" s="3" t="s">
         <v>34</v>
@@ -18721,7 +18721,7 @@
         <v>8</v>
       </c>
       <c r="J120" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K120" s="3" t="s">
         <v>34</v>
@@ -21539,7 +21539,7 @@
         <v>9</v>
       </c>
       <c r="J156" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K156" s="3" t="s">
         <v>34</v>
@@ -24791,7 +24791,7 @@
         <v>45</v>
       </c>
       <c r="X197" s="5" t="s">
-        <v>525</v>
+        <v>806</v>
       </c>
       <c r="Y197" s="5" t="s">
         <v>53</v>
@@ -24848,10 +24848,10 @@
         <v>337</v>
       </c>
       <c r="Q198" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="R198" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="S198" s="3" t="s">
         <v>97</v>
@@ -24875,7 +24875,7 @@
         <v>46</v>
       </c>
       <c r="Z198" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
     </row>
     <row r="199" spans="1:26">
@@ -24898,10 +24898,10 @@
         <v>31</v>
       </c>
       <c r="G199" s="5" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H199" s="5" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I199" s="5">
         <v>8</v>
@@ -24928,10 +24928,10 @@
         <v>337</v>
       </c>
       <c r="Q199" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="R199" s="5" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="S199" s="5" t="s">
         <v>340</v>
@@ -24976,10 +24976,10 @@
         <v>31</v>
       </c>
       <c r="G200" s="6" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H200" s="6" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="I200" s="6">
         <v>8</v>
@@ -25006,10 +25006,10 @@
         <v>337</v>
       </c>
       <c r="Q200" s="6" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="R200" s="6" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="S200" s="6" t="s">
         <v>340</v>
@@ -25054,10 +25054,10 @@
         <v>31</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H201" s="6" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="I201" s="6">
         <v>9</v>
@@ -25084,10 +25084,10 @@
         <v>337</v>
       </c>
       <c r="Q201" s="6" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="R201" s="6" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="S201" s="6" t="s">
         <v>97</v>
@@ -25162,16 +25162,16 @@
         <v>337</v>
       </c>
       <c r="Q202" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="R202" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="S202" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="T202" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="U202" s="3" t="s">
         <v>44</v>
@@ -25210,10 +25210,10 @@
         <v>31</v>
       </c>
       <c r="G203" s="5" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="H203" s="5" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="I203" s="5">
         <v>6</v>
@@ -25240,16 +25240,16 @@
         <v>337</v>
       </c>
       <c r="Q203" s="5" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="R203" s="5" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="S203" s="5" t="s">
         <v>197</v>
       </c>
       <c r="T203" s="5" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="U203" s="5" t="s">
         <v>44</v>
@@ -25288,10 +25288,10 @@
         <v>31</v>
       </c>
       <c r="G204" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H204" s="7" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I204" s="7">
         <v>7</v>
@@ -25318,10 +25318,10 @@
         <v>84</v>
       </c>
       <c r="Q204" s="7" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="R204" s="7" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="S204" s="7" t="s">
         <v>87</v>
@@ -25345,7 +25345,7 @@
         <v>53</v>
       </c>
       <c r="Z204" s="7" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
     </row>
     <row r="205" spans="1:26">
@@ -25398,10 +25398,10 @@
         <v>94</v>
       </c>
       <c r="Q205" s="5" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="R205" s="5" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="S205" s="5" t="s">
         <v>97</v>
@@ -25478,10 +25478,10 @@
         <v>118</v>
       </c>
       <c r="Q206" s="3" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="R206" s="3" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="S206" s="3" t="s">
         <v>108</v>
@@ -25558,10 +25558,10 @@
         <v>105</v>
       </c>
       <c r="Q207" s="5" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="R207" s="5" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="S207" s="5" t="s">
         <v>132</v>
@@ -25638,10 +25638,10 @@
         <v>105</v>
       </c>
       <c r="Q208" s="3" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="R208" s="3" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="S208" s="3" t="s">
         <v>108</v>
@@ -25686,10 +25686,10 @@
         <v>31</v>
       </c>
       <c r="G209" s="6" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H209" s="6" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I209" s="6">
         <v>10</v>
@@ -25716,10 +25716,10 @@
         <v>105</v>
       </c>
       <c r="Q209" s="6" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="R209" s="6" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="S209" s="6" t="s">
         <v>108</v>
@@ -25794,10 +25794,10 @@
         <v>149</v>
       </c>
       <c r="Q210" s="3" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="R210" s="3" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="S210" s="3" t="s">
         <v>97</v>
@@ -25821,7 +25821,7 @@
         <v>53</v>
       </c>
       <c r="Z210" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="211" spans="1:26">
@@ -25874,10 +25874,10 @@
         <v>158</v>
       </c>
       <c r="Q211" s="5" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="R211" s="5" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="S211" s="5" t="s">
         <v>68</v>
@@ -25901,7 +25901,7 @@
         <v>53</v>
       </c>
       <c r="Z211" s="5" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
     </row>
     <row r="212" spans="1:26">
@@ -25954,16 +25954,16 @@
         <v>170</v>
       </c>
       <c r="Q212" s="3" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="R212" s="3" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="S212" s="3" t="s">
         <v>97</v>
       </c>
       <c r="T212" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="U212" s="3" t="s">
         <v>44</v>
@@ -25981,7 +25981,7 @@
         <v>46</v>
       </c>
       <c r="Z212" s="3" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
     </row>
     <row r="213" spans="1:26">
@@ -26032,16 +26032,16 @@
         <v>170</v>
       </c>
       <c r="Q213" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="R213" s="4" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="S213" s="4" t="s">
         <v>197</v>
       </c>
       <c r="T213" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="U213" s="4" t="s">
         <v>44</v>
@@ -26110,10 +26110,10 @@
         <v>178</v>
       </c>
       <c r="Q214" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="R214" s="3" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="S214" s="3" t="s">
         <v>68</v>
@@ -26137,7 +26137,7 @@
         <v>53</v>
       </c>
       <c r="Z214" s="3" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
     </row>
     <row r="215" spans="1:26">
@@ -26190,10 +26190,10 @@
         <v>178</v>
       </c>
       <c r="Q215" s="5" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="R215" s="5" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="S215" s="5" t="s">
         <v>392</v>
@@ -26268,16 +26268,16 @@
         <v>178</v>
       </c>
       <c r="Q216" s="3" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="R216" s="3" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="S216" s="3" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="T216" s="3" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="U216" s="3" t="s">
         <v>44</v>
@@ -26316,10 +26316,10 @@
         <v>31</v>
       </c>
       <c r="G217" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H217" s="5" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I217" s="5">
         <v>9</v>
@@ -26346,10 +26346,10 @@
         <v>185</v>
       </c>
       <c r="Q217" s="5" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="R217" s="5" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="S217" s="5" t="s">
         <v>68</v>
@@ -26373,7 +26373,7 @@
         <v>46</v>
       </c>
       <c r="Z217" s="5" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
     </row>
     <row r="218" spans="1:26">
@@ -26396,10 +26396,10 @@
         <v>31</v>
       </c>
       <c r="G218" s="3" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="H218" s="3" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="I218" s="3">
         <v>10</v>
@@ -26426,10 +26426,10 @@
         <v>185</v>
       </c>
       <c r="Q218" s="3" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="R218" s="3" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="S218" s="3" t="s">
         <v>77</v>
@@ -26502,10 +26502,10 @@
         <v>185</v>
       </c>
       <c r="Q219" s="6" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="R219" s="6" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="S219" s="6" t="s">
         <v>238</v>
@@ -26580,10 +26580,10 @@
         <v>202</v>
       </c>
       <c r="Q220" s="3" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="R220" s="3" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="S220" s="3" t="s">
         <v>138</v>
@@ -26660,16 +26660,16 @@
         <v>202</v>
       </c>
       <c r="Q221" s="7" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="R221" s="7" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="S221" s="7" t="s">
         <v>138</v>
       </c>
       <c r="T221" s="7" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="U221" s="7" t="s">
         <v>44</v>
@@ -26738,10 +26738,10 @@
         <v>215</v>
       </c>
       <c r="Q222" s="3" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="R222" s="3" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="S222" s="3" t="s">
         <v>97</v>
@@ -26765,7 +26765,7 @@
         <v>53</v>
       </c>
       <c r="Z222" s="3" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
     </row>
     <row r="223" spans="1:26">
@@ -26818,10 +26818,10 @@
         <v>215</v>
       </c>
       <c r="Q223" s="5" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="R223" s="5" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="S223" s="5" t="s">
         <v>229</v>
@@ -26896,10 +26896,10 @@
         <v>221</v>
       </c>
       <c r="Q224" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="R224" s="3" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="S224" s="3" t="s">
         <v>108</v>
@@ -26923,7 +26923,7 @@
         <v>53</v>
       </c>
       <c r="Z224" s="3" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
     </row>
     <row r="225" spans="1:26">
@@ -26976,10 +26976,10 @@
         <v>221</v>
       </c>
       <c r="Q225" s="5" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="R225" s="5" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="S225" s="5" t="s">
         <v>229</v>
@@ -27024,10 +27024,10 @@
         <v>31</v>
       </c>
       <c r="G226" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H226" s="3" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="I226" s="3">
         <v>8</v>
@@ -27054,10 +27054,10 @@
         <v>221</v>
       </c>
       <c r="Q226" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="R226" s="3" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="S226" s="3" t="s">
         <v>229</v>
@@ -27130,16 +27130,16 @@
         <v>221</v>
       </c>
       <c r="Q227" s="6" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="R227" s="6" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="S227" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T227" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U227" s="6" t="s">
         <v>44</v>
@@ -27178,10 +27178,10 @@
         <v>31</v>
       </c>
       <c r="G228" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H228" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I228" s="3">
         <v>8</v>
@@ -27208,10 +27208,10 @@
         <v>221</v>
       </c>
       <c r="Q228" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="R228" s="3" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="S228" s="3" t="s">
         <v>243</v>
@@ -27286,16 +27286,16 @@
         <v>221</v>
       </c>
       <c r="Q229" s="5" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="R229" s="5" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="S229" s="5" t="s">
         <v>243</v>
       </c>
       <c r="T229" s="5" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="U229" s="5" t="s">
         <v>127</v>
@@ -27364,16 +27364,16 @@
         <v>221</v>
       </c>
       <c r="Q230" s="3" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="R230" s="3" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="S230" s="3" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="T230" s="3" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="U230" s="3" t="s">
         <v>127</v>
@@ -27442,10 +27442,10 @@
         <v>264</v>
       </c>
       <c r="Q231" s="5" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="R231" s="5" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="S231" s="5" t="s">
         <v>255</v>
@@ -27490,10 +27490,10 @@
         <v>101</v>
       </c>
       <c r="G232" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H232" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="I232" s="3">
         <v>10</v>
@@ -27520,10 +27520,10 @@
         <v>264</v>
       </c>
       <c r="Q232" s="3" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="R232" s="3" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="S232" s="3" t="s">
         <v>42</v>
@@ -27598,10 +27598,10 @@
         <v>252</v>
       </c>
       <c r="Q233" s="5" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="R233" s="5" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="S233" s="5" t="s">
         <v>255</v>
@@ -27678,10 +27678,10 @@
         <v>252</v>
       </c>
       <c r="Q234" s="3" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="R234" s="3" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="S234" s="3" t="s">
         <v>255</v>
@@ -27726,16 +27726,16 @@
         <v>31</v>
       </c>
       <c r="G235" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="I235" s="5">
         <v>8</v>
       </c>
       <c r="J235" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K235" s="5" t="s">
         <v>34</v>
@@ -27756,16 +27756,16 @@
         <v>252</v>
       </c>
       <c r="Q235" s="5" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="R235" s="5" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="S235" s="5" t="s">
         <v>138</v>
       </c>
       <c r="T235" s="5" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="U235" s="5" t="s">
         <v>44</v>
@@ -27804,10 +27804,10 @@
         <v>31</v>
       </c>
       <c r="G236" s="3" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H236" s="3" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I236" s="3">
         <v>9</v>
@@ -27834,10 +27834,10 @@
         <v>264</v>
       </c>
       <c r="Q236" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="R236" s="3" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="S236" s="3" t="s">
         <v>267</v>
@@ -27861,7 +27861,7 @@
         <v>53</v>
       </c>
       <c r="Z236" s="3" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="237" spans="1:26">
@@ -27884,10 +27884,10 @@
         <v>31</v>
       </c>
       <c r="G237" s="5" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H237" s="5" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I237" s="5">
         <v>10</v>
@@ -27914,10 +27914,10 @@
         <v>264</v>
       </c>
       <c r="Q237" s="5" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="R237" s="5" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="S237" s="5" t="s">
         <v>42</v>
@@ -27992,10 +27992,10 @@
         <v>264</v>
       </c>
       <c r="Q238" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="R238" s="3" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="S238" s="3" t="s">
         <v>255</v>
@@ -28040,10 +28040,10 @@
         <v>31</v>
       </c>
       <c r="G239" s="5" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H239" s="5" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I239" s="5">
         <v>9</v>
@@ -28070,10 +28070,10 @@
         <v>264</v>
       </c>
       <c r="Q239" s="5" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="R239" s="5" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="S239" s="5" t="s">
         <v>267</v>
@@ -28118,10 +28118,10 @@
         <v>31</v>
       </c>
       <c r="G240" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H240" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I240" s="3">
         <v>8</v>
@@ -28148,10 +28148,10 @@
         <v>264</v>
       </c>
       <c r="Q240" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="R240" s="3" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="S240" s="3" t="s">
         <v>285</v>
@@ -28226,16 +28226,16 @@
         <v>264</v>
       </c>
       <c r="Q241" s="5" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="R241" s="5" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="S241" s="5" t="s">
         <v>125</v>
       </c>
       <c r="T241" s="5" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="U241" s="5" t="s">
         <v>127</v>
@@ -28274,10 +28274,10 @@
         <v>31</v>
       </c>
       <c r="G242" s="3" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H242" s="3" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I242" s="3">
         <v>8</v>
@@ -28304,16 +28304,16 @@
         <v>264</v>
       </c>
       <c r="Q242" s="3" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="R242" s="3" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="S242" s="3" t="s">
         <v>138</v>
       </c>
       <c r="T242" s="3" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="U242" s="3" t="s">
         <v>44</v>
@@ -28382,16 +28382,16 @@
         <v>264</v>
       </c>
       <c r="Q243" s="5" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="R243" s="5" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="S243" s="5" t="s">
         <v>255</v>
       </c>
       <c r="T243" s="5" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="U243" s="5" t="s">
         <v>44</v>
@@ -28460,10 +28460,10 @@
         <v>291</v>
       </c>
       <c r="Q244" s="3" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="R244" s="3" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="S244" s="3" t="s">
         <v>87</v>
@@ -28485,7 +28485,7 @@
         <v>53</v>
       </c>
       <c r="Z244" s="3" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="245" spans="1:26">
@@ -28508,10 +28508,10 @@
         <v>31</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I245" s="5">
         <v>7</v>
@@ -28538,10 +28538,10 @@
         <v>291</v>
       </c>
       <c r="Q245" s="5" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="R245" s="5" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="S245" s="5" t="s">
         <v>87</v>
@@ -28571,7 +28571,7 @@
         <v>620</v>
       </c>
       <c r="B246" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C246" s="3" t="s">
         <v>460</v>
@@ -28616,10 +28616,10 @@
         <v>461</v>
       </c>
       <c r="Q246" s="3" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="R246" s="3" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="S246" s="3" t="s">
         <v>285</v>
@@ -28651,7 +28651,7 @@
         <v>620</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C247" s="5" t="s">
         <v>460</v>
@@ -28696,16 +28696,16 @@
         <v>461</v>
       </c>
       <c r="Q247" s="5" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="R247" s="5" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="S247" s="5" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="T247" s="5" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="U247" s="5" t="s">
         <v>127</v>
@@ -28729,7 +28729,7 @@
         <v>620</v>
       </c>
       <c r="B248" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C248" s="3" t="s">
         <v>460</v>
@@ -28774,10 +28774,10 @@
         <v>466</v>
       </c>
       <c r="Q248" s="3" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="R248" s="3" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="S248" s="3" t="s">
         <v>469</v>
@@ -28801,7 +28801,7 @@
         <v>53</v>
       </c>
       <c r="Z248" s="3" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="249" spans="1:26">
@@ -28809,7 +28809,7 @@
         <v>620</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C249" s="5" t="s">
         <v>460</v>
@@ -28854,10 +28854,10 @@
         <v>466</v>
       </c>
       <c r="Q249" s="5" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="R249" s="5" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="S249" s="5" t="s">
         <v>285</v>
@@ -28887,16 +28887,16 @@
         <v>620</v>
       </c>
       <c r="B250" s="3" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="C250" s="3" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D250" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E250" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>31</v>
@@ -28929,13 +28929,13 @@
         <v>38</v>
       </c>
       <c r="P250" s="3" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="Q250" s="3" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="R250" s="3" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="S250" s="3" t="s">
         <v>77</v>
@@ -28959,7 +28959,7 @@
         <v>53</v>
       </c>
       <c r="Z250" s="3" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="251" spans="1:26">
@@ -28967,7 +28967,7 @@
         <v>620</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C251" s="5" t="s">
         <v>314</v>
@@ -28982,10 +28982,10 @@
         <v>31</v>
       </c>
       <c r="G251" s="5" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H251" s="5" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="I251" s="5">
         <v>9</v>
@@ -29012,10 +29012,10 @@
         <v>320</v>
       </c>
       <c r="Q251" s="5" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="R251" s="5" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="S251" s="5" t="s">
         <v>108</v>
@@ -29039,7 +29039,7 @@
         <v>53</v>
       </c>
       <c r="Z251" s="5" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="252" spans="1:26">
@@ -29047,7 +29047,7 @@
         <v>620</v>
       </c>
       <c r="B252" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C252" s="3" t="s">
         <v>70</v>
@@ -29092,10 +29092,10 @@
         <v>74</v>
       </c>
       <c r="Q252" s="3" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="R252" s="3" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="S252" s="3" t="s">
         <v>77</v>
@@ -29125,7 +29125,7 @@
         <v>620</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C253" s="5" t="s">
         <v>328</v>
@@ -29170,10 +29170,10 @@
         <v>331</v>
       </c>
       <c r="Q253" s="5" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="R253" s="5" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="S253" s="5" t="s">
         <v>97</v>
@@ -29197,7 +29197,7 @@
         <v>53</v>
       </c>
       <c r="Z253" s="5" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="254" spans="1:26">
@@ -29205,7 +29205,7 @@
         <v>620</v>
       </c>
       <c r="B254" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C254" s="3" t="s">
         <v>328</v>
@@ -29250,10 +29250,10 @@
         <v>337</v>
       </c>
       <c r="Q254" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="R254" s="3" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="S254" s="3" t="s">
         <v>340</v>
@@ -29277,7 +29277,7 @@
         <v>46</v>
       </c>
       <c r="Z254" s="3" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
     </row>
     <row r="255" spans="1:26">
@@ -29285,7 +29285,7 @@
         <v>620</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C255" s="5" t="s">
         <v>328</v>
@@ -29300,10 +29300,10 @@
         <v>31</v>
       </c>
       <c r="G255" s="5" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="H255" s="5" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="I255" s="5">
         <v>8</v>
@@ -29330,10 +29330,10 @@
         <v>337</v>
       </c>
       <c r="Q255" s="5" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="R255" s="5" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="S255" s="5" t="s">
         <v>340</v>
@@ -29359,89 +29359,89 @@
       <c r="Z255" s="5"/>
     </row>
     <row r="256" spans="1:26">
-      <c r="A256" s="6" t="s">
+      <c r="A256" s="7" t="s">
         <v>620</v>
       </c>
-      <c r="B256" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="C256" s="6" t="s">
+      <c r="B256" s="7" t="s">
+        <v>933</v>
+      </c>
+      <c r="C256" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="D256" s="6" t="s">
+      <c r="D256" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E256" s="6" t="s">
+      <c r="E256" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F256" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G256" s="6" t="s">
-        <v>964</v>
-      </c>
-      <c r="H256" s="6" t="s">
+      <c r="F256" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G256" s="7" t="s">
         <v>965</v>
       </c>
-      <c r="I256" s="6">
+      <c r="H256" s="7" t="s">
+        <v>966</v>
+      </c>
+      <c r="I256" s="7">
         <v>9</v>
       </c>
-      <c r="J256" s="6">
-        <v>0</v>
-      </c>
-      <c r="K256" s="6" t="s">
+      <c r="J256" s="7">
+        <v>1</v>
+      </c>
+      <c r="K256" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L256" s="6" t="s">
+      <c r="L256" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="M256" s="6" t="s">
+      <c r="M256" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="N256" s="6" t="s">
+      <c r="N256" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="O256" s="6" t="s">
+      <c r="O256" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P256" s="6" t="s">
+      <c r="P256" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="Q256" s="6" t="s">
-        <v>960</v>
-      </c>
-      <c r="R256" s="6" t="s">
-        <v>966</v>
-      </c>
-      <c r="S256" s="6" t="s">
+      <c r="Q256" s="7" t="s">
+        <v>961</v>
+      </c>
+      <c r="R256" s="7" t="s">
+        <v>967</v>
+      </c>
+      <c r="S256" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="T256" s="6" t="s">
+      <c r="T256" s="7" t="s">
         <v>491</v>
       </c>
-      <c r="U256" s="6" t="s">
+      <c r="U256" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V256" s="6">
+      <c r="V256" s="7">
         <v>2024</v>
       </c>
-      <c r="W256" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="X256" s="6" t="s">
+      <c r="W256" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X256" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="Y256" s="6" t="s">
+      <c r="Y256" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="Z256" s="6"/>
+      <c r="Z256" s="7"/>
     </row>
     <row r="257" spans="1:26">
       <c r="A257" s="5" t="s">
         <v>620</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C257" s="5" t="s">
         <v>80</v>
@@ -29456,10 +29456,10 @@
         <v>31</v>
       </c>
       <c r="G257" s="5" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H257" s="5" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I257" s="5">
         <v>7</v>
@@ -29486,10 +29486,10 @@
         <v>84</v>
       </c>
       <c r="Q257" s="5" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="R257" s="5" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="S257" s="5" t="s">
         <v>87</v>
@@ -29519,7 +29519,7 @@
         <v>620</v>
       </c>
       <c r="B258" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C258" s="3" t="s">
         <v>90</v>
@@ -29564,10 +29564,10 @@
         <v>94</v>
       </c>
       <c r="Q258" s="3" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="R258" s="3" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="S258" s="3" t="s">
         <v>97</v>
@@ -29591,7 +29591,7 @@
         <v>46</v>
       </c>
       <c r="Z258" s="3" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="259" spans="1:26">
@@ -29599,7 +29599,7 @@
         <v>620</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C259" s="5" t="s">
         <v>100</v>
@@ -29644,10 +29644,10 @@
         <v>105</v>
       </c>
       <c r="Q259" s="5" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="R259" s="5" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="S259" s="5" t="s">
         <v>108</v>
@@ -29671,7 +29671,7 @@
         <v>53</v>
       </c>
       <c r="Z259" s="5" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="260" spans="1:26">
@@ -29679,7 +29679,7 @@
         <v>620</v>
       </c>
       <c r="B260" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C260" s="3" t="s">
         <v>100</v>
@@ -29724,10 +29724,10 @@
         <v>105</v>
       </c>
       <c r="Q260" s="3" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="R260" s="3" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="S260" s="3" t="s">
         <v>108</v>
@@ -29757,7 +29757,7 @@
         <v>620</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C261" s="5" t="s">
         <v>154</v>
@@ -29802,10 +29802,10 @@
         <v>158</v>
       </c>
       <c r="Q261" s="5" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="R261" s="5" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="S261" s="5" t="s">
         <v>68</v>
@@ -29829,7 +29829,7 @@
         <v>53</v>
       </c>
       <c r="Z261" s="5" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
     </row>
     <row r="262" spans="1:26">
@@ -29837,7 +29837,7 @@
         <v>620</v>
       </c>
       <c r="B262" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C262" s="3" t="s">
         <v>154</v>
@@ -29852,10 +29852,10 @@
         <v>31</v>
       </c>
       <c r="G262" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="H262" s="3" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="I262" s="3">
         <v>9</v>
@@ -29882,10 +29882,10 @@
         <v>158</v>
       </c>
       <c r="Q262" s="3" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="R262" s="3" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="S262" s="3" t="s">
         <v>68</v>
@@ -29915,7 +29915,7 @@
         <v>620</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C263" s="5" t="s">
         <v>167</v>
@@ -29930,10 +29930,10 @@
         <v>31</v>
       </c>
       <c r="G263" s="5" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="H263" s="5" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="I263" s="5">
         <v>9</v>
@@ -29960,16 +29960,16 @@
         <v>170</v>
       </c>
       <c r="Q263" s="5" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="R263" s="5" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="S263" s="5" t="s">
         <v>97</v>
       </c>
       <c r="T263" s="5" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="U263" s="5" t="s">
         <v>44</v>
@@ -29995,7 +29995,7 @@
         <v>620</v>
       </c>
       <c r="B264" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C264" s="3" t="s">
         <v>167</v>
@@ -30040,16 +30040,16 @@
         <v>170</v>
       </c>
       <c r="Q264" s="3" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="R264" s="3" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="S264" s="3" t="s">
         <v>42</v>
       </c>
       <c r="T264" s="3" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="U264" s="3" t="s">
         <v>44</v>
@@ -30073,7 +30073,7 @@
         <v>620</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C265" s="5" t="s">
         <v>175</v>
@@ -30118,10 +30118,10 @@
         <v>178</v>
       </c>
       <c r="Q265" s="5" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="R265" s="5" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="S265" s="5" t="s">
         <v>68</v>
@@ -30145,7 +30145,7 @@
         <v>53</v>
       </c>
       <c r="Z265" s="5" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="266" spans="1:26">
@@ -30153,7 +30153,7 @@
         <v>620</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C266" s="6" t="s">
         <v>175</v>
@@ -30168,10 +30168,10 @@
         <v>31</v>
       </c>
       <c r="G266" s="6" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H266" s="6" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="I266" s="6">
         <v>9</v>
@@ -30198,16 +30198,16 @@
         <v>178</v>
       </c>
       <c r="Q266" s="6" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="R266" s="6" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="S266" s="6" t="s">
         <v>68</v>
       </c>
       <c r="T266" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U266" s="6" t="s">
         <v>44</v>
@@ -30231,7 +30231,7 @@
         <v>620</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C267" s="5" t="s">
         <v>175</v>
@@ -30246,10 +30246,10 @@
         <v>31</v>
       </c>
       <c r="G267" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H267" s="5" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I267" s="5">
         <v>9</v>
@@ -30276,10 +30276,10 @@
         <v>185</v>
       </c>
       <c r="Q267" s="5" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="R267" s="5" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="S267" s="5" t="s">
         <v>68</v>
@@ -30303,7 +30303,7 @@
         <v>53</v>
       </c>
       <c r="Z267" s="5" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="268" spans="1:26">
@@ -30311,7 +30311,7 @@
         <v>620</v>
       </c>
       <c r="B268" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C268" s="3" t="s">
         <v>175</v>
@@ -30356,10 +30356,10 @@
         <v>185</v>
       </c>
       <c r="Q268" s="3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="R268" s="3" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="S268" s="3" t="s">
         <v>392</v>
@@ -30389,7 +30389,7 @@
         <v>620</v>
       </c>
       <c r="B269" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C269" s="6" t="s">
         <v>175</v>
@@ -30404,10 +30404,10 @@
         <v>31</v>
       </c>
       <c r="G269" s="6" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="H269" s="6" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="I269" s="6">
         <v>9</v>
@@ -30434,10 +30434,10 @@
         <v>185</v>
       </c>
       <c r="Q269" s="6" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="R269" s="6" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="S269" s="6" t="s">
         <v>238</v>
@@ -30467,7 +30467,7 @@
         <v>620</v>
       </c>
       <c r="B270" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C270" s="3" t="s">
         <v>175</v>
@@ -30482,10 +30482,10 @@
         <v>31</v>
       </c>
       <c r="G270" s="3" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H270" s="3" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I270" s="3">
         <v>10</v>
@@ -30512,16 +30512,16 @@
         <v>185</v>
       </c>
       <c r="Q270" s="3" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="R270" s="3" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="S270" s="3" t="s">
         <v>108</v>
       </c>
       <c r="T270" s="3" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="U270" s="3" t="s">
         <v>44</v>
@@ -30545,7 +30545,7 @@
         <v>620</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C271" s="5" t="s">
         <v>199</v>
@@ -30560,10 +30560,10 @@
         <v>31</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H271" s="5" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I271" s="5">
         <v>8</v>
@@ -30590,10 +30590,10 @@
         <v>202</v>
       </c>
       <c r="Q271" s="5" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="R271" s="5" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="S271" s="5" t="s">
         <v>138</v>
@@ -30621,89 +30621,89 @@
       </c>
     </row>
     <row r="272" spans="1:26">
-      <c r="A272" s="6" t="s">
+      <c r="A272" s="3" t="s">
         <v>620</v>
       </c>
-      <c r="B272" s="6" t="s">
-        <v>932</v>
-      </c>
-      <c r="C272" s="6" t="s">
+      <c r="B272" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="C272" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D272" s="6" t="s">
+      <c r="D272" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E272" s="6" t="s">
+      <c r="E272" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F272" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G272" s="6" t="s">
-        <v>1007</v>
-      </c>
-      <c r="H272" s="6" t="s">
+      <c r="F272" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G272" s="3" t="s">
         <v>1008</v>
       </c>
-      <c r="I272" s="6">
+      <c r="H272" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="I272" s="3">
         <v>8</v>
       </c>
-      <c r="J272" s="6">
-        <v>0</v>
-      </c>
-      <c r="K272" s="6" t="s">
+      <c r="J272" s="3">
+        <v>2</v>
+      </c>
+      <c r="K272" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L272" s="6" t="s">
+      <c r="L272" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="M272" s="6" t="s">
+      <c r="M272" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="N272" s="6" t="s">
+      <c r="N272" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O272" s="6" t="s">
+      <c r="O272" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="P272" s="6" t="s">
+      <c r="P272" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="Q272" s="6" t="s">
-        <v>1005</v>
-      </c>
-      <c r="R272" s="6" t="s">
-        <v>1009</v>
-      </c>
-      <c r="S272" s="6" t="s">
+      <c r="Q272" s="3" t="s">
+        <v>1006</v>
+      </c>
+      <c r="R272" s="3" t="s">
+        <v>1010</v>
+      </c>
+      <c r="S272" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="T272" s="6" t="s">
-        <v>1010</v>
-      </c>
-      <c r="U272" s="6" t="s">
+      <c r="T272" s="3" t="s">
+        <v>1011</v>
+      </c>
+      <c r="U272" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V272" s="6">
+      <c r="V272" s="3">
         <v>2023</v>
       </c>
-      <c r="W272" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="X272" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="Y272" s="6" t="s">
+      <c r="W272" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X272" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="Y272" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Z272" s="6"/>
+      <c r="Z272" s="3"/>
     </row>
     <row r="273" spans="1:26">
       <c r="A273" s="5" t="s">
         <v>620</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C273" s="5" t="s">
         <v>211</v>
@@ -30748,10 +30748,10 @@
         <v>215</v>
       </c>
       <c r="Q273" s="5" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="R273" s="5" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="S273" s="5" t="s">
         <v>108</v>
@@ -30775,7 +30775,7 @@
         <v>53</v>
       </c>
       <c r="Z273" s="5" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="274" spans="1:26">
@@ -30783,7 +30783,7 @@
         <v>620</v>
       </c>
       <c r="B274" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C274" s="3" t="s">
         <v>211</v>
@@ -30828,16 +30828,16 @@
         <v>215</v>
       </c>
       <c r="Q274" s="3" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="R274" s="3" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="S274" s="3" t="s">
         <v>643</v>
       </c>
       <c r="T274" s="3" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="U274" s="3" t="s">
         <v>127</v>
@@ -30861,7 +30861,7 @@
         <v>620</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C275" s="5" t="s">
         <v>211</v>
@@ -30876,10 +30876,10 @@
         <v>31</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H275" s="5" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="I275" s="5">
         <v>9</v>
@@ -30906,10 +30906,10 @@
         <v>221</v>
       </c>
       <c r="Q275" s="5" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="R275" s="5" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="S275" s="5" t="s">
         <v>97</v>
@@ -30933,7 +30933,7 @@
         <v>53</v>
       </c>
       <c r="Z275" s="5" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="276" spans="1:26">
@@ -30941,7 +30941,7 @@
         <v>620</v>
       </c>
       <c r="B276" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C276" s="3" t="s">
         <v>211</v>
@@ -30956,10 +30956,10 @@
         <v>31</v>
       </c>
       <c r="G276" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H276" s="3" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I276" s="3">
         <v>8</v>
@@ -30986,10 +30986,10 @@
         <v>221</v>
       </c>
       <c r="Q276" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="R276" s="3" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="S276" s="3" t="s">
         <v>229</v>
@@ -31019,7 +31019,7 @@
         <v>620</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C277" s="5" t="s">
         <v>211</v>
@@ -31034,10 +31034,10 @@
         <v>31</v>
       </c>
       <c r="G277" s="5" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H277" s="5" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I277" s="5">
         <v>8</v>
@@ -31064,10 +31064,10 @@
         <v>221</v>
       </c>
       <c r="Q277" s="5" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="R277" s="5" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="S277" s="5" t="s">
         <v>229</v>
@@ -31097,7 +31097,7 @@
         <v>620</v>
       </c>
       <c r="B278" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C278" s="3" t="s">
         <v>211</v>
@@ -31112,16 +31112,16 @@
         <v>31</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="H278" s="3" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="I278" s="3">
         <v>8</v>
       </c>
       <c r="J278" s="3">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K278" s="3" t="s">
         <v>34</v>
@@ -31142,10 +31142,10 @@
         <v>221</v>
       </c>
       <c r="Q278" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="R278" s="3" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="S278" s="3" t="s">
         <v>229</v>
@@ -31175,7 +31175,7 @@
         <v>620</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C279" s="5" t="s">
         <v>211</v>
@@ -31220,10 +31220,10 @@
         <v>221</v>
       </c>
       <c r="Q279" s="5" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="R279" s="5" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="S279" s="5" t="s">
         <v>243</v>
@@ -31253,7 +31253,7 @@
         <v>620</v>
       </c>
       <c r="B280" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C280" s="3" t="s">
         <v>211</v>
@@ -31268,16 +31268,16 @@
         <v>31</v>
       </c>
       <c r="G280" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H280" s="3" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I280" s="3">
         <v>8</v>
       </c>
       <c r="J280" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K280" s="3" t="s">
         <v>34</v>
@@ -31298,16 +31298,16 @@
         <v>221</v>
       </c>
       <c r="Q280" s="3" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="R280" s="3" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="S280" s="3" t="s">
         <v>243</v>
       </c>
       <c r="T280" s="3" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="U280" s="3" t="s">
         <v>127</v>
@@ -31331,7 +31331,7 @@
         <v>620</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C281" s="5" t="s">
         <v>249</v>
@@ -31376,16 +31376,16 @@
         <v>264</v>
       </c>
       <c r="Q281" s="5" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="R281" s="5" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="S281" s="5" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="T281" s="5" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="U281" s="5" t="s">
         <v>44</v>
@@ -31403,7 +31403,7 @@
         <v>53</v>
       </c>
       <c r="Z281" s="5" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="282" spans="1:26">
@@ -31411,7 +31411,7 @@
         <v>620</v>
       </c>
       <c r="B282" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C282" s="3" t="s">
         <v>249</v>
@@ -31456,10 +31456,10 @@
         <v>264</v>
       </c>
       <c r="Q282" s="3" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="R282" s="3" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="S282" s="3" t="s">
         <v>255</v>
@@ -31489,7 +31489,7 @@
         <v>620</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C283" s="5" t="s">
         <v>249</v>
@@ -31504,10 +31504,10 @@
         <v>31</v>
       </c>
       <c r="G283" s="5" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H283" s="5" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="I283" s="5">
         <v>8</v>
@@ -31534,10 +31534,10 @@
         <v>252</v>
       </c>
       <c r="Q283" s="5" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="R283" s="5" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="S283" s="5" t="s">
         <v>255</v>
@@ -31561,7 +31561,7 @@
         <v>53</v>
       </c>
       <c r="Z283" s="5" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="284" spans="1:26">
@@ -31569,7 +31569,7 @@
         <v>620</v>
       </c>
       <c r="B284" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C284" s="3" t="s">
         <v>249</v>
@@ -31614,10 +31614,10 @@
         <v>252</v>
       </c>
       <c r="Q284" s="3" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="R284" s="3" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="S284" s="3" t="s">
         <v>255</v>
@@ -31647,7 +31647,7 @@
         <v>620</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C285" s="5" t="s">
         <v>249</v>
@@ -31662,10 +31662,10 @@
         <v>101</v>
       </c>
       <c r="G285" s="5" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I285" s="5">
         <v>9</v>
@@ -31692,10 +31692,10 @@
         <v>264</v>
       </c>
       <c r="Q285" s="5" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="R285" s="5" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="S285" s="5" t="s">
         <v>267</v>
@@ -31719,7 +31719,7 @@
         <v>53</v>
       </c>
       <c r="Z285" s="5" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="286" spans="1:26">
@@ -31727,7 +31727,7 @@
         <v>620</v>
       </c>
       <c r="B286" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C286" s="3" t="s">
         <v>249</v>
@@ -31772,10 +31772,10 @@
         <v>264</v>
       </c>
       <c r="Q286" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="R286" s="3" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="S286" s="3" t="s">
         <v>267</v>
@@ -31805,7 +31805,7 @@
         <v>620</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C287" s="5" t="s">
         <v>249</v>
@@ -31820,10 +31820,10 @@
         <v>101</v>
       </c>
       <c r="G287" s="5" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H287" s="5" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I287" s="5">
         <v>10</v>
@@ -31850,10 +31850,10 @@
         <v>264</v>
       </c>
       <c r="Q287" s="5" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="R287" s="5" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="S287" s="5" t="s">
         <v>42</v>
@@ -31883,7 +31883,7 @@
         <v>620</v>
       </c>
       <c r="B288" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C288" s="3" t="s">
         <v>249</v>
@@ -31898,10 +31898,10 @@
         <v>101</v>
       </c>
       <c r="G288" s="3" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="H288" s="3" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="I288" s="3">
         <v>10</v>
@@ -31928,10 +31928,10 @@
         <v>264</v>
       </c>
       <c r="Q288" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="R288" s="3" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="S288" s="3" t="s">
         <v>42</v>
@@ -31961,7 +31961,7 @@
         <v>620</v>
       </c>
       <c r="B289" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C289" s="6" t="s">
         <v>249</v>
@@ -31976,10 +31976,10 @@
         <v>101</v>
       </c>
       <c r="G289" s="6" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H289" s="6" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="I289" s="6">
         <v>8</v>
@@ -32006,16 +32006,16 @@
         <v>264</v>
       </c>
       <c r="Q289" s="6" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="R289" s="6" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="S289" s="6" t="s">
         <v>138</v>
       </c>
       <c r="T289" s="6" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="U289" s="6" t="s">
         <v>44</v>
@@ -32039,7 +32039,7 @@
         <v>620</v>
       </c>
       <c r="B290" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C290" s="3" t="s">
         <v>249</v>
@@ -32054,10 +32054,10 @@
         <v>101</v>
       </c>
       <c r="G290" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H290" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I290" s="3">
         <v>8</v>
@@ -32084,10 +32084,10 @@
         <v>264</v>
       </c>
       <c r="Q290" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="R290" s="3" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="S290" s="3" t="s">
         <v>285</v>
@@ -32117,7 +32117,7 @@
         <v>620</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C291" s="5" t="s">
         <v>249</v>
@@ -32132,10 +32132,10 @@
         <v>101</v>
       </c>
       <c r="G291" s="5" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H291" s="5" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="I291" s="5">
         <v>10</v>
@@ -32162,16 +32162,16 @@
         <v>264</v>
       </c>
       <c r="Q291" s="5" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="R291" s="5" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="S291" s="5" t="s">
         <v>108</v>
       </c>
       <c r="T291" s="5" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="U291" s="5" t="s">
         <v>44</v>
@@ -32195,7 +32195,7 @@
         <v>620</v>
       </c>
       <c r="B292" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C292" s="3" t="s">
         <v>249</v>
@@ -32210,10 +32210,10 @@
         <v>101</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H292" s="3" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="I292" s="3">
         <v>6</v>
@@ -32240,16 +32240,16 @@
         <v>264</v>
       </c>
       <c r="Q292" s="3" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="R292" s="3" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="S292" s="3" t="s">
         <v>243</v>
       </c>
       <c r="T292" s="3" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="U292" s="3" t="s">
         <v>127</v>
@@ -32270,10 +32270,10 @@
     </row>
     <row r="293" spans="1:26">
       <c r="A293" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C293" s="5" t="s">
         <v>460</v>
@@ -32318,10 +32318,10 @@
         <v>466</v>
       </c>
       <c r="Q293" s="5" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="R293" s="5" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="S293" s="5" t="s">
         <v>469</v>
@@ -32348,10 +32348,10 @@
     </row>
     <row r="294" spans="1:26">
       <c r="A294" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B294" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C294" s="3" t="s">
         <v>460</v>
@@ -32396,10 +32396,10 @@
         <v>466</v>
       </c>
       <c r="Q294" s="3" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="R294" s="3" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="S294" s="3" t="s">
         <v>285</v>
@@ -32426,28 +32426,28 @@
     </row>
     <row r="295" spans="1:26">
       <c r="A295" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D295" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E295" s="5" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>31</v>
       </c>
       <c r="G295" s="5" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H295" s="5" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="I295" s="5">
         <v>9</v>
@@ -32471,13 +32471,13 @@
         <v>38</v>
       </c>
       <c r="P295" s="5" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="Q295" s="5" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="R295" s="5" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="S295" s="5" t="s">
         <v>68</v>
@@ -32501,15 +32501,15 @@
         <v>53</v>
       </c>
       <c r="Z295" s="5" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="296" spans="1:26">
       <c r="A296" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B296" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C296" s="3" t="s">
         <v>70</v>
@@ -32554,7 +32554,7 @@
         <v>74</v>
       </c>
       <c r="Q296" s="3" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="R296" s="3" t="s">
         <v>507</v>
@@ -32584,10 +32584,10 @@
     </row>
     <row r="297" spans="1:26">
       <c r="A297" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C297" s="5" t="s">
         <v>328</v>
@@ -32632,10 +32632,10 @@
         <v>331</v>
       </c>
       <c r="Q297" s="5" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="R297" s="5" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="S297" s="5" t="s">
         <v>97</v>
@@ -32659,15 +32659,15 @@
         <v>53</v>
       </c>
       <c r="Z297" s="5" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="298" spans="1:26">
       <c r="A298" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B298" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C298" s="3" t="s">
         <v>328</v>
@@ -32712,10 +32712,10 @@
         <v>337</v>
       </c>
       <c r="Q298" s="3" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="R298" s="3" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="S298" s="3" t="s">
         <v>340</v>
@@ -32739,15 +32739,15 @@
         <v>46</v>
       </c>
       <c r="Z298" s="3" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="299" spans="1:26">
       <c r="A299" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C299" s="5" t="s">
         <v>328</v>
@@ -32792,10 +32792,10 @@
         <v>337</v>
       </c>
       <c r="Q299" s="5" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="R299" s="5" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="S299" s="5" t="s">
         <v>340</v>
@@ -32822,10 +32822,10 @@
     </row>
     <row r="300" spans="1:26">
       <c r="A300" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B300" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C300" s="6" t="s">
         <v>328</v>
@@ -32840,10 +32840,10 @@
         <v>31</v>
       </c>
       <c r="G300" s="6" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H300" s="6" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="I300" s="6">
         <v>10</v>
@@ -32870,16 +32870,16 @@
         <v>337</v>
       </c>
       <c r="Q300" s="6" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="R300" s="6" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="S300" s="6" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="T300" s="6" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="U300" s="6" t="s">
         <v>44</v>
@@ -32900,10 +32900,10 @@
     </row>
     <row r="301" spans="1:26">
       <c r="A301" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C301" s="5" t="s">
         <v>328</v>
@@ -32918,10 +32918,10 @@
         <v>31</v>
       </c>
       <c r="G301" s="5" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H301" s="5" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="I301" s="5">
         <v>8</v>
@@ -32948,16 +32948,16 @@
         <v>337</v>
       </c>
       <c r="Q301" s="5" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="R301" s="5" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="S301" s="5" t="s">
         <v>108</v>
       </c>
       <c r="T301" s="5" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="U301" s="5" t="s">
         <v>44</v>
@@ -32978,10 +32978,10 @@
     </row>
     <row r="302" spans="1:26">
       <c r="A302" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B302" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C302" s="3" t="s">
         <v>90</v>
@@ -32996,10 +32996,10 @@
         <v>31</v>
       </c>
       <c r="G302" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H302" s="3" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="I302" s="3">
         <v>10</v>
@@ -33023,13 +33023,13 @@
         <v>117</v>
       </c>
       <c r="P302" s="3" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="Q302" s="3" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="R302" s="3" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="S302" s="3" t="s">
         <v>108</v>
@@ -33053,15 +33053,15 @@
         <v>53</v>
       </c>
       <c r="Z302" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="303" spans="1:26">
       <c r="A303" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C303" s="5" t="s">
         <v>90</v>
@@ -33106,10 +33106,10 @@
         <v>94</v>
       </c>
       <c r="Q303" s="5" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="R303" s="5" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="S303" s="5" t="s">
         <v>97</v>
@@ -33133,15 +33133,15 @@
         <v>53</v>
       </c>
       <c r="Z303" s="5" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="304" spans="1:26">
       <c r="A304" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B304" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C304" s="3" t="s">
         <v>100</v>
@@ -33156,10 +33156,10 @@
         <v>31</v>
       </c>
       <c r="G304" s="3" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="H304" s="3" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="I304" s="3">
         <v>10</v>
@@ -33186,10 +33186,10 @@
         <v>105</v>
       </c>
       <c r="Q304" s="3" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="R304" s="3" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="S304" s="3" t="s">
         <v>108</v>
@@ -33213,15 +33213,15 @@
         <v>53</v>
       </c>
       <c r="Z304" s="3" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="305" spans="1:26">
       <c r="A305" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C305" s="5" t="s">
         <v>100</v>
@@ -33236,10 +33236,10 @@
         <v>31</v>
       </c>
       <c r="G305" s="5" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H305" s="5" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="I305" s="5">
         <v>10</v>
@@ -33266,10 +33266,10 @@
         <v>105</v>
       </c>
       <c r="Q305" s="5" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="R305" s="5" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="S305" s="5" t="s">
         <v>108</v>
@@ -33296,10 +33296,10 @@
     </row>
     <row r="306" spans="1:26">
       <c r="A306" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B306" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C306" s="3" t="s">
         <v>145</v>
@@ -33344,16 +33344,16 @@
         <v>149</v>
       </c>
       <c r="Q306" s="3" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="R306" s="3" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="S306" s="3" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="T306" s="3" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="U306" s="3" t="s">
         <v>127</v>
@@ -33376,10 +33376,10 @@
     </row>
     <row r="307" spans="1:26">
       <c r="A307" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C307" s="5" t="s">
         <v>154</v>
@@ -33424,10 +33424,10 @@
         <v>158</v>
       </c>
       <c r="Q307" s="5" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="R307" s="5" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="S307" s="5" t="s">
         <v>68</v>
@@ -33451,15 +33451,15 @@
         <v>53</v>
       </c>
       <c r="Z307" s="5" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="308" spans="1:26">
       <c r="A308" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B308" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C308" s="3" t="s">
         <v>154</v>
@@ -33474,10 +33474,10 @@
         <v>31</v>
       </c>
       <c r="G308" s="3" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H308" s="3" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="I308" s="3">
         <v>9</v>
@@ -33504,10 +33504,10 @@
         <v>158</v>
       </c>
       <c r="Q308" s="3" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="R308" s="3" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="S308" s="3" t="s">
         <v>68</v>
@@ -33534,10 +33534,10 @@
     </row>
     <row r="309" spans="1:26">
       <c r="A309" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C309" s="5" t="s">
         <v>167</v>
@@ -33552,16 +33552,16 @@
         <v>31</v>
       </c>
       <c r="G309" s="5" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H309" s="5" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="I309" s="5">
         <v>10</v>
       </c>
       <c r="J309" s="5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K309" s="5" t="s">
         <v>34</v>
@@ -33582,10 +33582,10 @@
         <v>170</v>
       </c>
       <c r="Q309" s="5" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="R309" s="5" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="S309" s="5" t="s">
         <v>108</v>
@@ -33609,15 +33609,15 @@
         <v>53</v>
       </c>
       <c r="Z309" s="5" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="310" spans="1:26">
       <c r="A310" s="7" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B310" s="7" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C310" s="7" t="s">
         <v>167</v>
@@ -33662,16 +33662,16 @@
         <v>170</v>
       </c>
       <c r="Q310" s="7" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="R310" s="7" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="S310" s="7" t="s">
         <v>392</v>
       </c>
       <c r="T310" s="7" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="U310" s="7" t="s">
         <v>44</v>
@@ -33692,10 +33692,10 @@
     </row>
     <row r="311" spans="1:26">
       <c r="A311" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C311" s="5" t="s">
         <v>175</v>
@@ -33740,10 +33740,10 @@
         <v>178</v>
       </c>
       <c r="Q311" s="5" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="R311" s="5" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="S311" s="5" t="s">
         <v>238</v>
@@ -33770,10 +33770,10 @@
     </row>
     <row r="312" spans="1:26">
       <c r="A312" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B312" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C312" s="3" t="s">
         <v>175</v>
@@ -33788,10 +33788,10 @@
         <v>31</v>
       </c>
       <c r="G312" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H312" s="3" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="I312" s="3">
         <v>9</v>
@@ -33818,10 +33818,10 @@
         <v>185</v>
       </c>
       <c r="Q312" s="3" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="R312" s="3" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="S312" s="3" t="s">
         <v>68</v>
@@ -33845,15 +33845,15 @@
         <v>53</v>
       </c>
       <c r="Z312" s="3" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="313" spans="1:26">
       <c r="A313" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C313" s="5" t="s">
         <v>175</v>
@@ -33898,7 +33898,7 @@
         <v>185</v>
       </c>
       <c r="Q313" s="5" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="R313" s="5" t="s">
         <v>636</v>
@@ -33928,10 +33928,10 @@
     </row>
     <row r="314" spans="1:26">
       <c r="A314" s="7" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B314" s="7" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C314" s="7" t="s">
         <v>175</v>
@@ -33946,10 +33946,10 @@
         <v>31</v>
       </c>
       <c r="G314" s="7" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="H314" s="7" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="I314" s="7">
         <v>8</v>
@@ -33976,16 +33976,16 @@
         <v>185</v>
       </c>
       <c r="Q314" s="7" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="R314" s="7" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="S314" s="7" t="s">
         <v>655</v>
       </c>
       <c r="T314" s="7" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="U314" s="7" t="s">
         <v>44</v>
@@ -34006,10 +34006,10 @@
     </row>
     <row r="315" spans="1:26">
       <c r="A315" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C315" s="5" t="s">
         <v>199</v>
@@ -34054,10 +34054,10 @@
         <v>202</v>
       </c>
       <c r="Q315" s="5" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="R315" s="5" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="S315" s="5" t="s">
         <v>138</v>
@@ -34086,10 +34086,10 @@
     </row>
     <row r="316" spans="1:26">
       <c r="A316" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B316" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C316" s="3" t="s">
         <v>199</v>
@@ -34134,10 +34134,10 @@
         <v>202</v>
       </c>
       <c r="Q316" s="3" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="R316" s="3" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="S316" s="3" t="s">
         <v>132</v>
@@ -34164,10 +34164,10 @@
     </row>
     <row r="317" spans="1:26">
       <c r="A317" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C317" s="5" t="s">
         <v>199</v>
@@ -34182,10 +34182,10 @@
         <v>31</v>
       </c>
       <c r="G317" s="5" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H317" s="5" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="I317" s="5">
         <v>8</v>
@@ -34212,16 +34212,16 @@
         <v>202</v>
       </c>
       <c r="Q317" s="5" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="R317" s="5" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="S317" s="5" t="s">
         <v>267</v>
       </c>
       <c r="T317" s="5" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="U317" s="5" t="s">
         <v>44</v>
@@ -34242,10 +34242,10 @@
     </row>
     <row r="318" spans="1:26">
       <c r="A318" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B318" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C318" s="3" t="s">
         <v>211</v>
@@ -34260,16 +34260,16 @@
         <v>101</v>
       </c>
       <c r="G318" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H318" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I318" s="3">
         <v>8</v>
       </c>
       <c r="J318" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K318" s="3" t="s">
         <v>34</v>
@@ -34290,10 +34290,10 @@
         <v>221</v>
       </c>
       <c r="Q318" s="3" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="R318" s="3" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="S318" s="3" t="s">
         <v>229</v>
@@ -34317,15 +34317,15 @@
         <v>53</v>
       </c>
       <c r="Z318" s="3" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="319" spans="1:26">
       <c r="A319" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C319" s="5" t="s">
         <v>211</v>
@@ -34340,10 +34340,10 @@
         <v>31</v>
       </c>
       <c r="G319" s="5" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H319" s="5" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I319" s="5">
         <v>9</v>
@@ -34370,10 +34370,10 @@
         <v>215</v>
       </c>
       <c r="Q319" s="5" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="R319" s="5" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="S319" s="5" t="s">
         <v>97</v>
@@ -34402,10 +34402,10 @@
     </row>
     <row r="320" spans="1:26">
       <c r="A320" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B320" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C320" s="6" t="s">
         <v>211</v>
@@ -34450,16 +34450,16 @@
         <v>215</v>
       </c>
       <c r="Q320" s="6" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="R320" s="6" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="S320" s="6" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="T320" s="6" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="U320" s="6" t="s">
         <v>44</v>
@@ -34480,10 +34480,10 @@
     </row>
     <row r="321" spans="1:26">
       <c r="A321" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C321" s="5" t="s">
         <v>211</v>
@@ -34528,10 +34528,10 @@
         <v>221</v>
       </c>
       <c r="Q321" s="5" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="R321" s="5" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="S321" s="5" t="s">
         <v>108</v>
@@ -34555,15 +34555,15 @@
         <v>53</v>
       </c>
       <c r="Z321" s="5" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="322" spans="1:26">
       <c r="A322" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B322" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C322" s="6" t="s">
         <v>211</v>
@@ -34578,10 +34578,10 @@
         <v>101</v>
       </c>
       <c r="G322" s="6" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="H322" s="6" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="I322" s="6">
         <v>8</v>
@@ -34608,10 +34608,10 @@
         <v>221</v>
       </c>
       <c r="Q322" s="6" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="R322" s="6" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="S322" s="6" t="s">
         <v>229</v>
@@ -34638,10 +34638,10 @@
     </row>
     <row r="323" spans="1:26">
       <c r="A323" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B323" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C323" s="6" t="s">
         <v>211</v>
@@ -34656,10 +34656,10 @@
         <v>101</v>
       </c>
       <c r="G323" s="6" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H323" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I323" s="6">
         <v>8</v>
@@ -34686,10 +34686,10 @@
         <v>221</v>
       </c>
       <c r="Q323" s="6" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="R323" s="6" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="S323" s="6" t="s">
         <v>229</v>
@@ -34716,10 +34716,10 @@
     </row>
     <row r="324" spans="1:26">
       <c r="A324" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B324" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C324" s="3" t="s">
         <v>211</v>
@@ -34734,10 +34734,10 @@
         <v>101</v>
       </c>
       <c r="G324" s="3" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H324" s="3" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="I324" s="3">
         <v>10</v>
@@ -34764,16 +34764,16 @@
         <v>221</v>
       </c>
       <c r="Q324" s="3" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="R324" s="3" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="S324" s="3" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="T324" s="3" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="U324" s="3" t="s">
         <v>127</v>
@@ -34794,10 +34794,10 @@
     </row>
     <row r="325" spans="1:26">
       <c r="A325" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C325" s="5" t="s">
         <v>211</v>
@@ -34812,10 +34812,10 @@
         <v>101</v>
       </c>
       <c r="G325" s="5" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H325" s="5" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I325" s="5">
         <v>8</v>
@@ -34842,16 +34842,16 @@
         <v>221</v>
       </c>
       <c r="Q325" s="5" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="R325" s="5" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="S325" s="5" t="s">
         <v>243</v>
       </c>
       <c r="T325" s="5" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="U325" s="5" t="s">
         <v>127</v>
@@ -34872,10 +34872,10 @@
     </row>
     <row r="326" spans="1:26">
       <c r="A326" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B326" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C326" s="3" t="s">
         <v>249</v>
@@ -34890,16 +34890,16 @@
         <v>31</v>
       </c>
       <c r="G326" s="3" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H326" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="I326" s="3">
         <v>8</v>
       </c>
       <c r="J326" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K326" s="3" t="s">
         <v>34</v>
@@ -34920,10 +34920,10 @@
         <v>252</v>
       </c>
       <c r="Q326" s="3" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="R326" s="3" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="S326" s="3" t="s">
         <v>255</v>
@@ -34947,15 +34947,15 @@
         <v>53</v>
       </c>
       <c r="Z326" s="3" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="327" spans="1:26">
       <c r="A327" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B327" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C327" s="6" t="s">
         <v>249</v>
@@ -34970,10 +34970,10 @@
         <v>31</v>
       </c>
       <c r="G327" s="6" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H327" s="6" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="I327" s="6">
         <v>8</v>
@@ -35000,10 +35000,10 @@
         <v>252</v>
       </c>
       <c r="Q327" s="6" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="R327" s="6" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="S327" s="6" t="s">
         <v>255</v>
@@ -35030,10 +35030,10 @@
     </row>
     <row r="328" spans="1:26">
       <c r="A328" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B328" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C328" s="6" t="s">
         <v>249</v>
@@ -35048,10 +35048,10 @@
         <v>31</v>
       </c>
       <c r="G328" s="6" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="H328" s="6" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="I328" s="6">
         <v>8</v>
@@ -35078,16 +35078,16 @@
         <v>252</v>
       </c>
       <c r="Q328" s="6" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="R328" s="6" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="S328" s="6" t="s">
         <v>255</v>
       </c>
       <c r="T328" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U328" s="6" t="s">
         <v>44</v>
@@ -35108,10 +35108,10 @@
     </row>
     <row r="329" spans="1:26">
       <c r="A329" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C329" s="5" t="s">
         <v>249</v>
@@ -35156,10 +35156,10 @@
         <v>264</v>
       </c>
       <c r="Q329" s="5" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="R329" s="5" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="S329" s="5" t="s">
         <v>267</v>
@@ -35183,15 +35183,15 @@
         <v>53</v>
       </c>
       <c r="Z329" s="5" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="330" spans="1:26">
       <c r="A330" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B330" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C330" s="3" t="s">
         <v>249</v>
@@ -35236,10 +35236,10 @@
         <v>264</v>
       </c>
       <c r="Q330" s="3" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="R330" s="3" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="S330" s="3" t="s">
         <v>267</v>
@@ -35266,10 +35266,10 @@
     </row>
     <row r="331" spans="1:26">
       <c r="A331" s="5" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C331" s="5" t="s">
         <v>249</v>
@@ -35284,10 +35284,10 @@
         <v>31</v>
       </c>
       <c r="G331" s="5" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H331" s="5" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I331" s="5">
         <v>8</v>
@@ -35314,10 +35314,10 @@
         <v>264</v>
       </c>
       <c r="Q331" s="5" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="R331" s="5" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="S331" s="5" t="s">
         <v>255</v>
@@ -35343,89 +35343,89 @@
       <c r="Z331" s="5"/>
     </row>
     <row r="332" spans="1:26">
-      <c r="A332" s="7" t="s">
-        <v>932</v>
-      </c>
-      <c r="B332" s="7" t="s">
-        <v>949</v>
-      </c>
-      <c r="C332" s="7" t="s">
+      <c r="A332" s="3" t="s">
+        <v>933</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="C332" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="D332" s="7" t="s">
+      <c r="D332" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E332" s="7" t="s">
+      <c r="E332" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F332" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G332" s="7" t="s">
-        <v>1172</v>
-      </c>
-      <c r="H332" s="7" t="s">
+      <c r="F332" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G332" s="3" t="s">
         <v>1173</v>
       </c>
-      <c r="I332" s="7">
+      <c r="H332" s="3" t="s">
+        <v>1174</v>
+      </c>
+      <c r="I332" s="3">
         <v>8</v>
       </c>
-      <c r="J332" s="7">
+      <c r="J332" s="3">
         <v>3</v>
       </c>
-      <c r="K332" s="7" t="s">
+      <c r="K332" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L332" s="7" t="s">
+      <c r="L332" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="M332" s="7" t="s">
+      <c r="M332" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="N332" s="7" t="s">
+      <c r="N332" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O332" s="7" t="s">
+      <c r="O332" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="P332" s="7" t="s">
+      <c r="P332" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="Q332" s="7" t="s">
-        <v>1167</v>
-      </c>
-      <c r="R332" s="7" t="s">
-        <v>1174</v>
-      </c>
-      <c r="S332" s="7" t="s">
+      <c r="Q332" s="3" t="s">
+        <v>1168</v>
+      </c>
+      <c r="R332" s="3" t="s">
+        <v>1175</v>
+      </c>
+      <c r="S332" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="T332" s="7" t="s">
+      <c r="T332" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="U332" s="7" t="s">
+      <c r="U332" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V332" s="7">
+      <c r="V332" s="3">
         <v>2015</v>
       </c>
-      <c r="W332" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X332" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="Y332" s="7" t="s">
+      <c r="W332" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X332" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="Y332" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Z332" s="7"/>
+      <c r="Z332" s="3"/>
     </row>
     <row r="333" spans="1:26">
       <c r="A333" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B333" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C333" s="6" t="s">
         <v>249</v>
@@ -35470,10 +35470,10 @@
         <v>264</v>
       </c>
       <c r="Q333" s="6" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="R333" s="6" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="S333" s="6" t="s">
         <v>42</v>
@@ -35500,10 +35500,10 @@
     </row>
     <row r="334" spans="1:26">
       <c r="A334" s="3" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C334" s="3" t="s">
         <v>249</v>
@@ -35518,10 +35518,10 @@
         <v>31</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H334" s="3" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="I334" s="3">
         <v>10</v>
@@ -35548,16 +35548,16 @@
         <v>264</v>
       </c>
       <c r="Q334" s="3" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="R334" s="3" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="S334" s="3" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="T334" s="3" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="U334" s="3" t="s">
         <v>127</v>
@@ -35578,13 +35578,13 @@
     </row>
     <row r="335" spans="1:26">
       <c r="A335" s="6" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B335" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D335" s="6" t="s">
         <v>212</v>
@@ -35596,10 +35596,10 @@
         <v>31</v>
       </c>
       <c r="G335" s="6" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="H335" s="6" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="I335" s="6">
         <v>8</v>
@@ -35614,28 +35614,28 @@
         <v>35</v>
       </c>
       <c r="M335" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N335" s="6" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O335" s="6" t="s">
         <v>117</v>
       </c>
       <c r="P335" s="6" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="Q335" s="6" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="R335" s="6" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="S335" s="6" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="T335" s="6" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="U335" s="6" t="s">
         <v>127</v>
@@ -35653,24 +35653,24 @@
         <v>53</v>
       </c>
       <c r="Z335" s="6" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="336" spans="1:26">
       <c r="A336" s="3" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C336" s="3" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D336" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F336" s="3" t="s">
         <v>31</v>
@@ -35703,13 +35703,13 @@
         <v>38</v>
       </c>
       <c r="P336" s="3" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="Q336" s="3" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="R336" s="3" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="S336" s="3" t="s">
         <v>77</v>
@@ -35738,10 +35738,10 @@
     </row>
     <row r="337" spans="1:26">
       <c r="A337" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B337" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C337" s="5" t="s">
         <v>460</v>
@@ -35756,10 +35756,10 @@
         <v>31</v>
       </c>
       <c r="G337" s="5" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="H337" s="5" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="I337" s="5">
         <v>8</v>
@@ -35786,10 +35786,10 @@
         <v>466</v>
       </c>
       <c r="Q337" s="5" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="R337" s="5" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="S337" s="5" t="s">
         <v>469</v>
@@ -35813,15 +35813,15 @@
         <v>53</v>
       </c>
       <c r="Z337" s="5" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="338" spans="1:26">
       <c r="A338" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>460</v>
@@ -35866,10 +35866,10 @@
         <v>466</v>
       </c>
       <c r="Q338" s="3" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="R338" s="3" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="S338" s="3" t="s">
         <v>285</v>
@@ -35887,7 +35887,7 @@
         <v>45</v>
       </c>
       <c r="X338" s="3" t="s">
-        <v>1201</v>
+        <v>806</v>
       </c>
       <c r="Y338" s="3" t="s">
         <v>53</v>
@@ -35896,10 +35896,10 @@
     </row>
     <row r="339" spans="1:26">
       <c r="A339" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C339" s="5" t="s">
         <v>328</v>
@@ -35976,10 +35976,10 @@
     </row>
     <row r="340" spans="1:26">
       <c r="A340" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C340" s="3" t="s">
         <v>328</v>
@@ -35994,10 +35994,10 @@
         <v>31</v>
       </c>
       <c r="G340" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H340" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="I340" s="3">
         <v>8</v>
@@ -36054,10 +36054,10 @@
     </row>
     <row r="341" spans="1:26">
       <c r="A341" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C341" s="5" t="s">
         <v>328</v>
@@ -36132,10 +36132,10 @@
     </row>
     <row r="342" spans="1:26">
       <c r="A342" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B342" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C342" s="6" t="s">
         <v>328</v>
@@ -36210,10 +36210,10 @@
     </row>
     <row r="343" spans="1:26">
       <c r="A343" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C343" s="5" t="s">
         <v>328</v>
@@ -36290,10 +36290,10 @@
     </row>
     <row r="344" spans="1:26">
       <c r="A344" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B344" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C344" s="6" t="s">
         <v>328</v>
@@ -36344,10 +36344,10 @@
         <v>1218</v>
       </c>
       <c r="S344" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T344" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U344" s="6" t="s">
         <v>44</v>
@@ -36368,10 +36368,10 @@
     </row>
     <row r="345" spans="1:26">
       <c r="A345" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C345" s="5" t="s">
         <v>328</v>
@@ -36448,10 +36448,10 @@
     </row>
     <row r="346" spans="1:26">
       <c r="A346" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B346" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C346" s="3" t="s">
         <v>328</v>
@@ -36502,7 +36502,7 @@
         <v>1225</v>
       </c>
       <c r="S346" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T346" s="3" t="s">
         <v>1226</v>
@@ -36526,10 +36526,10 @@
     </row>
     <row r="347" spans="1:26">
       <c r="A347" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B347" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C347" s="5" t="s">
         <v>328</v>
@@ -36604,10 +36604,10 @@
     </row>
     <row r="348" spans="1:26">
       <c r="A348" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C348" s="3" t="s">
         <v>90</v>
@@ -36631,7 +36631,7 @@
         <v>9</v>
       </c>
       <c r="J348" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K348" s="3" t="s">
         <v>34</v>
@@ -36684,10 +36684,10 @@
     </row>
     <row r="349" spans="1:26">
       <c r="A349" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B349" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C349" s="6" t="s">
         <v>90</v>
@@ -36711,7 +36711,7 @@
         <v>8</v>
       </c>
       <c r="J349" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K349" s="6" t="s">
         <v>34</v>
@@ -36762,10 +36762,10 @@
     </row>
     <row r="350" spans="1:26">
       <c r="A350" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C350" s="3" t="s">
         <v>100</v>
@@ -36842,10 +36842,10 @@
     </row>
     <row r="351" spans="1:26">
       <c r="A351" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B351" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C351" s="6" t="s">
         <v>100</v>
@@ -36918,10 +36918,10 @@
     </row>
     <row r="352" spans="1:26">
       <c r="A352" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C352" s="3" t="s">
         <v>100</v>
@@ -36936,10 +36936,10 @@
         <v>31</v>
       </c>
       <c r="G352" s="3" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="H352" s="3" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="I352" s="3">
         <v>8</v>
@@ -36996,10 +36996,10 @@
     </row>
     <row r="353" spans="1:26">
       <c r="A353" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B353" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C353" s="5" t="s">
         <v>154</v>
@@ -37076,10 +37076,10 @@
     </row>
     <row r="354" spans="1:26">
       <c r="A354" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C354" s="3" t="s">
         <v>167</v>
@@ -37156,10 +37156,10 @@
     </row>
     <row r="355" spans="1:26">
       <c r="A355" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B355" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C355" s="5" t="s">
         <v>175</v>
@@ -37174,10 +37174,10 @@
         <v>31</v>
       </c>
       <c r="G355" s="5" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H355" s="5" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I355" s="5">
         <v>9</v>
@@ -37236,10 +37236,10 @@
     </row>
     <row r="356" spans="1:26">
       <c r="A356" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C356" s="3" t="s">
         <v>175</v>
@@ -37305,7 +37305,7 @@
         <v>45</v>
       </c>
       <c r="X356" s="3" t="s">
-        <v>525</v>
+        <v>806</v>
       </c>
       <c r="Y356" s="3" t="s">
         <v>53</v>
@@ -37314,10 +37314,10 @@
     </row>
     <row r="357" spans="1:26">
       <c r="A357" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B357" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C357" s="6" t="s">
         <v>175</v>
@@ -37392,10 +37392,10 @@
     </row>
     <row r="358" spans="1:26">
       <c r="A358" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B358" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C358" s="3" t="s">
         <v>199</v>
@@ -37472,10 +37472,10 @@
     </row>
     <row r="359" spans="1:26">
       <c r="A359" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B359" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C359" s="5" t="s">
         <v>199</v>
@@ -37550,10 +37550,10 @@
     </row>
     <row r="360" spans="1:26">
       <c r="A360" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B360" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C360" s="3" t="s">
         <v>211</v>
@@ -37630,10 +37630,10 @@
     </row>
     <row r="361" spans="1:26">
       <c r="A361" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B361" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C361" s="6" t="s">
         <v>211</v>
@@ -37682,10 +37682,10 @@
         <v>1264</v>
       </c>
       <c r="S361" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T361" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U361" s="6" t="s">
         <v>44</v>
@@ -37706,10 +37706,10 @@
     </row>
     <row r="362" spans="1:26">
       <c r="A362" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C362" s="3" t="s">
         <v>211</v>
@@ -37733,7 +37733,7 @@
         <v>10</v>
       </c>
       <c r="J362" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K362" s="3" t="s">
         <v>34</v>
@@ -37786,10 +37786,10 @@
     </row>
     <row r="363" spans="1:26">
       <c r="A363" s="7" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B363" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C363" s="7" t="s">
         <v>211</v>
@@ -37864,10 +37864,10 @@
     </row>
     <row r="364" spans="1:26">
       <c r="A364" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B364" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C364" s="6" t="s">
         <v>211</v>
@@ -37942,10 +37942,10 @@
     </row>
     <row r="365" spans="1:26">
       <c r="A365" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B365" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C365" s="6" t="s">
         <v>211</v>
@@ -38020,10 +38020,10 @@
     </row>
     <row r="366" spans="1:26">
       <c r="A366" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B366" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C366" s="6" t="s">
         <v>211</v>
@@ -38038,10 +38038,10 @@
         <v>31</v>
       </c>
       <c r="G366" s="6" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H366" s="6" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I366" s="6">
         <v>8</v>
@@ -38074,10 +38074,10 @@
         <v>1277</v>
       </c>
       <c r="S366" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T366" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U366" s="6" t="s">
         <v>44</v>
@@ -38098,10 +38098,10 @@
     </row>
     <row r="367" spans="1:26">
       <c r="A367" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B367" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C367" s="5" t="s">
         <v>211</v>
@@ -38116,10 +38116,10 @@
         <v>31</v>
       </c>
       <c r="G367" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H367" s="5" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I367" s="5">
         <v>8</v>
@@ -38176,10 +38176,10 @@
     </row>
     <row r="368" spans="1:26">
       <c r="A368" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C368" s="3" t="s">
         <v>249</v>
@@ -38256,10 +38256,10 @@
     </row>
     <row r="369" spans="1:26">
       <c r="A369" s="5" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B369" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C369" s="5" t="s">
         <v>249</v>
@@ -38334,10 +38334,10 @@
     </row>
     <row r="370" spans="1:26">
       <c r="A370" s="3" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C370" s="3" t="s">
         <v>249</v>
@@ -38352,10 +38352,10 @@
         <v>31</v>
       </c>
       <c r="G370" s="3" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H370" s="3" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="I370" s="3">
         <v>10</v>
@@ -38391,7 +38391,7 @@
         <v>42</v>
       </c>
       <c r="T370" s="3" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="U370" s="3" t="s">
         <v>44</v>
@@ -38412,10 +38412,10 @@
     </row>
     <row r="371" spans="1:26">
       <c r="A371" s="7" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B371" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C371" s="7" t="s">
         <v>249</v>
@@ -38490,10 +38490,10 @@
     </row>
     <row r="372" spans="1:26">
       <c r="A372" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B372" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C372" s="6" t="s">
         <v>249</v>
@@ -38545,7 +38545,7 @@
         <v>42</v>
       </c>
       <c r="T372" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U372" s="6" t="s">
         <v>44</v>
@@ -38566,10 +38566,10 @@
     </row>
     <row r="373" spans="1:26">
       <c r="A373" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B373" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C373" s="6" t="s">
         <v>249</v>
@@ -38621,7 +38621,7 @@
         <v>255</v>
       </c>
       <c r="T373" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U373" s="6" t="s">
         <v>44</v>
@@ -38642,10 +38642,10 @@
     </row>
     <row r="374" spans="1:26">
       <c r="A374" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C374" s="4" t="s">
         <v>249</v>
@@ -38694,7 +38694,7 @@
         <v>1290</v>
       </c>
       <c r="S374" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="T374" s="4" t="s">
         <v>1291</v>
@@ -38718,13 +38718,13 @@
     </row>
     <row r="375" spans="1:26">
       <c r="A375" s="6" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B375" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="C375" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D375" s="6" t="s">
         <v>212</v>
@@ -38754,16 +38754,16 @@
         <v>35</v>
       </c>
       <c r="M375" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N375" s="6" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O375" s="6" t="s">
         <v>117</v>
       </c>
       <c r="P375" s="6" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="Q375" s="6" t="s">
         <v>1292</v>
@@ -38793,24 +38793,24 @@
         <v>53</v>
       </c>
       <c r="Z375" s="6" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="376" spans="1:26">
       <c r="A376" s="3" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>1295</v>
       </c>
       <c r="C376" s="3" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="D376" s="3" t="s">
         <v>29</v>
       </c>
       <c r="E376" s="3" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F376" s="3" t="s">
         <v>31</v>
@@ -38843,7 +38843,7 @@
         <v>38</v>
       </c>
       <c r="P376" s="3" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="Q376" s="3" t="s">
         <v>1298</v>
@@ -38878,7 +38878,7 @@
     </row>
     <row r="377" spans="1:26">
       <c r="A377" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B377" s="5" t="s">
         <v>1295</v>
@@ -38958,7 +38958,7 @@
     </row>
     <row r="378" spans="1:26">
       <c r="A378" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B378" s="7" t="s">
         <v>1295</v>
@@ -39036,7 +39036,7 @@
     </row>
     <row r="379" spans="1:26">
       <c r="A379" s="7" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B379" s="7" t="s">
         <v>1304</v>
@@ -39116,7 +39116,7 @@
     </row>
     <row r="380" spans="1:26">
       <c r="A380" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>1295</v>
@@ -39196,7 +39196,7 @@
     </row>
     <row r="381" spans="1:26">
       <c r="A381" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B381" s="6" t="s">
         <v>1295</v>
@@ -39274,7 +39274,7 @@
     </row>
     <row r="382" spans="1:26">
       <c r="A382" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B382" s="6" t="s">
         <v>1295</v>
@@ -39352,7 +39352,7 @@
     </row>
     <row r="383" spans="1:26">
       <c r="A383" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B383" s="5" t="s">
         <v>1295</v>
@@ -39432,7 +39432,7 @@
     </row>
     <row r="384" spans="1:26">
       <c r="A384" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B384" s="6" t="s">
         <v>1295</v>
@@ -39486,10 +39486,10 @@
         <v>1320</v>
       </c>
       <c r="S384" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T384" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U384" s="6" t="s">
         <v>44</v>
@@ -39510,7 +39510,7 @@
     </row>
     <row r="385" spans="1:26">
       <c r="A385" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B385" s="5" t="s">
         <v>1295</v>
@@ -39588,7 +39588,7 @@
     </row>
     <row r="386" spans="1:26">
       <c r="A386" s="4" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B386" s="4" t="s">
         <v>1295</v>
@@ -39640,7 +39640,7 @@
         <v>1323</v>
       </c>
       <c r="S386" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T386" s="4" t="s">
         <v>1324</v>
@@ -39664,7 +39664,7 @@
     </row>
     <row r="387" spans="1:26">
       <c r="A387" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B387" s="6" t="s">
         <v>1295</v>
@@ -39721,7 +39721,7 @@
         <v>97</v>
       </c>
       <c r="T387" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U387" s="6" t="s">
         <v>44</v>
@@ -39742,7 +39742,7 @@
     </row>
     <row r="388" spans="1:26">
       <c r="A388" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>1295</v>
@@ -39822,7 +39822,7 @@
     </row>
     <row r="389" spans="1:26">
       <c r="A389" s="4" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B389" s="4" t="s">
         <v>1295</v>
@@ -39898,7 +39898,7 @@
     </row>
     <row r="390" spans="1:26">
       <c r="A390" s="4" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B390" s="4" t="s">
         <v>1295</v>
@@ -39923,7 +39923,7 @@
         <v>10</v>
       </c>
       <c r="J390" s="4">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K390" s="4" t="s">
         <v>34</v>
@@ -39976,7 +39976,7 @@
     </row>
     <row r="391" spans="1:26">
       <c r="A391" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B391" s="5" t="s">
         <v>1295</v>
@@ -40054,7 +40054,7 @@
     </row>
     <row r="392" spans="1:26">
       <c r="A392" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>1295</v>
@@ -40108,7 +40108,7 @@
         <v>1344</v>
       </c>
       <c r="S392" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T392" s="3" t="s">
         <v>1345</v>
@@ -40132,7 +40132,7 @@
     </row>
     <row r="393" spans="1:26">
       <c r="A393" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B393" s="5" t="s">
         <v>1295</v>
@@ -40212,7 +40212,7 @@
     </row>
     <row r="394" spans="1:26">
       <c r="A394" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>1295</v>
@@ -40290,7 +40290,7 @@
     </row>
     <row r="395" spans="1:26">
       <c r="A395" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B395" s="6" t="s">
         <v>1295</v>
@@ -40308,10 +40308,10 @@
         <v>101</v>
       </c>
       <c r="G395" s="6" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H395" s="6" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="I395" s="6">
         <v>9</v>
@@ -40368,7 +40368,7 @@
     </row>
     <row r="396" spans="1:26">
       <c r="A396" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>1295</v>
@@ -40446,7 +40446,7 @@
     </row>
     <row r="397" spans="1:26">
       <c r="A397" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B397" s="5" t="s">
         <v>1295</v>
@@ -40526,7 +40526,7 @@
     </row>
     <row r="398" spans="1:26">
       <c r="A398" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>1295</v>
@@ -40606,7 +40606,7 @@
     </row>
     <row r="399" spans="1:26">
       <c r="A399" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B399" s="6" t="s">
         <v>1295</v>
@@ -40684,7 +40684,7 @@
     </row>
     <row r="400" spans="1:26">
       <c r="A400" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B400" s="6" t="s">
         <v>1295</v>
@@ -40762,7 +40762,7 @@
     </row>
     <row r="401" spans="1:26">
       <c r="A401" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B401" s="6" t="s">
         <v>1295</v>
@@ -40819,7 +40819,7 @@
         <v>229</v>
       </c>
       <c r="T401" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U401" s="6" t="s">
         <v>44</v>
@@ -40840,7 +40840,7 @@
     </row>
     <row r="402" spans="1:26">
       <c r="A402" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>1295</v>
@@ -40918,7 +40918,7 @@
     </row>
     <row r="403" spans="1:26">
       <c r="A403" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B403" s="5" t="s">
         <v>1295</v>
@@ -40996,7 +40996,7 @@
     </row>
     <row r="404" spans="1:26">
       <c r="A404" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>1295</v>
@@ -41074,7 +41074,7 @@
     </row>
     <row r="405" spans="1:26">
       <c r="A405" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B405" s="5" t="s">
         <v>1295</v>
@@ -41154,7 +41154,7 @@
     </row>
     <row r="406" spans="1:26">
       <c r="A406" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B406" s="6" t="s">
         <v>1295</v>
@@ -41211,7 +41211,7 @@
         <v>1378</v>
       </c>
       <c r="T406" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U406" s="6" t="s">
         <v>44</v>
@@ -41232,7 +41232,7 @@
     </row>
     <row r="407" spans="1:26">
       <c r="A407" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B407" s="5" t="s">
         <v>1384</v>
@@ -41271,7 +41271,7 @@
         <v>1390</v>
       </c>
       <c r="N407" s="5" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O407" s="5" t="s">
         <v>38</v>
@@ -41312,7 +41312,7 @@
     </row>
     <row r="408" spans="1:26">
       <c r="A408" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>1384</v>
@@ -41351,7 +41351,7 @@
         <v>1390</v>
       </c>
       <c r="N408" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O408" s="3" t="s">
         <v>38</v>
@@ -41390,7 +41390,7 @@
     </row>
     <row r="409" spans="1:26">
       <c r="A409" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B409" s="5" t="s">
         <v>1384</v>
@@ -41429,7 +41429,7 @@
         <v>1390</v>
       </c>
       <c r="N409" s="5" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O409" s="5" t="s">
         <v>38</v>
@@ -41468,7 +41468,7 @@
     </row>
     <row r="410" spans="1:26">
       <c r="A410" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>1384</v>
@@ -41507,7 +41507,7 @@
         <v>1390</v>
       </c>
       <c r="N410" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O410" s="3" t="s">
         <v>38</v>
@@ -41546,7 +41546,7 @@
     </row>
     <row r="411" spans="1:26">
       <c r="A411" s="5" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B411" s="5" t="s">
         <v>1295</v>
@@ -41626,7 +41626,7 @@
     </row>
     <row r="412" spans="1:26">
       <c r="A412" s="3" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>1295</v>
@@ -41704,7 +41704,7 @@
     </row>
     <row r="413" spans="1:26">
       <c r="A413" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B413" s="6" t="s">
         <v>1295</v>
@@ -41782,7 +41782,7 @@
     </row>
     <row r="414" spans="1:26">
       <c r="A414" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B414" s="6" t="s">
         <v>1295</v>
@@ -41860,7 +41860,7 @@
     </row>
     <row r="415" spans="1:26">
       <c r="A415" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B415" s="6" t="s">
         <v>1295</v>
@@ -41917,7 +41917,7 @@
         <v>42</v>
       </c>
       <c r="T415" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U415" s="6" t="s">
         <v>44</v>
@@ -41938,7 +41938,7 @@
     </row>
     <row r="416" spans="1:26">
       <c r="A416" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B416" s="6" t="s">
         <v>1295</v>
@@ -41995,7 +41995,7 @@
         <v>255</v>
       </c>
       <c r="T416" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U416" s="6" t="s">
         <v>44</v>
@@ -42016,13 +42016,13 @@
     </row>
     <row r="417" spans="1:26">
       <c r="A417" s="6" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B417" s="6" t="s">
         <v>1295</v>
       </c>
       <c r="C417" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D417" s="6" t="s">
         <v>212</v>
@@ -42052,16 +42052,16 @@
         <v>35</v>
       </c>
       <c r="M417" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N417" s="6" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O417" s="6" t="s">
         <v>117</v>
       </c>
       <c r="P417" s="6" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="Q417" s="6" t="s">
         <v>1415</v>
@@ -42309,7 +42309,7 @@
         <v>340</v>
       </c>
       <c r="T420" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U420" s="6" t="s">
         <v>44</v>
@@ -42458,10 +42458,10 @@
         <v>1425</v>
       </c>
       <c r="S422" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T422" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U422" s="6" t="s">
         <v>44</v>
@@ -42616,7 +42616,7 @@
         <v>1429</v>
       </c>
       <c r="S424" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T424" s="3" t="s">
         <v>1226</v>
@@ -42827,7 +42827,7 @@
         <v>9</v>
       </c>
       <c r="J427" s="5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K427" s="5" t="s">
         <v>34</v>
@@ -43035,82 +43035,82 @@
       </c>
     </row>
     <row r="430" spans="1:26">
-      <c r="A430" s="7" t="s">
+      <c r="A430" s="3" t="s">
         <v>1295</v>
       </c>
-      <c r="B430" s="7" t="s">
+      <c r="B430" s="3" t="s">
         <v>1384</v>
       </c>
-      <c r="C430" s="7" t="s">
+      <c r="C430" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="D430" s="7" t="s">
+      <c r="D430" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E430" s="7" t="s">
+      <c r="E430" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="F430" s="7" t="s">
+      <c r="F430" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G430" s="7" t="s">
+      <c r="G430" s="3" t="s">
         <v>1442</v>
       </c>
-      <c r="H430" s="7" t="s">
+      <c r="H430" s="3" t="s">
         <v>1443</v>
       </c>
-      <c r="I430" s="7">
+      <c r="I430" s="3">
         <v>9</v>
       </c>
-      <c r="J430" s="7">
+      <c r="J430" s="3">
         <v>2</v>
       </c>
-      <c r="K430" s="7" t="s">
+      <c r="K430" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="L430" s="7" t="s">
+      <c r="L430" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="M430" s="7" t="s">
+      <c r="M430" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="N430" s="7" t="s">
+      <c r="N430" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="O430" s="7" t="s">
+      <c r="O430" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="P430" s="7" t="s">
+      <c r="P430" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="Q430" s="7" t="s">
+      <c r="Q430" s="3" t="s">
         <v>1439</v>
       </c>
-      <c r="R430" s="7" t="s">
+      <c r="R430" s="3" t="s">
         <v>1444</v>
       </c>
-      <c r="S430" s="7" t="s">
+      <c r="S430" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="T430" s="7" t="s">
+      <c r="T430" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="U430" s="7" t="s">
+      <c r="U430" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="V430" s="7">
+      <c r="V430" s="3">
         <v>2023</v>
       </c>
-      <c r="W430" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X430" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="Y430" s="7" t="s">
+      <c r="W430" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="X430" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="Y430" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="Z430" s="7"/>
+      <c r="Z430" s="3"/>
     </row>
     <row r="431" spans="1:26">
       <c r="A431" s="6" t="s">
@@ -43171,7 +43171,7 @@
         <v>229</v>
       </c>
       <c r="T431" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U431" s="6" t="s">
         <v>44</v>
@@ -43561,7 +43561,7 @@
         <v>1378</v>
       </c>
       <c r="T436" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U436" s="6" t="s">
         <v>44</v>
@@ -43887,7 +43887,7 @@
         <v>45</v>
       </c>
       <c r="X440" s="3" t="s">
-        <v>1201</v>
+        <v>806</v>
       </c>
       <c r="Y440" s="3" t="s">
         <v>53</v>
@@ -43914,10 +43914,10 @@
         <v>31</v>
       </c>
       <c r="G441" s="6" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H441" s="6" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I441" s="6">
         <v>8</v>
@@ -43980,7 +43980,7 @@
         <v>1384</v>
       </c>
       <c r="C442" s="3" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D442" s="3" t="s">
         <v>212</v>
@@ -44010,16 +44010,16 @@
         <v>35</v>
       </c>
       <c r="M442" s="3" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N442" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O442" s="3" t="s">
         <v>117</v>
       </c>
       <c r="P442" s="3" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="Q442" s="3" t="s">
         <v>1463</v>
@@ -44028,10 +44028,10 @@
         <v>1464</v>
       </c>
       <c r="S442" s="3" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="T442" s="3" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="U442" s="3" t="s">
         <v>127</v>
@@ -44043,7 +44043,7 @@
         <v>45</v>
       </c>
       <c r="X442" s="3" t="s">
-        <v>525</v>
+        <v>45</v>
       </c>
       <c r="Y442" s="3" t="s">
         <v>53</v>
@@ -44228,10 +44228,10 @@
         <v>31</v>
       </c>
       <c r="G445" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H445" s="5" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I445" s="5">
         <v>6</v>
@@ -44393,7 +44393,7 @@
         <v>6</v>
       </c>
       <c r="J447" s="5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K447" s="5" t="s">
         <v>34</v>
@@ -44897,7 +44897,7 @@
         <v>108</v>
       </c>
       <c r="T453" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U453" s="6" t="s">
         <v>44</v>
@@ -45339,7 +45339,7 @@
         <v>6</v>
       </c>
       <c r="J459" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K459" s="5" t="s">
         <v>34</v>
@@ -45449,7 +45449,7 @@
         <v>1378</v>
       </c>
       <c r="T460" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U460" s="6" t="s">
         <v>44</v>
@@ -45587,7 +45587,7 @@
         <v>1390</v>
       </c>
       <c r="N462" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O462" s="3" t="s">
         <v>38</v>
@@ -45667,7 +45667,7 @@
         <v>1390</v>
       </c>
       <c r="N463" s="5" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O463" s="5" t="s">
         <v>38</v>
@@ -45745,7 +45745,7 @@
         <v>1390</v>
       </c>
       <c r="N464" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O464" s="3" t="s">
         <v>38</v>
@@ -45823,7 +45823,7 @@
         <v>1390</v>
       </c>
       <c r="N465" s="5" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O465" s="5" t="s">
         <v>38</v>
@@ -45868,7 +45868,7 @@
         <v>1475</v>
       </c>
       <c r="C466" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D466" s="6" t="s">
         <v>212</v>
@@ -45898,16 +45898,16 @@
         <v>35</v>
       </c>
       <c r="M466" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N466" s="6" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O466" s="6" t="s">
         <v>117</v>
       </c>
       <c r="P466" s="6" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="Q466" s="6" t="s">
         <v>1525</v>
@@ -45916,10 +45916,10 @@
         <v>1526</v>
       </c>
       <c r="S466" s="6" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="T466" s="6" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="U466" s="6" t="s">
         <v>127</v>
@@ -46076,10 +46076,10 @@
         <v>1530</v>
       </c>
       <c r="S468" s="6" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T468" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U468" s="6" t="s">
         <v>44</v>
@@ -46179,82 +46179,82 @@
       </c>
     </row>
     <row r="470" spans="1:26">
-      <c r="A470" s="6" t="s">
+      <c r="A470" s="7" t="s">
         <v>1475</v>
       </c>
-      <c r="B470" s="6" t="s">
+      <c r="B470" s="7" t="s">
         <v>1517</v>
       </c>
-      <c r="C470" s="6" t="s">
+      <c r="C470" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="D470" s="6" t="s">
+      <c r="D470" s="7" t="s">
         <v>1212</v>
       </c>
-      <c r="E470" s="6" t="s">
+      <c r="E470" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F470" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G470" s="6" t="s">
-        <v>1051</v>
-      </c>
-      <c r="H470" s="6" t="s">
+      <c r="F470" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G470" s="7" t="s">
         <v>1052</v>
       </c>
-      <c r="I470" s="6">
+      <c r="H470" s="7" t="s">
+        <v>1053</v>
+      </c>
+      <c r="I470" s="7">
         <v>6</v>
       </c>
-      <c r="J470" s="6">
-        <v>0</v>
-      </c>
-      <c r="K470" s="6" t="s">
+      <c r="J470" s="7">
+        <v>1</v>
+      </c>
+      <c r="K470" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L470" s="6" t="s">
+      <c r="L470" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="M470" s="6" t="s">
+      <c r="M470" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="N470" s="6" t="s">
+      <c r="N470" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="O470" s="6" t="s">
+      <c r="O470" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="P470" s="6" t="s">
+      <c r="P470" s="7" t="s">
         <v>1221</v>
       </c>
-      <c r="Q470" s="6" t="s">
+      <c r="Q470" s="7" t="s">
         <v>1531</v>
       </c>
-      <c r="R470" s="6" t="s">
+      <c r="R470" s="7" t="s">
         <v>1534</v>
       </c>
-      <c r="S470" s="6" t="s">
-        <v>883</v>
-      </c>
-      <c r="T470" s="6" t="s">
+      <c r="S470" s="7" t="s">
+        <v>884</v>
+      </c>
+      <c r="T470" s="7" t="s">
         <v>1226</v>
       </c>
-      <c r="U470" s="6" t="s">
+      <c r="U470" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="V470" s="6">
+      <c r="V470" s="7">
         <v>2017</v>
       </c>
-      <c r="W470" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="X470" s="6" t="s">
+      <c r="W470" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X470" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="Y470" s="6" t="s">
+      <c r="Y470" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="Z470" s="6"/>
+      <c r="Z470" s="7"/>
     </row>
     <row r="471" spans="1:26">
       <c r="A471" s="5" t="s">
@@ -46592,10 +46592,10 @@
         <v>101</v>
       </c>
       <c r="G475" s="7" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H475" s="7" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="I475" s="7">
         <v>8</v>
@@ -46789,7 +46789,7 @@
         <v>229</v>
       </c>
       <c r="T477" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U477" s="6" t="s">
         <v>44</v>
@@ -46986,10 +46986,10 @@
         <v>31</v>
       </c>
       <c r="G480" s="6" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="H480" s="6" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="I480" s="6">
         <v>6</v>
@@ -47025,7 +47025,7 @@
         <v>1378</v>
       </c>
       <c r="T480" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U480" s="6" t="s">
         <v>44</v>
@@ -47052,7 +47052,7 @@
         <v>1517</v>
       </c>
       <c r="C481" s="7" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D481" s="7" t="s">
         <v>212</v>
@@ -47082,16 +47082,16 @@
         <v>63</v>
       </c>
       <c r="M481" s="7" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N481" s="7" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O481" s="7" t="s">
         <v>117</v>
       </c>
       <c r="P481" s="7" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="Q481" s="7" t="s">
         <v>1558</v>
@@ -47100,10 +47100,10 @@
         <v>1559</v>
       </c>
       <c r="S481" s="7" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="T481" s="7" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="U481" s="7" t="s">
         <v>127</v>
@@ -47300,10 +47300,10 @@
         <v>31</v>
       </c>
       <c r="G484" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H484" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I484" s="3">
         <v>6</v>
@@ -47602,7 +47602,7 @@
         <v>1576</v>
       </c>
       <c r="C488" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="D488" s="6" t="s">
         <v>212</v>
@@ -47632,16 +47632,16 @@
         <v>63</v>
       </c>
       <c r="M488" s="6" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="N488" s="6" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O488" s="6" t="s">
         <v>117</v>
       </c>
       <c r="P488" s="6" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="Q488" s="6" t="s">
         <v>1577</v>
@@ -47650,10 +47650,10 @@
         <v>1578</v>
       </c>
       <c r="S488" s="6" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="T488" s="6" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="U488" s="6" t="s">
         <v>127</v>
@@ -47852,10 +47852,10 @@
         <v>31</v>
       </c>
       <c r="G491" s="5" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H491" s="5" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I491" s="5">
         <v>8</v>
@@ -48010,16 +48010,16 @@
         <v>31</v>
       </c>
       <c r="G493" s="6" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H493" s="6" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I493" s="6">
         <v>8</v>
       </c>
       <c r="J493" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K493" s="6" t="s">
         <v>1388</v>
@@ -48046,7 +48046,7 @@
         <v>1600</v>
       </c>
       <c r="S493" s="6" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="T493" s="6" t="s">
         <v>1601</v>
@@ -48082,7 +48082,7 @@
         <v>29</v>
       </c>
       <c r="E494" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F494" s="3" t="s">
         <v>31</v>
@@ -48097,7 +48097,7 @@
         <v>8</v>
       </c>
       <c r="J494" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K494" s="3" t="s">
         <v>1388</v>
@@ -48109,7 +48109,7 @@
         <v>1604</v>
       </c>
       <c r="N494" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O494" s="3" t="s">
         <v>38</v>
@@ -48162,7 +48162,7 @@
         <v>29</v>
       </c>
       <c r="E495" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F495" s="4" t="s">
         <v>31</v>
@@ -48187,7 +48187,7 @@
         <v>1604</v>
       </c>
       <c r="N495" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O495" s="4" t="s">
         <v>38</v>
@@ -48244,10 +48244,10 @@
         <v>31</v>
       </c>
       <c r="G496" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H496" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="I496" s="3">
         <v>9</v>
@@ -48301,7 +48301,7 @@
         <v>53</v>
       </c>
       <c r="Z496" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="497" spans="1:26">
@@ -48318,7 +48318,7 @@
         <v>29</v>
       </c>
       <c r="E497" s="5" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F497" s="5" t="s">
         <v>31</v>
@@ -48491,7 +48491,7 @@
         <v>8</v>
       </c>
       <c r="J499" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K499" s="6" t="s">
         <v>1388</v>
@@ -48581,7 +48581,7 @@
         <v>1604</v>
       </c>
       <c r="N500" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O500" s="3" t="s">
         <v>38</v>
@@ -48634,7 +48634,7 @@
         <v>29</v>
       </c>
       <c r="E501" s="5" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F501" s="5" t="s">
         <v>101</v>
@@ -48649,7 +48649,7 @@
         <v>8</v>
       </c>
       <c r="J501" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K501" s="5" t="s">
         <v>1388</v>
@@ -48661,7 +48661,7 @@
         <v>1604</v>
       </c>
       <c r="N501" s="5" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O501" s="5" t="s">
         <v>38</v>
@@ -48714,7 +48714,7 @@
         <v>29</v>
       </c>
       <c r="E502" s="7" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F502" s="7" t="s">
         <v>101</v>
@@ -48741,7 +48741,7 @@
         <v>1604</v>
       </c>
       <c r="N502" s="7" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O502" s="7" t="s">
         <v>38</v>
@@ -48792,7 +48792,7 @@
         <v>1647</v>
       </c>
       <c r="E503" s="5" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F503" s="5" t="s">
         <v>31</v>
@@ -48819,7 +48819,7 @@
         <v>1604</v>
       </c>
       <c r="N503" s="5" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O503" s="5" t="s">
         <v>117</v>
@@ -48872,7 +48872,7 @@
         <v>29</v>
       </c>
       <c r="E504" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F504" s="3" t="s">
         <v>101</v>
@@ -48899,7 +48899,7 @@
         <v>1604</v>
       </c>
       <c r="N504" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O504" s="3" t="s">
         <v>38</v>
@@ -49391,7 +49391,7 @@
         <v>285</v>
       </c>
       <c r="T510" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U510" s="4" t="s">
         <v>127</v>
@@ -49466,7 +49466,7 @@
         <v>1678</v>
       </c>
       <c r="S511" s="5" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="T511" s="5" t="s">
         <v>1679</v>
@@ -49510,16 +49510,16 @@
         <v>31</v>
       </c>
       <c r="G512" s="7" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H512" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I512" s="7">
         <v>7</v>
       </c>
       <c r="J512" s="7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K512" s="7" t="s">
         <v>1388</v>
@@ -49588,10 +49588,10 @@
         <v>31</v>
       </c>
       <c r="G513" s="5" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="H513" s="5" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="I513" s="5">
         <v>9</v>
@@ -49707,7 +49707,7 @@
         <v>132</v>
       </c>
       <c r="T514" s="7" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U514" s="7" t="s">
         <v>44</v>
@@ -49740,7 +49740,7 @@
         <v>29</v>
       </c>
       <c r="E515" s="5" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F515" s="5" t="s">
         <v>31</v>
@@ -49911,7 +49911,7 @@
         <v>9</v>
       </c>
       <c r="J517" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K517" s="5" t="s">
         <v>1388</v>
@@ -50018,7 +50018,7 @@
         <v>1701</v>
       </c>
       <c r="S518" s="3" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="T518" s="3" t="s">
         <v>1679</v>
@@ -50060,10 +50060,10 @@
         <v>31</v>
       </c>
       <c r="G519" s="7" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H519" s="7" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I519" s="7">
         <v>7</v>
@@ -50255,7 +50255,7 @@
         <v>132</v>
       </c>
       <c r="T521" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U521" s="4" t="s">
         <v>44</v>
@@ -50288,7 +50288,7 @@
         <v>29</v>
       </c>
       <c r="E522" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F522" s="3" t="s">
         <v>31</v>
@@ -50315,7 +50315,7 @@
         <v>1604</v>
       </c>
       <c r="N522" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O522" s="3" t="s">
         <v>38</v>
@@ -50368,7 +50368,7 @@
         <v>29</v>
       </c>
       <c r="E523" s="7" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F523" s="7" t="s">
         <v>31</v>
@@ -50395,7 +50395,7 @@
         <v>1604</v>
       </c>
       <c r="N523" s="7" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O523" s="7" t="s">
         <v>38</v>
@@ -50600,7 +50600,7 @@
         <v>29</v>
       </c>
       <c r="E526" s="7" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F526" s="7" t="s">
         <v>31</v>
@@ -50627,7 +50627,7 @@
         <v>1604</v>
       </c>
       <c r="N526" s="7" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O526" s="7" t="s">
         <v>38</v>
@@ -50680,7 +50680,7 @@
         <v>29</v>
       </c>
       <c r="E527" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F527" s="4" t="s">
         <v>31</v>
@@ -50705,7 +50705,7 @@
         <v>1604</v>
       </c>
       <c r="N527" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O527" s="4" t="s">
         <v>38</v>
@@ -50931,7 +50931,7 @@
         <v>8</v>
       </c>
       <c r="J530" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K530" s="3" t="s">
         <v>34</v>
@@ -51080,10 +51080,10 @@
         <v>101</v>
       </c>
       <c r="G532" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H532" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I532" s="3">
         <v>8</v>
@@ -51310,7 +51310,7 @@
         <v>29</v>
       </c>
       <c r="E535" s="7" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F535" s="7" t="s">
         <v>31</v>
@@ -51591,7 +51591,7 @@
         <v>777</v>
       </c>
       <c r="T538" s="6" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U538" s="6" t="s">
         <v>127</v>
@@ -51702,7 +51702,7 @@
         <v>29</v>
       </c>
       <c r="E540" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F540" s="4" t="s">
         <v>31</v>
@@ -51780,7 +51780,7 @@
         <v>29</v>
       </c>
       <c r="E541" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F541" s="4" t="s">
         <v>31</v>
@@ -51856,7 +51856,7 @@
         <v>29</v>
       </c>
       <c r="E542" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F542" s="4" t="s">
         <v>31</v>
@@ -51932,7 +51932,7 @@
         <v>29</v>
       </c>
       <c r="E543" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F543" s="4" t="s">
         <v>31</v>
@@ -52014,10 +52014,10 @@
         <v>31</v>
       </c>
       <c r="G544" s="3" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="H544" s="3" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="I544" s="3">
         <v>9</v>
@@ -52166,7 +52166,7 @@
         <v>1647</v>
       </c>
       <c r="E546" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F546" s="3" t="s">
         <v>31</v>
@@ -52193,7 +52193,7 @@
         <v>1604</v>
       </c>
       <c r="N546" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O546" s="3" t="s">
         <v>117</v>
@@ -52246,7 +52246,7 @@
         <v>1647</v>
       </c>
       <c r="E547" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F547" s="4" t="s">
         <v>31</v>
@@ -52271,7 +52271,7 @@
         <v>1604</v>
       </c>
       <c r="N547" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O547" s="4" t="s">
         <v>117</v>
@@ -52322,7 +52322,7 @@
         <v>29</v>
       </c>
       <c r="E548" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F548" s="3" t="s">
         <v>101</v>
@@ -52349,7 +52349,7 @@
         <v>1604</v>
       </c>
       <c r="N548" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O548" s="3" t="s">
         <v>38</v>
@@ -52402,7 +52402,7 @@
         <v>29</v>
       </c>
       <c r="E549" s="5" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F549" s="5" t="s">
         <v>101</v>
@@ -52429,7 +52429,7 @@
         <v>1604</v>
       </c>
       <c r="N549" s="5" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O549" s="5" t="s">
         <v>38</v>
@@ -52480,7 +52480,7 @@
         <v>29</v>
       </c>
       <c r="E550" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F550" s="3" t="s">
         <v>101</v>
@@ -52507,7 +52507,7 @@
         <v>1604</v>
       </c>
       <c r="N550" s="3" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O550" s="3" t="s">
         <v>38</v>
@@ -52679,7 +52679,7 @@
         <v>285</v>
       </c>
       <c r="T552" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U552" s="4" t="s">
         <v>127</v>
@@ -52712,7 +52712,7 @@
         <v>29</v>
       </c>
       <c r="E553" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F553" s="4" t="s">
         <v>31</v>
@@ -52737,7 +52737,7 @@
         <v>1604</v>
       </c>
       <c r="N553" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O553" s="4" t="s">
         <v>38</v>
@@ -52790,7 +52790,7 @@
         <v>29</v>
       </c>
       <c r="E554" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F554" s="4" t="s">
         <v>31</v>
@@ -52815,7 +52815,7 @@
         <v>1604</v>
       </c>
       <c r="N554" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O554" s="4" t="s">
         <v>38</v>
@@ -52833,7 +52833,7 @@
         <v>1608</v>
       </c>
       <c r="T554" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U554" s="4" t="s">
         <v>127</v>
@@ -52987,7 +52987,7 @@
         <v>285</v>
       </c>
       <c r="T556" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U556" s="4" t="s">
         <v>127</v>
@@ -53020,7 +53020,7 @@
         <v>29</v>
       </c>
       <c r="E557" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F557" s="4" t="s">
         <v>31</v>
@@ -53045,7 +53045,7 @@
         <v>1604</v>
       </c>
       <c r="N557" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O557" s="4" t="s">
         <v>38</v>
@@ -53098,7 +53098,7 @@
         <v>29</v>
       </c>
       <c r="E558" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F558" s="4" t="s">
         <v>31</v>
@@ -53123,7 +53123,7 @@
         <v>1604</v>
       </c>
       <c r="N558" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O558" s="4" t="s">
         <v>38</v>
@@ -53141,7 +53141,7 @@
         <v>1608</v>
       </c>
       <c r="T558" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U558" s="4" t="s">
         <v>127</v>
@@ -53174,7 +53174,7 @@
         <v>29</v>
       </c>
       <c r="E559" s="7" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F559" s="7" t="s">
         <v>31</v>
@@ -53201,7 +53201,7 @@
         <v>1604</v>
       </c>
       <c r="N559" s="7" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O559" s="7" t="s">
         <v>38</v>
@@ -53451,7 +53451,7 @@
         <v>285</v>
       </c>
       <c r="T562" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U562" s="4" t="s">
         <v>127</v>
@@ -53562,7 +53562,7 @@
         <v>29</v>
       </c>
       <c r="E564" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F564" s="4" t="s">
         <v>31</v>
@@ -53638,7 +53638,7 @@
         <v>29</v>
       </c>
       <c r="E565" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F565" s="4" t="s">
         <v>31</v>
@@ -53716,7 +53716,7 @@
         <v>29</v>
       </c>
       <c r="E566" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F566" s="4" t="s">
         <v>31</v>
@@ -53792,7 +53792,7 @@
         <v>29</v>
       </c>
       <c r="E567" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F567" s="4" t="s">
         <v>31</v>
@@ -53817,7 +53817,7 @@
         <v>1604</v>
       </c>
       <c r="N567" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O567" s="4" t="s">
         <v>38</v>
@@ -53870,7 +53870,7 @@
         <v>29</v>
       </c>
       <c r="E568" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F568" s="4" t="s">
         <v>31</v>
@@ -53895,7 +53895,7 @@
         <v>1604</v>
       </c>
       <c r="N568" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O568" s="4" t="s">
         <v>38</v>
@@ -53913,7 +53913,7 @@
         <v>1608</v>
       </c>
       <c r="T568" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U568" s="4" t="s">
         <v>127</v>
@@ -54267,7 +54267,7 @@
         <v>8</v>
       </c>
       <c r="J573" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K573" s="4" t="s">
         <v>1388</v>
@@ -54375,7 +54375,7 @@
         <v>777</v>
       </c>
       <c r="T574" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U574" s="4" t="s">
         <v>127</v>
@@ -54607,7 +54607,7 @@
         <v>132</v>
       </c>
       <c r="T577" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U577" s="4" t="s">
         <v>44</v>
@@ -54640,7 +54640,7 @@
         <v>29</v>
       </c>
       <c r="E578" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F578" s="4" t="s">
         <v>31</v>
@@ -54716,7 +54716,7 @@
         <v>1647</v>
       </c>
       <c r="E579" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F579" s="4" t="s">
         <v>31</v>
@@ -54741,7 +54741,7 @@
         <v>1604</v>
       </c>
       <c r="N579" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O579" s="4" t="s">
         <v>117</v>
@@ -54794,7 +54794,7 @@
         <v>29</v>
       </c>
       <c r="E580" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F580" s="4" t="s">
         <v>31</v>
@@ -54819,7 +54819,7 @@
         <v>1604</v>
       </c>
       <c r="N580" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O580" s="4" t="s">
         <v>38</v>
@@ -54872,7 +54872,7 @@
         <v>29</v>
       </c>
       <c r="E581" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F581" s="4" t="s">
         <v>31</v>
@@ -54897,7 +54897,7 @@
         <v>1604</v>
       </c>
       <c r="N581" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O581" s="4" t="s">
         <v>38</v>
@@ -54915,7 +54915,7 @@
         <v>1608</v>
       </c>
       <c r="T581" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U581" s="4" t="s">
         <v>127</v>
@@ -55223,7 +55223,7 @@
         <v>285</v>
       </c>
       <c r="T585" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U585" s="4" t="s">
         <v>127</v>
@@ -55256,7 +55256,7 @@
         <v>29</v>
       </c>
       <c r="E586" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F586" s="4" t="s">
         <v>31</v>
@@ -55334,7 +55334,7 @@
         <v>29</v>
       </c>
       <c r="E587" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F587" s="4" t="s">
         <v>31</v>
@@ -55410,7 +55410,7 @@
         <v>29</v>
       </c>
       <c r="E588" s="3" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F588" s="3" t="s">
         <v>31</v>
@@ -55609,7 +55609,7 @@
         <v>132</v>
       </c>
       <c r="T590" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U590" s="4" t="s">
         <v>44</v>
@@ -55763,7 +55763,7 @@
         <v>132</v>
       </c>
       <c r="T592" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U592" s="4" t="s">
         <v>44</v>
@@ -55796,7 +55796,7 @@
         <v>29</v>
       </c>
       <c r="E593" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F593" s="4" t="s">
         <v>101</v>
@@ -55821,7 +55821,7 @@
         <v>1604</v>
       </c>
       <c r="N593" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O593" s="4" t="s">
         <v>38</v>
@@ -55874,7 +55874,7 @@
         <v>29</v>
       </c>
       <c r="E594" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F594" s="4" t="s">
         <v>101</v>
@@ -55899,7 +55899,7 @@
         <v>1604</v>
       </c>
       <c r="N594" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O594" s="4" t="s">
         <v>38</v>
@@ -55917,7 +55917,7 @@
         <v>1608</v>
       </c>
       <c r="T594" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U594" s="4" t="s">
         <v>127</v>
@@ -55950,7 +55950,7 @@
         <v>29</v>
       </c>
       <c r="E595" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F595" s="4" t="s">
         <v>101</v>
@@ -55975,7 +55975,7 @@
         <v>1604</v>
       </c>
       <c r="N595" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O595" s="4" t="s">
         <v>38</v>
@@ -56223,7 +56223,7 @@
         <v>285</v>
       </c>
       <c r="T598" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U598" s="4" t="s">
         <v>127</v>
@@ -56317,7 +56317,7 @@
         <v>53</v>
       </c>
       <c r="Z599" s="4" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="600" spans="1:26">
@@ -56488,7 +56488,7 @@
         <v>1647</v>
       </c>
       <c r="E602" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F602" s="4" t="s">
         <v>31</v>
@@ -56564,7 +56564,7 @@
         <v>1647</v>
       </c>
       <c r="E603" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F603" s="4" t="s">
         <v>31</v>
@@ -56607,7 +56607,7 @@
         <v>285</v>
       </c>
       <c r="T603" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U603" s="4" t="s">
         <v>127</v>
@@ -56761,7 +56761,7 @@
         <v>132</v>
       </c>
       <c r="T605" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U605" s="4" t="s">
         <v>44</v>
@@ -56819,7 +56819,7 @@
         <v>1604</v>
       </c>
       <c r="N606" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O606" s="4" t="s">
         <v>38</v>
@@ -56872,7 +56872,7 @@
         <v>29</v>
       </c>
       <c r="E607" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F607" s="4" t="s">
         <v>31</v>
@@ -56897,7 +56897,7 @@
         <v>1604</v>
       </c>
       <c r="N607" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O607" s="4" t="s">
         <v>38</v>
@@ -56950,7 +56950,7 @@
         <v>29</v>
       </c>
       <c r="E608" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F608" s="4" t="s">
         <v>31</v>
@@ -56975,7 +56975,7 @@
         <v>1604</v>
       </c>
       <c r="N608" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O608" s="4" t="s">
         <v>38</v>
@@ -56993,7 +56993,7 @@
         <v>1608</v>
       </c>
       <c r="T608" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U608" s="4" t="s">
         <v>127</v>
@@ -57104,7 +57104,7 @@
         <v>29</v>
       </c>
       <c r="E610" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F610" s="4" t="s">
         <v>31</v>
@@ -57455,7 +57455,7 @@
         <v>132</v>
       </c>
       <c r="T614" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U614" s="4" t="s">
         <v>44</v>
@@ -57841,7 +57841,7 @@
         <v>285</v>
       </c>
       <c r="T619" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U619" s="4" t="s">
         <v>127</v>
@@ -58260,7 +58260,7 @@
         <v>29</v>
       </c>
       <c r="E625" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F625" s="4" t="s">
         <v>31</v>
@@ -58321,7 +58321,7 @@
         <v>53</v>
       </c>
       <c r="Z625" s="4" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="626" spans="1:26">
@@ -58338,7 +58338,7 @@
         <v>29</v>
       </c>
       <c r="E626" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F626" s="4" t="s">
         <v>31</v>
@@ -58535,7 +58535,7 @@
         <v>132</v>
       </c>
       <c r="T628" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U628" s="4" t="s">
         <v>44</v>
@@ -58568,7 +58568,7 @@
         <v>29</v>
       </c>
       <c r="E629" s="5" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F629" s="5" t="s">
         <v>31</v>
@@ -58648,7 +58648,7 @@
         <v>29</v>
       </c>
       <c r="E630" s="4" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="F630" s="4" t="s">
         <v>31</v>
@@ -58724,7 +58724,7 @@
         <v>1647</v>
       </c>
       <c r="E631" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F631" s="4" t="s">
         <v>31</v>
@@ -58749,7 +58749,7 @@
         <v>1604</v>
       </c>
       <c r="N631" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O631" s="4" t="s">
         <v>117</v>
@@ -58802,7 +58802,7 @@
         <v>29</v>
       </c>
       <c r="E632" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F632" s="4" t="s">
         <v>31</v>
@@ -58827,7 +58827,7 @@
         <v>1604</v>
       </c>
       <c r="N632" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O632" s="4" t="s">
         <v>38</v>
@@ -58880,7 +58880,7 @@
         <v>29</v>
       </c>
       <c r="E633" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F633" s="4" t="s">
         <v>31</v>
@@ -58905,7 +58905,7 @@
         <v>1604</v>
       </c>
       <c r="N633" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O633" s="4" t="s">
         <v>38</v>
@@ -58923,7 +58923,7 @@
         <v>1608</v>
       </c>
       <c r="T633" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U633" s="4" t="s">
         <v>127</v>
@@ -58956,7 +58956,7 @@
         <v>29</v>
       </c>
       <c r="E634" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F634" s="4" t="s">
         <v>31</v>
@@ -59093,7 +59093,7 @@
         <v>53</v>
       </c>
       <c r="Z635" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="636" spans="1:26">
@@ -59231,7 +59231,7 @@
         <v>777</v>
       </c>
       <c r="T637" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U637" s="4" t="s">
         <v>127</v>
@@ -59385,7 +59385,7 @@
         <v>132</v>
       </c>
       <c r="T639" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="U639" s="4" t="s">
         <v>44</v>
@@ -59445,7 +59445,7 @@
         <v>1604</v>
       </c>
       <c r="N640" s="7" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O640" s="7" t="s">
         <v>38</v>
@@ -59521,7 +59521,7 @@
         <v>1390</v>
       </c>
       <c r="N641" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O641" s="4" t="s">
         <v>38</v>
@@ -59599,7 +59599,7 @@
         <v>1390</v>
       </c>
       <c r="N642" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O642" s="4" t="s">
         <v>38</v>
@@ -59675,7 +59675,7 @@
         <v>1390</v>
       </c>
       <c r="N643" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O643" s="4" t="s">
         <v>38</v>
@@ -59753,7 +59753,7 @@
         <v>1390</v>
       </c>
       <c r="N644" s="4" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="O644" s="4" t="s">
         <v>38</v>
@@ -60325,10 +60325,10 @@
         <v>31</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="I7" s="5">
         <v>9</v>
@@ -60485,10 +60485,10 @@
         <v>31</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="I9" s="5">
         <v>8</v>
@@ -60782,7 +60782,7 @@
         <v>53</v>
       </c>
       <c r="Z12" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="13" spans="1:26">
@@ -61102,7 +61102,7 @@
         <v>53</v>
       </c>
       <c r="Z16" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="17" spans="1:26">
@@ -61125,10 +61125,10 @@
         <v>31</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I17" s="5">
         <v>9</v>
@@ -61365,10 +61365,10 @@
         <v>31</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="I20" s="3">
         <v>10</v>
@@ -61422,7 +61422,7 @@
         <v>53</v>
       </c>
       <c r="Z20" s="3" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="21" spans="1:26">
@@ -62442,7 +62442,7 @@
         <v>267</v>
       </c>
       <c r="T33" s="5" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="U33" s="5" t="s">
         <v>44</v>
@@ -64173,7 +64173,7 @@
         <v>53</v>
       </c>
       <c r="Z3" s="5" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="4" spans="1:26">
@@ -64196,10 +64196,10 @@
         <v>31</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="I4" s="3">
         <v>8</v>
@@ -64950,7 +64950,7 @@
         <v>2183</v>
       </c>
       <c r="S13" s="5" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="T13" s="5" t="s">
         <v>2184</v>
@@ -65234,10 +65234,10 @@
         <v>31</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="I17" s="5">
         <v>10</v>
@@ -65314,10 +65314,10 @@
         <v>31</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="I18" s="3">
         <v>10</v>
@@ -65371,7 +65371,7 @@
         <v>53</v>
       </c>
       <c r="Z18" s="3" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="19" spans="1:26">
@@ -65794,10 +65794,10 @@
         <v>31</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I24" s="3">
         <v>9</v>
@@ -65833,7 +65833,7 @@
         <v>97</v>
       </c>
       <c r="T24" s="3" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>44</v>
@@ -65931,7 +65931,7 @@
         <v>53</v>
       </c>
       <c r="Z25" s="5" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="26" spans="1:26">
@@ -66708,7 +66708,7 @@
         <v>2229</v>
       </c>
       <c r="S35" s="5" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="T35" s="5" t="s">
         <v>2230</v>
@@ -66912,10 +66912,10 @@
         <v>31</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I38" s="3">
         <v>8</v>
@@ -67232,10 +67232,10 @@
         <v>31</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I42" s="3">
         <v>8</v>
@@ -69146,10 +69146,10 @@
         <v>31</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I66" s="3">
         <v>9</v>
@@ -69862,10 +69862,10 @@
         <v>31</v>
       </c>
       <c r="G75" s="5" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="H75" s="5" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="I75" s="5">
         <v>8</v>
@@ -69901,7 +69901,7 @@
         <v>267</v>
       </c>
       <c r="T75" s="5" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="U75" s="5" t="s">
         <v>44</v>
@@ -69940,7 +69940,7 @@
         <v>31</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>2322</v>
@@ -70018,10 +70018,10 @@
         <v>31</v>
       </c>
       <c r="G77" s="5" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H77" s="5" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="I77" s="5">
         <v>10</v>
@@ -70496,10 +70496,10 @@
         <v>31</v>
       </c>
       <c r="G83" s="5" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H83" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="I83" s="5">
         <v>8</v>
@@ -70652,10 +70652,10 @@
         <v>31</v>
       </c>
       <c r="G85" s="5" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="H85" s="5" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="I85" s="5">
         <v>8</v>
@@ -70691,7 +70691,7 @@
         <v>138</v>
       </c>
       <c r="T85" s="5" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="U85" s="5" t="s">
         <v>44</v>
@@ -70890,10 +70890,10 @@
         <v>31</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I88" s="3">
         <v>8</v>
@@ -71050,10 +71050,10 @@
         <v>31</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="I90" s="3">
         <v>10</v>
@@ -71130,10 +71130,10 @@
         <v>31</v>
       </c>
       <c r="G91" s="5" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H91" s="5" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I91" s="5">
         <v>8</v>
@@ -71922,10 +71922,10 @@
         <v>31</v>
       </c>
       <c r="G101" s="5" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H101" s="5" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="I101" s="5">
         <v>9</v>
@@ -72638,10 +72638,10 @@
         <v>31</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="I110" s="3">
         <v>7</v>
@@ -72695,7 +72695,7 @@
         <v>53</v>
       </c>
       <c r="Z110" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="111" spans="1:26">
@@ -73276,10 +73276,10 @@
         <v>31</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I118" s="3">
         <v>8</v>
@@ -73573,7 +73573,7 @@
         <v>46</v>
       </c>
       <c r="Z121" s="5" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="122" spans="1:26">
@@ -73653,7 +73653,7 @@
         <v>53</v>
       </c>
       <c r="Z122" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="123" spans="1:26">
@@ -73835,7 +73835,7 @@
         <v>2447</v>
       </c>
       <c r="H125" s="5" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="I125" s="5">
         <v>10</v>
@@ -74546,10 +74546,10 @@
         <v>31</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="I134" s="3">
         <v>9</v>
@@ -74626,10 +74626,10 @@
         <v>31</v>
       </c>
       <c r="G135" s="5" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H135" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="I135" s="5">
         <v>8</v>
@@ -75498,10 +75498,10 @@
         <v>31</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="I146" s="3">
         <v>10</v>
@@ -75738,10 +75738,10 @@
         <v>31</v>
       </c>
       <c r="G149" s="5" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="H149" s="5" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="I149" s="5">
         <v>8</v>
@@ -75818,10 +75818,10 @@
         <v>31</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="I150" s="3">
         <v>7</v>
@@ -75875,7 +75875,7 @@
         <v>53</v>
       </c>
       <c r="Z150" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="151" spans="1:26">
@@ -75978,10 +75978,10 @@
         <v>31</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I152" s="3">
         <v>10</v>
@@ -76138,10 +76138,10 @@
         <v>31</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="I154" s="3">
         <v>9</v>
@@ -77071,7 +77071,7 @@
         <v>53</v>
       </c>
       <c r="Z165" s="5" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="166" spans="1:26">
@@ -77151,7 +77151,7 @@
         <v>53</v>
       </c>
       <c r="Z166" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="167" spans="1:26">
@@ -77861,7 +77861,7 @@
         <v>45</v>
       </c>
       <c r="X175" s="5" t="s">
-        <v>1201</v>
+        <v>806</v>
       </c>
       <c r="Y175" s="5" t="s">
         <v>53</v>
@@ -77890,10 +77890,10 @@
         <v>31</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="I176" s="3">
         <v>9</v>
@@ -78210,10 +78210,10 @@
         <v>31</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="I180" s="3">
         <v>9</v>
@@ -78290,10 +78290,10 @@
         <v>31</v>
       </c>
       <c r="G181" s="5" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="H181" s="5" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="I181" s="5">
         <v>7</v>
@@ -78528,10 +78528,10 @@
         <v>31</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I184" s="3">
         <v>10</v>
@@ -79699,7 +79699,7 @@
         <v>53</v>
       </c>
       <c r="Z198" s="3" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="199" spans="1:26">
@@ -79882,10 +79882,10 @@
         <v>31</v>
       </c>
       <c r="G201" s="5" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="H201" s="5" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="I201" s="5">
         <v>8</v>
@@ -79918,10 +79918,10 @@
         <v>2619</v>
       </c>
       <c r="S201" s="5" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="T201" s="5" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="U201" s="5" t="s">
         <v>127</v>
@@ -80553,7 +80553,7 @@
         <v>2631</v>
       </c>
       <c r="R209" s="5" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="S209" s="5" t="s">
         <v>108</v>
@@ -80600,10 +80600,10 @@
         <v>31</v>
       </c>
       <c r="G210" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="H210" s="3" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="I210" s="3">
         <v>6</v>
@@ -81478,10 +81478,10 @@
         <v>31</v>
       </c>
       <c r="G221" s="5" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H221" s="5" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I221" s="5">
         <v>9</v>
@@ -81558,10 +81558,10 @@
         <v>31</v>
       </c>
       <c r="G222" s="3" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="H222" s="3" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="I222" s="3">
         <v>8</v>
@@ -82118,10 +82118,10 @@
         <v>31</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I229" s="5">
         <v>10</v>
@@ -82601,7 +82601,7 @@
         <v>2447</v>
       </c>
       <c r="H235" s="5" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="I235" s="5">
         <v>10</v>
@@ -82717,7 +82717,7 @@
         <v>267</v>
       </c>
       <c r="T236" s="3" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="U236" s="3" t="s">
         <v>44</v>
@@ -83195,7 +83195,7 @@
         <v>243</v>
       </c>
       <c r="T242" s="3" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="U242" s="3" t="s">
         <v>127</v>
@@ -83394,10 +83394,10 @@
         <v>31</v>
       </c>
       <c r="G245" s="5" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="H245" s="5" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="I245" s="5">
         <v>8</v>
@@ -84106,10 +84106,10 @@
         <v>31</v>
       </c>
       <c r="G254" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H254" s="3" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I254" s="3">
         <v>6</v>
@@ -84266,10 +84266,10 @@
         <v>31</v>
       </c>
       <c r="G256" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H256" s="3" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="I256" s="3">
         <v>9</v>
@@ -84462,7 +84462,7 @@
         <v>2734</v>
       </c>
       <c r="S258" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T258" s="3" t="s">
         <v>239</v>
@@ -84906,10 +84906,10 @@
         <v>31</v>
       </c>
       <c r="G264" s="3" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="H264" s="3" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="I264" s="3">
         <v>8</v>
@@ -85043,7 +85043,7 @@
         <v>53</v>
       </c>
       <c r="Z265" s="5" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="266" spans="1:26">
@@ -85462,10 +85462,10 @@
         <v>31</v>
       </c>
       <c r="G271" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H271" s="5" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="I271" s="5">
         <v>10</v>
@@ -85780,10 +85780,10 @@
         <v>31</v>
       </c>
       <c r="G275" s="5" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="H275" s="5" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="I275" s="5">
         <v>9</v>
@@ -86016,10 +86016,10 @@
         <v>31</v>
       </c>
       <c r="G278" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H278" s="3" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I278" s="3">
         <v>9</v>
@@ -86096,10 +86096,10 @@
         <v>31</v>
       </c>
       <c r="G279" s="5" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="H279" s="5" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="I279" s="5">
         <v>9</v>
@@ -86256,10 +86256,10 @@
         <v>31</v>
       </c>
       <c r="G281" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H281" s="5" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I281" s="5">
         <v>6</v>
@@ -86372,7 +86372,7 @@
         <v>2793</v>
       </c>
       <c r="S282" s="3" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="T282" s="3" t="s">
         <v>1226</v>
@@ -86416,10 +86416,10 @@
         <v>31</v>
       </c>
       <c r="G283" s="5" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="H283" s="5" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="I283" s="5">
         <v>9</v>
@@ -86575,7 +86575,7 @@
         <v>2447</v>
       </c>
       <c r="H285" s="5" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="I285" s="5">
         <v>10</v>
@@ -86892,10 +86892,10 @@
         <v>31</v>
       </c>
       <c r="G289" s="5" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="H289" s="5" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="I289" s="5">
         <v>9</v>
@@ -87130,10 +87130,10 @@
         <v>31</v>
       </c>
       <c r="G292" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H292" s="3" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I292" s="3">
         <v>6</v>
@@ -88960,10 +88960,10 @@
         <v>31</v>
       </c>
       <c r="G315" s="5" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="H315" s="5" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="I315" s="5">
         <v>9</v>
@@ -90230,10 +90230,10 @@
         <v>31</v>
       </c>
       <c r="G331" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H331" s="5" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I331" s="5">
         <v>6</v>
@@ -90550,10 +90550,10 @@
         <v>31</v>
       </c>
       <c r="G335" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="H335" s="5" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="I335" s="5">
         <v>6</v>
@@ -91036,7 +91036,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B22" s="8">
         <v>14111</v>
@@ -91376,7 +91376,7 @@
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B42" s="8">
         <v>15492</v>
@@ -91393,7 +91393,7 @@
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B43" s="10">
         <v>23628</v>
@@ -91410,7 +91410,7 @@
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B44" s="8">
         <v>19891</v>
@@ -91682,7 +91682,7 @@
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="B60" s="8">
         <v>25974</v>
@@ -91699,7 +91699,7 @@
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B61" s="10">
         <v>24701</v>
@@ -91716,7 +91716,7 @@
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B62" s="8">
         <v>23061</v>
@@ -91733,7 +91733,7 @@
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B63" s="10">
         <v>5443</v>
@@ -92209,7 +92209,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B91" s="10">
         <v>23592</v>
@@ -92226,7 +92226,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="B92" s="8">
         <v>40896</v>
@@ -92243,7 +92243,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B93" s="10">
         <v>9676</v>
@@ -92260,7 +92260,7 @@
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B94" s="8">
         <v>7191</v>
@@ -92277,7 +92277,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B95" s="10">
         <v>20228</v>
@@ -92294,7 +92294,7 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="3" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B96" s="8">
         <v>20741</v>
@@ -92311,7 +92311,7 @@
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B97" s="10">
         <v>5205</v>
@@ -92328,7 +92328,7 @@
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="3" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B98" s="8">
         <v>20516</v>
@@ -92345,7 +92345,7 @@
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="B99" s="10">
         <v>25299</v>
@@ -92362,7 +92362,7 @@
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="3" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B100" s="8">
         <v>5688</v>
@@ -92379,7 +92379,7 @@
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B101" s="10">
         <v>11162</v>
@@ -92396,7 +92396,7 @@
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="3" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B102" s="8">
         <v>18695</v>
@@ -92413,7 +92413,7 @@
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B103" s="10">
         <v>33177</v>
@@ -92430,7 +92430,7 @@
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="3" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B104" s="8">
         <v>23898</v>
@@ -93280,7 +93280,7 @@
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B154" s="8">
         <v>34963</v>
@@ -93297,7 +93297,7 @@
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B155" s="10">
         <v>23068</v>
@@ -93314,7 +93314,7 @@
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="B156" s="8">
         <v>26938</v>
@@ -93331,7 +93331,7 @@
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B157" s="10">
         <v>6565</v>
@@ -93348,7 +93348,7 @@
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B158" s="8">
         <v>41770</v>
@@ -93365,7 +93365,7 @@
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B159" s="10">
         <v>25322</v>
@@ -93382,7 +93382,7 @@
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="3" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B160" s="8">
         <v>5079</v>
@@ -93399,7 +93399,7 @@
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B161" s="10">
         <v>5</v>
@@ -93416,7 +93416,7 @@
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B162" s="8">
         <v>15416</v>
@@ -93433,7 +93433,7 @@
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B163" s="10">
         <v>6971</v>
@@ -93450,7 +93450,7 @@
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B164" s="8">
         <v>5865</v>
@@ -93467,7 +93467,7 @@
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B165" s="10">
         <v>15788</v>
@@ -93484,7 +93484,7 @@
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="3" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B166" s="8">
         <v>6292</v>
@@ -93501,7 +93501,7 @@
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B167" s="10">
         <v>18863</v>
@@ -93518,7 +93518,7 @@
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="3" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B168" s="8">
         <v>9740</v>
@@ -93535,7 +93535,7 @@
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="B169" s="10">
         <v>27112</v>
@@ -93552,7 +93552,7 @@
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="3" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B170" s="8">
         <v>10596</v>
@@ -93569,7 +93569,7 @@
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B171" s="10">
         <v>19184</v>
@@ -93586,7 +93586,7 @@
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="3" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B172" s="8">
         <v>17475</v>
@@ -93603,7 +93603,7 @@
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="5" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B173" s="10">
         <v>20520</v>
@@ -93620,7 +93620,7 @@
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="3" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B174" s="8">
         <v>1463</v>
@@ -93637,7 +93637,7 @@
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="5" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B175" s="10">
         <v>26167</v>
@@ -93654,7 +93654,7 @@
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="3" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B176" s="8">
         <v>7526</v>
@@ -93671,7 +93671,7 @@
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="5" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B177" s="10">
         <v>22163</v>
@@ -93688,7 +93688,7 @@
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="3" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B178" s="8">
         <v>3984</v>
@@ -93705,7 +93705,7 @@
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="5" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B179" s="10">
         <v>9375</v>
@@ -93722,7 +93722,7 @@
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="3" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B180" s="8">
         <v>38191</v>
@@ -93739,7 +93739,7 @@
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="5" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B181" s="10">
         <v>40808</v>
@@ -93756,7 +93756,7 @@
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="3" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B182" s="8">
         <v>18875</v>
@@ -93773,7 +93773,7 @@
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="5" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B183" s="10">
         <v>3762</v>

--- a/skipperplan.xlsx
+++ b/skipperplan.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23480" uniqueCount="2938">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23464" uniqueCount="2935">
   <si>
     <t>Startdatum</t>
   </si>
@@ -1752,105 +1752,105 @@
     <t>15181</t>
   </si>
   <si>
+    <t>Remo H</t>
+  </si>
+  <si>
+    <t>38535</t>
+  </si>
+  <si>
+    <t>8256</t>
+  </si>
+  <si>
+    <t>16388</t>
+  </si>
+  <si>
+    <t>Emiliano R, Susanne M, Remo H, Bianca G</t>
+  </si>
+  <si>
+    <t>16389</t>
+  </si>
+  <si>
+    <t>8239</t>
+  </si>
+  <si>
+    <t>16345</t>
+  </si>
+  <si>
+    <t>Nils K, Nico B</t>
+  </si>
+  <si>
+    <t>Moritz K</t>
+  </si>
+  <si>
+    <t>9283</t>
+  </si>
+  <si>
+    <t>16348</t>
+  </si>
+  <si>
+    <t>Florian H</t>
+  </si>
+  <si>
+    <t>32458</t>
+  </si>
+  <si>
+    <t>16347</t>
+  </si>
+  <si>
+    <t>7837</t>
+  </si>
+  <si>
+    <t>15465</t>
+  </si>
+  <si>
+    <t>Nico B</t>
+  </si>
+  <si>
+    <t>17859</t>
+  </si>
+  <si>
+    <t>15466</t>
+  </si>
+  <si>
+    <t>Maximilian W</t>
+  </si>
+  <si>
+    <t>26972</t>
+  </si>
+  <si>
+    <t>17095</t>
+  </si>
+  <si>
+    <t>8020</t>
+  </si>
+  <si>
+    <t>15822</t>
+  </si>
+  <si>
+    <t>15823</t>
+  </si>
+  <si>
+    <t>M T POCKETS</t>
+  </si>
+  <si>
+    <t>7984</t>
+  </si>
+  <si>
+    <t>15741</t>
+  </si>
+  <si>
+    <t>Nils K, Martin W, Marc D</t>
+  </si>
+  <si>
+    <t>15743</t>
+  </si>
+  <si>
+    <t>15744</t>
+  </si>
+  <si>
     <t>Zugeteilt (offen)</t>
   </si>
   <si>
-    <t>Remo H</t>
-  </si>
-  <si>
-    <t>38535</t>
-  </si>
-  <si>
-    <t>8256</t>
-  </si>
-  <si>
-    <t>16388</t>
-  </si>
-  <si>
-    <t>Emiliano R, Susanne M, Remo H, Bianca G</t>
-  </si>
-  <si>
-    <t>16389</t>
-  </si>
-  <si>
-    <t>8239</t>
-  </si>
-  <si>
-    <t>16345</t>
-  </si>
-  <si>
-    <t>Nils K, Nico B</t>
-  </si>
-  <si>
-    <t>Moritz K</t>
-  </si>
-  <si>
-    <t>9283</t>
-  </si>
-  <si>
-    <t>16348</t>
-  </si>
-  <si>
-    <t>Florian H</t>
-  </si>
-  <si>
-    <t>32458</t>
-  </si>
-  <si>
-    <t>16347</t>
-  </si>
-  <si>
-    <t>7837</t>
-  </si>
-  <si>
-    <t>15465</t>
-  </si>
-  <si>
-    <t>Nico B</t>
-  </si>
-  <si>
-    <t>17859</t>
-  </si>
-  <si>
-    <t>15466</t>
-  </si>
-  <si>
-    <t>Maximilian W</t>
-  </si>
-  <si>
-    <t>26972</t>
-  </si>
-  <si>
-    <t>17095</t>
-  </si>
-  <si>
-    <t>8020</t>
-  </si>
-  <si>
-    <t>15822</t>
-  </si>
-  <si>
-    <t>15823</t>
-  </si>
-  <si>
-    <t>M T POCKETS</t>
-  </si>
-  <si>
-    <t>7984</t>
-  </si>
-  <si>
-    <t>15741</t>
-  </si>
-  <si>
-    <t>Nils K, Martin W, Marc D</t>
-  </si>
-  <si>
-    <t>15743</t>
-  </si>
-  <si>
-    <t>15744</t>
-  </si>
-  <si>
     <t>17083</t>
   </si>
   <si>
@@ -8809,15 +8809,6 @@
   </si>
   <si>
     <t>Neue Bewerbungen</t>
-  </si>
-  <si>
-    <t>Skipper geändert</t>
-  </si>
-  <si>
-    <t>(Kein Skipper)</t>
-  </si>
-  <si>
-    <t>Neue Bewerbung(en)</t>
   </si>
   <si>
     <t>ID</t>
@@ -8874,7 +8865,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8919,12 +8910,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -8963,7 +8948,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8986,19 +8971,16 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9840,7 +9822,7 @@
         <v>10</v>
       </c>
       <c r="J7" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>34</v>
@@ -10156,7 +10138,7 @@
         <v>8</v>
       </c>
       <c r="J11" s="5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>34</v>
@@ -10552,7 +10534,7 @@
         <v>10</v>
       </c>
       <c r="J16" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K16" s="3" t="s">
         <v>34</v>
@@ -10946,7 +10928,7 @@
         <v>9</v>
       </c>
       <c r="J21" s="4">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>34</v>
@@ -11250,7 +11232,7 @@
         <v>30</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G25" s="5" t="s">
         <v>211</v>
@@ -11262,7 +11244,7 @@
         <v>9</v>
       </c>
       <c r="J25" s="5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K25" s="5" t="s">
         <v>34</v>
@@ -12900,7 +12882,7 @@
         <v>30</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G46" s="3" t="s">
         <v>327</v>
@@ -12980,7 +12962,7 @@
         <v>30</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G47" s="5" t="s">
         <v>335</v>
@@ -14168,7 +14150,7 @@
         <v>10</v>
       </c>
       <c r="J62" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>34</v>
@@ -14246,7 +14228,7 @@
         <v>9</v>
       </c>
       <c r="J63" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K63" s="5" t="s">
         <v>34</v>
@@ -15114,7 +15096,7 @@
         <v>8</v>
       </c>
       <c r="J74" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K74" s="3" t="s">
         <v>34</v>
@@ -16364,7 +16346,7 @@
         <v>8</v>
       </c>
       <c r="J90" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K90" s="3" t="s">
         <v>34</v>
@@ -17932,7 +17914,7 @@
         <v>10</v>
       </c>
       <c r="J110" s="4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>34</v>
@@ -18610,82 +18592,82 @@
       </c>
     </row>
     <row r="119" spans="1:26">
-      <c r="A119" s="6" t="s">
+      <c r="A119" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B119" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="C119" s="6" t="s">
+      <c r="C119" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="D119" s="6" t="s">
+      <c r="D119" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E119" s="6" t="s">
+      <c r="E119" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F119" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G119" s="6" t="s">
+      <c r="F119" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G119" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="H119" s="6" t="s">
+      <c r="H119" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="I119" s="6">
+      <c r="I119" s="5">
         <v>8</v>
       </c>
-      <c r="J119" s="6">
-        <v>0</v>
-      </c>
-      <c r="K119" s="6" t="s">
+      <c r="J119" s="5">
+        <v>2</v>
+      </c>
+      <c r="K119" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L119" s="6" t="s">
+      <c r="L119" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="M119" s="6" t="s">
+      <c r="M119" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="N119" s="6" t="s">
+      <c r="N119" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O119" s="6" t="s">
+      <c r="O119" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P119" s="6" t="s">
+      <c r="P119" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="Q119" s="6" t="s">
+      <c r="Q119" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="R119" s="6" t="s">
+      <c r="R119" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="S119" s="6" t="s">
+      <c r="S119" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="T119" s="6" t="s">
+      <c r="T119" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="U119" s="6" t="s">
+      <c r="U119" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="V119" s="6">
+      <c r="V119" s="5">
         <v>2019</v>
       </c>
-      <c r="W119" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="X119" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="Y119" s="6" t="s">
+      <c r="W119" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X119" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y119" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z119" s="6"/>
+      <c r="Z119" s="5"/>
     </row>
     <row r="120" spans="1:26">
       <c r="A120" s="3" t="s">
@@ -18707,10 +18689,10 @@
         <v>31</v>
       </c>
       <c r="G120" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="H120" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="H120" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="I120" s="3">
         <v>10</v>
@@ -18737,10 +18719,10 @@
         <v>201</v>
       </c>
       <c r="Q120" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="R120" s="3" t="s">
         <v>578</v>
-      </c>
-      <c r="R120" s="3" t="s">
-        <v>579</v>
       </c>
       <c r="S120" s="3" t="s">
         <v>90</v>
@@ -18764,7 +18746,7 @@
         <v>46</v>
       </c>
       <c r="Z120" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="121" spans="1:26">
@@ -18796,7 +18778,7 @@
         <v>9</v>
       </c>
       <c r="J121" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K121" s="5" t="s">
         <v>34</v>
@@ -18817,10 +18799,10 @@
         <v>201</v>
       </c>
       <c r="Q121" s="5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="R121" s="5" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="S121" s="5" t="s">
         <v>68</v>
@@ -18895,10 +18877,10 @@
         <v>194</v>
       </c>
       <c r="Q122" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="R122" s="3" t="s">
         <v>582</v>
-      </c>
-      <c r="R122" s="3" t="s">
-        <v>583</v>
       </c>
       <c r="S122" s="3" t="s">
         <v>68</v>
@@ -18922,7 +18904,7 @@
         <v>46</v>
       </c>
       <c r="Z122" s="3" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="123" spans="1:26">
@@ -18945,10 +18927,10 @@
         <v>31</v>
       </c>
       <c r="G123" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="H123" s="5" t="s">
         <v>585</v>
-      </c>
-      <c r="H123" s="5" t="s">
-        <v>586</v>
       </c>
       <c r="I123" s="5">
         <v>8</v>
@@ -18975,10 +18957,10 @@
         <v>194</v>
       </c>
       <c r="Q123" s="5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="R123" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="S123" s="5" t="s">
         <v>209</v>
@@ -19023,10 +19005,10 @@
         <v>31</v>
       </c>
       <c r="G124" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="H124" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="H124" s="3" t="s">
-        <v>589</v>
       </c>
       <c r="I124" s="3">
         <v>9</v>
@@ -19053,10 +19035,10 @@
         <v>194</v>
       </c>
       <c r="Q124" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="R124" s="3" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="S124" s="3" t="s">
         <v>187</v>
@@ -19131,10 +19113,10 @@
         <v>220</v>
       </c>
       <c r="Q125" s="5" t="s">
+        <v>590</v>
+      </c>
+      <c r="R125" s="5" t="s">
         <v>591</v>
-      </c>
-      <c r="R125" s="5" t="s">
-        <v>592</v>
       </c>
       <c r="S125" s="5" t="s">
         <v>142</v>
@@ -19179,10 +19161,10 @@
         <v>31</v>
       </c>
       <c r="G126" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="H126" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="H126" s="3" t="s">
-        <v>594</v>
       </c>
       <c r="I126" s="3">
         <v>8</v>
@@ -19209,10 +19191,10 @@
         <v>220</v>
       </c>
       <c r="Q126" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="R126" s="3" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="S126" s="3" t="s">
         <v>142</v>
@@ -19257,10 +19239,10 @@
         <v>31</v>
       </c>
       <c r="G127" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="H127" s="5" t="s">
         <v>596</v>
-      </c>
-      <c r="H127" s="5" t="s">
-        <v>597</v>
       </c>
       <c r="I127" s="5">
         <v>10</v>
@@ -19287,10 +19269,10 @@
         <v>220</v>
       </c>
       <c r="Q127" s="5" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="R127" s="5" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="S127" s="5" t="s">
         <v>80</v>
@@ -19365,10 +19347,10 @@
         <v>228</v>
       </c>
       <c r="Q128" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="R128" s="3" t="s">
         <v>599</v>
-      </c>
-      <c r="R128" s="3" t="s">
-        <v>600</v>
       </c>
       <c r="S128" s="3" t="s">
         <v>102</v>
@@ -19445,16 +19427,16 @@
         <v>228</v>
       </c>
       <c r="Q129" s="5" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="R129" s="5" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="S129" s="5" t="s">
         <v>507</v>
       </c>
       <c r="T129" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="U129" s="5" t="s">
         <v>44</v>
@@ -19490,7 +19472,7 @@
         <v>30</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G130" s="3" t="s">
         <v>115</v>
@@ -19523,10 +19505,10 @@
         <v>239</v>
       </c>
       <c r="Q130" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="R130" s="3" t="s">
         <v>603</v>
-      </c>
-      <c r="R130" s="3" t="s">
-        <v>604</v>
       </c>
       <c r="S130" s="3" t="s">
         <v>80</v>
@@ -19550,7 +19532,7 @@
         <v>46</v>
       </c>
       <c r="Z130" s="3" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="131" spans="1:26">
@@ -19570,7 +19552,7 @@
         <v>30</v>
       </c>
       <c r="F131" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G131" s="5" t="s">
         <v>152</v>
@@ -19603,10 +19585,10 @@
         <v>239</v>
       </c>
       <c r="Q131" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R131" s="5" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="S131" s="5" t="s">
         <v>235</v>
@@ -19648,7 +19630,7 @@
         <v>30</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G132" s="7" t="s">
         <v>48</v>
@@ -19681,10 +19663,10 @@
         <v>239</v>
       </c>
       <c r="Q132" s="7" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R132" s="7" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="S132" s="7" t="s">
         <v>235</v>
@@ -19702,7 +19684,7 @@
         <v>45</v>
       </c>
       <c r="X132" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y132" s="7" t="s">
         <v>46</v>
@@ -19726,7 +19708,7 @@
         <v>30</v>
       </c>
       <c r="F133" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G133" s="5" t="s">
         <v>431</v>
@@ -19759,7 +19741,7 @@
         <v>239</v>
       </c>
       <c r="Q133" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R133" s="5" t="s">
         <v>608</v>
@@ -19804,7 +19786,7 @@
         <v>30</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G134" s="3" t="s">
         <v>610</v>
@@ -19837,7 +19819,7 @@
         <v>239</v>
       </c>
       <c r="Q134" s="3" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R134" s="3" t="s">
         <v>612</v>
@@ -19882,7 +19864,7 @@
         <v>30</v>
       </c>
       <c r="F135" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G135" s="5" t="s">
         <v>614</v>
@@ -19915,7 +19897,7 @@
         <v>239</v>
       </c>
       <c r="Q135" s="5" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="R135" s="5" t="s">
         <v>616</v>
@@ -20206,7 +20188,7 @@
         <v>10</v>
       </c>
       <c r="J139" s="5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K139" s="5" t="s">
         <v>34</v>
@@ -21108,7 +21090,7 @@
         <v>343</v>
       </c>
       <c r="X150" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y150" s="6" t="s">
         <v>46</v>
@@ -21894,7 +21876,7 @@
         <v>45</v>
       </c>
       <c r="X160" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y160" s="7" t="s">
         <v>46</v>
@@ -21972,7 +21954,7 @@
         <v>343</v>
       </c>
       <c r="X161" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y161" s="6" t="s">
         <v>46</v>
@@ -22324,7 +22306,7 @@
         <v>10</v>
       </c>
       <c r="J166" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K166" s="3" t="s">
         <v>34</v>
@@ -22395,10 +22377,10 @@
         <v>31</v>
       </c>
       <c r="G167" s="5" t="s">
+        <v>595</v>
+      </c>
+      <c r="H167" s="5" t="s">
         <v>596</v>
-      </c>
-      <c r="H167" s="5" t="s">
-        <v>597</v>
       </c>
       <c r="I167" s="5">
         <v>10</v>
@@ -22604,7 +22586,7 @@
         <v>343</v>
       </c>
       <c r="X169" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y169" s="6" t="s">
         <v>46</v>
@@ -22880,7 +22862,7 @@
         <v>7</v>
       </c>
       <c r="J173" s="5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K173" s="5" t="s">
         <v>34</v>
@@ -23038,7 +23020,7 @@
         <v>8</v>
       </c>
       <c r="J175" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K175" s="5" t="s">
         <v>34</v>
@@ -23107,10 +23089,10 @@
         <v>31</v>
       </c>
       <c r="G176" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="H176" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="H176" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="I176" s="3">
         <v>6</v>
@@ -23423,10 +23405,10 @@
         <v>31</v>
       </c>
       <c r="G180" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="H180" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="H180" s="3" t="s">
-        <v>594</v>
       </c>
       <c r="I180" s="3">
         <v>8</v>
@@ -23826,7 +23808,7 @@
         <v>8</v>
       </c>
       <c r="J185" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K185" s="5" t="s">
         <v>34</v>
@@ -23946,7 +23928,7 @@
         <v>343</v>
       </c>
       <c r="X186" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y186" s="6" t="s">
         <v>46</v>
@@ -24608,7 +24590,7 @@
         <v>8</v>
       </c>
       <c r="J195" s="5">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K195" s="5" t="s">
         <v>34</v>
@@ -24922,7 +24904,7 @@
         <v>9</v>
       </c>
       <c r="J199" s="5">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K199" s="5" t="s">
         <v>34</v>
@@ -26302,7 +26284,7 @@
         <v>45</v>
       </c>
       <c r="X216" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y216" s="7" t="s">
         <v>46</v>
@@ -26567,10 +26549,10 @@
         <v>31</v>
       </c>
       <c r="G220" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="H220" s="3" t="s">
         <v>593</v>
-      </c>
-      <c r="H220" s="3" t="s">
-        <v>594</v>
       </c>
       <c r="I220" s="3">
         <v>10</v>
@@ -26734,7 +26716,7 @@
         <v>9</v>
       </c>
       <c r="J222" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K222" s="3" t="s">
         <v>34</v>
@@ -27092,7 +27074,7 @@
         <v>343</v>
       </c>
       <c r="X226" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y226" s="6" t="s">
         <v>46</v>
@@ -27328,7 +27310,7 @@
         <v>343</v>
       </c>
       <c r="X229" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y229" s="6" t="s">
         <v>46</v>
@@ -28466,7 +28448,7 @@
         <v>8</v>
       </c>
       <c r="J244" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K244" s="3" t="s">
         <v>34</v>
@@ -28532,7 +28514,7 @@
         <v>30</v>
       </c>
       <c r="F245" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G245" s="5" t="s">
         <v>801</v>
@@ -28612,7 +28594,7 @@
         <v>30</v>
       </c>
       <c r="F246" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G246" s="3" t="s">
         <v>641</v>
@@ -28690,7 +28672,7 @@
         <v>30</v>
       </c>
       <c r="F247" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G247" s="5" t="s">
         <v>806</v>
@@ -28768,7 +28750,7 @@
         <v>30</v>
       </c>
       <c r="F248" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G248" s="3" t="s">
         <v>948</v>
@@ -28846,7 +28828,7 @@
         <v>30</v>
       </c>
       <c r="F249" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G249" s="5" t="s">
         <v>951</v>
@@ -28924,7 +28906,7 @@
         <v>30</v>
       </c>
       <c r="F250" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G250" s="3" t="s">
         <v>777</v>
@@ -29002,7 +28984,7 @@
         <v>30</v>
       </c>
       <c r="F251" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G251" s="5" t="s">
         <v>816</v>
@@ -29080,7 +29062,7 @@
         <v>30</v>
       </c>
       <c r="F252" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G252" s="3" t="s">
         <v>957</v>
@@ -29644,7 +29626,7 @@
         <v>8</v>
       </c>
       <c r="J259" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K259" s="5" t="s">
         <v>34</v>
@@ -29764,7 +29746,7 @@
         <v>343</v>
       </c>
       <c r="X260" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y260" s="6" t="s">
         <v>46</v>
@@ -30118,7 +30100,7 @@
         <v>10</v>
       </c>
       <c r="J265" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K265" s="5" t="s">
         <v>34</v>
@@ -30505,10 +30487,10 @@
         <v>31</v>
       </c>
       <c r="G270" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="H270" s="7" t="s">
         <v>596</v>
-      </c>
-      <c r="H270" s="7" t="s">
-        <v>597</v>
       </c>
       <c r="I270" s="7">
         <v>8</v>
@@ -30556,7 +30538,7 @@
         <v>45</v>
       </c>
       <c r="X270" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y270" s="7" t="s">
         <v>46</v>
@@ -31142,7 +31124,7 @@
         <v>8</v>
       </c>
       <c r="J278" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K278" s="3" t="s">
         <v>34</v>
@@ -31344,7 +31326,7 @@
         <v>343</v>
       </c>
       <c r="X280" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y280" s="6" t="s">
         <v>46</v>
@@ -31368,7 +31350,7 @@
         <v>30</v>
       </c>
       <c r="F281" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G281" s="5" t="s">
         <v>748</v>
@@ -31448,7 +31430,7 @@
         <v>30</v>
       </c>
       <c r="F282" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G282" s="3" t="s">
         <v>1045</v>
@@ -31526,7 +31508,7 @@
         <v>30</v>
       </c>
       <c r="F283" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G283" s="5" t="s">
         <v>1048</v>
@@ -31604,7 +31586,7 @@
         <v>30</v>
       </c>
       <c r="F284" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G284" s="3" t="s">
         <v>1051</v>
@@ -31682,7 +31664,7 @@
         <v>30</v>
       </c>
       <c r="F285" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G285" s="5" t="s">
         <v>917</v>
@@ -31852,7 +31834,7 @@
         <v>8</v>
       </c>
       <c r="J287" s="5">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K287" s="5" t="s">
         <v>34</v>
@@ -31972,7 +31954,7 @@
         <v>343</v>
       </c>
       <c r="X288" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y288" s="6" t="s">
         <v>46</v>
@@ -32364,7 +32346,7 @@
         <v>343</v>
       </c>
       <c r="X293" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y293" s="6" t="s">
         <v>46</v>
@@ -32520,7 +32502,7 @@
         <v>343</v>
       </c>
       <c r="X295" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y295" s="6" t="s">
         <v>46</v>
@@ -32718,7 +32700,7 @@
         <v>8</v>
       </c>
       <c r="J298" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K298" s="3" t="s">
         <v>34</v>
@@ -33074,7 +33056,7 @@
         <v>343</v>
       </c>
       <c r="X302" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y302" s="6" t="s">
         <v>46</v>
@@ -33232,7 +33214,7 @@
         <v>343</v>
       </c>
       <c r="X304" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y304" s="6" t="s">
         <v>46</v>
@@ -33740,7 +33722,7 @@
         <v>10</v>
       </c>
       <c r="J311" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K311" s="6" t="s">
         <v>34</v>
@@ -34256,7 +34238,7 @@
         <v>343</v>
       </c>
       <c r="X317" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y317" s="6" t="s">
         <v>46</v>
@@ -34450,7 +34432,7 @@
         <v>9</v>
       </c>
       <c r="J320" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K320" s="3" t="s">
         <v>34</v>
@@ -34686,7 +34668,7 @@
         <v>8</v>
       </c>
       <c r="J323" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K323" s="7" t="s">
         <v>34</v>
@@ -34728,7 +34710,7 @@
         <v>45</v>
       </c>
       <c r="X323" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y323" s="7" t="s">
         <v>46</v>
@@ -34806,7 +34788,7 @@
         <v>343</v>
       </c>
       <c r="X324" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y324" s="6" t="s">
         <v>46</v>
@@ -34884,7 +34866,7 @@
         <v>343</v>
       </c>
       <c r="X325" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y325" s="6" t="s">
         <v>46</v>
@@ -34962,7 +34944,7 @@
         <v>343</v>
       </c>
       <c r="X326" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y326" s="6" t="s">
         <v>46</v>
@@ -35354,7 +35336,7 @@
         <v>45</v>
       </c>
       <c r="X331" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y331" s="7" t="s">
         <v>46</v>
@@ -35438,82 +35420,82 @@
       <c r="Z332" s="4"/>
     </row>
     <row r="333" spans="1:26">
-      <c r="A333" s="6" t="s">
+      <c r="A333" s="7" t="s">
         <v>845</v>
       </c>
-      <c r="B333" s="6" t="s">
+      <c r="B333" s="7" t="s">
         <v>1087</v>
       </c>
-      <c r="C333" s="6" t="s">
+      <c r="C333" s="7" t="s">
         <v>1077</v>
       </c>
-      <c r="D333" s="6" t="s">
+      <c r="D333" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E333" s="6" t="s">
+      <c r="E333" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="F333" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="G333" s="6" t="s">
+      <c r="F333" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G333" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="H333" s="6" t="s">
+      <c r="H333" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="I333" s="6">
+      <c r="I333" s="7">
         <v>8</v>
       </c>
-      <c r="J333" s="6">
-        <v>0</v>
-      </c>
-      <c r="K333" s="6" t="s">
+      <c r="J333" s="7">
+        <v>1</v>
+      </c>
+      <c r="K333" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="L333" s="6" t="s">
+      <c r="L333" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="M333" s="6" t="s">
+      <c r="M333" s="7" t="s">
         <v>1077</v>
       </c>
-      <c r="N333" s="6" t="s">
+      <c r="N333" s="7" t="s">
         <v>1080</v>
       </c>
-      <c r="O333" s="6" t="s">
+      <c r="O333" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="P333" s="6" t="s">
+      <c r="P333" s="7" t="s">
         <v>1081</v>
       </c>
-      <c r="Q333" s="6" t="s">
+      <c r="Q333" s="7" t="s">
         <v>1193</v>
       </c>
-      <c r="R333" s="6" t="s">
+      <c r="R333" s="7" t="s">
         <v>1194</v>
       </c>
-      <c r="S333" s="6" t="s">
+      <c r="S333" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="T333" s="6" t="s">
+      <c r="T333" s="7" t="s">
         <v>1195</v>
       </c>
-      <c r="U333" s="6" t="s">
+      <c r="U333" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="V333" s="6">
+      <c r="V333" s="7">
         <v>2023</v>
       </c>
-      <c r="W333" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="X333" s="6" t="s">
-        <v>575</v>
-      </c>
-      <c r="Y333" s="6" t="s">
+      <c r="W333" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="X333" s="7" t="s">
+        <v>607</v>
+      </c>
+      <c r="Y333" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="Z333" s="6" t="s">
+      <c r="Z333" s="7" t="s">
         <v>980</v>
       </c>
     </row>
@@ -35626,7 +35608,7 @@
         <v>8</v>
       </c>
       <c r="J335" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K335" s="5" t="s">
         <v>34</v>
@@ -35748,7 +35730,7 @@
         <v>45</v>
       </c>
       <c r="X336" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y336" s="7" t="s">
         <v>46</v>
@@ -35756,82 +35738,82 @@
       <c r="Z336" s="7"/>
     </row>
     <row r="337" spans="1:26">
-      <c r="A337" s="7" t="s">
+      <c r="A337" s="5" t="s">
         <v>1087</v>
       </c>
-      <c r="B337" s="7" t="s">
+      <c r="B337" s="5" t="s">
         <v>1204</v>
       </c>
-      <c r="C337" s="7" t="s">
+      <c r="C337" s="5" t="s">
         <v>1205</v>
       </c>
-      <c r="D337" s="7" t="s">
+      <c r="D337" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E337" s="7" t="s">
+      <c r="E337" s="5" t="s">
         <v>1206</v>
       </c>
-      <c r="F337" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G337" s="7" t="s">
+      <c r="F337" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G337" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="H337" s="7" t="s">
+      <c r="H337" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="I337" s="7">
+      <c r="I337" s="5">
         <v>8</v>
       </c>
-      <c r="J337" s="7">
-        <v>1</v>
-      </c>
-      <c r="K337" s="7" t="s">
+      <c r="J337" s="5">
+        <v>2</v>
+      </c>
+      <c r="K337" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L337" s="7" t="s">
+      <c r="L337" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="M337" s="7" t="s">
+      <c r="M337" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="N337" s="7" t="s">
+      <c r="N337" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O337" s="7" t="s">
+      <c r="O337" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="P337" s="7" t="s">
+      <c r="P337" s="5" t="s">
         <v>1207</v>
       </c>
-      <c r="Q337" s="7" t="s">
+      <c r="Q337" s="5" t="s">
         <v>1208</v>
       </c>
-      <c r="R337" s="7" t="s">
+      <c r="R337" s="5" t="s">
         <v>1209</v>
       </c>
-      <c r="S337" s="7" t="s">
+      <c r="S337" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="T337" s="7" t="s">
+      <c r="T337" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="U337" s="7" t="s">
+      <c r="U337" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="V337" s="7">
+      <c r="V337" s="5">
         <v>2023</v>
       </c>
-      <c r="W337" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="X337" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="Y337" s="7" t="s">
+      <c r="W337" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="X337" s="5" t="s">
+        <v>712</v>
+      </c>
+      <c r="Y337" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="Z337" s="7" t="s">
+      <c r="Z337" s="5" t="s">
         <v>1210</v>
       </c>
     </row>
@@ -35864,7 +35846,7 @@
         <v>9</v>
       </c>
       <c r="J338" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K338" s="3" t="s">
         <v>34</v>
@@ -35986,7 +35968,7 @@
         <v>343</v>
       </c>
       <c r="X339" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y339" s="6" t="s">
         <v>46</v>
@@ -36064,7 +36046,7 @@
         <v>343</v>
       </c>
       <c r="X340" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y340" s="6" t="s">
         <v>46</v>
@@ -36222,7 +36204,7 @@
         <v>343</v>
       </c>
       <c r="X342" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y342" s="6" t="s">
         <v>46</v>
@@ -36416,7 +36398,7 @@
         <v>9</v>
       </c>
       <c r="J345" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K345" s="6" t="s">
         <v>34</v>
@@ -36458,7 +36440,7 @@
         <v>343</v>
       </c>
       <c r="X345" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y345" s="6" t="s">
         <v>46</v>
@@ -36876,7 +36858,7 @@
         <v>30</v>
       </c>
       <c r="F351" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G351" s="5" t="s">
         <v>1251</v>
@@ -36956,7 +36938,7 @@
         <v>30</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G352" s="3" t="s">
         <v>478</v>
@@ -36968,7 +36950,7 @@
         <v>10</v>
       </c>
       <c r="J352" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K352" s="3" t="s">
         <v>34</v>
@@ -37034,7 +37016,7 @@
         <v>30</v>
       </c>
       <c r="F353" s="6" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G353" s="6" t="s">
         <v>806</v>
@@ -37088,7 +37070,7 @@
         <v>343</v>
       </c>
       <c r="X353" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y353" s="6" t="s">
         <v>46</v>
@@ -37112,7 +37094,7 @@
         <v>30</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G354" s="3" t="s">
         <v>534</v>
@@ -37482,7 +37464,7 @@
         <v>343</v>
       </c>
       <c r="X358" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y358" s="6" t="s">
         <v>46</v>
@@ -37560,7 +37542,7 @@
         <v>343</v>
       </c>
       <c r="X359" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y359" s="6" t="s">
         <v>46</v>
@@ -38502,7 +38484,7 @@
         <v>343</v>
       </c>
       <c r="X371" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y371" s="6" t="s">
         <v>46</v>
@@ -38580,7 +38562,7 @@
         <v>343</v>
       </c>
       <c r="X372" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y372" s="6" t="s">
         <v>46</v>
@@ -38658,7 +38640,7 @@
         <v>343</v>
       </c>
       <c r="X373" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y373" s="6" t="s">
         <v>46</v>
@@ -38736,7 +38718,7 @@
         <v>343</v>
       </c>
       <c r="X374" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y374" s="6" t="s">
         <v>46</v>
@@ -38774,7 +38756,7 @@
         <v>9</v>
       </c>
       <c r="J375" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K375" s="5" t="s">
         <v>34</v>
@@ -38896,7 +38878,7 @@
         <v>343</v>
       </c>
       <c r="X376" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y376" s="6" t="s">
         <v>46</v>
@@ -39448,7 +39430,7 @@
         <v>45</v>
       </c>
       <c r="X383" s="5" t="s">
-        <v>712</v>
+        <v>45</v>
       </c>
       <c r="Y383" s="5" t="s">
         <v>46</v>
@@ -39606,7 +39588,7 @@
         <v>45</v>
       </c>
       <c r="X385" s="5" t="s">
-        <v>712</v>
+        <v>940</v>
       </c>
       <c r="Y385" s="5" t="s">
         <v>46</v>
@@ -39684,7 +39666,7 @@
         <v>343</v>
       </c>
       <c r="X386" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y386" s="6" t="s">
         <v>46</v>
@@ -40032,7 +40014,7 @@
         <v>6</v>
       </c>
       <c r="J391" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K391" s="6" t="s">
         <v>34</v>
@@ -40074,7 +40056,7 @@
         <v>343</v>
       </c>
       <c r="X391" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y391" s="6" t="s">
         <v>46</v>
@@ -41014,7 +40996,7 @@
         <v>343</v>
       </c>
       <c r="X403" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y403" s="6" t="s">
         <v>46</v>
@@ -41330,7 +41312,7 @@
         <v>343</v>
       </c>
       <c r="X407" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y407" s="6" t="s">
         <v>46</v>
@@ -41408,7 +41390,7 @@
         <v>343</v>
       </c>
       <c r="X408" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y408" s="6" t="s">
         <v>46</v>
@@ -41512,7 +41494,7 @@
         <v>30</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G410" s="3" t="s">
         <v>169</v>
@@ -41592,7 +41574,7 @@
         <v>30</v>
       </c>
       <c r="F411" s="6" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G411" s="6" t="s">
         <v>392</v>
@@ -41646,7 +41628,7 @@
         <v>343</v>
       </c>
       <c r="X411" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y411" s="6" t="s">
         <v>46</v>
@@ -41670,7 +41652,7 @@
         <v>30</v>
       </c>
       <c r="F412" s="6" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G412" s="6" t="s">
         <v>1405</v>
@@ -41724,7 +41706,7 @@
         <v>343</v>
       </c>
       <c r="X412" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y412" s="6" t="s">
         <v>46</v>
@@ -41748,7 +41730,7 @@
         <v>30</v>
       </c>
       <c r="F413" s="6" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G413" s="6" t="s">
         <v>641</v>
@@ -41802,7 +41784,7 @@
         <v>343</v>
       </c>
       <c r="X413" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y413" s="6" t="s">
         <v>46</v>
@@ -41960,7 +41942,7 @@
         <v>343</v>
       </c>
       <c r="X415" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y415" s="6" t="s">
         <v>46</v>
@@ -42432,7 +42414,7 @@
         <v>343</v>
       </c>
       <c r="X421" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y421" s="6" t="s">
         <v>46</v>
@@ -42592,7 +42574,7 @@
         <v>343</v>
       </c>
       <c r="X423" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y423" s="6" t="s">
         <v>46</v>
@@ -42750,7 +42732,7 @@
         <v>45</v>
       </c>
       <c r="X425" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y425" s="7" t="s">
         <v>46</v>
@@ -43090,7 +43072,7 @@
         <v>30</v>
       </c>
       <c r="F430" s="7" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G430" s="7" t="s">
         <v>708</v>
@@ -43144,7 +43126,7 @@
         <v>45</v>
       </c>
       <c r="X430" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y430" s="7" t="s">
         <v>46</v>
@@ -43170,7 +43152,7 @@
         <v>30</v>
       </c>
       <c r="F431" s="6" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G431" s="6" t="s">
         <v>84</v>
@@ -43224,7 +43206,7 @@
         <v>343</v>
       </c>
       <c r="X431" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y431" s="6" t="s">
         <v>46</v>
@@ -43248,7 +43230,7 @@
         <v>30</v>
       </c>
       <c r="F432" s="6" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G432" s="6" t="s">
         <v>669</v>
@@ -43302,7 +43284,7 @@
         <v>343</v>
       </c>
       <c r="X432" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y432" s="6" t="s">
         <v>46</v>
@@ -43326,7 +43308,7 @@
         <v>30</v>
       </c>
       <c r="F433" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G433" s="5" t="s">
         <v>169</v>
@@ -43338,7 +43320,7 @@
         <v>10</v>
       </c>
       <c r="J433" s="5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K433" s="5" t="s">
         <v>34</v>
@@ -43458,7 +43440,7 @@
         <v>343</v>
       </c>
       <c r="X434" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y434" s="6" t="s">
         <v>46</v>
@@ -43538,7 +43520,7 @@
         <v>343</v>
       </c>
       <c r="X435" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y435" s="6" t="s">
         <v>46</v>
@@ -43694,7 +43676,7 @@
         <v>45</v>
       </c>
       <c r="X437" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y437" s="7" t="s">
         <v>46</v>
@@ -44166,7 +44148,7 @@
         <v>45</v>
       </c>
       <c r="X443" s="5" t="s">
-        <v>940</v>
+        <v>45</v>
       </c>
       <c r="Y443" s="5" t="s">
         <v>46</v>
@@ -44244,7 +44226,7 @@
         <v>343</v>
       </c>
       <c r="X444" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y444" s="6" t="s">
         <v>46</v>
@@ -44598,7 +44580,7 @@
         <v>8</v>
       </c>
       <c r="J449" s="5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K449" s="5" t="s">
         <v>1290</v>
@@ -45112,7 +45094,7 @@
         <v>45</v>
       </c>
       <c r="X455" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y455" s="7" t="s">
         <v>46</v>
@@ -45350,7 +45332,7 @@
         <v>45</v>
       </c>
       <c r="X458" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y458" s="7" t="s">
         <v>46</v>
@@ -45454,7 +45436,7 @@
         <v>840</v>
       </c>
       <c r="F460" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G460" s="3" t="s">
         <v>48</v>
@@ -45668,7 +45650,7 @@
         <v>343</v>
       </c>
       <c r="X462" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y462" s="6" t="s">
         <v>46</v>
@@ -45746,7 +45728,7 @@
         <v>45</v>
       </c>
       <c r="X463" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y463" s="7" t="s">
         <v>46</v>
@@ -45906,7 +45888,7 @@
         <v>45</v>
       </c>
       <c r="X465" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y465" s="7" t="s">
         <v>46</v>
@@ -46140,7 +46122,7 @@
         <v>45</v>
       </c>
       <c r="X468" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y468" s="7" t="s">
         <v>46</v>
@@ -46298,7 +46280,7 @@
         <v>45</v>
       </c>
       <c r="X470" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y470" s="7" t="s">
         <v>46</v>
@@ -46334,7 +46316,7 @@
         <v>8</v>
       </c>
       <c r="J471" s="5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K471" s="5" t="s">
         <v>1290</v>
@@ -46690,7 +46672,7 @@
         <v>45</v>
       </c>
       <c r="X475" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y475" s="7" t="s">
         <v>46</v>
@@ -47004,7 +46986,7 @@
         <v>45</v>
       </c>
       <c r="X479" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y479" s="7" t="s">
         <v>46</v>
@@ -47236,7 +47218,7 @@
         <v>45</v>
       </c>
       <c r="X482" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y482" s="7" t="s">
         <v>46</v>
@@ -47430,7 +47412,7 @@
         <v>8</v>
       </c>
       <c r="J485" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K485" s="5" t="s">
         <v>1290</v>
@@ -47632,7 +47614,7 @@
         <v>45</v>
       </c>
       <c r="X487" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y487" s="7" t="s">
         <v>46</v>
@@ -47656,7 +47638,7 @@
         <v>72</v>
       </c>
       <c r="F488" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G488" s="3" t="s">
         <v>777</v>
@@ -47668,7 +47650,7 @@
         <v>8</v>
       </c>
       <c r="J488" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K488" s="3" t="s">
         <v>1290</v>
@@ -47736,7 +47718,7 @@
         <v>72</v>
       </c>
       <c r="F489" s="6" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G489" s="6" t="s">
         <v>48</v>
@@ -47790,7 +47772,7 @@
         <v>343</v>
       </c>
       <c r="X489" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y489" s="6" t="s">
         <v>46</v>
@@ -47814,7 +47796,7 @@
         <v>72</v>
       </c>
       <c r="F490" s="6" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G490" s="6" t="s">
         <v>675</v>
@@ -47868,7 +47850,7 @@
         <v>343</v>
       </c>
       <c r="X490" s="6" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y490" s="6" t="s">
         <v>46</v>
@@ -47946,7 +47928,7 @@
         <v>45</v>
       </c>
       <c r="X491" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y491" s="7" t="s">
         <v>46</v>
@@ -48026,7 +48008,7 @@
         <v>45</v>
       </c>
       <c r="X492" s="3" t="s">
-        <v>690</v>
+        <v>45</v>
       </c>
       <c r="Y492" s="3" t="s">
         <v>46</v>
@@ -48372,7 +48354,7 @@
         <v>8</v>
       </c>
       <c r="J497" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K497" s="4" t="s">
         <v>1290</v>
@@ -48724,7 +48706,7 @@
         <v>45</v>
       </c>
       <c r="X501" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y501" s="7" t="s">
         <v>46</v>
@@ -48904,7 +48886,7 @@
         <v>840</v>
       </c>
       <c r="F504" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G504" s="3" t="s">
         <v>431</v>
@@ -48984,7 +48966,7 @@
         <v>840</v>
       </c>
       <c r="F505" s="5" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G505" s="5" t="s">
         <v>1346</v>
@@ -49062,7 +49044,7 @@
         <v>840</v>
       </c>
       <c r="F506" s="3" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G506" s="3" t="s">
         <v>1274</v>
@@ -49150,7 +49132,7 @@
         <v>8</v>
       </c>
       <c r="J507" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K507" s="4" t="s">
         <v>1290</v>
@@ -49810,7 +49792,7 @@
         <v>45</v>
       </c>
       <c r="X515" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y515" s="7" t="s">
         <v>46</v>
@@ -49922,7 +49904,7 @@
         <v>8</v>
       </c>
       <c r="J517" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K517" s="4" t="s">
         <v>1290</v>
@@ -50528,7 +50510,7 @@
         <v>72</v>
       </c>
       <c r="F525" s="4" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G525" s="4" t="s">
         <v>185</v>
@@ -50606,7 +50588,7 @@
         <v>72</v>
       </c>
       <c r="F526" s="4" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G526" s="4" t="s">
         <v>185</v>
@@ -50682,7 +50664,7 @@
         <v>72</v>
       </c>
       <c r="F527" s="4" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G527" s="4" t="s">
         <v>185</v>
@@ -51044,7 +51026,7 @@
         <v>45</v>
       </c>
       <c r="X531" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y531" s="7" t="s">
         <v>46</v>
@@ -52378,7 +52360,7 @@
         <v>840</v>
       </c>
       <c r="F549" s="4" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G549" s="4" t="s">
         <v>185</v>
@@ -52456,7 +52438,7 @@
         <v>840</v>
       </c>
       <c r="F550" s="4" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G550" s="4" t="s">
         <v>185</v>
@@ -52532,7 +52514,7 @@
         <v>840</v>
       </c>
       <c r="F551" s="4" t="s">
-        <v>31</v>
+        <v>191</v>
       </c>
       <c r="G551" s="4" t="s">
         <v>185</v>
@@ -56054,7 +56036,7 @@
         <v>45</v>
       </c>
       <c r="X596" s="7" t="s">
-        <v>575</v>
+        <v>607</v>
       </c>
       <c r="Y596" s="7" t="s">
         <v>46</v>
@@ -63079,10 +63061,10 @@
         <v>191</v>
       </c>
       <c r="G42" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="H42" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="I42" s="3">
         <v>8</v>
@@ -66755,10 +66737,10 @@
         <v>31</v>
       </c>
       <c r="G88" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="H88" s="3" t="s">
         <v>576</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>577</v>
       </c>
       <c r="I88" s="3">
         <v>8</v>
@@ -72481,10 +72463,10 @@
         <v>31</v>
       </c>
       <c r="G160" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="H160" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="H160" s="3" t="s">
-        <v>586</v>
       </c>
       <c r="I160" s="3">
         <v>9</v>
@@ -72538,7 +72520,7 @@
         <v>46</v>
       </c>
       <c r="Z160" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="161" spans="1:26">
@@ -73874,7 +73856,7 @@
         <v>507</v>
       </c>
       <c r="T177" s="5" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="U177" s="5" t="s">
         <v>44</v>
@@ -75661,10 +75643,10 @@
         <v>31</v>
       </c>
       <c r="G200" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="H200" s="3" t="s">
         <v>585</v>
-      </c>
-      <c r="H200" s="3" t="s">
-        <v>586</v>
       </c>
       <c r="I200" s="3">
         <v>9</v>
@@ -75718,7 +75700,7 @@
         <v>46</v>
       </c>
       <c r="Z200" s="3" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
     </row>
     <row r="201" spans="1:26">
@@ -90381,7 +90363,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.7109375" customWidth="1"/>
@@ -90420,60 +90402,6 @@
       </c>
       <c r="I1" s="1" t="s">
         <v>2927</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="8" t="s">
-        <v>2928</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>1196</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>775</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>1227</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>1224</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>2929</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="3" t="s">
-        <v>2930</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>1196</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="s">
-        <v>1123</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>1128</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
-        <v>1224</v>
       </c>
     </row>
   </sheetData>
@@ -90499,3399 +90427,3399 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>2928</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2929</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2930</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2931</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2932</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2933</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>2934</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="9">
+      <c r="B2" s="8">
         <v>26133</v>
       </c>
-      <c r="C2" s="9">
+      <c r="C2" s="8">
         <v>11</v>
       </c>
-      <c r="D2" s="9">
+      <c r="D2" s="8">
         <v>13</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>2935</v>
+      <c r="E2" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="11">
+      <c r="B3" s="10">
         <v>26767</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>10</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>14</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>2935</v>
+      <c r="E3" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B4" s="9">
+      <c r="B4" s="8">
         <v>951</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="8">
         <v>9</v>
       </c>
-      <c r="D4" s="9">
+      <c r="D4" s="8">
         <v>11</v>
       </c>
-      <c r="E4" s="12" t="s">
-        <v>2936</v>
+      <c r="E4" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
         <v>296</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="10">
         <v>20147</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>9</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>11</v>
       </c>
-      <c r="E5" s="12" t="s">
-        <v>2936</v>
+      <c r="E5" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="8">
         <v>31914</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="8">
         <v>8</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="8">
         <v>8</v>
       </c>
-      <c r="E6" s="10" t="s">
-        <v>2935</v>
+      <c r="E6" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B7" s="11">
+      <c r="B7" s="10">
         <v>2430</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>8</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="10">
         <v>8</v>
       </c>
-      <c r="E7" s="12" t="s">
-        <v>2936</v>
+      <c r="E7" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="B8" s="9">
+      <c r="B8" s="8">
         <v>38249</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="8">
         <v>8</v>
       </c>
-      <c r="D8" s="9">
+      <c r="D8" s="8">
         <v>9</v>
       </c>
-      <c r="E8" s="10" t="s">
-        <v>2935</v>
+      <c r="E8" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
         <v>478</v>
       </c>
-      <c r="B9" s="11">
+      <c r="B9" s="10">
         <v>13045</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>8</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="10">
         <v>10</v>
       </c>
-      <c r="E9" s="10" t="s">
-        <v>2935</v>
+      <c r="E9" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B10" s="9">
+      <c r="B10" s="8">
         <v>13707</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="8">
         <v>8</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D10" s="8">
         <v>9</v>
       </c>
-      <c r="E10" s="12" t="s">
-        <v>2936</v>
+      <c r="E10" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B11" s="11">
+      <c r="B11" s="10">
         <v>25583</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>7</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="10">
         <v>9</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="8">
         <v>17056</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="8">
         <v>7</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="8">
         <v>8</v>
       </c>
-      <c r="E12" s="10" t="s">
-        <v>2935</v>
+      <c r="E12" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="B13" s="11">
+      <c r="B13" s="10">
         <v>27428</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>7</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>7</v>
       </c>
-      <c r="E13" s="10" t="s">
-        <v>2935</v>
+      <c r="E13" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B14" s="9">
+      <c r="B14" s="8">
         <v>38991</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="8">
         <v>7</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D14" s="8">
         <v>8</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>2935</v>
+      <c r="E14" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B15" s="11">
+      <c r="B15" s="10">
         <v>27191</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>7</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <v>9</v>
       </c>
-      <c r="E15" s="10" t="s">
-        <v>2935</v>
+      <c r="E15" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B16" s="9">
+      <c r="B16" s="8">
         <v>15339</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="8">
         <v>7</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D16" s="8">
         <v>8</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>2935</v>
+      <c r="E16" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="5" t="s">
         <v>388</v>
       </c>
-      <c r="B17" s="11">
+      <c r="B17" s="10">
         <v>13035</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>7</v>
       </c>
-      <c r="D17" s="11">
+      <c r="D17" s="10">
         <v>8</v>
       </c>
-      <c r="E17" s="12" t="s">
-        <v>2936</v>
+      <c r="E17" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="B18" s="9">
+      <c r="B18" s="8">
         <v>9630</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="8">
         <v>7</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D18" s="8">
         <v>7</v>
       </c>
-      <c r="E18" s="10" t="s">
-        <v>2935</v>
+      <c r="E18" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="5" t="s">
         <v>675</v>
       </c>
-      <c r="B19" s="11">
+      <c r="B19" s="10">
         <v>25998</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>7</v>
       </c>
-      <c r="D19" s="11">
+      <c r="D19" s="10">
         <v>8</v>
       </c>
-      <c r="E19" s="10" t="s">
-        <v>2935</v>
+      <c r="E19" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="B20" s="9">
+      <c r="B20" s="8">
         <v>14111</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="8">
         <v>7</v>
       </c>
-      <c r="D20" s="9">
+      <c r="D20" s="8">
         <v>8</v>
       </c>
-      <c r="E20" s="12" t="s">
-        <v>2936</v>
+      <c r="E20" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="B21" s="11">
+      <c r="B21" s="10">
         <v>28325</v>
       </c>
-      <c r="C21" s="11">
+      <c r="C21" s="10">
         <v>6</v>
       </c>
-      <c r="D21" s="11">
+      <c r="D21" s="10">
         <v>7</v>
       </c>
-      <c r="E21" s="12" t="s">
-        <v>2936</v>
+      <c r="E21" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="B22" s="9">
+      <c r="B22" s="8">
         <v>7022</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="8">
         <v>6</v>
       </c>
-      <c r="D22" s="9">
+      <c r="D22" s="8">
         <v>7</v>
       </c>
-      <c r="E22" s="12" t="s">
-        <v>2936</v>
+      <c r="E22" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
         <v>400</v>
       </c>
-      <c r="B23" s="11">
+      <c r="B23" s="10">
         <v>38409</v>
       </c>
-      <c r="C23" s="11">
+      <c r="C23" s="10">
         <v>6</v>
       </c>
-      <c r="D23" s="11">
+      <c r="D23" s="10">
         <v>9</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B24" s="9">
+      <c r="B24" s="8">
         <v>6429</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C24" s="8">
         <v>6</v>
       </c>
-      <c r="D24" s="9">
+      <c r="D24" s="8">
         <v>7</v>
       </c>
-      <c r="E24" s="12" t="s">
-        <v>2936</v>
+      <c r="E24" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
         <v>572</v>
       </c>
-      <c r="B25" s="11">
+      <c r="B25" s="10">
         <v>27366</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="10">
         <v>6</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="10">
         <v>9</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>2935</v>
+      <c r="E25" s="9" t="s">
+        <v>2932</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="8">
         <v>9849</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="8">
         <v>5</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="8">
         <v>6</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B27" s="11">
+      <c r="B27" s="10">
         <v>17277</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="10">
         <v>5</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="10">
         <v>8</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>2936</v>
+      <c r="E27" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="B28" s="9">
+      <c r="B28" s="8">
         <v>14023</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C28" s="8">
         <v>5</v>
       </c>
-      <c r="D28" s="9">
+      <c r="D28" s="8">
         <v>5</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
         <v>669</v>
       </c>
-      <c r="B29" s="11">
+      <c r="B29" s="10">
         <v>13834</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="10">
         <v>5</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="10">
         <v>5</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B30" s="9">
+      <c r="B30" s="8">
         <v>3163</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C30" s="8">
         <v>4</v>
       </c>
-      <c r="D30" s="9">
+      <c r="D30" s="8">
         <v>4</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
         <v>381</v>
       </c>
-      <c r="B31" s="11">
+      <c r="B31" s="10">
         <v>6758</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="10">
         <v>4</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="10">
         <v>6</v>
       </c>
-      <c r="E31" s="12" t="s">
-        <v>2936</v>
+      <c r="E31" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="B32" s="9">
+      <c r="B32" s="8">
         <v>10468</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C32" s="8">
         <v>4</v>
       </c>
-      <c r="D32" s="9">
+      <c r="D32" s="8">
         <v>4</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="B33" s="11">
+      <c r="B33" s="10">
         <v>27342</v>
       </c>
-      <c r="C33" s="11">
+      <c r="C33" s="10">
         <v>4</v>
       </c>
-      <c r="D33" s="11">
+      <c r="D33" s="10">
         <v>4</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="B34" s="9">
+      <c r="B34" s="8">
         <v>16666</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C34" s="8">
         <v>4</v>
       </c>
-      <c r="D34" s="9">
+      <c r="D34" s="8">
         <v>4</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
         <v>466</v>
       </c>
-      <c r="B35" s="11">
+      <c r="B35" s="10">
         <v>22825</v>
       </c>
-      <c r="C35" s="11">
+      <c r="C35" s="10">
         <v>4</v>
       </c>
-      <c r="D35" s="11">
+      <c r="D35" s="10">
         <v>4</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="B36" s="9">
+      <c r="B36" s="8">
         <v>18683</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C36" s="8">
         <v>4</v>
       </c>
-      <c r="D36" s="9">
+      <c r="D36" s="8">
         <v>5</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="B37" s="11">
+      <c r="B37" s="10">
         <v>28683</v>
       </c>
-      <c r="C37" s="11">
+      <c r="C37" s="10">
         <v>4</v>
       </c>
-      <c r="D37" s="11">
+      <c r="D37" s="10">
         <v>4</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="B38" s="9">
+      <c r="B38" s="8">
         <v>2257</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C38" s="8">
         <v>4</v>
       </c>
-      <c r="D38" s="9">
+      <c r="D38" s="8">
         <v>6</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
         <v>748</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="10">
         <v>15492</v>
       </c>
-      <c r="C39" s="11">
+      <c r="C39" s="10">
         <v>4</v>
       </c>
-      <c r="D39" s="11">
+      <c r="D39" s="10">
         <v>4</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
         <v>806</v>
       </c>
-      <c r="B40" s="9">
+      <c r="B40" s="8">
         <v>23628</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="8">
         <v>4</v>
       </c>
-      <c r="D40" s="9">
+      <c r="D40" s="8">
         <v>4</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
         <v>917</v>
       </c>
-      <c r="B41" s="11">
+      <c r="B41" s="10">
         <v>19891</v>
       </c>
-      <c r="C41" s="11">
+      <c r="C41" s="10">
         <v>4</v>
       </c>
-      <c r="D41" s="11">
+      <c r="D41" s="10">
         <v>5</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B42" s="9">
+      <c r="B42" s="8">
         <v>5432</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C42" s="8">
         <v>3</v>
       </c>
-      <c r="D42" s="9">
+      <c r="D42" s="8">
         <v>3</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="B43" s="11">
+      <c r="B43" s="10">
         <v>31002</v>
       </c>
-      <c r="C43" s="11">
+      <c r="C43" s="10">
         <v>3</v>
       </c>
-      <c r="D43" s="11">
+      <c r="D43" s="10">
         <v>3</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B44" s="9">
+      <c r="B44" s="8">
         <v>10463</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C44" s="8">
         <v>3</v>
       </c>
-      <c r="D44" s="9">
+      <c r="D44" s="8">
         <v>3</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="B45" s="11">
+      <c r="B45" s="10">
         <v>21701</v>
       </c>
-      <c r="C45" s="11">
+      <c r="C45" s="10">
         <v>3</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <v>3</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B46" s="9">
+      <c r="B46" s="8">
         <v>31118</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C46" s="8">
         <v>3</v>
       </c>
-      <c r="D46" s="9">
+      <c r="D46" s="8">
         <v>3</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B47" s="11">
+      <c r="B47" s="10">
         <v>12507</v>
       </c>
-      <c r="C47" s="11">
+      <c r="C47" s="10">
         <v>3</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <v>4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="48" spans="1:5">
       <c r="A48" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="B48" s="9">
+      <c r="B48" s="8">
         <v>6773</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C48" s="8">
         <v>3</v>
       </c>
-      <c r="D48" s="9">
+      <c r="D48" s="8">
         <v>3</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="49" spans="1:5">
       <c r="A49" s="5" t="s">
         <v>292</v>
       </c>
-      <c r="B49" s="11">
+      <c r="B49" s="10">
         <v>39495</v>
       </c>
-      <c r="C49" s="11">
+      <c r="C49" s="10">
         <v>3</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="10">
         <v>3</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="B50" s="9">
+      <c r="B50" s="8">
         <v>51060</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C50" s="8">
         <v>3</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="8">
         <v>3</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="51" spans="1:5">
       <c r="A51" s="5" t="s">
-        <v>593</v>
-      </c>
-      <c r="B51" s="11">
+        <v>592</v>
+      </c>
+      <c r="B51" s="10">
         <v>17859</v>
       </c>
-      <c r="C51" s="11">
+      <c r="C51" s="10">
         <v>3</v>
       </c>
-      <c r="D51" s="11">
+      <c r="D51" s="10">
         <v>3</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" s="3" t="s">
-        <v>596</v>
-      </c>
-      <c r="B52" s="9">
+        <v>595</v>
+      </c>
+      <c r="B52" s="8">
         <v>26972</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C52" s="8">
         <v>3</v>
       </c>
-      <c r="D52" s="9">
+      <c r="D52" s="8">
         <v>3</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="53" spans="1:5">
       <c r="A53" s="5" t="s">
         <v>632</v>
       </c>
-      <c r="B53" s="11">
+      <c r="B53" s="10">
         <v>23592</v>
       </c>
-      <c r="C53" s="11">
+      <c r="C53" s="10">
         <v>3</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <v>3</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="54" spans="1:5">
       <c r="A54" s="3" t="s">
         <v>686</v>
       </c>
-      <c r="B54" s="9">
+      <c r="B54" s="8">
         <v>26443</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C54" s="8">
         <v>3</v>
       </c>
-      <c r="D54" s="9">
+      <c r="D54" s="8">
         <v>4</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="55" spans="1:5">
       <c r="A55" s="5" t="s">
         <v>708</v>
       </c>
-      <c r="B55" s="11">
+      <c r="B55" s="10">
         <v>25974</v>
       </c>
-      <c r="C55" s="11">
+      <c r="C55" s="10">
         <v>3</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="10">
         <v>3</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="56" spans="1:5">
       <c r="A56" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="B56" s="9">
+      <c r="B56" s="8">
         <v>24701</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C56" s="8">
         <v>3</v>
       </c>
-      <c r="D56" s="9">
+      <c r="D56" s="8">
         <v>3</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="57" spans="1:5">
       <c r="A57" s="5" t="s">
         <v>898</v>
       </c>
-      <c r="B57" s="11">
+      <c r="B57" s="10">
         <v>23061</v>
       </c>
-      <c r="C57" s="11">
+      <c r="C57" s="10">
         <v>3</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="10">
         <v>4</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="58" spans="1:5">
       <c r="A58" s="3" t="s">
         <v>980</v>
       </c>
-      <c r="B58" s="9">
+      <c r="B58" s="8">
         <v>5443</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C58" s="8">
         <v>3</v>
       </c>
-      <c r="D58" s="9">
+      <c r="D58" s="8">
         <v>4</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="59" spans="1:5">
       <c r="A59" s="5" t="s">
         <v>1274</v>
       </c>
-      <c r="B59" s="11">
+      <c r="B59" s="10">
         <v>14767</v>
       </c>
-      <c r="C59" s="11">
+      <c r="C59" s="10">
         <v>3</v>
       </c>
-      <c r="D59" s="11">
+      <c r="D59" s="10">
         <v>4</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="60" spans="1:5">
       <c r="A60" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B60" s="9">
+      <c r="B60" s="8">
         <v>22942</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C60" s="8">
         <v>2</v>
       </c>
-      <c r="D60" s="9">
+      <c r="D60" s="8">
         <v>3</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="61" spans="1:5">
       <c r="A61" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="B61" s="11">
+      <c r="B61" s="10">
         <v>21510</v>
       </c>
-      <c r="C61" s="11">
+      <c r="C61" s="10">
         <v>2</v>
       </c>
-      <c r="D61" s="11">
+      <c r="D61" s="10">
         <v>2</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="62" spans="1:5">
       <c r="A62" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B62" s="9">
+      <c r="B62" s="8">
         <v>5331</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C62" s="8">
         <v>2</v>
       </c>
-      <c r="D62" s="9">
+      <c r="D62" s="8">
         <v>2</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="63" spans="1:5">
       <c r="A63" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="B63" s="11">
+      <c r="B63" s="10">
         <v>17321</v>
       </c>
-      <c r="C63" s="11">
+      <c r="C63" s="10">
         <v>2</v>
       </c>
-      <c r="D63" s="11">
+      <c r="D63" s="10">
         <v>2</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="64" spans="1:5">
       <c r="A64" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="B64" s="9">
+      <c r="B64" s="8">
         <v>20707</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C64" s="8">
         <v>2</v>
       </c>
-      <c r="D64" s="9">
+      <c r="D64" s="8">
         <v>2</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="B65" s="11">
+      <c r="B65" s="10">
         <v>10711</v>
       </c>
-      <c r="C65" s="11">
+      <c r="C65" s="10">
         <v>2</v>
       </c>
-      <c r="D65" s="11">
+      <c r="D65" s="10">
         <v>2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="B66" s="9">
+      <c r="B66" s="8">
         <v>6896</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C66" s="8">
         <v>2</v>
       </c>
-      <c r="D66" s="9">
+      <c r="D66" s="8">
         <v>2</v>
       </c>
-      <c r="E66" s="12" t="s">
-        <v>2936</v>
+      <c r="E66" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" s="5" t="s">
         <v>276</v>
       </c>
-      <c r="B67" s="11">
+      <c r="B67" s="10">
         <v>16471</v>
       </c>
-      <c r="C67" s="11">
+      <c r="C67" s="10">
         <v>2</v>
       </c>
-      <c r="D67" s="11">
+      <c r="D67" s="10">
         <v>2</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B68" s="9">
+      <c r="B68" s="8">
         <v>27871</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C68" s="8">
         <v>2</v>
       </c>
-      <c r="D68" s="9">
+      <c r="D68" s="8">
         <v>2</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="69" spans="1:5">
       <c r="A69" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="B69" s="11">
+      <c r="B69" s="10">
         <v>6935</v>
       </c>
-      <c r="C69" s="11">
+      <c r="C69" s="10">
         <v>2</v>
       </c>
-      <c r="D69" s="11">
+      <c r="D69" s="10">
         <v>3</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="70" spans="1:5">
       <c r="A70" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="B70" s="9">
+      <c r="B70" s="8">
         <v>33600</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C70" s="8">
         <v>2</v>
       </c>
-      <c r="D70" s="9">
+      <c r="D70" s="8">
         <v>2</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="71" spans="1:5">
       <c r="A71" s="5" t="s">
         <v>384</v>
       </c>
-      <c r="B71" s="11">
+      <c r="B71" s="10">
         <v>30709</v>
       </c>
-      <c r="C71" s="11">
+      <c r="C71" s="10">
         <v>2</v>
       </c>
-      <c r="D71" s="11">
+      <c r="D71" s="10">
         <v>2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="72" spans="1:5">
       <c r="A72" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="B72" s="9">
+      <c r="B72" s="8">
         <v>27276</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C72" s="8">
         <v>2</v>
       </c>
-      <c r="D72" s="9">
+      <c r="D72" s="8">
         <v>2</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="73" spans="1:5">
       <c r="A73" s="5" t="s">
         <v>504</v>
       </c>
-      <c r="B73" s="11">
+      <c r="B73" s="10">
         <v>50516</v>
       </c>
-      <c r="C73" s="11">
+      <c r="C73" s="10">
         <v>2</v>
       </c>
-      <c r="D73" s="11">
+      <c r="D73" s="10">
         <v>2</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="74" spans="1:5">
       <c r="A74" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="B74" s="9">
+      <c r="B74" s="8">
         <v>27838</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C74" s="8">
         <v>2</v>
       </c>
-      <c r="D74" s="9">
+      <c r="D74" s="8">
         <v>3</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="75" spans="1:5">
       <c r="A75" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="B75" s="11">
+      <c r="B75" s="10">
         <v>20508</v>
       </c>
-      <c r="C75" s="11">
+      <c r="C75" s="10">
         <v>2</v>
       </c>
-      <c r="D75" s="11">
+      <c r="D75" s="10">
         <v>2</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="76" spans="1:5">
       <c r="A76" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="B76" s="9">
+        <v>575</v>
+      </c>
+      <c r="B76" s="8">
         <v>38535</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C76" s="8">
         <v>2</v>
       </c>
-      <c r="D76" s="9">
+      <c r="D76" s="8">
         <v>2</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="77" spans="1:5">
       <c r="A77" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="B77" s="11">
+      <c r="B77" s="10">
         <v>17023</v>
       </c>
-      <c r="C77" s="11">
+      <c r="C77" s="10">
         <v>2</v>
       </c>
-      <c r="D77" s="11">
+      <c r="D77" s="10">
         <v>2</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="78" spans="1:5">
       <c r="A78" s="3" t="s">
         <v>647</v>
       </c>
-      <c r="B78" s="9">
+      <c r="B78" s="8">
         <v>7841</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C78" s="8">
         <v>2</v>
       </c>
-      <c r="D78" s="9">
+      <c r="D78" s="8">
         <v>2</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="79" spans="1:5">
       <c r="A79" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="B79" s="11">
+      <c r="B79" s="10">
         <v>12209</v>
       </c>
-      <c r="C79" s="11">
+      <c r="C79" s="10">
         <v>2</v>
       </c>
-      <c r="D79" s="11">
+      <c r="D79" s="10">
         <v>2</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="80" spans="1:5">
       <c r="A80" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="B80" s="9">
+      <c r="B80" s="8">
         <v>40896</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C80" s="8">
         <v>2</v>
       </c>
-      <c r="D80" s="9">
+      <c r="D80" s="8">
         <v>2</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" s="5" t="s">
         <v>816</v>
       </c>
-      <c r="B81" s="11">
+      <c r="B81" s="10">
         <v>9676</v>
       </c>
-      <c r="C81" s="11">
+      <c r="C81" s="10">
         <v>2</v>
       </c>
-      <c r="D81" s="11">
+      <c r="D81" s="10">
         <v>2</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="82" spans="1:5">
       <c r="A82" s="3" t="s">
         <v>825</v>
       </c>
-      <c r="B82" s="9">
+      <c r="B82" s="8">
         <v>7191</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C82" s="8">
         <v>2</v>
       </c>
-      <c r="D82" s="9">
+      <c r="D82" s="8">
         <v>2</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" s="5" t="s">
         <v>860</v>
       </c>
-      <c r="B83" s="11">
+      <c r="B83" s="10">
         <v>20228</v>
       </c>
-      <c r="C83" s="11">
+      <c r="C83" s="10">
         <v>2</v>
       </c>
-      <c r="D83" s="11">
+      <c r="D83" s="10">
         <v>2</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" s="3" t="s">
         <v>887</v>
       </c>
-      <c r="B84" s="9">
+      <c r="B84" s="8">
         <v>20741</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C84" s="8">
         <v>2</v>
       </c>
-      <c r="D84" s="9">
+      <c r="D84" s="8">
         <v>2</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="5" t="s">
         <v>912</v>
       </c>
-      <c r="B85" s="11">
+      <c r="B85" s="10">
         <v>5205</v>
       </c>
-      <c r="C85" s="11">
+      <c r="C85" s="10">
         <v>2</v>
       </c>
-      <c r="D85" s="11">
+      <c r="D85" s="10">
         <v>2</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" s="3" t="s">
         <v>936</v>
       </c>
-      <c r="B86" s="9">
+      <c r="B86" s="8">
         <v>20516</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C86" s="8">
         <v>2</v>
       </c>
-      <c r="D86" s="9">
+      <c r="D86" s="8">
         <v>2</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="87" spans="1:5">
       <c r="A87" s="5" t="s">
         <v>948</v>
       </c>
-      <c r="B87" s="11">
+      <c r="B87" s="10">
         <v>25299</v>
       </c>
-      <c r="C87" s="11">
+      <c r="C87" s="10">
         <v>2</v>
       </c>
-      <c r="D87" s="11">
+      <c r="D87" s="10">
         <v>2</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="88" spans="1:5">
       <c r="A88" s="3" t="s">
         <v>951</v>
       </c>
-      <c r="B88" s="9">
+      <c r="B88" s="8">
         <v>5688</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C88" s="8">
         <v>2</v>
       </c>
-      <c r="D88" s="9">
+      <c r="D88" s="8">
         <v>2</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" s="5" t="s">
         <v>965</v>
       </c>
-      <c r="B89" s="11">
+      <c r="B89" s="10">
         <v>11162</v>
       </c>
-      <c r="C89" s="11">
+      <c r="C89" s="10">
         <v>2</v>
       </c>
-      <c r="D89" s="11">
+      <c r="D89" s="10">
         <v>3</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="90" spans="1:5">
       <c r="A90" s="3" t="s">
         <v>997</v>
       </c>
-      <c r="B90" s="9">
+      <c r="B90" s="8">
         <v>18695</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C90" s="8">
         <v>2</v>
       </c>
-      <c r="D90" s="9">
+      <c r="D90" s="8">
         <v>2</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="91" spans="1:5">
       <c r="A91" s="5" t="s">
         <v>1037</v>
       </c>
-      <c r="B91" s="11">
+      <c r="B91" s="10">
         <v>3853</v>
       </c>
-      <c r="C91" s="11">
+      <c r="C91" s="10">
         <v>2</v>
       </c>
-      <c r="D91" s="11">
+      <c r="D91" s="10">
         <v>2</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="92" spans="1:5">
       <c r="A92" s="3" t="s">
         <v>1048</v>
       </c>
-      <c r="B92" s="9">
+      <c r="B92" s="8">
         <v>33177</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C92" s="8">
         <v>2</v>
       </c>
-      <c r="D92" s="9">
+      <c r="D92" s="8">
         <v>2</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="5" t="s">
         <v>1070</v>
       </c>
-      <c r="B93" s="11">
+      <c r="B93" s="10">
         <v>23898</v>
       </c>
-      <c r="C93" s="11">
+      <c r="C93" s="10">
         <v>2</v>
       </c>
-      <c r="D93" s="11">
+      <c r="D93" s="10">
         <v>2</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="94" spans="1:5">
       <c r="A94" s="3" t="s">
         <v>1099</v>
       </c>
-      <c r="B94" s="9">
+      <c r="B94" s="8">
         <v>12024</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C94" s="8">
         <v>2</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="8">
         <v>2</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="5" t="s">
         <v>1128</v>
       </c>
-      <c r="B95" s="11">
+      <c r="B95" s="10">
         <v>26955</v>
       </c>
-      <c r="C95" s="11">
+      <c r="C95" s="10">
         <v>2</v>
       </c>
-      <c r="D95" s="11">
+      <c r="D95" s="10">
         <v>2</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="3" t="s">
         <v>1215</v>
       </c>
-      <c r="B96" s="9">
+      <c r="B96" s="8">
         <v>36958</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="8">
         <v>2</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="8">
         <v>2</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="97" spans="1:5">
       <c r="A97" s="5" t="s">
         <v>1269</v>
       </c>
-      <c r="B97" s="11">
+      <c r="B97" s="10">
         <v>44643</v>
       </c>
-      <c r="C97" s="11">
+      <c r="C97" s="10">
         <v>2</v>
       </c>
-      <c r="D97" s="11">
+      <c r="D97" s="10">
         <v>2</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="98" spans="1:5">
       <c r="A98" s="3" t="s">
         <v>1288</v>
       </c>
-      <c r="B98" s="9">
+      <c r="B98" s="8">
         <v>9724</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C98" s="8">
         <v>2</v>
       </c>
-      <c r="D98" s="9">
+      <c r="D98" s="8">
         <v>4</v>
       </c>
-      <c r="E98" s="12" t="s">
-        <v>2936</v>
+      <c r="E98" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="99" spans="1:5">
       <c r="A99" s="5" t="s">
         <v>1338</v>
       </c>
-      <c r="B99" s="11">
+      <c r="B99" s="10">
         <v>3641</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="10">
         <v>2</v>
       </c>
-      <c r="D99" s="11">
+      <c r="D99" s="10">
         <v>2</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="100" spans="1:5">
       <c r="A100" s="3" t="s">
         <v>1343</v>
       </c>
-      <c r="B100" s="9">
+      <c r="B100" s="8">
         <v>3223</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C100" s="8">
         <v>2</v>
       </c>
-      <c r="D100" s="9">
+      <c r="D100" s="8">
         <v>2</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="101" spans="1:5">
       <c r="A101" s="5" t="s">
         <v>1346</v>
       </c>
-      <c r="B101" s="11">
+      <c r="B101" s="10">
         <v>14252</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="10">
         <v>2</v>
       </c>
-      <c r="D101" s="11">
+      <c r="D101" s="10">
         <v>3</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="102" spans="1:5">
       <c r="A102" s="3" t="s">
         <v>1381</v>
       </c>
-      <c r="B102" s="9">
+      <c r="B102" s="8">
         <v>27634</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C102" s="8">
         <v>2</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="8">
         <v>2</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="103" spans="1:5">
       <c r="A103" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="B103" s="11">
+      <c r="B103" s="10">
         <v>39389</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="10">
         <v>1</v>
       </c>
-      <c r="D103" s="11">
+      <c r="D103" s="10">
         <v>1</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="104" spans="1:5">
       <c r="A104" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B104" s="9">
+      <c r="B104" s="8">
         <v>23531</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C104" s="8">
         <v>1</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="8">
         <v>1</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="105" spans="1:5">
       <c r="A105" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="B105" s="11">
+      <c r="B105" s="10">
         <v>13451</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="10">
         <v>1</v>
       </c>
-      <c r="D105" s="11">
+      <c r="D105" s="10">
         <v>1</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="106" spans="1:5">
       <c r="A106" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="B106" s="9">
+      <c r="B106" s="8">
         <v>8650</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C106" s="8">
         <v>1</v>
       </c>
-      <c r="D106" s="9">
+      <c r="D106" s="8">
         <v>1</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="107" spans="1:5">
       <c r="A107" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="B107" s="11">
+      <c r="B107" s="10">
         <v>27408</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="10">
         <v>1</v>
       </c>
-      <c r="D107" s="11">
+      <c r="D107" s="10">
         <v>1</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="108" spans="1:5">
       <c r="A108" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B108" s="9">
+      <c r="B108" s="8">
         <v>21133</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C108" s="8">
         <v>1</v>
       </c>
-      <c r="D108" s="9">
+      <c r="D108" s="8">
         <v>1</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="109" spans="1:5">
       <c r="A109" s="5" t="s">
         <v>272</v>
       </c>
-      <c r="B109" s="11">
+      <c r="B109" s="10">
         <v>51089</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="10">
         <v>1</v>
       </c>
-      <c r="D109" s="11">
+      <c r="D109" s="10">
         <v>1</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="110" spans="1:5">
       <c r="A110" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B110" s="9">
+      <c r="B110" s="8">
         <v>3826</v>
       </c>
-      <c r="C110" s="9">
+      <c r="C110" s="8">
         <v>1</v>
       </c>
-      <c r="D110" s="9">
+      <c r="D110" s="8">
         <v>1</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="111" spans="1:5">
       <c r="A111" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="B111" s="11">
+      <c r="B111" s="10">
         <v>44116</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="10">
         <v>1</v>
       </c>
-      <c r="D111" s="11">
+      <c r="D111" s="10">
         <v>1</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="112" spans="1:5">
       <c r="A112" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="B112" s="9">
+      <c r="B112" s="8">
         <v>10666</v>
       </c>
-      <c r="C112" s="9">
+      <c r="C112" s="8">
         <v>1</v>
       </c>
-      <c r="D112" s="9">
+      <c r="D112" s="8">
         <v>1</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="113" spans="1:5">
       <c r="A113" s="5" t="s">
         <v>359</v>
       </c>
-      <c r="B113" s="11">
+      <c r="B113" s="10">
         <v>7436</v>
       </c>
-      <c r="C113" s="11">
+      <c r="C113" s="10">
         <v>1</v>
       </c>
-      <c r="D113" s="11">
+      <c r="D113" s="10">
         <v>1</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="114" spans="1:5">
       <c r="A114" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="B114" s="9">
+      <c r="B114" s="8">
         <v>40001</v>
       </c>
-      <c r="C114" s="9">
+      <c r="C114" s="8">
         <v>1</v>
       </c>
-      <c r="D114" s="9">
+      <c r="D114" s="8">
         <v>1</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="115" spans="1:5">
       <c r="A115" s="5" t="s">
         <v>378</v>
       </c>
-      <c r="B115" s="11">
+      <c r="B115" s="10">
         <v>14118</v>
       </c>
-      <c r="C115" s="11">
+      <c r="C115" s="10">
         <v>1</v>
       </c>
-      <c r="D115" s="11">
+      <c r="D115" s="10">
         <v>1</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="116" spans="1:5">
       <c r="A116" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="B116" s="9">
+      <c r="B116" s="8">
         <v>37682</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C116" s="8">
         <v>1</v>
       </c>
-      <c r="D116" s="9">
+      <c r="D116" s="8">
         <v>1</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="117" spans="1:5">
       <c r="A117" s="5" t="s">
         <v>419</v>
       </c>
-      <c r="B117" s="11">
+      <c r="B117" s="10">
         <v>17561</v>
       </c>
-      <c r="C117" s="11">
+      <c r="C117" s="10">
         <v>1</v>
       </c>
-      <c r="D117" s="11">
+      <c r="D117" s="10">
         <v>1</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="118" spans="1:5">
       <c r="A118" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B118" s="9">
+      <c r="B118" s="8">
         <v>6044</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C118" s="8">
         <v>1</v>
       </c>
-      <c r="D118" s="9">
+      <c r="D118" s="8">
         <v>1</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="119" spans="1:5">
       <c r="A119" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="B119" s="11">
+      <c r="B119" s="10">
         <v>26124</v>
       </c>
-      <c r="C119" s="11">
+      <c r="C119" s="10">
         <v>1</v>
       </c>
-      <c r="D119" s="11">
+      <c r="D119" s="10">
         <v>1</v>
       </c>
       <c r="E119" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="120" spans="1:5">
       <c r="A120" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="B120" s="9">
+      <c r="B120" s="8">
         <v>23188</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C120" s="8">
         <v>1</v>
       </c>
-      <c r="D120" s="9">
+      <c r="D120" s="8">
         <v>1</v>
       </c>
       <c r="E120" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="121" spans="1:5">
       <c r="A121" s="5" t="s">
         <v>462</v>
       </c>
-      <c r="B121" s="11">
+      <c r="B121" s="10">
         <v>21381</v>
       </c>
-      <c r="C121" s="11">
+      <c r="C121" s="10">
         <v>1</v>
       </c>
-      <c r="D121" s="11">
+      <c r="D121" s="10">
         <v>1</v>
       </c>
       <c r="E121" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="122" spans="1:5">
       <c r="A122" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="B122" s="9">
+      <c r="B122" s="8">
         <v>20483</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C122" s="8">
         <v>1</v>
       </c>
-      <c r="D122" s="9">
+      <c r="D122" s="8">
         <v>1</v>
       </c>
       <c r="E122" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="123" spans="1:5">
       <c r="A123" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="B123" s="11">
+      <c r="B123" s="10">
         <v>27417</v>
       </c>
-      <c r="C123" s="11">
+      <c r="C123" s="10">
         <v>1</v>
       </c>
-      <c r="D123" s="11">
+      <c r="D123" s="10">
         <v>1</v>
       </c>
       <c r="E123" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="124" spans="1:5">
       <c r="A124" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="B124" s="9">
+      <c r="B124" s="8">
         <v>18797</v>
       </c>
-      <c r="C124" s="9">
+      <c r="C124" s="8">
         <v>1</v>
       </c>
-      <c r="D124" s="9">
+      <c r="D124" s="8">
         <v>1</v>
       </c>
       <c r="E124" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="125" spans="1:5">
       <c r="A125" s="5" t="s">
         <v>513</v>
       </c>
-      <c r="B125" s="11">
+      <c r="B125" s="10">
         <v>16503</v>
       </c>
-      <c r="C125" s="11">
+      <c r="C125" s="10">
         <v>1</v>
       </c>
-      <c r="D125" s="11">
+      <c r="D125" s="10">
         <v>1</v>
       </c>
       <c r="E125" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="126" spans="1:5">
       <c r="A126" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="B126" s="9">
+      <c r="B126" s="8">
         <v>19273</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C126" s="8">
         <v>1</v>
       </c>
-      <c r="D126" s="9">
+      <c r="D126" s="8">
         <v>1</v>
       </c>
       <c r="E126" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="127" spans="1:5">
       <c r="A127" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="B127" s="11">
+      <c r="B127" s="10">
         <v>7195</v>
       </c>
-      <c r="C127" s="11">
+      <c r="C127" s="10">
         <v>1</v>
       </c>
-      <c r="D127" s="11">
+      <c r="D127" s="10">
         <v>1</v>
       </c>
       <c r="E127" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="128" spans="1:5">
       <c r="A128" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B128" s="9">
+      <c r="B128" s="8">
         <v>19127</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C128" s="8">
         <v>1</v>
       </c>
-      <c r="D128" s="9">
+      <c r="D128" s="8">
         <v>1</v>
       </c>
       <c r="E128" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="129" spans="1:5">
       <c r="A129" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="B129" s="11">
+      <c r="B129" s="10">
         <v>20450</v>
       </c>
-      <c r="C129" s="11">
+      <c r="C129" s="10">
         <v>1</v>
       </c>
-      <c r="D129" s="11">
+      <c r="D129" s="10">
         <v>1</v>
       </c>
       <c r="E129" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="130" spans="1:5">
       <c r="A130" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="B130" s="9">
+      <c r="B130" s="8">
         <v>37857</v>
       </c>
-      <c r="C130" s="9">
+      <c r="C130" s="8">
         <v>1</v>
       </c>
-      <c r="D130" s="9">
+      <c r="D130" s="8">
         <v>1</v>
       </c>
       <c r="E130" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="131" spans="1:5">
       <c r="A131" s="5" t="s">
-        <v>585</v>
-      </c>
-      <c r="B131" s="11">
+        <v>584</v>
+      </c>
+      <c r="B131" s="10">
         <v>9283</v>
       </c>
-      <c r="C131" s="11">
+      <c r="C131" s="10">
         <v>1</v>
       </c>
-      <c r="D131" s="11">
+      <c r="D131" s="10">
         <v>1</v>
       </c>
       <c r="E131" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="132" spans="1:5">
       <c r="A132" s="3" t="s">
-        <v>588</v>
-      </c>
-      <c r="B132" s="9">
+        <v>587</v>
+      </c>
+      <c r="B132" s="8">
         <v>32458</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C132" s="8">
         <v>1</v>
       </c>
-      <c r="D132" s="9">
+      <c r="D132" s="8">
         <v>1</v>
       </c>
       <c r="E132" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="B133" s="11">
+      <c r="B133" s="10">
         <v>3156</v>
       </c>
-      <c r="C133" s="11">
+      <c r="C133" s="10">
         <v>1</v>
       </c>
-      <c r="D133" s="11">
+      <c r="D133" s="10">
         <v>1</v>
       </c>
       <c r="E133" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="B134" s="9">
+      <c r="B134" s="8">
         <v>26745</v>
       </c>
-      <c r="C134" s="9">
+      <c r="C134" s="8">
         <v>1</v>
       </c>
-      <c r="D134" s="9">
+      <c r="D134" s="8">
         <v>1</v>
       </c>
       <c r="E134" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="135" spans="1:5">
       <c r="A135" s="5" t="s">
         <v>636</v>
       </c>
-      <c r="B135" s="11">
+      <c r="B135" s="10">
         <v>53539</v>
       </c>
-      <c r="C135" s="11">
+      <c r="C135" s="10">
         <v>1</v>
       </c>
-      <c r="D135" s="11">
+      <c r="D135" s="10">
         <v>1</v>
       </c>
       <c r="E135" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="3" t="s">
         <v>644</v>
       </c>
-      <c r="B136" s="9">
+      <c r="B136" s="8">
         <v>17172</v>
       </c>
-      <c r="C136" s="9">
+      <c r="C136" s="8">
         <v>1</v>
       </c>
-      <c r="D136" s="9">
+      <c r="D136" s="8">
         <v>1</v>
       </c>
       <c r="E136" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="137" spans="1:5">
       <c r="A137" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="B137" s="11">
+      <c r="B137" s="10">
         <v>21321</v>
       </c>
-      <c r="C137" s="11">
+      <c r="C137" s="10">
         <v>1</v>
       </c>
-      <c r="D137" s="11">
+      <c r="D137" s="10">
         <v>1</v>
       </c>
       <c r="E137" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="138" spans="1:5">
       <c r="A138" s="3" t="s">
         <v>654</v>
       </c>
-      <c r="B138" s="9">
+      <c r="B138" s="8">
         <v>27456</v>
       </c>
-      <c r="C138" s="9">
+      <c r="C138" s="8">
         <v>1</v>
       </c>
-      <c r="D138" s="9">
+      <c r="D138" s="8">
         <v>1</v>
       </c>
       <c r="E138" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="139" spans="1:5">
       <c r="A139" s="5" t="s">
         <v>694</v>
       </c>
-      <c r="B139" s="11">
+      <c r="B139" s="10">
         <v>34963</v>
       </c>
-      <c r="C139" s="11">
+      <c r="C139" s="10">
         <v>1</v>
       </c>
-      <c r="D139" s="11">
+      <c r="D139" s="10">
         <v>1</v>
       </c>
       <c r="E139" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B140" s="9">
+      <c r="B140" s="8">
         <v>23068</v>
       </c>
-      <c r="C140" s="9">
+      <c r="C140" s="8">
         <v>1</v>
       </c>
-      <c r="D140" s="9">
+      <c r="D140" s="8">
         <v>1</v>
       </c>
       <c r="E140" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="141" spans="1:5">
       <c r="A141" s="5" t="s">
         <v>704</v>
       </c>
-      <c r="B141" s="11">
+      <c r="B141" s="10">
         <v>26938</v>
       </c>
-      <c r="C141" s="11">
+      <c r="C141" s="10">
         <v>1</v>
       </c>
-      <c r="D141" s="11">
+      <c r="D141" s="10">
         <v>1</v>
       </c>
       <c r="E141" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="B142" s="9">
+      <c r="B142" s="8">
         <v>8329</v>
       </c>
-      <c r="C142" s="9">
+      <c r="C142" s="8">
         <v>1</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="8">
         <v>1</v>
       </c>
       <c r="E142" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="5" t="s">
         <v>737</v>
       </c>
-      <c r="B143" s="11">
+      <c r="B143" s="10">
         <v>8456</v>
       </c>
-      <c r="C143" s="11">
+      <c r="C143" s="10">
         <v>1</v>
       </c>
-      <c r="D143" s="11">
+      <c r="D143" s="10">
         <v>1</v>
       </c>
       <c r="E143" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" s="3" t="s">
         <v>753</v>
       </c>
-      <c r="B144" s="9">
+      <c r="B144" s="8">
         <v>6565</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C144" s="8">
         <v>1</v>
       </c>
-      <c r="D144" s="9">
+      <c r="D144" s="8">
         <v>1</v>
       </c>
       <c r="E144" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="145" spans="1:5">
       <c r="A145" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="B145" s="11">
+      <c r="B145" s="10">
         <v>14975</v>
       </c>
-      <c r="C145" s="11">
+      <c r="C145" s="10">
         <v>1</v>
       </c>
-      <c r="D145" s="11">
+      <c r="D145" s="10">
         <v>1</v>
       </c>
       <c r="E145" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="146" spans="1:5">
       <c r="A146" s="3" t="s">
         <v>698</v>
       </c>
-      <c r="B146" s="9">
+      <c r="B146" s="8">
         <v>41770</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C146" s="8">
         <v>1</v>
       </c>
-      <c r="D146" s="9">
+      <c r="D146" s="8">
         <v>1</v>
       </c>
       <c r="E146" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="147" spans="1:5">
       <c r="A147" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="B147" s="11">
+      <c r="B147" s="10">
         <v>39723</v>
       </c>
-      <c r="C147" s="11">
+      <c r="C147" s="10">
         <v>1</v>
       </c>
-      <c r="D147" s="11">
+      <c r="D147" s="10">
         <v>1</v>
       </c>
       <c r="E147" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="148" spans="1:5">
       <c r="A148" s="3" t="s">
         <v>777</v>
       </c>
-      <c r="B148" s="9">
+      <c r="B148" s="8">
         <v>25322</v>
       </c>
-      <c r="C148" s="9">
+      <c r="C148" s="8">
         <v>1</v>
       </c>
-      <c r="D148" s="9">
+      <c r="D148" s="8">
         <v>1</v>
       </c>
       <c r="E148" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="149" spans="1:5">
       <c r="A149" s="5" t="s">
         <v>785</v>
       </c>
-      <c r="B149" s="11">
+      <c r="B149" s="10">
         <v>20625</v>
       </c>
-      <c r="C149" s="11">
+      <c r="C149" s="10">
         <v>1</v>
       </c>
-      <c r="D149" s="11">
+      <c r="D149" s="10">
         <v>1</v>
       </c>
       <c r="E149" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="150" spans="1:5">
       <c r="A150" s="3" t="s">
         <v>791</v>
       </c>
-      <c r="B150" s="9">
+      <c r="B150" s="8">
         <v>5079</v>
       </c>
-      <c r="C150" s="9">
+      <c r="C150" s="8">
         <v>1</v>
       </c>
-      <c r="D150" s="9">
+      <c r="D150" s="8">
         <v>1</v>
       </c>
       <c r="E150" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="151" spans="1:5">
       <c r="A151" s="5" t="s">
         <v>797</v>
       </c>
-      <c r="B151" s="11">
+      <c r="B151" s="10">
         <v>5</v>
       </c>
-      <c r="C151" s="11">
+      <c r="C151" s="10">
         <v>1</v>
       </c>
-      <c r="D151" s="11">
+      <c r="D151" s="10">
         <v>1</v>
       </c>
       <c r="E151" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="152" spans="1:5">
       <c r="A152" s="3" t="s">
         <v>727</v>
       </c>
-      <c r="B152" s="9">
+      <c r="B152" s="8">
         <v>15416</v>
       </c>
-      <c r="C152" s="9">
+      <c r="C152" s="8">
         <v>1</v>
       </c>
-      <c r="D152" s="9">
+      <c r="D152" s="8">
         <v>1</v>
       </c>
       <c r="E152" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="153" spans="1:5">
       <c r="A153" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="B153" s="11">
+      <c r="B153" s="10">
         <v>6971</v>
       </c>
-      <c r="C153" s="11">
+      <c r="C153" s="10">
         <v>1</v>
       </c>
-      <c r="D153" s="11">
+      <c r="D153" s="10">
         <v>2</v>
       </c>
       <c r="E153" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="154" spans="1:5">
       <c r="A154" s="3" t="s">
         <v>875</v>
       </c>
-      <c r="B154" s="9">
+      <c r="B154" s="8">
         <v>5865</v>
       </c>
-      <c r="C154" s="9">
+      <c r="C154" s="8">
         <v>1</v>
       </c>
-      <c r="D154" s="9">
+      <c r="D154" s="8">
         <v>1</v>
       </c>
       <c r="E154" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="155" spans="1:5">
       <c r="A155" s="5" t="s">
         <v>878</v>
       </c>
-      <c r="B155" s="11">
+      <c r="B155" s="10">
         <v>15788</v>
       </c>
-      <c r="C155" s="11">
+      <c r="C155" s="10">
         <v>1</v>
       </c>
-      <c r="D155" s="11">
+      <c r="D155" s="10">
         <v>1</v>
       </c>
       <c r="E155" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="156" spans="1:5">
       <c r="A156" s="3" t="s">
         <v>895</v>
       </c>
-      <c r="B156" s="9">
+      <c r="B156" s="8">
         <v>6292</v>
       </c>
-      <c r="C156" s="9">
+      <c r="C156" s="8">
         <v>1</v>
       </c>
-      <c r="D156" s="9">
+      <c r="D156" s="8">
         <v>1</v>
       </c>
       <c r="E156" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="157" spans="1:5">
       <c r="A157" s="5" t="s">
         <v>753</v>
       </c>
-      <c r="B157" s="11">
+      <c r="B157" s="10">
         <v>14058</v>
       </c>
-      <c r="C157" s="11">
+      <c r="C157" s="10">
         <v>1</v>
       </c>
-      <c r="D157" s="11">
+      <c r="D157" s="10">
         <v>1</v>
       </c>
       <c r="E157" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="158" spans="1:5">
       <c r="A158" s="3" t="s">
         <v>920</v>
       </c>
-      <c r="B158" s="9">
+      <c r="B158" s="8">
         <v>9740</v>
       </c>
-      <c r="C158" s="9">
+      <c r="C158" s="8">
         <v>1</v>
       </c>
-      <c r="D158" s="9">
+      <c r="D158" s="8">
         <v>1</v>
       </c>
       <c r="E158" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="159" spans="1:5">
       <c r="A159" s="5" t="s">
         <v>923</v>
       </c>
-      <c r="B159" s="11">
+      <c r="B159" s="10">
         <v>27112</v>
       </c>
-      <c r="C159" s="11">
+      <c r="C159" s="10">
         <v>1</v>
       </c>
-      <c r="D159" s="11">
+      <c r="D159" s="10">
         <v>1</v>
       </c>
       <c r="E159" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="160" spans="1:5">
       <c r="A160" s="3" t="s">
         <v>927</v>
       </c>
-      <c r="B160" s="9">
+      <c r="B160" s="8">
         <v>10596</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C160" s="8">
         <v>1</v>
       </c>
-      <c r="D160" s="9">
+      <c r="D160" s="8">
         <v>1</v>
       </c>
       <c r="E160" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="161" spans="1:5">
       <c r="A161" s="5" t="s">
         <v>957</v>
       </c>
-      <c r="B161" s="11">
+      <c r="B161" s="10">
         <v>19184</v>
       </c>
-      <c r="C161" s="11">
+      <c r="C161" s="10">
         <v>1</v>
       </c>
-      <c r="D161" s="11">
+      <c r="D161" s="10">
         <v>1</v>
       </c>
       <c r="E161" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="162" spans="1:5">
       <c r="A162" s="3" t="s">
         <v>984</v>
       </c>
-      <c r="B162" s="9">
+      <c r="B162" s="8">
         <v>17475</v>
       </c>
-      <c r="C162" s="9">
+      <c r="C162" s="8">
         <v>1</v>
       </c>
-      <c r="D162" s="9">
+      <c r="D162" s="8">
         <v>1</v>
       </c>
       <c r="E162" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="163" spans="1:5">
       <c r="A163" s="5" t="s">
         <v>992</v>
       </c>
-      <c r="B163" s="11">
+      <c r="B163" s="10">
         <v>20520</v>
       </c>
-      <c r="C163" s="11">
+      <c r="C163" s="10">
         <v>1</v>
       </c>
-      <c r="D163" s="11">
+      <c r="D163" s="10">
         <v>1</v>
       </c>
       <c r="E163" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="164" spans="1:5">
       <c r="A164" s="3" t="s">
         <v>1007</v>
       </c>
-      <c r="B164" s="9">
+      <c r="B164" s="8">
         <v>1463</v>
       </c>
-      <c r="C164" s="9">
+      <c r="C164" s="8">
         <v>1</v>
       </c>
-      <c r="D164" s="9">
+      <c r="D164" s="8">
         <v>1</v>
       </c>
       <c r="E164" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="165" spans="1:5">
       <c r="A165" s="5" t="s">
         <v>1010</v>
       </c>
-      <c r="B165" s="11">
+      <c r="B165" s="10">
         <v>26167</v>
       </c>
-      <c r="C165" s="11">
+      <c r="C165" s="10">
         <v>1</v>
       </c>
-      <c r="D165" s="11">
+      <c r="D165" s="10">
         <v>1</v>
       </c>
       <c r="E165" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="166" spans="1:5">
       <c r="A166" s="3" t="s">
         <v>1022</v>
       </c>
-      <c r="B166" s="9">
+      <c r="B166" s="8">
         <v>7526</v>
       </c>
-      <c r="C166" s="9">
+      <c r="C166" s="8">
         <v>1</v>
       </c>
-      <c r="D166" s="9">
+      <c r="D166" s="8">
         <v>1</v>
       </c>
       <c r="E166" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="167" spans="1:5">
       <c r="A167" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="B167" s="11">
+      <c r="B167" s="10">
         <v>22163</v>
       </c>
-      <c r="C167" s="11">
+      <c r="C167" s="10">
         <v>1</v>
       </c>
-      <c r="D167" s="11">
+      <c r="D167" s="10">
         <v>1</v>
       </c>
       <c r="E167" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="168" spans="1:5">
       <c r="A168" s="3" t="s">
         <v>1045</v>
       </c>
-      <c r="B168" s="9">
+      <c r="B168" s="8">
         <v>3984</v>
       </c>
-      <c r="C168" s="9">
+      <c r="C168" s="8">
         <v>1</v>
       </c>
-      <c r="D168" s="9">
+      <c r="D168" s="8">
         <v>1</v>
       </c>
       <c r="E168" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="169" spans="1:5">
       <c r="A169" s="5" t="s">
         <v>1051</v>
       </c>
-      <c r="B169" s="11">
+      <c r="B169" s="10">
         <v>9375</v>
       </c>
-      <c r="C169" s="11">
+      <c r="C169" s="10">
         <v>1</v>
       </c>
-      <c r="D169" s="11">
+      <c r="D169" s="10">
         <v>1</v>
       </c>
-      <c r="E169" s="12" t="s">
-        <v>2936</v>
+      <c r="E169" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="170" spans="1:5">
       <c r="A170" s="3" t="s">
         <v>1057</v>
       </c>
-      <c r="B170" s="9">
+      <c r="B170" s="8">
         <v>38191</v>
       </c>
-      <c r="C170" s="9">
+      <c r="C170" s="8">
         <v>1</v>
       </c>
-      <c r="D170" s="9">
+      <c r="D170" s="8">
         <v>1</v>
       </c>
       <c r="E170" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="171" spans="1:5">
       <c r="A171" s="5" t="s">
         <v>1061</v>
       </c>
-      <c r="B171" s="11">
+      <c r="B171" s="10">
         <v>40808</v>
       </c>
-      <c r="C171" s="11">
+      <c r="C171" s="10">
         <v>1</v>
       </c>
-      <c r="D171" s="11">
+      <c r="D171" s="10">
         <v>1</v>
       </c>
       <c r="E171" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="172" spans="1:5">
       <c r="A172" s="3" t="s">
         <v>1078</v>
       </c>
-      <c r="B172" s="9">
+      <c r="B172" s="8">
         <v>18875</v>
       </c>
-      <c r="C172" s="9">
+      <c r="C172" s="8">
         <v>1</v>
       </c>
-      <c r="D172" s="9">
+      <c r="D172" s="8">
         <v>1</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="173" spans="1:5">
       <c r="A173" s="5" t="s">
         <v>1093</v>
       </c>
-      <c r="B173" s="11">
+      <c r="B173" s="10">
         <v>3762</v>
       </c>
-      <c r="C173" s="11">
+      <c r="C173" s="10">
         <v>1</v>
       </c>
-      <c r="D173" s="11">
+      <c r="D173" s="10">
         <v>1</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="174" spans="1:5">
       <c r="A174" s="3" t="s">
         <v>1105</v>
       </c>
-      <c r="B174" s="9">
+      <c r="B174" s="8">
         <v>39941</v>
       </c>
-      <c r="C174" s="9">
+      <c r="C174" s="8">
         <v>1</v>
       </c>
-      <c r="D174" s="9">
+      <c r="D174" s="8">
         <v>1</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="175" spans="1:5">
       <c r="A175" s="5" t="s">
         <v>1108</v>
       </c>
-      <c r="B175" s="11">
+      <c r="B175" s="10">
         <v>5695</v>
       </c>
-      <c r="C175" s="11">
+      <c r="C175" s="10">
         <v>1</v>
       </c>
-      <c r="D175" s="11">
+      <c r="D175" s="10">
         <v>1</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="176" spans="1:5">
       <c r="A176" s="3" t="s">
         <v>1118</v>
       </c>
-      <c r="B176" s="9">
+      <c r="B176" s="8">
         <v>9265</v>
       </c>
-      <c r="C176" s="9">
+      <c r="C176" s="8">
         <v>1</v>
       </c>
-      <c r="D176" s="9">
+      <c r="D176" s="8">
         <v>1</v>
       </c>
       <c r="E176" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="177" spans="1:5">
       <c r="A177" s="5" t="s">
         <v>1124</v>
       </c>
-      <c r="B177" s="11">
+      <c r="B177" s="10">
         <v>5081</v>
       </c>
-      <c r="C177" s="11">
+      <c r="C177" s="10">
         <v>1</v>
       </c>
-      <c r="D177" s="11">
+      <c r="D177" s="10">
         <v>1</v>
       </c>
       <c r="E177" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="178" spans="1:5">
       <c r="A178" s="3" t="s">
         <v>1134</v>
       </c>
-      <c r="B178" s="9">
+      <c r="B178" s="8">
         <v>20953</v>
       </c>
-      <c r="C178" s="9">
+      <c r="C178" s="8">
         <v>1</v>
       </c>
-      <c r="D178" s="9">
+      <c r="D178" s="8">
         <v>1</v>
       </c>
       <c r="E178" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="179" spans="1:5">
       <c r="A179" s="5" t="s">
         <v>1153</v>
       </c>
-      <c r="B179" s="11">
+      <c r="B179" s="10">
         <v>19484</v>
       </c>
-      <c r="C179" s="11">
+      <c r="C179" s="10">
         <v>1</v>
       </c>
-      <c r="D179" s="11">
+      <c r="D179" s="10">
         <v>1</v>
       </c>
       <c r="E179" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="180" spans="1:5">
       <c r="A180" s="3" t="s">
         <v>1157</v>
       </c>
-      <c r="B180" s="9">
+      <c r="B180" s="8">
         <v>26653</v>
       </c>
-      <c r="C180" s="9">
+      <c r="C180" s="8">
         <v>1</v>
       </c>
-      <c r="D180" s="9">
+      <c r="D180" s="8">
         <v>1</v>
       </c>
       <c r="E180" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="181" spans="1:5">
       <c r="A181" s="5" t="s">
         <v>1171</v>
       </c>
-      <c r="B181" s="11">
+      <c r="B181" s="10">
         <v>20050</v>
       </c>
-      <c r="C181" s="11">
+      <c r="C181" s="10">
         <v>1</v>
       </c>
-      <c r="D181" s="11">
+      <c r="D181" s="10">
         <v>1</v>
       </c>
       <c r="E181" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="182" spans="1:5">
       <c r="A182" s="3" t="s">
         <v>1174</v>
       </c>
-      <c r="B182" s="9">
+      <c r="B182" s="8">
         <v>1194</v>
       </c>
-      <c r="C182" s="9">
+      <c r="C182" s="8">
         <v>1</v>
       </c>
-      <c r="D182" s="9">
+      <c r="D182" s="8">
         <v>1</v>
       </c>
       <c r="E182" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="183" spans="1:5">
       <c r="A183" s="5" t="s">
         <v>1177</v>
       </c>
-      <c r="B183" s="11">
+      <c r="B183" s="10">
         <v>7418</v>
       </c>
-      <c r="C183" s="11">
+      <c r="C183" s="10">
         <v>1</v>
       </c>
-      <c r="D183" s="11">
+      <c r="D183" s="10">
         <v>1</v>
       </c>
       <c r="E183" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="3" t="s">
         <v>1186</v>
       </c>
-      <c r="B184" s="9">
+      <c r="B184" s="8">
         <v>19229</v>
       </c>
-      <c r="C184" s="9">
+      <c r="C184" s="8">
         <v>1</v>
       </c>
-      <c r="D184" s="9">
+      <c r="D184" s="8">
         <v>1</v>
       </c>
       <c r="E184" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="185" spans="1:5">
       <c r="A185" s="5" t="s">
         <v>1197</v>
       </c>
-      <c r="B185" s="11">
+      <c r="B185" s="10">
         <v>22102</v>
       </c>
-      <c r="C185" s="11">
+      <c r="C185" s="10">
         <v>1</v>
       </c>
-      <c r="D185" s="11">
+      <c r="D185" s="10">
         <v>2</v>
       </c>
       <c r="E185" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="186" spans="1:5">
       <c r="A186" s="3" t="s">
         <v>1099</v>
       </c>
-      <c r="B186" s="9">
+      <c r="B186" s="8">
         <v>19061</v>
       </c>
-      <c r="C186" s="9">
+      <c r="C186" s="8">
         <v>1</v>
       </c>
-      <c r="D186" s="9">
+      <c r="D186" s="8">
         <v>1</v>
       </c>
       <c r="E186" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="187" spans="1:5">
       <c r="A187" s="5" t="s">
         <v>1224</v>
       </c>
-      <c r="B187" s="11">
+      <c r="B187" s="10">
         <v>23794</v>
       </c>
-      <c r="C187" s="11">
+      <c r="C187" s="10">
         <v>1</v>
       </c>
-      <c r="D187" s="11">
+      <c r="D187" s="10">
         <v>1</v>
       </c>
       <c r="E187" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="188" spans="1:5">
       <c r="A188" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="B188" s="9">
+      <c r="B188" s="8">
         <v>10551</v>
       </c>
-      <c r="C188" s="9">
+      <c r="C188" s="8">
         <v>1</v>
       </c>
-      <c r="D188" s="9">
+      <c r="D188" s="8">
         <v>1</v>
       </c>
       <c r="E188" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="189" spans="1:5">
       <c r="A189" s="5" t="s">
         <v>1244</v>
       </c>
-      <c r="B189" s="11">
+      <c r="B189" s="10">
         <v>13592</v>
       </c>
-      <c r="C189" s="11">
+      <c r="C189" s="10">
         <v>1</v>
       </c>
-      <c r="D189" s="11">
+      <c r="D189" s="10">
         <v>1</v>
       </c>
       <c r="E189" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="190" spans="1:5">
       <c r="A190" s="3" t="s">
         <v>1251</v>
       </c>
-      <c r="B190" s="9">
+      <c r="B190" s="8">
         <v>6756</v>
       </c>
-      <c r="C190" s="9">
+      <c r="C190" s="8">
         <v>1</v>
       </c>
-      <c r="D190" s="9">
+      <c r="D190" s="8">
         <v>1</v>
       </c>
       <c r="E190" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="191" spans="1:5">
       <c r="A191" s="5" t="s">
         <v>1263</v>
       </c>
-      <c r="B191" s="11">
+      <c r="B191" s="10">
         <v>37876</v>
       </c>
-      <c r="C191" s="11">
+      <c r="C191" s="10">
         <v>1</v>
       </c>
-      <c r="D191" s="11">
+      <c r="D191" s="10">
         <v>1</v>
       </c>
       <c r="E191" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="192" spans="1:5">
       <c r="A192" s="3" t="s">
         <v>1312</v>
       </c>
-      <c r="B192" s="9">
+      <c r="B192" s="8">
         <v>27712</v>
       </c>
-      <c r="C192" s="9">
+      <c r="C192" s="8">
         <v>1</v>
       </c>
-      <c r="D192" s="9">
+      <c r="D192" s="8">
         <v>1</v>
       </c>
       <c r="E192" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="193" spans="1:5">
       <c r="A193" s="5" t="s">
         <v>1352</v>
       </c>
-      <c r="B193" s="11">
+      <c r="B193" s="10">
         <v>347</v>
       </c>
-      <c r="C193" s="11">
+      <c r="C193" s="10">
         <v>1</v>
       </c>
-      <c r="D193" s="11">
+      <c r="D193" s="10">
         <v>1</v>
       </c>
-      <c r="E193" s="12" t="s">
-        <v>2936</v>
+      <c r="E193" s="11" t="s">
+        <v>2933</v>
       </c>
     </row>
     <row r="194" spans="1:5">
       <c r="A194" s="3" t="s">
         <v>1394</v>
       </c>
-      <c r="B194" s="9">
+      <c r="B194" s="8">
         <v>11122</v>
       </c>
-      <c r="C194" s="9">
+      <c r="C194" s="8">
         <v>1</v>
       </c>
-      <c r="D194" s="9">
+      <c r="D194" s="8">
         <v>1</v>
       </c>
       <c r="E194" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="195" spans="1:5">
       <c r="A195" s="5" t="s">
         <v>392</v>
       </c>
-      <c r="B195" s="11">
+      <c r="B195" s="10">
         <v>22489</v>
       </c>
-      <c r="C195" s="11">
+      <c r="C195" s="10">
         <v>1</v>
       </c>
-      <c r="D195" s="11">
+      <c r="D195" s="10">
         <v>1</v>
       </c>
       <c r="E195" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="196" spans="1:5">
       <c r="A196" s="3" t="s">
         <v>1405</v>
       </c>
-      <c r="B196" s="9">
+      <c r="B196" s="8">
         <v>4911</v>
       </c>
-      <c r="C196" s="9">
+      <c r="C196" s="8">
         <v>1</v>
       </c>
-      <c r="D196" s="9">
+      <c r="D196" s="8">
         <v>1</v>
       </c>
       <c r="E196" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="197" spans="1:5">
       <c r="A197" s="5" t="s">
         <v>1443</v>
       </c>
-      <c r="B197" s="11">
+      <c r="B197" s="10">
         <v>14124</v>
       </c>
-      <c r="C197" s="11">
+      <c r="C197" s="10">
         <v>1</v>
       </c>
-      <c r="D197" s="11">
+      <c r="D197" s="10">
         <v>1</v>
       </c>
       <c r="E197" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="198" spans="1:5">
       <c r="A198" s="3" t="s">
         <v>1659</v>
       </c>
-      <c r="B198" s="9">
+      <c r="B198" s="8">
         <v>23196</v>
       </c>
-      <c r="C198" s="9">
+      <c r="C198" s="8">
         <v>1</v>
       </c>
-      <c r="D198" s="9">
+      <c r="D198" s="8">
         <v>2</v>
       </c>
       <c r="E198" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="199" spans="1:5">
       <c r="A199" s="5" t="s">
         <v>1714</v>
       </c>
-      <c r="B199" s="11">
+      <c r="B199" s="10">
         <v>26388</v>
       </c>
-      <c r="C199" s="11">
+      <c r="C199" s="10">
         <v>1</v>
       </c>
-      <c r="D199" s="11">
+      <c r="D199" s="10">
         <v>2</v>
       </c>
       <c r="E199" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
     <row r="200" spans="1:5">
       <c r="A200" s="3" t="s">
         <v>1890</v>
       </c>
-      <c r="B200" s="9">
+      <c r="B200" s="8">
         <v>5335</v>
       </c>
-      <c r="C200" s="9">
+      <c r="C200" s="8">
         <v>1</v>
       </c>
-      <c r="D200" s="9">
+      <c r="D200" s="8">
         <v>2</v>
       </c>
       <c r="E200" s="5" t="s">
-        <v>2937</v>
+        <v>2934</v>
       </c>
     </row>
   </sheetData>
